--- a/workbooks/scenarios/ApplianceRAGScenarios.xlsx
+++ b/workbooks/scenarios/ApplianceRAGScenarios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R91"/>
+  <dimension ref="A1:R106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,7 +444,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>appliance_age_type</t>
+          <t>appliance_age</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -510,226 +510,226 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>It's late (around 2 AM) and I need to run the dishwasher. Should I do it now or wait?</t>
+          <t>It's mid-morning, about 10 and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Johnstown, PA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2:00 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>9.19</v>
+        <v>8.33</v>
       </c>
       <c r="L2" t="n">
-        <v>6.7</v>
+        <v>2.14</v>
       </c>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>8.449999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="O2" t="n">
-        <v>8.369499999999999</v>
+        <v>6.512500000000001</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1064</v>
+        <v>0.2016</v>
       </c>
       <c r="R2" t="n">
-        <v>1.366</v>
+        <v>2.915</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>It's late (around 2 AM) and I need to run the dishwasher. Should I do it now or wait?</t>
+          <t>It's mid-morning, about 10 and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Johnstown, PA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6.09</v>
+        <v>8.33</v>
       </c>
       <c r="L3" t="n">
-        <v>6.43</v>
+        <v>2.14</v>
       </c>
       <c r="M3" t="n">
-        <v>4.78</v>
+        <v>8.9</v>
       </c>
       <c r="N3" t="n">
-        <v>4.64</v>
+        <v>8.23</v>
       </c>
       <c r="O3" t="n">
-        <v>5.7295</v>
+        <v>6.2625</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.448</v>
+        <v>0.2016</v>
       </c>
       <c r="R3" t="n">
-        <v>1.457</v>
+        <v>2.915</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>It's late (around 2 AM) and I need to run the dishwasher. Should I do it now or wait?</t>
+          <t>It's mid-morning, about 10 and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Johnstown, PA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9.19</v>
+        <v>5.46</v>
       </c>
       <c r="L4" t="n">
-        <v>6.43</v>
+        <v>2.14</v>
       </c>
       <c r="M4" t="n">
-        <v>6.6</v>
+        <v>6.74</v>
       </c>
       <c r="N4" t="n">
-        <v>5.22</v>
+        <v>5.4</v>
       </c>
       <c r="O4" t="n">
-        <v>7.1105</v>
+        <v>4.545</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1064</v>
+        <v>0.518</v>
       </c>
       <c r="R4" t="n">
-        <v>1.457</v>
+        <v>2.915</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>It's late (around midnight) and I need to run the dishwasher. Should I do it now or wait?</t>
+          <t>It's just past 9 AM � when should I run the dryer?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lancaster, PA</t>
+          <t>Meadville, PA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -740,62 +740,62 @@
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12:00 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.880000000000001</v>
+        <v>7.87</v>
       </c>
       <c r="L5" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>10</v>
       </c>
       <c r="N5" t="n">
-        <v>8.449999999999999</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>8.2765</v>
+        <v>5.861</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.14</v>
+        <v>0.252</v>
       </c>
       <c r="R5" t="n">
-        <v>1.366</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>It's late (around midnight) and I need to run the dishwasher. Should I do it now or wait?</t>
+          <t>It's just past 9 AM � when should I run the dryer?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lancaster, PA</t>
+          <t>Meadville, PA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -806,62 +806,62 @@
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>8.880000000000001</v>
+        <v>7.87</v>
       </c>
       <c r="L6" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>7.56</v>
+        <v>7.81</v>
       </c>
       <c r="N6" t="n">
-        <v>6.37</v>
+        <v>6.66</v>
       </c>
       <c r="O6" t="n">
-        <v>7.382000000000001</v>
+        <v>4.922</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.14</v>
+        <v>0.252</v>
       </c>
       <c r="R6" t="n">
-        <v>1.457</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>It's late (around midnight) and I need to run the dishwasher. Should I do it now or wait?</t>
+          <t>It's just past 9 AM � when should I run the dryer?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lancaster, PA</t>
+          <t>Meadville, PA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -872,139 +872,139 @@
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>8.380000000000001</v>
+        <v>4.28</v>
       </c>
       <c r="L7" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5.26</v>
+        <v>5.92</v>
       </c>
       <c r="N7" t="n">
-        <v>4.64</v>
+        <v>4.31</v>
       </c>
       <c r="O7" t="n">
-        <v>6.512499999999999</v>
+        <v>3.1145</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.196</v>
+        <v>0.6475</v>
       </c>
       <c r="R7" t="n">
-        <v>1.457</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>It's late (around 10 PM) and I need to run the dishwasher. Should I do it now or wait?</t>
+          <t>It's just past 9 AM and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Lancaster, PA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>0.95</v>
+        <v>0.35</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>8.970000000000001</v>
+        <v>9.84</v>
       </c>
       <c r="L8" t="n">
-        <v>7.81</v>
+        <v>9.65</v>
       </c>
       <c r="M8" t="n">
         <v>10</v>
       </c>
       <c r="N8" t="n">
-        <v>9.25</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
-        <v>8.811999999999999</v>
+        <v>9.829499999999999</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1306</v>
+        <v>0.035</v>
       </c>
       <c r="R8" t="n">
-        <v>0.989</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>It's late (around 10 PM) and I need to run the dishwasher. Should I do it now or wait?</t>
+          <t>It's just past 9 AM and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Lancaster, PA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>0.95</v>
+        <v>0.35</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1012,112 +1012,112 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>8.970000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>7.81</v>
+        <v>9.65</v>
       </c>
       <c r="M9" t="n">
-        <v>7</v>
+        <v>6.92</v>
       </c>
       <c r="N9" t="n">
-        <v>5.71</v>
+        <v>5.61</v>
       </c>
       <c r="O9" t="n">
-        <v>7.681</v>
+        <v>8.516</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1306</v>
+        <v>0.049</v>
       </c>
       <c r="R9" t="n">
-        <v>0.989</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>It's late (around 10 PM) and I need to run the dishwasher. Should I do it now or wait?</t>
+          <t>It's just past 9 AM and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Lancaster, PA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>0.95</v>
+        <v>0.35</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>12:00 AM</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>8.970000000000001</v>
+        <v>9.84</v>
       </c>
       <c r="L10" t="n">
-        <v>7.81</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>6.65</v>
+        <v>3.83</v>
       </c>
       <c r="N10" t="n">
-        <v>5.19</v>
+        <v>1.51</v>
       </c>
       <c r="O10" t="n">
-        <v>7.533</v>
+        <v>7.343</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1306</v>
+        <v>0.035</v>
       </c>
       <c r="R10" t="n">
-        <v>0.989</v>
+        <v>0.342</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dinner's done around 5 PM. What's the best time to run the dishwasher?</t>
+          <t>It's late morning, around 11 and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Allentown, PA</t>
+          <t>Norristown, PA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1125,29 +1125,29 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H11" t="n">
         <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>8.57</v>
+        <v>9.4</v>
       </c>
       <c r="L11" t="n">
-        <v>6.89</v>
+        <v>7.35</v>
       </c>
       <c r="M11" t="n">
         <v>10</v>
@@ -1156,34 +1156,34 @@
         <v>10</v>
       </c>
       <c r="O11" t="n">
-        <v>8.4825</v>
+        <v>8.8925</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.175</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>1.301</v>
+        <v>1.145</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dinner's done around 5 PM. What's the best time to run the dishwasher?</t>
+          <t>It's late morning, around 11 and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Allentown, PA</t>
+          <t>Norristown, PA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1191,65 +1191,65 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H12" t="n">
         <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>9.02</v>
+        <v>6.96</v>
       </c>
       <c r="L12" t="n">
-        <v>6.89</v>
+        <v>7.35</v>
       </c>
       <c r="M12" t="n">
-        <v>9.09</v>
+        <v>7.83</v>
       </c>
       <c r="N12" t="n">
-        <v>8.449999999999999</v>
+        <v>6.69</v>
       </c>
       <c r="O12" t="n">
-        <v>8.202999999999999</v>
+        <v>7.23</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.125</v>
+        <v>0.352</v>
       </c>
       <c r="R12" t="n">
-        <v>1.301</v>
+        <v>1.145</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dinner's done around 5 PM. What's the best time to run the dishwasher?</t>
+          <t>It's late morning, around 11 and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Allentown, PA</t>
+          <t>Norristown, PA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1257,73 +1257,73 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>8.57</v>
+        <v>9.4</v>
       </c>
       <c r="L13" t="n">
-        <v>6.89</v>
+        <v>7.35</v>
       </c>
       <c r="M13" t="n">
-        <v>9.550000000000001</v>
+        <v>6.29</v>
       </c>
       <c r="N13" t="n">
-        <v>9.25</v>
+        <v>4.78</v>
       </c>
       <c r="O13" t="n">
-        <v>8.279999999999999</v>
+        <v>7.3675</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.175</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>1.301</v>
+        <v>1.145</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dinner's done around 5 PM. What's the best time to run the dishwasher?</t>
+          <t>It's just past 9 AM and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Erie, PA</t>
+          <t>Reading, PA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1331,21 +1331,21 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>1.25</v>
+        <v>0.45</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>8.06</v>
+        <v>9.75</v>
       </c>
       <c r="L14" t="n">
-        <v>6.89</v>
+        <v>9.34</v>
       </c>
       <c r="M14" t="n">
         <v>10</v>
@@ -1354,42 +1354,42 @@
         <v>10</v>
       </c>
       <c r="O14" t="n">
-        <v>8.329499999999999</v>
+        <v>9.693999999999999</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2313</v>
+        <v>0.045</v>
       </c>
       <c r="R14" t="n">
-        <v>1.301</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dinner's done around 5 PM. What's the best time to run the dishwasher?</t>
+          <t>It's just past 9 AM and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Erie, PA</t>
+          <t>Reading, PA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1397,65 +1397,65 @@
         </is>
       </c>
       <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O15" t="n">
+        <v>7.578499999999999</v>
+      </c>
+      <c r="P15" t="n">
         <v>2</v>
       </c>
-      <c r="I15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>11:00 PM</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>9.34</v>
-      </c>
-      <c r="L15" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="M15" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="N15" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="O15" t="n">
-        <v>7.561999999999999</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3</v>
-      </c>
       <c r="Q15" t="n">
-        <v>0.09</v>
+        <v>0.045</v>
       </c>
       <c r="R15" t="n">
-        <v>1.22</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dinner's done around 5 PM. What's the best time to run the dishwasher?</t>
+          <t>It's just past 9 AM and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Erie, PA</t>
+          <t>Reading, PA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1463,87 +1463,87 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>1.25</v>
+        <v>0.45</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>12:00 AM</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>8.06</v>
+        <v>9.75</v>
       </c>
       <c r="L16" t="n">
-        <v>6.89</v>
+        <v>9.43</v>
       </c>
       <c r="M16" t="n">
-        <v>9.550000000000001</v>
+        <v>2.86</v>
       </c>
       <c r="N16" t="n">
-        <v>9.25</v>
+        <v>1.51</v>
       </c>
       <c r="O16" t="n">
-        <v>8.126999999999999</v>
+        <v>7.023999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2313</v>
+        <v>0.045</v>
       </c>
       <c r="R16" t="n">
-        <v>1.301</v>
+        <v>0.439</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>I'm ready to run the dishwasher after dinner (around 8 PM). When should I start it?</t>
+          <t>It's just past 9 AM � when should I run the dryer?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scranton, PA</t>
+          <t>McKeesport, PA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>1.25</v>
+        <v>2.8</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>9.02</v>
+        <v>6.66</v>
       </c>
       <c r="L17" t="n">
-        <v>6.89</v>
+        <v>2.14</v>
       </c>
       <c r="M17" t="n">
         <v>10</v>
@@ -1552,162 +1552,162 @@
         <v>10</v>
       </c>
       <c r="O17" t="n">
-        <v>8.6175</v>
+        <v>6.247</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.125</v>
+        <v>0.385</v>
       </c>
       <c r="R17" t="n">
-        <v>1.301</v>
+        <v>2.915</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>I'm ready to run the dishwasher after dinner (around 8 PM). When should I start it?</t>
+          <t>It's just past 9 AM � when should I run the dryer?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scranton, PA</t>
+          <t>McKeesport, PA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M18" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="O18" t="n">
+        <v>5.111</v>
+      </c>
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>3:00 PM</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="L18" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="M18" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="N18" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="O18" t="n">
-        <v>7.552</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3</v>
-      </c>
       <c r="Q18" t="n">
-        <v>0.175</v>
+        <v>0.385</v>
       </c>
       <c r="R18" t="n">
-        <v>1.301</v>
+        <v>2.915</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>I'm ready to run the dishwasher after dinner (around 8 PM). When should I start it?</t>
+          <t>It's just past 9 AM � when should I run the dryer?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scranton, PA</t>
+          <t>McKeesport, PA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.25</v>
+        <v>2.8</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>11:00 PM</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>8.57</v>
+        <v>6.66</v>
       </c>
       <c r="L19" t="n">
-        <v>6.89</v>
+        <v>2.68</v>
       </c>
       <c r="M19" t="n">
-        <v>8.23</v>
+        <v>2.35</v>
       </c>
       <c r="N19" t="n">
-        <v>7.15</v>
+        <v>2.13</v>
       </c>
       <c r="O19" t="n">
-        <v>7.701</v>
+        <v>3.7255</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.175</v>
+        <v>0.385</v>
       </c>
       <c r="R19" t="n">
-        <v>1.301</v>
+        <v>2.733</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>I just finished dinner around 8 PM. When should I run my dishwasher?</t>
+          <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bethlehem, PA</t>
+          <t>State College, PA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1723,25 +1723,25 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>1.55</v>
+        <v>0.2</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>8.75</v>
+        <v>9.9</v>
       </c>
       <c r="L20" t="n">
-        <v>5.97</v>
+        <v>10</v>
       </c>
       <c r="M20" t="n">
         <v>10</v>
@@ -1750,30 +1750,30 @@
         <v>10</v>
       </c>
       <c r="O20" t="n">
-        <v>8.214499999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.155</v>
+        <v>0.028</v>
       </c>
       <c r="R20" t="n">
-        <v>1.614</v>
+        <v>0.208</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>I just finished dinner around 8 PM. When should I run my dishwasher?</t>
+          <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bethlehem, PA</t>
+          <t>State College, PA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1789,57 +1789,57 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>1.55</v>
+        <v>0.2</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>8.19</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>5.97</v>
+        <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>8.02</v>
+        <v>7</v>
       </c>
       <c r="N21" t="n">
-        <v>6.91</v>
+        <v>5.71</v>
       </c>
       <c r="O21" t="n">
-        <v>7.187</v>
+        <v>8.7475</v>
       </c>
       <c r="P21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.217</v>
+        <v>0.02</v>
       </c>
       <c r="R21" t="n">
-        <v>1.614</v>
+        <v>0.208</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>I just finished dinner around 8 PM. When should I run my dishwasher?</t>
+          <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bethlehem, PA</t>
+          <t>State College, PA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1855,57 +1855,57 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>1.55</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>12:00 AM</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>8.19</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>5.97</v>
+        <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>8.460000000000001</v>
+        <v>3.59</v>
       </c>
       <c r="N22" t="n">
-        <v>7.65</v>
+        <v>2.86</v>
       </c>
       <c r="O22" t="n">
-        <v>7.386</v>
+        <v>7.638</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.217</v>
+        <v>0.02</v>
       </c>
       <c r="R22" t="n">
-        <v>1.614</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Planning to clean up from lunch around 2 PM. When's the best time for the dishwasher?</t>
+          <t>It's around 5 in the evening � when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Reading, PA</t>
+          <t>Harrisburg, PA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1913,33 +1913,33 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Single-family</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="L23" t="n">
         <v>10</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Townhouse</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>4</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2:00 PM</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>8.19</v>
-      </c>
-      <c r="L23" t="n">
-        <v>5.97</v>
       </c>
       <c r="M23" t="n">
         <v>10</v>
@@ -1948,30 +1948,30 @@
         <v>10</v>
       </c>
       <c r="O23" t="n">
-        <v>8.0465</v>
+        <v>9.958</v>
       </c>
       <c r="P23" t="n">
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.217</v>
+        <v>0.0322</v>
       </c>
       <c r="R23" t="n">
-        <v>1.614</v>
+        <v>0.239</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Planning to clean up from lunch around 2 PM. When's the best time for the dishwasher?</t>
+          <t>It's around 5 in the evening � when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Reading, PA</t>
+          <t>Harrisburg, PA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1979,65 +1979,65 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Single-family</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="L24" t="n">
         <v>10</v>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Townhouse</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>4</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>3:00 PM</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>8.19</v>
-      </c>
-      <c r="L24" t="n">
-        <v>5.97</v>
-      </c>
       <c r="M24" t="n">
-        <v>9.51</v>
+        <v>5.92</v>
       </c>
       <c r="N24" t="n">
-        <v>9.199999999999999</v>
+        <v>4.64</v>
       </c>
       <c r="O24" t="n">
-        <v>7.8285</v>
+        <v>8.365</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.217</v>
+        <v>0.023</v>
       </c>
       <c r="R24" t="n">
-        <v>1.614</v>
+        <v>0.239</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Planning to clean up from lunch around 2 PM. When's the best time for the dishwasher?</t>
+          <t>It's around 5 in the evening � when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Reading, PA</t>
+          <t>Harrisburg, PA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2045,77 +2045,77 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Single-family</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>10:00 PM</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="L25" t="n">
         <v>10</v>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Townhouse</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>4</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L25" t="n">
-        <v>5.97</v>
-      </c>
       <c r="M25" t="n">
-        <v>7.56</v>
+        <v>6.01</v>
       </c>
       <c r="N25" t="n">
-        <v>6.37</v>
+        <v>5.19</v>
       </c>
       <c r="O25" t="n">
-        <v>7.182</v>
+        <v>8.465499999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.155</v>
+        <v>0.023</v>
       </c>
       <c r="R25" t="n">
-        <v>1.614</v>
+        <v>0.239</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>I want to run my dishwasher this afternoon (around 2 PM). When should I start it?</t>
+          <t>It's just past 7 PM � when should I run the dryer?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>York, PA</t>
+          <t>Bethlehem, PA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2123,21 +2123,21 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>7.36</v>
+        <v>6.98</v>
       </c>
       <c r="L26" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>10</v>
@@ -2146,42 +2146,42 @@
         <v>10</v>
       </c>
       <c r="O26" t="n">
-        <v>7.9585</v>
+        <v>5.593999999999999</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.308</v>
+        <v>0.35</v>
       </c>
       <c r="R26" t="n">
-        <v>1.457</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>I want to run my dishwasher this afternoon (around 2 PM). When should I start it?</t>
+          <t>It's just past 7 PM � when should I run the dryer?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>York, PA</t>
+          <t>Bethlehem, PA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2189,65 +2189,65 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>7.36</v>
+        <v>6.98</v>
       </c>
       <c r="L27" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>9.51</v>
+        <v>5.13</v>
       </c>
       <c r="N27" t="n">
-        <v>9.199999999999999</v>
+        <v>3.42</v>
       </c>
       <c r="O27" t="n">
-        <v>7.7405</v>
+        <v>3.633</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.308</v>
+        <v>0.35</v>
       </c>
       <c r="R27" t="n">
-        <v>1.457</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>I want to run my dishwasher this afternoon (around 2 PM). When should I start it?</t>
+          <t>It's just past 7 PM � when should I run the dryer?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>York, PA</t>
+          <t>Bethlehem, PA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2255,57 +2255,57 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>11:00 PM</t>
+          <t>12:00 AM</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>9.140000000000001</v>
+        <v>6.98</v>
       </c>
       <c r="L28" t="n">
-        <v>6.7</v>
+        <v>0.67</v>
       </c>
       <c r="M28" t="n">
-        <v>5.73</v>
+        <v>5.06</v>
       </c>
       <c r="N28" t="n">
-        <v>2.89</v>
+        <v>3.88</v>
       </c>
       <c r="O28" t="n">
-        <v>6.666499999999999</v>
+        <v>3.9225</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.112</v>
+        <v>0.35</v>
       </c>
       <c r="R28" t="n">
-        <v>1.366</v>
+        <v>3.416</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Planning to clean up from lunch around 2 PM. When's the best time for the dishwasher?</t>
+          <t>It's around 3 in the afternoon and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Exton, PA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2313,29 +2313,29 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>0.72</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>6.09</v>
+        <v>8.07</v>
       </c>
       <c r="L29" t="n">
-        <v>6.43</v>
+        <v>8.51</v>
       </c>
       <c r="M29" t="n">
         <v>10</v>
@@ -2344,34 +2344,34 @@
         <v>10</v>
       </c>
       <c r="O29" t="n">
-        <v>7.5775</v>
+        <v>8.8995</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.448</v>
+        <v>0.2304</v>
       </c>
       <c r="R29" t="n">
-        <v>1.457</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Planning to clean up from lunch around 2 PM. When's the best time for the dishwasher?</t>
+          <t>It's around 3 in the afternoon and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Exton, PA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2379,65 +2379,65 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>0.72</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>10:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>9.19</v>
+        <v>9.66</v>
       </c>
       <c r="L30" t="n">
-        <v>6.43</v>
+        <v>8.51</v>
       </c>
       <c r="M30" t="n">
-        <v>6.17</v>
+        <v>7.43</v>
       </c>
       <c r="N30" t="n">
-        <v>3.44</v>
+        <v>6.21</v>
       </c>
       <c r="O30" t="n">
-        <v>6.757499999999999</v>
+        <v>8.294</v>
       </c>
       <c r="P30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.1064</v>
+        <v>0.0547</v>
       </c>
       <c r="R30" t="n">
-        <v>1.457</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Planning to clean up from lunch around 2 PM. When's the best time for the dishwasher?</t>
+          <t>It's around 3 in the afternoon and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Exton, PA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2445,667 +2445,667 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>0.72</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>9:00 PM</t>
+          <t>10:00 PM</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>9.19</v>
+        <v>9.66</v>
       </c>
       <c r="L31" t="n">
-        <v>6.43</v>
+        <v>8.51</v>
       </c>
       <c r="M31" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="N31" t="n">
-        <v>5.22</v>
+        <v>4.64</v>
       </c>
       <c r="O31" t="n">
-        <v>7.1105</v>
+        <v>7.9725</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1064</v>
+        <v>0.0547</v>
       </c>
       <c r="R31" t="n">
-        <v>1.457</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>When should I do dishes today?</t>
+          <t>It's late � just past 10 PM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Williamsport, PA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>265</v>
+        <v>150</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>0.98</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>10:00 PM</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>9.27</v>
+        <v>8.43</v>
       </c>
       <c r="L32" t="n">
-        <v>7.72</v>
+        <v>3.06</v>
       </c>
       <c r="M32" t="n">
-        <v>10</v>
+        <v>7.83</v>
       </c>
       <c r="N32" t="n">
-        <v>10</v>
+        <v>9.25</v>
       </c>
       <c r="O32" t="n">
-        <v>8.983000000000001</v>
+        <v>6.5535</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.098</v>
+        <v>0.19</v>
       </c>
       <c r="R32" t="n">
-        <v>1.02</v>
+        <v>2.603</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>When should I do dishes today?</t>
+          <t>It's late � just past 10 PM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Williamsport, PA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>265</v>
+        <v>150</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>0.98</v>
+        <v>2.5</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>11:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>9.27</v>
+        <v>8.43</v>
       </c>
       <c r="L33" t="n">
-        <v>7.9</v>
+        <v>3.06</v>
       </c>
       <c r="M33" t="n">
-        <v>8.460000000000001</v>
+        <v>4.71</v>
       </c>
       <c r="N33" t="n">
-        <v>6.74</v>
+        <v>2.95</v>
       </c>
       <c r="O33" t="n">
-        <v>8.248999999999999</v>
+        <v>4.9845</v>
       </c>
       <c r="P33" t="n">
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.098</v>
+        <v>0.19</v>
       </c>
       <c r="R33" t="n">
-        <v>0.956</v>
+        <v>2.603</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>When should I do dishes today?</t>
+          <t>It's late � just past 10 PM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Williamsport, PA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>265</v>
+        <v>150</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H34" t="n">
         <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>0.98</v>
+        <v>2.5</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2:00 AM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>9.27</v>
+        <v>2.9</v>
       </c>
       <c r="L34" t="n">
-        <v>7.9</v>
+        <v>3.06</v>
       </c>
       <c r="M34" t="n">
-        <v>7.09</v>
+        <v>5.92</v>
       </c>
       <c r="N34" t="n">
-        <v>3.6</v>
+        <v>4.31</v>
       </c>
       <c r="O34" t="n">
-        <v>7.504</v>
+        <v>3.7715</v>
       </c>
       <c r="P34" t="n">
         <v>3</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.098</v>
+        <v>0.8</v>
       </c>
       <c r="R34" t="n">
-        <v>0.956</v>
+        <v>2.603</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>When should I do dishes today?</t>
+          <t>It's getting close to midnight � when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>McKeesport, PA</t>
+          <t>Greensburg, PA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>340</v>
+        <v>175</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>1.55</v>
+        <v>0.45</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>11:00 PM</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>8.220000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>5.97</v>
+        <v>9.43</v>
       </c>
       <c r="M35" t="n">
-        <v>5.13</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>4.64</v>
+        <v>9.25</v>
       </c>
       <c r="O35" t="n">
-        <v>6.2775</v>
+        <v>9.311999999999999</v>
       </c>
       <c r="P35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.2131</v>
+        <v>0.0302</v>
       </c>
       <c r="R35" t="n">
-        <v>1.614</v>
+        <v>0.439</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>When should I do dishes today?</t>
+          <t>It's getting close to midnight � when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>McKeesport, PA</t>
+          <t>Greensburg, PA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>340</v>
+        <v>175</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>1.55</v>
+        <v>0.45</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>10:00 PM</t>
+          <t>8:00 AM</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>8.220000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>5.97</v>
+        <v>9.34</v>
       </c>
       <c r="M36" t="n">
-        <v>6.29</v>
+        <v>5.53</v>
       </c>
       <c r="N36" t="n">
-        <v>3.63</v>
+        <v>3.87</v>
       </c>
       <c r="O36" t="n">
-        <v>6.358000000000001</v>
+        <v>7.919499999999999</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.2131</v>
+        <v>0.0302</v>
       </c>
       <c r="R36" t="n">
-        <v>1.614</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>When should I do dishes today?</t>
+          <t>It's getting close to midnight � when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>McKeesport, PA</t>
+          <t>Greensburg, PA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>340</v>
+        <v>175</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="H37" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="L37" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="M37" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="N37" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="O37" t="n">
+        <v>7.992999999999999</v>
+      </c>
+      <c r="P37" t="n">
         <v>2</v>
       </c>
-      <c r="I37" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>12:00 AM</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="L37" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="M37" t="n">
-        <v>7</v>
-      </c>
-      <c r="N37" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="O37" t="n">
-        <v>6.5825</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1</v>
-      </c>
       <c r="Q37" t="n">
-        <v>0.2131</v>
+        <v>0.0743</v>
       </c>
       <c r="R37" t="n">
-        <v>1.513</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>When should I do laundry today?</t>
+          <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Altoona, PA</t>
+          <t>Wilkes-Barre, PA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>washer</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I38" t="n">
-        <v>0.22</v>
+        <v>2.5</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>7:00 AM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="K38" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="L38" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M38" t="n">
         <v>10</v>
       </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
         <v>10</v>
       </c>
-      <c r="M38" t="n">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="N38" t="n">
-        <v>9.25</v>
-      </c>
       <c r="O38" t="n">
-        <v>9.797499999999999</v>
+        <v>6.665</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.0158</v>
+        <v>0.35</v>
       </c>
       <c r="R38" t="n">
-        <v>0.229</v>
+        <v>2.603</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>When should I do laundry today?</t>
+          <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Altoona, PA</t>
+          <t>Wilkes-Barre, PA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>washer</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I39" t="n">
-        <v>0.22</v>
+        <v>2.5</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>10</v>
+        <v>6.98</v>
       </c>
       <c r="L39" t="n">
-        <v>10</v>
+        <v>3.06</v>
       </c>
       <c r="M39" t="n">
-        <v>9.09</v>
+        <v>8.73</v>
       </c>
       <c r="N39" t="n">
-        <v>8.449999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>9.5855</v>
+        <v>6.115500000000001</v>
       </c>
       <c r="P39" t="n">
         <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.0158</v>
+        <v>0.35</v>
       </c>
       <c r="R39" t="n">
-        <v>0.229</v>
+        <v>2.603</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>When should I do laundry today?</t>
+          <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Altoona, PA</t>
+          <t>Wilkes-Barre, PA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>washer</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I40" t="n">
-        <v>0.22</v>
+        <v>2.5</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>10</v>
+        <v>7.89</v>
       </c>
       <c r="L40" t="n">
-        <v>10</v>
+        <v>3.06</v>
       </c>
       <c r="M40" t="n">
-        <v>7.83</v>
+        <v>6.11</v>
       </c>
       <c r="N40" t="n">
-        <v>6.69</v>
+        <v>4.64</v>
       </c>
       <c r="O40" t="n">
-        <v>9.0695</v>
+        <v>5.356</v>
       </c>
       <c r="P40" t="n">
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.0158</v>
+        <v>0.25</v>
       </c>
       <c r="R40" t="n">
-        <v>0.229</v>
+        <v>2.603</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>When should I do laundry today?</t>
+          <t>It's just after 8 AM � when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chester, PA</t>
+          <t>Lebanon, PA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>295</v>
+        <v>150</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>washer</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3116,62 +3116,62 @@
         <v>4</v>
       </c>
       <c r="I41" t="n">
-        <v>0.38</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>9.890000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="L41" t="n">
-        <v>9.550000000000001</v>
+        <v>7.35</v>
       </c>
       <c r="M41" t="n">
-        <v>9.49</v>
+        <v>10</v>
       </c>
       <c r="N41" t="n">
-        <v>9.17</v>
+        <v>10</v>
       </c>
       <c r="O41" t="n">
-        <v>9.583</v>
+        <v>8.820499999999999</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.0289</v>
+        <v>0.11</v>
       </c>
       <c r="R41" t="n">
-        <v>0.396</v>
+        <v>1.145</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>When should I do laundry today?</t>
+          <t>It's just after 8 AM � when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chester, PA</t>
+          <t>Lebanon, PA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>295</v>
+        <v>150</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>washer</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -3182,62 +3182,62 @@
         <v>4</v>
       </c>
       <c r="I42" t="n">
-        <v>0.38</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>9.890000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="L42" t="n">
-        <v>9.550000000000001</v>
+        <v>7.35</v>
       </c>
       <c r="M42" t="n">
-        <v>7.91</v>
+        <v>7.09</v>
       </c>
       <c r="N42" t="n">
-        <v>6.78</v>
+        <v>5.81</v>
       </c>
       <c r="O42" t="n">
-        <v>8.9085</v>
+        <v>7.49</v>
       </c>
       <c r="P42" t="n">
         <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.0289</v>
+        <v>0.154</v>
       </c>
       <c r="R42" t="n">
-        <v>0.396</v>
+        <v>1.145</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>When should I do laundry today?</t>
+          <t>It's just after 8 AM � when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chester, PA</t>
+          <t>Lebanon, PA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>295</v>
+        <v>150</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>washer</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3248,139 +3248,139 @@
         <v>4</v>
       </c>
       <c r="I43" t="n">
-        <v>0.38</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>9.050000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="L43" t="n">
-        <v>9.550000000000001</v>
+        <v>7.35</v>
       </c>
       <c r="M43" t="n">
-        <v>5.92</v>
+        <v>4.78</v>
       </c>
       <c r="N43" t="n">
         <v>4.64</v>
       </c>
       <c r="O43" t="n">
-        <v>7.937500000000001</v>
+        <v>6.972499999999999</v>
       </c>
       <c r="P43" t="n">
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.1216</v>
+        <v>0.11</v>
       </c>
       <c r="R43" t="n">
-        <v>0.396</v>
+        <v>1.145</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>When should I do laundry today?</t>
+          <t>It's around 2 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Easton, PA</t>
+          <t>Allentown, PA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>washer</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I44" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>7:00 AM</t>
+          <t>2:00 AM</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>9.83</v>
+        <v>9.81</v>
       </c>
       <c r="L44" t="n">
-        <v>9.34</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>9.49</v>
+        <v>7.83</v>
       </c>
       <c r="N44" t="n">
-        <v>9.17</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O44" t="n">
-        <v>9.4915</v>
+        <v>9.147</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.036</v>
+        <v>0.038</v>
       </c>
       <c r="R44" t="n">
-        <v>0.468</v>
+        <v>0.371</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>When should I do laundry today?</t>
+          <t>It's around 2 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Easton, PA</t>
+          <t>Allentown, PA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>washer</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I45" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3388,120 +3388,120 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>9.83</v>
+        <v>9.81</v>
       </c>
       <c r="L45" t="n">
-        <v>9.34</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>8.949999999999999</v>
+        <v>5.23</v>
       </c>
       <c r="N45" t="n">
-        <v>8.289999999999999</v>
+        <v>4.64</v>
       </c>
       <c r="O45" t="n">
-        <v>9.251499999999998</v>
+        <v>8.027500000000002</v>
       </c>
       <c r="P45" t="n">
         <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.036</v>
+        <v>0.038</v>
       </c>
       <c r="R45" t="n">
-        <v>0.468</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>When should I do laundry today?</t>
+          <t>It's around 2 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Easton, PA</t>
+          <t>Allentown, PA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>washer</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I46" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>9.26</v>
+        <v>9.67</v>
       </c>
       <c r="L46" t="n">
-        <v>9.34</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>6.92</v>
+        <v>3.94</v>
       </c>
       <c r="N46" t="n">
-        <v>5.61</v>
+        <v>2.03</v>
       </c>
       <c r="O46" t="n">
-        <v>8.272500000000001</v>
+        <v>7.336</v>
       </c>
       <c r="P46" t="n">
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.099</v>
+        <v>0.0532</v>
       </c>
       <c r="R46" t="n">
-        <v>0.468</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>When should I do laundry today?</t>
+          <t>It's late morning, just before noon and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lebanon, PA</t>
+          <t>Easton, PA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>385</v>
+        <v>190</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>washer</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3509,65 +3509,65 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>0.28</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>9.9</v>
+        <v>8.34</v>
       </c>
       <c r="L47" t="n">
-        <v>9.859999999999999</v>
+        <v>3.06</v>
       </c>
       <c r="M47" t="n">
-        <v>9.43</v>
+        <v>10</v>
       </c>
       <c r="N47" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="O47" t="n">
-        <v>9.672000000000001</v>
+        <v>7.073</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.028</v>
+        <v>0.2</v>
       </c>
       <c r="R47" t="n">
-        <v>0.291</v>
+        <v>2.603</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>When should I do laundry today?</t>
+          <t>It's late morning, just before noon and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lebanon, PA</t>
+          <t>Easton, PA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>385</v>
+        <v>190</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>washer</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3575,65 +3575,65 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>0.28</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>9.9</v>
+        <v>5.17</v>
       </c>
       <c r="L48" t="n">
-        <v>9.859999999999999</v>
+        <v>3.06</v>
       </c>
       <c r="M48" t="n">
-        <v>8.18</v>
+        <v>7.81</v>
       </c>
       <c r="N48" t="n">
-        <v>7.32</v>
+        <v>6.66</v>
       </c>
       <c r="O48" t="n">
-        <v>9.154999999999999</v>
+        <v>5.183</v>
       </c>
       <c r="P48" t="n">
         <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.028</v>
+        <v>0.55</v>
       </c>
       <c r="R48" t="n">
-        <v>0.291</v>
+        <v>2.603</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>When should I do laundry today?</t>
+          <t>It's late morning, just before noon and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lebanon, PA</t>
+          <t>Easton, PA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>385</v>
+        <v>190</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>washer</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -3641,285 +3641,285 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>0.28</v>
+        <v>2.5</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>12:00 AM</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>9.800000000000001</v>
+        <v>8.34</v>
       </c>
       <c r="L49" t="n">
-        <v>9.859999999999999</v>
+        <v>3.54</v>
       </c>
       <c r="M49" t="n">
-        <v>5.81</v>
+        <v>2.86</v>
       </c>
       <c r="N49" t="n">
-        <v>4.64</v>
+        <v>1.51</v>
       </c>
       <c r="O49" t="n">
-        <v>8.249000000000001</v>
+        <v>4.539499999999999</v>
       </c>
       <c r="P49" t="n">
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.0392</v>
+        <v>0.2</v>
       </c>
       <c r="R49" t="n">
-        <v>0.291</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>When should I run my dryer after washing clothes?</t>
+          <t>It's around 10 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Johnstown, PA</t>
+          <t>Chambersburg, PA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>260</v>
+        <v>165</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>dryer</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
-        <v>2.8</v>
+        <v>0.32</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>8.33</v>
+        <v>9.92</v>
       </c>
       <c r="L50" t="n">
-        <v>2.14</v>
+        <v>9.74</v>
       </c>
       <c r="M50" t="n">
-        <v>9.460000000000001</v>
+        <v>10</v>
       </c>
       <c r="N50" t="n">
-        <v>9.15</v>
+        <v>10</v>
       </c>
       <c r="O50" t="n">
-        <v>6.512500000000001</v>
+        <v>9.885</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.2016</v>
+        <v>0.0256</v>
       </c>
       <c r="R50" t="n">
-        <v>2.915</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>When should I run my dryer after washing clothes?</t>
+          <t>It's around 10 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Johnstown, PA</t>
+          <t>Chambersburg, PA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>260</v>
+        <v>165</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>dryer</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I51" t="n">
-        <v>2.8</v>
+        <v>0.32</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>8.33</v>
+        <v>9.52</v>
       </c>
       <c r="L51" t="n">
-        <v>2.14</v>
+        <v>9.74</v>
       </c>
       <c r="M51" t="n">
-        <v>8.9</v>
+        <v>7.43</v>
       </c>
       <c r="N51" t="n">
-        <v>8.23</v>
+        <v>6.21</v>
       </c>
       <c r="O51" t="n">
-        <v>6.2625</v>
+        <v>8.682499999999999</v>
       </c>
       <c r="P51" t="n">
         <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.2016</v>
+        <v>0.0704</v>
       </c>
       <c r="R51" t="n">
-        <v>2.915</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>When should I run my dryer after washing clothes?</t>
+          <t>It's around 10 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Johnstown, PA</t>
+          <t>Chambersburg, PA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>260</v>
+        <v>165</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>dryer</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I52" t="n">
-        <v>2.8</v>
+        <v>0.32</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>10:00 PM</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>5.46</v>
+        <v>9.92</v>
       </c>
       <c r="L52" t="n">
-        <v>2.14</v>
+        <v>9.74</v>
       </c>
       <c r="M52" t="n">
-        <v>6.74</v>
+        <v>1.53</v>
       </c>
       <c r="N52" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="O52" t="n">
-        <v>4.545</v>
+        <v>7.021</v>
       </c>
       <c r="P52" t="n">
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.518</v>
+        <v>0.0256</v>
       </c>
       <c r="R52" t="n">
-        <v>2.915</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>When should I run my dryer after washing clothes?</t>
+          <t>It's around 3 in the afternoon and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hazleton, PA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>dryer</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>1.2</v>
+        <v>0.15</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>9.07</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>7.04</v>
+        <v>10</v>
       </c>
       <c r="M53" t="n">
         <v>10</v>
@@ -3928,166 +3928,166 @@
         <v>10</v>
       </c>
       <c r="O53" t="n">
-        <v>8.685</v>
+        <v>9.916</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.12</v>
+        <v>0.048</v>
       </c>
       <c r="R53" t="n">
-        <v>1.249</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>When should I run my dryer after washing clothes?</t>
+          <t>It's around 3 in the afternoon and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hazleton, PA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>dryer</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>0.15</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>9.07</v>
+        <v>10</v>
       </c>
       <c r="L54" t="n">
-        <v>7.04</v>
+        <v>10</v>
       </c>
       <c r="M54" t="n">
-        <v>7.81</v>
+        <v>7.43</v>
       </c>
       <c r="N54" t="n">
-        <v>6.66</v>
+        <v>6.21</v>
       </c>
       <c r="O54" t="n">
-        <v>7.746</v>
+        <v>8.9175</v>
       </c>
       <c r="P54" t="n">
         <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.12</v>
+        <v>0.0114</v>
       </c>
       <c r="R54" t="n">
-        <v>1.249</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>When should I run my dryer after washing clothes?</t>
+          <t>It's around 3 in the afternoon and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hazleton, PA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>dryer</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>0.15</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>11:00 PM</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>8.630000000000001</v>
+        <v>10</v>
       </c>
       <c r="L55" t="n">
-        <v>7.04</v>
+        <v>10</v>
       </c>
       <c r="M55" t="n">
-        <v>5.92</v>
+        <v>3.59</v>
       </c>
       <c r="N55" t="n">
-        <v>4.31</v>
+        <v>4.08</v>
       </c>
       <c r="O55" t="n">
-        <v>6.8835</v>
+        <v>7.83</v>
       </c>
       <c r="P55" t="n">
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.168</v>
+        <v>0.0114</v>
       </c>
       <c r="R55" t="n">
-        <v>1.249</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>When should I run my dryer after washing clothes?</t>
+          <t>It's just past midnight and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scranton, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -4103,57 +4103,57 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I56" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>12:00 AM</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>6.98</v>
+        <v>7.04</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="M56" t="n">
-        <v>10</v>
+        <v>7.83</v>
       </c>
       <c r="N56" t="n">
-        <v>10</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O56" t="n">
-        <v>5.593999999999999</v>
+        <v>6.1845</v>
       </c>
       <c r="P56" t="n">
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.35</v>
+        <v>0.3438</v>
       </c>
       <c r="R56" t="n">
-        <v>3.643</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>When should I run my dryer after washing clothes?</t>
+          <t>It's just past midnight and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scranton, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -4169,57 +4169,57 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I57" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>6.98</v>
+        <v>7.04</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M57" t="n">
-        <v>8.6</v>
+        <v>5.53</v>
       </c>
       <c r="N57" t="n">
-        <v>7.82</v>
+        <v>3.87</v>
       </c>
       <c r="O57" t="n">
-        <v>4.987</v>
+        <v>4.869499999999999</v>
       </c>
       <c r="P57" t="n">
         <v>2</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.35</v>
+        <v>0.3438</v>
       </c>
       <c r="R57" t="n">
-        <v>3.643</v>
+        <v>2.603</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>When should I run my dryer after washing clothes?</t>
+          <t>It's just past midnight and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Scranton, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -4235,61 +4235,61 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I58" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>5.71</v>
+        <v>7.04</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M58" t="n">
-        <v>7.43</v>
+        <v>5.13</v>
       </c>
       <c r="N58" t="n">
-        <v>6.21</v>
+        <v>3.42</v>
       </c>
       <c r="O58" t="n">
-        <v>4.1305</v>
+        <v>4.722</v>
       </c>
       <c r="P58" t="n">
         <v>3</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.49</v>
+        <v>0.3438</v>
       </c>
       <c r="R58" t="n">
-        <v>3.643</v>
+        <v>2.603</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>My laundry is ready to dry (around 11 AM). Should I run the dryer now or wait?</t>
+          <t>It's nearly 11 at night � when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Easton, PA</t>
+          <t>Altoona, PA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>dryer</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -4297,65 +4297,65 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>0.42</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>11:00 PM</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>8.34</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>3.06</v>
+        <v>9.51</v>
       </c>
       <c r="M59" t="n">
-        <v>10</v>
+        <v>7.83</v>
       </c>
       <c r="N59" t="n">
-        <v>10</v>
+        <v>9.25</v>
       </c>
       <c r="O59" t="n">
-        <v>7.073</v>
+        <v>9.245999999999999</v>
       </c>
       <c r="P59" t="n">
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.2</v>
+        <v>0.0302</v>
       </c>
       <c r="R59" t="n">
-        <v>2.603</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>My laundry is ready to dry (around 11 AM). Should I run the dryer now or wait?</t>
+          <t>It's nearly 11 at night � when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Easton, PA</t>
+          <t>Altoona, PA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>dryer</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -4363,65 +4363,65 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I60" t="n">
-        <v>2.5</v>
+        <v>0.42</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>5.17</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>3.06</v>
+        <v>9.43</v>
       </c>
       <c r="M60" t="n">
-        <v>7.81</v>
+        <v>4.71</v>
       </c>
       <c r="N60" t="n">
-        <v>6.66</v>
+        <v>2.95</v>
       </c>
       <c r="O60" t="n">
-        <v>5.183</v>
+        <v>7.649</v>
       </c>
       <c r="P60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.55</v>
+        <v>0.0302</v>
       </c>
       <c r="R60" t="n">
-        <v>2.603</v>
+        <v>0.437</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>My laundry is ready to dry (around 11 AM). Should I run the dryer now or wait?</t>
+          <t>It's nearly 11 at night � when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Easton, PA</t>
+          <t>Altoona, PA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>dryer</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -4429,57 +4429,57 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I61" t="n">
-        <v>2.5</v>
+        <v>0.42</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>12:00 AM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>8.34</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>3.54</v>
+        <v>9.43</v>
       </c>
       <c r="M61" t="n">
-        <v>2.86</v>
+        <v>5.92</v>
       </c>
       <c r="N61" t="n">
-        <v>1.51</v>
+        <v>4.64</v>
       </c>
       <c r="O61" t="n">
-        <v>4.539499999999999</v>
+        <v>8.015499999999999</v>
       </c>
       <c r="P61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.2</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="R61" t="n">
-        <v>2.44</v>
+        <v>0.437</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>I have time to do laundry this morning (around 10 AM). When should I start?</t>
+          <t>It's barely 5 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chambersburg, PA</t>
+          <t>King of Prussia, PA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -4495,57 +4495,57 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I62" t="n">
-        <v>0.32</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>5:00 AM</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>9.92</v>
+        <v>9.33</v>
       </c>
       <c r="L62" t="n">
-        <v>9.74</v>
+        <v>7.27</v>
       </c>
       <c r="M62" t="n">
         <v>10</v>
       </c>
       <c r="N62" t="n">
-        <v>10</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O62" t="n">
-        <v>9.885</v>
+        <v>8.610999999999999</v>
       </c>
       <c r="P62" t="n">
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.0256</v>
+        <v>0.0912</v>
       </c>
       <c r="R62" t="n">
-        <v>0.333</v>
+        <v>1.171</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>I have time to do laundry this morning (around 10 AM). When should I start?</t>
+          <t>It's barely 5 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chambersburg, PA</t>
+          <t>King of Prussia, PA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -4561,57 +4561,57 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I63" t="n">
-        <v>0.32</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>9.52</v>
+        <v>9.33</v>
       </c>
       <c r="L63" t="n">
-        <v>9.74</v>
+        <v>7.04</v>
       </c>
       <c r="M63" t="n">
-        <v>7.43</v>
+        <v>8.02</v>
       </c>
       <c r="N63" t="n">
-        <v>6.21</v>
+        <v>6.91</v>
       </c>
       <c r="O63" t="n">
-        <v>8.682499999999999</v>
+        <v>7.9035</v>
       </c>
       <c r="P63" t="n">
         <v>2</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.0704</v>
+        <v>0.0912</v>
       </c>
       <c r="R63" t="n">
-        <v>0.333</v>
+        <v>1.249</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>I have time to do laundry this morning (around 10 AM). When should I start?</t>
+          <t>It's barely 5 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chambersburg, PA</t>
+          <t>King of Prussia, PA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -4627,69 +4627,69 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I64" t="n">
-        <v>0.32</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>10:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>9.92</v>
+        <v>9.33</v>
       </c>
       <c r="L64" t="n">
-        <v>9.74</v>
+        <v>7.04</v>
       </c>
       <c r="M64" t="n">
-        <v>1.53</v>
+        <v>5.26</v>
       </c>
       <c r="N64" t="n">
-        <v>2.2</v>
+        <v>4.64</v>
       </c>
       <c r="O64" t="n">
-        <v>7.021</v>
+        <v>7.010999999999999</v>
       </c>
       <c r="P64" t="n">
         <v>3</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.0256</v>
+        <v>0.0912</v>
       </c>
       <c r="R64" t="n">
-        <v>0.333</v>
+        <v>1.249</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>I need to dry clothes this afternoon (around 2 PM). When should I start?</t>
+          <t>It's late afternoon, just past 3 � when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>McKeesport, PA</t>
+          <t>Greensburg, PA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>dryer</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4697,21 +4697,21 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I65" t="n">
-        <v>2.6</v>
+        <v>1.05</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>6.91</v>
+        <v>8.58</v>
       </c>
       <c r="L65" t="n">
-        <v>2.76</v>
+        <v>7.5</v>
       </c>
       <c r="M65" t="n">
         <v>10</v>
@@ -4720,42 +4720,42 @@
         <v>10</v>
       </c>
       <c r="O65" t="n">
-        <v>6.539</v>
+        <v>8.699</v>
       </c>
       <c r="P65" t="n">
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.3575</v>
+        <v>0.1733</v>
       </c>
       <c r="R65" t="n">
-        <v>2.707</v>
+        <v>1.093</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>I need to dry clothes this afternoon (around 2 PM). When should I start?</t>
+          <t>It's late afternoon, just past 3 � when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>McKeesport, PA</t>
+          <t>Greensburg, PA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>dryer</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4763,65 +4763,65 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I66" t="n">
-        <v>2.6</v>
+        <v>1.05</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>9:00 PM</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>6.91</v>
+        <v>9.52</v>
       </c>
       <c r="L66" t="n">
-        <v>2.76</v>
+        <v>7.5</v>
       </c>
       <c r="M66" t="n">
-        <v>7.29</v>
+        <v>7.09</v>
       </c>
       <c r="N66" t="n">
-        <v>6.04</v>
+        <v>5.81</v>
       </c>
       <c r="O66" t="n">
-        <v>5.403</v>
+        <v>7.7705</v>
       </c>
       <c r="P66" t="n">
         <v>2</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.3575</v>
+        <v>0.0704</v>
       </c>
       <c r="R66" t="n">
-        <v>2.707</v>
+        <v>1.093</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>I need to dry clothes this afternoon (around 2 PM). When should I start?</t>
+          <t>It's late afternoon, just past 3 � when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>McKeesport, PA</t>
+          <t>Greensburg, PA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>dryer</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4829,48 +4829,48 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I67" t="n">
-        <v>2.6</v>
+        <v>1.05</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>10:00 PM</t>
+          <t>11:00 PM</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>6.91</v>
+        <v>9.52</v>
       </c>
       <c r="L67" t="n">
-        <v>2.76</v>
+        <v>7.7</v>
       </c>
       <c r="M67" t="n">
-        <v>3.36</v>
+        <v>6.17</v>
       </c>
       <c r="N67" t="n">
-        <v>3.11</v>
+        <v>3.44</v>
       </c>
       <c r="O67" t="n">
-        <v>4.1775</v>
+        <v>7.301</v>
       </c>
       <c r="P67" t="n">
         <v>3</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.3575</v>
+        <v>0.0704</v>
       </c>
       <c r="R67" t="n">
-        <v>2.707</v>
+        <v>1.025</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Dinner's done around 8 PM. What's the best time to run the dishwasher?</t>
+          <t>It's around 8 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -4895,21 +4895,21 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>1.85</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>8:00 AM</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>8.779999999999999</v>
+        <v>7.85</v>
       </c>
       <c r="L68" t="n">
-        <v>7.35</v>
+        <v>5.05</v>
       </c>
       <c r="M68" t="n">
         <v>10</v>
@@ -4918,25 +4918,25 @@
         <v>10</v>
       </c>
       <c r="O68" t="n">
-        <v>8.7065</v>
+        <v>7.6225</v>
       </c>
       <c r="P68" t="n">
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.1513</v>
+        <v>0.2544</v>
       </c>
       <c r="R68" t="n">
-        <v>1.145</v>
+        <v>1.926</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dinner's done around 8 PM. What's the best time to run the dishwasher?</t>
+          <t>It's around 8 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4961,48 +4961,48 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>1.85</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>8.779999999999999</v>
+        <v>7.85</v>
       </c>
       <c r="L69" t="n">
-        <v>7.35</v>
+        <v>5.05</v>
       </c>
       <c r="M69" t="n">
-        <v>4.08</v>
+        <v>7.09</v>
       </c>
       <c r="N69" t="n">
-        <v>4.64</v>
+        <v>5.81</v>
       </c>
       <c r="O69" t="n">
-        <v>6.7185</v>
+        <v>6.412</v>
       </c>
       <c r="P69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.1513</v>
+        <v>0.2544</v>
       </c>
       <c r="R69" t="n">
-        <v>1.145</v>
+        <v>1.926</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dinner's done around 8 PM. What's the best time to run the dishwasher?</t>
+          <t>It's around 8 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5011,7 +5011,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>1.85</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -5038,76 +5038,76 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>8.779999999999999</v>
+        <v>7.85</v>
       </c>
       <c r="L70" t="n">
-        <v>7.56</v>
+        <v>5.41</v>
       </c>
       <c r="M70" t="n">
-        <v>8.32</v>
+        <v>5.73</v>
       </c>
       <c r="N70" t="n">
-        <v>6.57</v>
+        <v>2.89</v>
       </c>
       <c r="O70" t="n">
-        <v>7.929499999999999</v>
+        <v>5.827999999999999</v>
       </c>
       <c r="P70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.1513</v>
+        <v>0.2544</v>
       </c>
       <c r="R70" t="n">
-        <v>1.074</v>
+        <v>1.806</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>I have time to do a quick load of laundry this afternoon (around 3 PM). When should I start?</t>
+          <t>It's around 2 in the afternoon and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Erie, PA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>140</v>
+        <v>215</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I71" t="n">
-        <v>0.15</v>
+        <v>4.1</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>9.720000000000001</v>
+        <v>3.28</v>
       </c>
       <c r="L71" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
         <v>10</v>
@@ -5116,162 +5116,162 @@
         <v>10</v>
       </c>
       <c r="O71" t="n">
-        <v>9.916</v>
+        <v>4.484</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.048</v>
+        <v>0.7585</v>
       </c>
       <c r="R71" t="n">
-        <v>0.156</v>
+        <v>4.268</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>I have time to do a quick load of laundry this afternoon (around 3 PM). When should I start?</t>
+          <t>It's around 2 in the afternoon and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Erie, PA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>140</v>
+        <v>215</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I72" t="n">
-        <v>0.15</v>
+        <v>4.1</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>9:00 PM</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>10</v>
+        <v>7.48</v>
       </c>
       <c r="L72" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>7.43</v>
+        <v>6.29</v>
       </c>
       <c r="N72" t="n">
-        <v>6.21</v>
+        <v>4.86</v>
       </c>
       <c r="O72" t="n">
-        <v>8.9175</v>
+        <v>4.231</v>
       </c>
       <c r="P72" t="n">
         <v>2</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.0114</v>
+        <v>0.2952</v>
       </c>
       <c r="R72" t="n">
-        <v>0.156</v>
+        <v>4.268</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>I have time to do a quick load of laundry this afternoon (around 3 PM). When should I start?</t>
+          <t>It's around 2 in the afternoon and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Erie, PA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>140</v>
+        <v>215</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I73" t="n">
-        <v>0.15</v>
+        <v>4.1</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>11:00 PM</t>
+          <t>2:00 AM</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>10</v>
+        <v>7.48</v>
       </c>
       <c r="L73" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.59</v>
+        <v>1.24</v>
       </c>
       <c r="N73" t="n">
-        <v>4.08</v>
+        <v>1.51</v>
       </c>
       <c r="O73" t="n">
-        <v>7.83</v>
+        <v>2.7185</v>
       </c>
       <c r="P73" t="n">
         <v>3</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.0114</v>
+        <v>0.2952</v>
       </c>
       <c r="R73" t="n">
-        <v>0.146</v>
+        <v>4.002</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Planning to run the dishwasher around 6 PM. Is that a good time?</t>
+          <t>It's about 10 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Harrisburg, PA</t>
+          <t>Allentown, PA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -5291,21 +5291,21 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>8.609999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="L74" t="n">
-        <v>5.51</v>
+        <v>4.29</v>
       </c>
       <c r="M74" t="n">
         <v>10</v>
@@ -5314,30 +5314,30 @@
         <v>10</v>
       </c>
       <c r="O74" t="n">
-        <v>8.0115</v>
+        <v>7.4765</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="R74" t="n">
-        <v>1.77</v>
+        <v>2.186</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Planning to run the dishwasher around 6 PM. Is that a good time?</t>
+          <t>It's about 10 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Harrisburg, PA</t>
+          <t>Allentown, PA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -5357,53 +5357,53 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>8.609999999999999</v>
+        <v>7.49</v>
       </c>
       <c r="L75" t="n">
-        <v>5.51</v>
+        <v>4.29</v>
       </c>
       <c r="M75" t="n">
-        <v>5.21</v>
+        <v>8.02</v>
       </c>
       <c r="N75" t="n">
-        <v>4.64</v>
+        <v>6.91</v>
       </c>
       <c r="O75" t="n">
-        <v>6.249499999999999</v>
+        <v>6.389</v>
       </c>
       <c r="P75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.17</v>
+        <v>0.294</v>
       </c>
       <c r="R75" t="n">
-        <v>1.77</v>
+        <v>2.186</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Planning to run the dishwasher around 6 PM. Is that a good time?</t>
+          <t>It's about 10 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Harrisburg, PA</t>
+          <t>Allentown, PA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -5423,255 +5423,255 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>10:00 PM</t>
+          <t>11:00 PM</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>8.609999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="L76" t="n">
-        <v>5.51</v>
+        <v>4.69</v>
       </c>
       <c r="M76" t="n">
-        <v>7.83</v>
+        <v>4.78</v>
       </c>
       <c r="N76" t="n">
-        <v>5.71</v>
+        <v>1.71</v>
       </c>
       <c r="O76" t="n">
-        <v>6.933999999999999</v>
+        <v>5.329000000000001</v>
       </c>
       <c r="P76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="R76" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>It's late (around midnight) and I need to dry laundry. Should I start now or wait?</t>
+          <t>It's just past 5 PM and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>King of Prussia, PA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>dryer</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I77" t="n">
-        <v>2.5</v>
+        <v>1.15</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>12:00 AM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>7.04</v>
+        <v>6.82</v>
       </c>
       <c r="L77" t="n">
-        <v>3.54</v>
+        <v>7.2</v>
       </c>
       <c r="M77" t="n">
-        <v>7.83</v>
+        <v>10</v>
       </c>
       <c r="N77" t="n">
-        <v>8.449999999999999</v>
+        <v>10</v>
       </c>
       <c r="O77" t="n">
-        <v>6.1845</v>
+        <v>8.065999999999999</v>
       </c>
       <c r="P77" t="n">
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.3438</v>
+        <v>0.368</v>
       </c>
       <c r="R77" t="n">
-        <v>2.44</v>
+        <v>1.197</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>It's late (around midnight) and I need to dry laundry. Should I start now or wait?</t>
+          <t>It's just past 5 PM and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>King of Prussia, PA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>dryer</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I78" t="n">
-        <v>2.5</v>
+        <v>1.15</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>11:00 PM</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>7.04</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>3.06</v>
+        <v>7.42</v>
       </c>
       <c r="M78" t="n">
-        <v>5.53</v>
+        <v>7.43</v>
       </c>
       <c r="N78" t="n">
-        <v>3.87</v>
+        <v>5.19</v>
       </c>
       <c r="O78" t="n">
-        <v>4.8695</v>
+        <v>7.669499999999999</v>
       </c>
       <c r="P78" t="n">
         <v>2</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.3438</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="R78" t="n">
-        <v>2.603</v>
+        <v>1.122</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>It's late (around midnight) and I need to dry laundry. Should I start now or wait?</t>
+          <t>It's just past 5 PM and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>King of Prussia, PA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>dryer</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I79" t="n">
-        <v>2.5</v>
+        <v>1.15</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>8:00 AM</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>7.04</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>3.06</v>
+        <v>7.2</v>
       </c>
       <c r="M79" t="n">
-        <v>5.13</v>
+        <v>6.29</v>
       </c>
       <c r="N79" t="n">
-        <v>3.42</v>
+        <v>4.78</v>
       </c>
       <c r="O79" t="n">
-        <v>4.722</v>
+        <v>7.302999999999999</v>
       </c>
       <c r="P79" t="n">
         <v>3</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.3438</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="R79" t="n">
-        <v>2.603</v>
+        <v>1.197</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Planning to run the washing machine around 11 PM. Is that okay or should I wait?</t>
+          <t>It's around 10 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Altoona, PA</t>
+          <t>Blue Bell, PA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -5679,65 +5679,65 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I80" t="n">
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>11:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>9.880000000000001</v>
+        <v>9.93</v>
       </c>
       <c r="L80" t="n">
-        <v>9.51</v>
+        <v>9.74</v>
       </c>
       <c r="M80" t="n">
-        <v>7.83</v>
+        <v>10</v>
       </c>
       <c r="N80" t="n">
-        <v>9.25</v>
+        <v>10</v>
       </c>
       <c r="O80" t="n">
-        <v>9.246</v>
+        <v>9.888</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.0302</v>
+        <v>0.0243</v>
       </c>
       <c r="R80" t="n">
-        <v>0.41</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Planning to run the washing machine around 11 PM. Is that okay or should I wait?</t>
+          <t>It's around 10 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Altoona, PA</t>
+          <t>Blue Bell, PA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -5745,65 +5745,65 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I81" t="n">
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>9.880000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="L81" t="n">
-        <v>9.43</v>
+        <v>9.74</v>
       </c>
       <c r="M81" t="n">
-        <v>4.71</v>
+        <v>7.83</v>
       </c>
       <c r="N81" t="n">
-        <v>2.95</v>
+        <v>6.69</v>
       </c>
       <c r="O81" t="n">
-        <v>7.649</v>
+        <v>8.7475</v>
       </c>
       <c r="P81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.0302</v>
+        <v>0.1024</v>
       </c>
       <c r="R81" t="n">
-        <v>0.437</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Planning to run the washing machine around 11 PM. Is that okay or should I wait?</t>
+          <t>It's around 10 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Altoona, PA</t>
+          <t>Blue Bell, PA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -5811,293 +5811,293 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I82" t="n">
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>11:00 PM</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>9.449999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="L82" t="n">
-        <v>9.43</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M82" t="n">
-        <v>5.92</v>
+        <v>2.08</v>
       </c>
       <c r="N82" t="n">
-        <v>4.64</v>
+        <v>2.7</v>
       </c>
       <c r="O82" t="n">
-        <v>8.015499999999999</v>
+        <v>7.23</v>
       </c>
       <c r="P82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0243</v>
       </c>
       <c r="R82" t="n">
-        <v>0.437</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>I want to run the dishwasher at 5 AM before work. Should I wait?</t>
+          <t>It's just past 9 AM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>King of Prussia, PA</t>
+          <t>Doylestown, PA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="H83" t="n">
         <v>3</v>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>5:00 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>9.33</v>
+        <v>8.16</v>
       </c>
       <c r="L83" t="n">
-        <v>7.27</v>
+        <v>1.84</v>
       </c>
       <c r="M83" t="n">
         <v>10</v>
       </c>
       <c r="N83" t="n">
-        <v>8.449999999999999</v>
+        <v>10</v>
       </c>
       <c r="O83" t="n">
-        <v>8.610999999999999</v>
+        <v>6.592000000000001</v>
       </c>
       <c r="P83" t="n">
         <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.0912</v>
+        <v>0.2204</v>
       </c>
       <c r="R83" t="n">
-        <v>1.171</v>
+        <v>3.019</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>I want to run the dishwasher at 5 AM before work. Should I wait?</t>
+          <t>It's just past 9 AM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>King of Prussia, PA</t>
+          <t>Doylestown, PA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="H84" t="n">
         <v>3</v>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>9.33</v>
+        <v>1.74</v>
       </c>
       <c r="L84" t="n">
-        <v>7.04</v>
+        <v>1.84</v>
       </c>
       <c r="M84" t="n">
-        <v>8.02</v>
+        <v>7.29</v>
       </c>
       <c r="N84" t="n">
-        <v>6.91</v>
+        <v>6.04</v>
       </c>
       <c r="O84" t="n">
-        <v>7.9035</v>
+        <v>3.53</v>
       </c>
       <c r="P84" t="n">
         <v>2</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.0912</v>
+        <v>0.928</v>
       </c>
       <c r="R84" t="n">
-        <v>1.249</v>
+        <v>3.019</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>I want to run the dishwasher at 5 AM before work. Should I wait?</t>
+          <t>It's just past 9 AM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>King of Prussia, PA</t>
+          <t>Doylestown, PA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="H85" t="n">
         <v>3</v>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>10:00 PM</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>9.33</v>
+        <v>8.16</v>
       </c>
       <c r="L85" t="n">
-        <v>7.04</v>
+        <v>1.84</v>
       </c>
       <c r="M85" t="n">
-        <v>5.26</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N85" t="n">
-        <v>4.64</v>
+        <v>1.61</v>
       </c>
       <c r="O85" t="n">
-        <v>7.010999999999999</v>
+        <v>3.5215</v>
       </c>
       <c r="P85" t="n">
         <v>3</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.0912</v>
+        <v>0.2204</v>
       </c>
       <c r="R85" t="n">
-        <v>1.249</v>
+        <v>3.019</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>My laundry is ready to dry around 4 PM. Should I start now or wait?</t>
+          <t>It's around 2 in the afternoon and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bethlehem, PA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>dryer</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Rowhouse</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I86" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>6.6</v>
+        <v>6.67</v>
       </c>
       <c r="L86" t="n">
-        <v>2.14</v>
+        <v>7.04</v>
       </c>
       <c r="M86" t="n">
         <v>10</v>
@@ -6106,196 +6106,196 @@
         <v>10</v>
       </c>
       <c r="O86" t="n">
-        <v>6.228999999999999</v>
+        <v>7.965</v>
       </c>
       <c r="P86" t="n">
         <v>1</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.392</v>
+        <v>0.384</v>
       </c>
       <c r="R86" t="n">
-        <v>2.915</v>
+        <v>1.249</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>My laundry is ready to dry around 4 PM. Should I start now or wait?</t>
+          <t>It's around 2 in the afternoon and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bethlehem, PA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>dryer</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Rowhouse</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I87" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>7.62</v>
+        <v>9.33</v>
       </c>
       <c r="L87" t="n">
-        <v>2.14</v>
+        <v>7.04</v>
       </c>
       <c r="M87" t="n">
-        <v>8.9</v>
+        <v>7.09</v>
       </c>
       <c r="N87" t="n">
-        <v>8.23</v>
+        <v>5.81</v>
       </c>
       <c r="O87" t="n">
-        <v>6.0495</v>
+        <v>7.5525</v>
       </c>
       <c r="P87" t="n">
         <v>2</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.28</v>
+        <v>0.0912</v>
       </c>
       <c r="R87" t="n">
-        <v>2.915</v>
+        <v>1.249</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>My laundry is ready to dry around 4 PM. Should I start now or wait?</t>
+          <t>It's around 2 in the afternoon and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bethlehem, PA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>dryer</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Rowhouse</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I88" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>10:00 PM</t>
+          <t>2:00 AM</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>7.62</v>
+        <v>9.33</v>
       </c>
       <c r="L88" t="n">
-        <v>2.14</v>
+        <v>7.27</v>
       </c>
       <c r="M88" t="n">
-        <v>4.39</v>
+        <v>4.28</v>
       </c>
       <c r="N88" t="n">
-        <v>4.31</v>
+        <v>1.51</v>
       </c>
       <c r="O88" t="n">
-        <v>4.5595</v>
+        <v>6.425999999999999</v>
       </c>
       <c r="P88" t="n">
         <v>3</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.28</v>
+        <v>0.0912</v>
       </c>
       <c r="R88" t="n">
-        <v>2.915</v>
+        <v>1.171</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>The dishwasher is ready in Greensburg around 3 PM. Should I run it now or delay?</t>
+          <t>It's about 7 in the evening and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Greensburg, PA</t>
+          <t>Lancaster, PA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Rowhouse</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I89" t="n">
-        <v>1.05</v>
+        <v>0.42</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>8.58</v>
+        <v>9.77</v>
       </c>
       <c r="L89" t="n">
-        <v>7.5</v>
+        <v>9.43</v>
       </c>
       <c r="M89" t="n">
         <v>10</v>
@@ -6304,147 +6304,1137 @@
         <v>10</v>
       </c>
       <c r="O89" t="n">
-        <v>8.699</v>
+        <v>9.731499999999999</v>
       </c>
       <c r="P89" t="n">
         <v>1</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.1733</v>
+        <v>0.042</v>
       </c>
       <c r="R89" t="n">
-        <v>1.093</v>
+        <v>0.437</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>The dishwasher is ready in Greensburg around 3 PM. Should I run it now or delay?</t>
+          <t>It's about 7 in the evening and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Greensburg, PA</t>
+          <t>Lancaster, PA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>dishwasher</t>
+          <t>washing_machine</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Rowhouse</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I90" t="n">
-        <v>1.05</v>
+        <v>0.42</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>9:00 PM</t>
+          <t>11:00 PM</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>9.52</v>
+        <v>9.77</v>
       </c>
       <c r="L90" t="n">
-        <v>7.5</v>
+        <v>9.51</v>
       </c>
       <c r="M90" t="n">
-        <v>7.09</v>
+        <v>5.82</v>
       </c>
       <c r="N90" t="n">
         <v>5.81</v>
       </c>
       <c r="O90" t="n">
-        <v>7.7705</v>
+        <v>8.294999999999998</v>
       </c>
       <c r="P90" t="n">
         <v>2</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.0704</v>
+        <v>0.042</v>
       </c>
       <c r="R90" t="n">
-        <v>1.093</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The dishwasher is ready in Greensburg around 3 PM. Should I run it now or delay?</t>
+          <t>It's about 7 in the evening and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Greensburg, PA</t>
+          <t>Lancaster, PA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
+          <t>washing_machine</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>8</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Rowhouse</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>4</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="L91" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="M91" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O91" t="n">
+        <v>7.615999999999999</v>
+      </c>
+      <c r="P91" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0.437</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>85</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>It's around 8 in the morning and I need to run the dryer. When should I start it?</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Norristown, PA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>195</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>dryer</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>11</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Rowhouse</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>3</v>
+      </c>
+      <c r="I92" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="L92" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M92" t="n">
+        <v>10</v>
+      </c>
+      <c r="N92" t="n">
+        <v>10</v>
+      </c>
+      <c r="O92" t="n">
+        <v>6.336499999999999</v>
+      </c>
+      <c r="P92" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0.2356</v>
+      </c>
+      <c r="R92" t="n">
+        <v>3.227</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>85</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>It's around 8 in the morning and I need to run the dryer. When should I start it?</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Norristown, PA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>195</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>dryer</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>11</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Rowhouse</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>3</v>
+      </c>
+      <c r="I93" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L93" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M93" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="N93" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="O93" t="n">
+        <v>2.7655</v>
+      </c>
+      <c r="P93" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="R93" t="n">
+        <v>3.227</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>85</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>It's around 8 in the morning and I need to run the dryer. When should I start it?</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Norristown, PA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>195</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>dryer</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>11</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Rowhouse</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>3</v>
+      </c>
+      <c r="I94" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>11:00 PM</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="L94" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="M94" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N94" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O94" t="n">
+        <v>4.0095</v>
+      </c>
+      <c r="P94" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0.2356</v>
+      </c>
+      <c r="R94" t="n">
+        <v>3.026</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>96</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>It's around 2 in the afternoon � when should I run the dryer?</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>McKeesport, PA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>220</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>dryer</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>7</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>4</v>
+      </c>
+      <c r="I95" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="L95" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M95" t="n">
+        <v>10</v>
+      </c>
+      <c r="N95" t="n">
+        <v>10</v>
+      </c>
+      <c r="O95" t="n">
+        <v>6.539</v>
+      </c>
+      <c r="P95" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="R95" t="n">
+        <v>2.707</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>96</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>It's around 2 in the afternoon � when should I run the dryer?</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>McKeesport, PA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>220</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>dryer</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>7</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>4</v>
+      </c>
+      <c r="I96" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="L96" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M96" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="N96" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="O96" t="n">
+        <v>5.403</v>
+      </c>
+      <c r="P96" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="R96" t="n">
+        <v>2.707</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>It's around 2 in the afternoon � when should I run the dryer?</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>McKeesport, PA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>220</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>dryer</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>7</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>4</v>
+      </c>
+      <c r="I97" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>10:00 PM</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="L97" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M97" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="N97" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="O97" t="n">
+        <v>4.1775</v>
+      </c>
+      <c r="P97" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="R97" t="n">
+        <v>2.707</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>It's just got home � it's around 6 PM � and I need to run the dishwasher. When should I start it?</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>200</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F91" t="n">
+      <c r="F98" t="n">
+        <v>10</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Single-family</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
         <v>6</v>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="I98" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="L98" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="M98" t="n">
+        <v>10</v>
+      </c>
+      <c r="N98" t="n">
+        <v>10</v>
+      </c>
+      <c r="O98" t="n">
+        <v>8.0115</v>
+      </c>
+      <c r="P98" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="R98" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>It's just got home � it's around 6 PM � and I need to run the dishwasher. When should I start it?</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>200</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>dishwasher</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>10</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Single-family</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>6</v>
+      </c>
+      <c r="I99" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="L99" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="M99" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="N99" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="O99" t="n">
+        <v>6.249499999999999</v>
+      </c>
+      <c r="P99" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="R99" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>97</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>It's just got home � it's around 6 PM � and I need to run the dishwasher. When should I start it?</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>200</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>dishwasher</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>10</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Single-family</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>6</v>
+      </c>
+      <c r="I100" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>10:00 PM</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="L100" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="M100" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="N100" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="O100" t="n">
+        <v>6.933999999999999</v>
+      </c>
+      <c r="P100" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="R100" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>98</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Laundry finished around 6 PM in Harrisburg. When should I run the dryer?</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>260</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Dryer</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>9</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Rowhouse</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>4</v>
+      </c>
+      <c r="I101" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>6pm</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="L101" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="M101" t="n">
+        <v>10</v>
+      </c>
+      <c r="N101" t="n">
+        <v>10</v>
+      </c>
+      <c r="O101" t="n">
+        <v>7.0735</v>
+      </c>
+      <c r="P101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="R101" t="n">
+        <v>2.498</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>98</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Laundry finished around 6 PM in Harrisburg. When should I run the dryer?</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>260</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Dryer</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>9</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Rowhouse</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>4</v>
+      </c>
+      <c r="I102" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>10pm</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="L102" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="M102" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="N102" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="O102" t="n">
+        <v>5.562</v>
+      </c>
+      <c r="P102" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="R102" t="n">
+        <v>2.498</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>98</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Laundry finished around 6 PM in Harrisburg. When should I run the dryer?</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>260</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Dryer</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>9</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Rowhouse</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>4</v>
+      </c>
+      <c r="I103" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="L103" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="N103" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O103" t="n">
+        <v>4.353</v>
+      </c>
+      <c r="P103" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="R103" t="n">
+        <v>2.342</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>99</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>It's around 8 in the morning and I need to run the dishwasher in Doylestown. When should I start it?</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Doylestown, PA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>210</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Dishwasher</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>6</v>
+      </c>
+      <c r="G104" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H91" t="n">
-        <v>3</v>
-      </c>
-      <c r="I91" t="n">
+      <c r="H104" t="n">
+        <v>3</v>
+      </c>
+      <c r="I104" t="n">
         <v>1.05</v>
       </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>11:00 PM</t>
-        </is>
-      </c>
-      <c r="K91" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="L91" t="n">
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>8am</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="L104" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M104" t="n">
+        <v>10</v>
+      </c>
+      <c r="N104" t="n">
+        <v>10</v>
+      </c>
+      <c r="O104" t="n">
+        <v>8.954000000000001</v>
+      </c>
+      <c r="P104" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0.0798</v>
+      </c>
+      <c r="R104" t="n">
+        <v>1.093</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>99</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>It's around 8 in the morning and I need to run the dishwasher in Doylestown. When should I start it?</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Doylestown, PA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>210</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Dishwasher</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>6</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>3</v>
+      </c>
+      <c r="I105" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2pm</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="L105" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M105" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="N105" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="O105" t="n">
+        <v>7.0475</v>
+      </c>
+      <c r="P105" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="R105" t="n">
+        <v>1.093</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>99</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>It's around 8 in the morning and I need to run the dishwasher in Doylestown. When should I start it?</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Doylestown, PA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>210</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Dishwasher</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>6</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>3</v>
+      </c>
+      <c r="I106" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>11pm</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="L106" t="n">
         <v>7.7</v>
       </c>
-      <c r="M91" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="N91" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="O91" t="n">
-        <v>7.301</v>
-      </c>
-      <c r="P91" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0.0704</v>
-      </c>
-      <c r="R91" t="n">
+      <c r="M106" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="N106" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O106" t="n">
+        <v>7.103499999999999</v>
+      </c>
+      <c r="P106" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0.0798</v>
+      </c>
+      <c r="R106" t="n">
         <v>1.025</v>
       </c>
     </row>

--- a/workbooks/scenarios/ApplianceRAGScenarios.xlsx
+++ b/workbooks/scenarios/ApplianceRAGScenarios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/workbooks/scenarios/ApplianceRAGScenarios.xlsx
+++ b/workbooks/scenarios/ApplianceRAGScenarios.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>question</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>occupants</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>It's just past 9 AM � when should I run the dryer?</t>
+          <t>It's just past 9 AM — when should I run the dryer?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>It's just past 9 AM � when should I run the dryer?</t>
+          <t>It's just past 9 AM — when should I run the dryer?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>It's just past 9 AM � when should I run the dryer?</t>
+          <t>It's just past 9 AM — when should I run the dryer?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>It's just past 9 AM � when should I run the dryer?</t>
+          <t>It's just past 9 AM — when should I run the dryer?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>It's just past 9 AM � when should I run the dryer?</t>
+          <t>It's just past 9 AM — when should I run the dryer?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>It's just past 9 AM � when should I run the dryer?</t>
+          <t>It's just past 9 AM — when should I run the dryer?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>It's around 5 in the evening � when should I run the washing machine?</t>
+          <t>It's around 5 in the evening — when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>It's around 5 in the evening � when should I run the washing machine?</t>
+          <t>It's around 5 in the evening — when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>It's around 5 in the evening � when should I run the washing machine?</t>
+          <t>It's around 5 in the evening — when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>It's just past 7 PM � when should I run the dryer?</t>
+          <t>It's just past 7 PM — when should I run the dryer?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>It's just past 7 PM � when should I run the dryer?</t>
+          <t>It's just past 7 PM — when should I run the dryer?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>It's just past 7 PM � when should I run the dryer?</t>
+          <t>It's just past 7 PM — when should I run the dryer?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>It's late � just past 10 PM and I need to run the dryer. When should I start it?</t>
+          <t>It's late — just past 10 PM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>It's late � just past 10 PM and I need to run the dryer. When should I start it?</t>
+          <t>It's late — just past 10 PM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>It's late � just past 10 PM and I need to run the dryer. When should I start it?</t>
+          <t>It's late — just past 10 PM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>It's getting close to midnight � when should I run the washing machine?</t>
+          <t>It's getting close to midnight — when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>It's getting close to midnight � when should I run the washing machine?</t>
+          <t>It's getting close to midnight — when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>It's getting close to midnight � when should I run the washing machine?</t>
+          <t>It's getting close to midnight — when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>It's just after 8 AM � when should I run the dishwasher?</t>
+          <t>It's just after 8 AM — when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>It's just after 8 AM � when should I run the dishwasher?</t>
+          <t>It's just after 8 AM — when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>It's just after 8 AM � when should I run the dishwasher?</t>
+          <t>It's just after 8 AM — when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>It's nearly 11 at night � when should I run the washing machine?</t>
+          <t>It's nearly 11 at night — when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>It's nearly 11 at night � when should I run the washing machine?</t>
+          <t>It's nearly 11 at night — when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>It's nearly 11 at night � when should I run the washing machine?</t>
+          <t>It's nearly 11 at night — when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3 � when should I run the dishwasher?</t>
+          <t>It's late afternoon, just past 3 — when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3 � when should I run the dishwasher?</t>
+          <t>It's late afternoon, just past 3 — when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3 � when should I run the dishwasher?</t>
+          <t>It's late afternoon, just past 3 — when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>It's around 2 in the afternoon � when should I run the dryer?</t>
+          <t>It's around 2 in the afternoon — when should I run the dryer?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>It's around 2 in the afternoon � when should I run the dryer?</t>
+          <t>It's around 2 in the afternoon — when should I run the dryer?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>It's around 2 in the afternoon � when should I run the dryer?</t>
+          <t>It's around 2 in the afternoon — when should I run the dryer?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>It's just got home � it's around 6 PM � and I need to run the dishwasher. When should I start it?</t>
+          <t>I've just got home — it's around 6 PM — and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>It's just got home � it's around 6 PM � and I need to run the dishwasher. When should I start it?</t>
+          <t>I've just got home — it's around 6 PM — and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>It's just got home � it's around 6 PM � and I need to run the dishwasher. When should I start it?</t>
+          <t>I've just got home — it's around 6 PM — and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Dryer</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Dryer</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Dryer</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Dishwasher</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Dishwasher</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Dishwasher</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="F106" t="n">

--- a/workbooks/scenarios/ApplianceRAGScenarios.xlsx
+++ b/workbooks/scenarios/ApplianceRAGScenarios.xlsx
@@ -530,8 +530,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>6</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -596,8 +598,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>6</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -662,8 +666,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>6</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -728,8 +734,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>8</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -794,8 +802,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>8</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -860,8 +870,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>8</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -926,8 +938,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>6</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -992,8 +1006,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>6</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1058,8 +1074,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>6</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1124,8 +1142,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>3</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1190,8 +1210,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>3</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1256,8 +1278,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>3</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1322,8 +1346,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>7</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1388,8 +1414,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>7</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1454,8 +1482,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>7</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1520,8 +1550,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>6</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1586,8 +1618,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>6</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1652,8 +1686,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>6</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1718,8 +1754,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>2</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1784,8 +1822,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>2</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1850,8 +1890,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>2</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1916,8 +1958,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>1</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1982,8 +2026,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>1</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2048,8 +2094,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>1</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2114,8 +2162,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>12</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2180,8 +2230,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>12</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2246,8 +2298,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>12</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2312,8 +2366,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>2</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2378,8 +2434,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>2</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2444,8 +2502,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>2</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2510,8 +2570,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>6</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2576,8 +2638,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>6</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2642,8 +2706,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>6</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2708,8 +2774,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>5</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2774,8 +2842,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>5</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2840,8 +2910,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>5</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2906,8 +2978,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>7</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2972,8 +3046,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>7</v>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3038,8 +3114,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>7</v>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3104,8 +3182,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>5</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3170,8 +3250,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>5</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -3236,8 +3318,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>5</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3302,8 +3386,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>6</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3368,8 +3454,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v>6</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3434,8 +3522,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>6</v>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3500,8 +3590,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>6</v>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3566,8 +3658,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v>6</v>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3632,8 +3726,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v>6</v>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -3698,8 +3794,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>4</v>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3764,8 +3862,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>4</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3830,8 +3930,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F52" t="n">
-        <v>4</v>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3896,8 +3998,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v>1</v>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3962,8 +4066,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>1</v>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -4028,8 +4134,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v>1</v>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -4094,8 +4202,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v>5</v>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -4160,8 +4270,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v>5</v>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -4226,8 +4338,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v>5</v>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -4292,8 +4406,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F59" t="n">
-        <v>6</v>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -4358,8 +4474,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v>6</v>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -4424,8 +4542,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v>6</v>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4490,8 +4610,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v>4</v>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -4556,8 +4678,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F63" t="n">
-        <v>4</v>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -4622,8 +4746,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F64" t="n">
-        <v>4</v>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4688,8 +4814,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F65" t="n">
-        <v>6</v>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4754,8 +4882,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F66" t="n">
-        <v>6</v>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4820,8 +4950,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F67" t="n">
-        <v>6</v>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4886,8 +5018,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F68" t="n">
-        <v>35</v>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -4952,8 +5086,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F69" t="n">
-        <v>35</v>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -5018,8 +5154,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F70" t="n">
-        <v>35</v>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -5084,8 +5222,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F71" t="n">
-        <v>38</v>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -5150,8 +5290,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F72" t="n">
-        <v>38</v>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -5216,8 +5358,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F73" t="n">
-        <v>38</v>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -5282,8 +5426,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F74" t="n">
-        <v>40</v>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -5348,8 +5494,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F75" t="n">
-        <v>40</v>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -5414,8 +5562,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F76" t="n">
-        <v>40</v>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -5480,8 +5630,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F77" t="n">
-        <v>7</v>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -5546,8 +5698,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F78" t="n">
-        <v>7</v>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -5612,8 +5766,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F79" t="n">
-        <v>7</v>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -5678,8 +5834,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F80" t="n">
-        <v>5</v>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -5744,8 +5902,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F81" t="n">
-        <v>5</v>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -5810,8 +5970,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F82" t="n">
-        <v>5</v>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -5876,8 +6038,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F83" t="n">
-        <v>9</v>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5942,8 +6106,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F84" t="n">
-        <v>9</v>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -6008,8 +6174,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F85" t="n">
-        <v>9</v>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -6074,8 +6242,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F86" t="n">
-        <v>6</v>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -6140,8 +6310,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F87" t="n">
-        <v>6</v>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -6206,8 +6378,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F88" t="n">
-        <v>6</v>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -6272,8 +6446,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F89" t="n">
-        <v>8</v>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -6338,8 +6514,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F90" t="n">
-        <v>8</v>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -6404,8 +6582,10 @@
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F91" t="n">
-        <v>8</v>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -6470,8 +6650,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F92" t="n">
-        <v>11</v>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -6536,8 +6718,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F93" t="n">
-        <v>11</v>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -6602,8 +6786,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F94" t="n">
-        <v>11</v>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -6668,8 +6854,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F95" t="n">
-        <v>7</v>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -6734,8 +6922,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F96" t="n">
-        <v>7</v>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -6800,8 +6990,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F97" t="n">
-        <v>7</v>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -6866,8 +7058,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F98" t="n">
-        <v>10</v>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -6932,8 +7126,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F99" t="n">
-        <v>10</v>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -6998,8 +7194,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F100" t="n">
-        <v>10</v>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -7064,8 +7262,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F101" t="n">
-        <v>9</v>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -7130,8 +7330,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F102" t="n">
-        <v>9</v>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -7196,8 +7398,10 @@
           <t>dryer</t>
         </is>
       </c>
-      <c r="F103" t="n">
-        <v>9</v>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -7262,8 +7466,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F104" t="n">
-        <v>6</v>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -7328,8 +7534,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F105" t="n">
-        <v>6</v>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -7394,8 +7602,10 @@
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F106" t="n">
-        <v>6</v>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>

--- a/workbooks/scenarios/ApplianceRAGScenarios.xlsx
+++ b/workbooks/scenarios/ApplianceRAGScenarios.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>It's just past 9 AM — when should I run the dryer?</t>
+          <t>It's just past 9 AM, when should I run the dryer?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>It's just past 9 AM — when should I run the dryer?</t>
+          <t>It's just past 9 AM, when should I run the dryer?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>It's just past 9 AM — when should I run the dryer?</t>
+          <t>It's just past 9 AM, when should I run the dryer?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>It's just past 9 AM — when should I run the dryer?</t>
+          <t>It's just past 9 AM, when should I run the dryer?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>It's just past 9 AM — when should I run the dryer?</t>
+          <t>It's just past 9 AM, when should I run the dryer?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>It's just past 9 AM — when should I run the dryer?</t>
+          <t>It's just past 9 AM, when should I run the dryer?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>It's around 5 in the evening — when should I run the washing machine?</t>
+          <t>It's around 5 in the evening, when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>It's around 5 in the evening — when should I run the washing machine?</t>
+          <t>It's around 5 in the evening, when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>It's around 5 in the evening — when should I run the washing machine?</t>
+          <t>It's around 5 in the evening, when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>It's just past 7 PM — when should I run the dryer?</t>
+          <t>It's just past 7 PM, when should I run the dryer?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>It's just past 7 PM — when should I run the dryer?</t>
+          <t>It's just past 7 PM, when should I run the dryer?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>It's just past 7 PM — when should I run the dryer?</t>
+          <t>It's just past 7 PM, when should I run the dryer?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>It's late — just past 10 PM and I need to run the dryer. When should I start it?</t>
+          <t>It's late, just past 10 PM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>It's late — just past 10 PM and I need to run the dryer. When should I start it?</t>
+          <t>It's late, just past 10 PM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>It's late — just past 10 PM and I need to run the dryer. When should I start it?</t>
+          <t>It's late, just past 10 PM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>It's getting close to midnight — when should I run the washing machine?</t>
+          <t>It's getting close to midnight, when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>It's getting close to midnight — when should I run the washing machine?</t>
+          <t>It's getting close to midnight, when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>It's getting close to midnight — when should I run the washing machine?</t>
+          <t>It's getting close to midnight, when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>It's just after 8 AM — when should I run the dishwasher?</t>
+          <t>It's just after 8 AM, when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>It's just after 8 AM — when should I run the dishwasher?</t>
+          <t>It's just after 8 AM, when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>It's just after 8 AM — when should I run the dishwasher?</t>
+          <t>It's just after 8 AM, when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>It's nearly 11 at night — when should I run the washing machine?</t>
+          <t>It's nearly 11 at night, when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>It's nearly 11 at night — when should I run the washing machine?</t>
+          <t>It's nearly 11 at night, when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>It's nearly 11 at night — when should I run the washing machine?</t>
+          <t>It's nearly 11 at night, when should I run the washing machine?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3 — when should I run the dishwasher?</t>
+          <t>It's late afternoon, just past 3, when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3 — when should I run the dishwasher?</t>
+          <t>It's late afternoon, just past 3, when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3 — when should I run the dishwasher?</t>
+          <t>It's late afternoon, just past 3, when should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>It's around 2 in the afternoon — when should I run the dryer?</t>
+          <t>It's around 2 in the afternoon, when should I run the dryer?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>It's around 2 in the afternoon — when should I run the dryer?</t>
+          <t>It's around 2 in the afternoon, when should I run the dryer?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>It's around 2 in the afternoon — when should I run the dryer?</t>
+          <t>It's around 2 in the afternoon, when should I run the dryer?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>I've just got home — it's around 6 PM — and I need to run the dishwasher. When should I start it?</t>
+          <t>I've just got home, it's around 6 PM, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>I've just got home — it's around 6 PM — and I need to run the dishwasher. When should I start it?</t>
+          <t>I've just got home, it's around 6 PM, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>I've just got home — it's around 6 PM — and I need to run the dishwasher. When should I start it?</t>
+          <t>I've just got home, it's around 6 PM, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">

--- a/workbooks/scenarios/ApplianceRAGScenarios.xlsx
+++ b/workbooks/scenarios/ApplianceRAGScenarios.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.######"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +48,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7234 +422,7234 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>scenario_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>question</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>utility_budget</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>appliance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>appliance_age</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>housing_type</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>household_size</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>kwh_per_cycle</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>alternative</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>energy_cost_score</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>environmental_score</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>comfort_score</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>practicality_score</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>mavt_score</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>raw_cost</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>raw_emissions</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>39</v>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>It's mid-morning, about 10 and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Johnstown, PA</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="H2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="3" t="n">
         <v>8.33</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="3" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="3" t="n">
         <v>9.15</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2" s="3" t="n">
         <v>6.512500000000001</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="3" t="n">
         <v>0.2016</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2" s="3" t="n">
         <v>2.915</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>39</v>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>It's mid-morning, about 10 and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>Johnstown, PA</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="H3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="3" t="n">
         <v>8.33</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="3" t="n">
         <v>8.23</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3" s="3" t="n">
         <v>6.2625</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="3" t="n">
         <v>0.2016</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" s="3" t="n">
         <v>2.915</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>39</v>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>It's mid-morning, about 10 and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Johnstown, PA</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="H4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="1" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="3" t="n">
         <v>5.46</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="3" t="n">
         <v>6.74</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" s="3" t="n">
         <v>4.545</v>
       </c>
-      <c r="P4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="P4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="3" t="n">
         <v>0.518</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R4" s="3" t="n">
         <v>2.915</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>40</v>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>It's just past 9 AM, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>Meadville, PA</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="1" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="3" t="n">
         <v>7.87</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" s="3" t="n">
         <v>5.861</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="3" t="n">
         <v>0.252</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R5" s="3" t="n">
         <v>3.643</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>40</v>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>It's just past 9 AM, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>Meadville, PA</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="1" t="inlineStr">
         <is>
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="3" t="n">
         <v>7.87</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="3" t="n">
         <v>7.81</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="3" t="n">
         <v>6.66</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" s="3" t="n">
         <v>4.922</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" s="3" t="n">
         <v>0.252</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R6" s="3" t="n">
         <v>3.643</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>It's just past 9 AM, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>Meadville, PA</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="1" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="3" t="n">
         <v>4.28</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="3" t="n">
         <v>5.92</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="3" t="n">
         <v>4.31</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7" s="3" t="n">
         <v>3.1145</v>
       </c>
-      <c r="P7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="P7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="3" t="n">
         <v>0.6475</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R7" s="3" t="n">
         <v>3.643</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>43</v>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="A8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>It's just past 9 AM and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>Lancaster, PA</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="1" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="3" t="n">
         <v>9.84</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="3" t="n">
         <v>9.65</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8" s="3" t="n">
         <v>9.829499999999999</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8" s="3" t="n">
         <v>0.035</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R8" s="3" t="n">
         <v>0.364</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>43</v>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>It's just past 9 AM and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>Lancaster, PA</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="1" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="3" t="n">
         <v>9.710000000000001</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="3" t="n">
         <v>9.65</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="3" t="n">
         <v>6.92</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="3" t="n">
         <v>5.61</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="3" t="n">
         <v>8.516</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9" s="3" t="n">
         <v>0.049</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R9" s="3" t="n">
         <v>0.364</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>43</v>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>It's just past 9 AM and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>Lancaster, PA</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="1" t="inlineStr">
         <is>
           <t>12:00 AM</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="3" t="n">
         <v>9.84</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="3" t="n">
         <v>9.710000000000001</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="3" t="n">
         <v>3.83</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="3" t="n">
         <v>1.51</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" s="3" t="n">
         <v>7.343</v>
       </c>
-      <c r="P10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="P10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3" t="n">
         <v>0.035</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R10" s="3" t="n">
         <v>0.342</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>45</v>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>It's late morning, around 11 and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>Norristown, PA</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="3" t="n">
         <v>7.35</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11" s="3" t="n">
         <v>8.8925</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11" s="3" t="n">
         <v>0.08359999999999999</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R11" s="3" t="n">
         <v>1.145</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>45</v>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>It's late morning, around 11 and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>Norristown, PA</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="1" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="3" t="n">
         <v>6.96</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="3" t="n">
         <v>7.35</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="3" t="n">
         <v>7.83</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" s="3" t="n">
         <v>6.69</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12" s="3" t="n">
         <v>7.23</v>
       </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="P12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3" t="n">
         <v>0.352</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R12" s="3" t="n">
         <v>1.145</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>45</v>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>It's late morning, around 11 and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>Norristown, PA</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="1" t="inlineStr">
         <is>
           <t>8:00 PM</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="3" t="n">
         <v>7.35</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="3" t="n">
         <v>6.29</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" s="3" t="n">
         <v>4.78</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13" s="3" t="n">
         <v>7.3675</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q13" s="3" t="n">
         <v>0.08359999999999999</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R13" s="3" t="n">
         <v>1.145</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>46</v>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>It's just past 9 AM and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>Reading, PA</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H14" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="H14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="n">
         <v>0.45</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="1" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="3" t="n">
         <v>9.75</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="3" t="n">
         <v>9.34</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O14" s="3" t="n">
         <v>9.693999999999999</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q14" s="3" t="n">
         <v>0.045</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R14" s="3" t="n">
         <v>0.468</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>46</v>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>It's just past 9 AM and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>Reading, PA</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H15" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="H15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="3" t="n">
         <v>0.45</v>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="1" t="inlineStr">
         <is>
           <t>8:00 PM</t>
         </is>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="3" t="n">
         <v>9.75</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="3" t="n">
         <v>9.34</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="3" t="n">
         <v>4.71</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" s="3" t="n">
         <v>2.95</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O15" s="3" t="n">
         <v>7.578499999999999</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15" s="3" t="n">
         <v>0.045</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R15" s="3" t="n">
         <v>0.468</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>46</v>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="A16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>It's just past 9 AM and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>Reading, PA</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H16" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" t="n">
+      <c r="H16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="3" t="n">
         <v>0.45</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="1" t="inlineStr">
         <is>
           <t>12:00 AM</t>
         </is>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="3" t="n">
         <v>9.75</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="3" t="n">
         <v>9.43</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="3" t="n">
         <v>2.86</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" s="3" t="n">
         <v>1.51</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16" s="3" t="n">
         <v>7.023999999999999</v>
       </c>
-      <c r="P16" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="P16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="3" t="n">
         <v>0.045</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R16" s="3" t="n">
         <v>0.439</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>49</v>
-      </c>
-      <c r="B17" t="inlineStr">
+      <c r="A17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>It's just past 9 AM, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H17" t="n">
-        <v>3</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="H17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="1" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="3" t="n">
         <v>6.66</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17" s="3" t="n">
         <v>6.247</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q17" s="3" t="n">
         <v>0.385</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R17" s="3" t="n">
         <v>2.915</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>49</v>
-      </c>
-      <c r="B18" t="inlineStr">
+      <c r="A18" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>It's just past 9 AM, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H18" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="H18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="1" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" s="3" t="n">
         <v>6.66</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" s="3" t="n">
         <v>7.29</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" s="3" t="n">
         <v>6.04</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18" s="3" t="n">
         <v>5.111</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P18" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q18" s="3" t="n">
         <v>0.385</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R18" s="3" t="n">
         <v>2.915</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>49</v>
-      </c>
-      <c r="B19" t="inlineStr">
+      <c r="A19" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>It's just past 9 AM, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="H19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="1" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" s="3" t="n">
         <v>6.66</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="3" t="n">
         <v>2.68</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" s="3" t="n">
         <v>2.13</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O19" s="3" t="n">
         <v>3.7255</v>
       </c>
-      <c r="P19" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="P19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" s="3" t="n">
         <v>0.385</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R19" s="3" t="n">
         <v>2.733</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>52</v>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="A20" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>State College, PA</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="1" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="1" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20" s="3" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q20" s="3" t="n">
         <v>0.028</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R20" s="3" t="n">
         <v>0.208</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>52</v>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="A21" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>State College, PA</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="1" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="3" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" s="3" t="n">
         <v>5.71</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O21" s="3" t="n">
         <v>8.7475</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P21" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q21" s="3" t="n">
         <v>0.02</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R21" s="3" t="n">
         <v>0.208</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>52</v>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="A22" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
         <is>
           <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>State College, PA</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="1" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="1" t="inlineStr">
         <is>
           <t>12:00 AM</t>
         </is>
       </c>
-      <c r="K22" t="n">
+      <c r="K22" s="3" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" s="3" t="n">
         <v>3.59</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" s="3" t="n">
         <v>2.86</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22" s="3" t="n">
         <v>7.638</v>
       </c>
-      <c r="P22" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="P22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3" t="n">
         <v>0.02</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R22" s="3" t="n">
         <v>0.195</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>53</v>
-      </c>
-      <c r="B23" t="inlineStr">
+      <c r="A23" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
         <is>
           <t>It's around 5 in the evening, when should I run the washing machine?</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H23" t="n">
-        <v>3</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="H23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3" t="n">
         <v>0.23</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="1" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="K23" t="n">
+      <c r="K23" s="3" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O23" s="3" t="n">
         <v>9.958</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q23" s="3" t="n">
         <v>0.0322</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R23" s="3" t="n">
         <v>0.239</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>53</v>
-      </c>
-      <c r="B24" t="inlineStr">
+      <c r="A24" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
         <is>
           <t>It's around 5 in the evening, when should I run the washing machine?</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H24" t="n">
-        <v>3</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="H24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="n">
         <v>0.23</v>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="1" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K24" t="n">
+      <c r="K24" s="3" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24" s="3" t="n">
         <v>5.92</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N24" s="3" t="n">
         <v>4.64</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O24" s="3" t="n">
         <v>8.365</v>
       </c>
-      <c r="P24" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="P24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3" t="n">
         <v>0.023</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R24" s="3" t="n">
         <v>0.239</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>53</v>
-      </c>
-      <c r="B25" t="inlineStr">
+      <c r="A25" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>It's around 5 in the evening, when should I run the washing machine?</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="H25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" s="3" t="n">
         <v>0.23</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="1" t="inlineStr">
         <is>
           <t>10:00 PM</t>
         </is>
       </c>
-      <c r="K25" t="n">
+      <c r="K25" s="3" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25" s="3" t="n">
         <v>6.01</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N25" s="3" t="n">
         <v>5.19</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O25" s="3" t="n">
         <v>8.465499999999999</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P25" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q25" s="3" t="n">
         <v>0.023</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R25" s="3" t="n">
         <v>0.239</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>55</v>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="A26" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
         <is>
           <t>It's just past 7 PM, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>Bethlehem, PA</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="1" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H26" t="n">
-        <v>3</v>
-      </c>
-      <c r="I26" t="n">
+      <c r="H26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="1" t="inlineStr">
         <is>
           <t>7:00 PM</t>
         </is>
       </c>
-      <c r="K26" t="n">
+      <c r="K26" s="3" t="n">
         <v>6.98</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N26" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O26" s="3" t="n">
         <v>5.593999999999999</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q26" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R26" s="3" t="n">
         <v>3.643</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>55</v>
-      </c>
-      <c r="B27" t="inlineStr">
+      <c r="A27" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t>It's just past 7 PM, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>Bethlehem, PA</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="1" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H27" t="n">
-        <v>3</v>
-      </c>
-      <c r="I27" t="n">
+      <c r="H27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="1" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K27" t="n">
+      <c r="K27" s="3" t="n">
         <v>6.98</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27" s="3" t="n">
         <v>5.13</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N27" s="3" t="n">
         <v>3.42</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O27" s="3" t="n">
         <v>3.633</v>
       </c>
-      <c r="P27" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="P27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="R27" t="n">
+      <c r="R27" s="3" t="n">
         <v>3.643</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>55</v>
-      </c>
-      <c r="B28" t="inlineStr">
+      <c r="A28" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
         <is>
           <t>It's just past 7 PM, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>Bethlehem, PA</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="1" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v>3</v>
-      </c>
-      <c r="I28" t="n">
+      <c r="H28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="1" t="inlineStr">
         <is>
           <t>12:00 AM</t>
         </is>
       </c>
-      <c r="K28" t="n">
+      <c r="K28" s="3" t="n">
         <v>6.98</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L28" s="3" t="n">
         <v>0.67</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M28" s="3" t="n">
         <v>5.06</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N28" s="3" t="n">
         <v>3.88</v>
       </c>
-      <c r="O28" t="n">
+      <c r="O28" s="3" t="n">
         <v>3.9225</v>
       </c>
-      <c r="P28" t="n">
+      <c r="P28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q28" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R28" s="3" t="n">
         <v>3.416</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>56</v>
-      </c>
-      <c r="B29" t="inlineStr">
+      <c r="A29" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
         <is>
           <t>It's around 3 in the afternoon and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>Exton, PA</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="1" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29" s="3" t="n">
         <v>0.72</v>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="1" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K29" t="n">
+      <c r="K29" s="3" t="n">
         <v>8.07</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29" s="3" t="n">
         <v>8.51</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N29" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O29" s="3" t="n">
         <v>8.8995</v>
       </c>
-      <c r="P29" t="n">
+      <c r="P29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="Q29" s="3" t="n">
         <v>0.2304</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R29" s="3" t="n">
         <v>0.75</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>56</v>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="A30" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
         <is>
           <t>It's around 3 in the afternoon and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>Exton, PA</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="1" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H30" t="n">
+      <c r="H30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30" s="3" t="n">
         <v>0.72</v>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="1" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K30" t="n">
+      <c r="K30" s="3" t="n">
         <v>9.66</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30" s="3" t="n">
         <v>8.51</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30" s="3" t="n">
         <v>7.43</v>
       </c>
-      <c r="N30" t="n">
+      <c r="N30" s="3" t="n">
         <v>6.21</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O30" s="3" t="n">
         <v>8.294</v>
       </c>
-      <c r="P30" t="n">
+      <c r="P30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="Q30" s="3" t="n">
         <v>0.0547</v>
       </c>
-      <c r="R30" t="n">
+      <c r="R30" s="3" t="n">
         <v>0.75</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>56</v>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="A31" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
         <is>
           <t>It's around 3 in the afternoon and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>Exton, PA</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="1" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31" s="3" t="n">
         <v>0.72</v>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="1" t="inlineStr">
         <is>
           <t>10:00 PM</t>
         </is>
       </c>
-      <c r="K31" t="n">
+      <c r="K31" s="3" t="n">
         <v>9.66</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L31" s="3" t="n">
         <v>8.51</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M31" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="N31" t="n">
+      <c r="N31" s="3" t="n">
         <v>4.64</v>
       </c>
-      <c r="O31" t="n">
+      <c r="O31" s="3" t="n">
         <v>7.9725</v>
       </c>
-      <c r="P31" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q31" t="n">
+      <c r="P31" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q31" s="3" t="n">
         <v>0.0547</v>
       </c>
-      <c r="R31" t="n">
+      <c r="R31" s="3" t="n">
         <v>0.75</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>58</v>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="A32" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>It's late, just past 10 PM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="1" t="inlineStr">
         <is>
           <t>10:00 PM</t>
         </is>
       </c>
-      <c r="K32" t="n">
+      <c r="K32" s="3" t="n">
         <v>8.43</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L32" s="3" t="n">
         <v>3.06</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M32" s="3" t="n">
         <v>7.83</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N32" s="3" t="n">
         <v>9.25</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O32" s="3" t="n">
         <v>6.5535</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q32" s="3" t="n">
         <v>0.19</v>
       </c>
-      <c r="R32" t="n">
+      <c r="R32" s="3" t="n">
         <v>2.603</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>58</v>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="A33" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
         <is>
           <t>It's late, just past 10 PM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="1" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K33" t="n">
+      <c r="K33" s="3" t="n">
         <v>8.43</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L33" s="3" t="n">
         <v>3.06</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M33" s="3" t="n">
         <v>4.71</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N33" s="3" t="n">
         <v>2.95</v>
       </c>
-      <c r="O33" t="n">
+      <c r="O33" s="3" t="n">
         <v>4.9845</v>
       </c>
-      <c r="P33" t="n">
+      <c r="P33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q33" s="3" t="n">
         <v>0.19</v>
       </c>
-      <c r="R33" t="n">
+      <c r="R33" s="3" t="n">
         <v>2.603</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>58</v>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="A34" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
         <is>
           <t>It's late, just past 10 PM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="1" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K34" t="n">
+      <c r="K34" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L34" s="3" t="n">
         <v>3.06</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M34" s="3" t="n">
         <v>5.92</v>
       </c>
-      <c r="N34" t="n">
+      <c r="N34" s="3" t="n">
         <v>4.31</v>
       </c>
-      <c r="O34" t="n">
+      <c r="O34" s="3" t="n">
         <v>3.7715</v>
       </c>
-      <c r="P34" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="P34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q34" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="R34" t="n">
+      <c r="R34" s="3" t="n">
         <v>2.603</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>61</v>
-      </c>
-      <c r="B35" t="inlineStr">
+      <c r="A35" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
         <is>
           <t>It's getting close to midnight, when should I run the washing machine?</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>Greensburg, PA</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H35" t="n">
-        <v>3</v>
-      </c>
-      <c r="I35" t="n">
+      <c r="H35" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3" t="n">
         <v>0.45</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="1" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K35" t="n">
+      <c r="K35" s="3" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L35" s="3" t="n">
         <v>9.43</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M35" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="N35" t="n">
+      <c r="N35" s="3" t="n">
         <v>9.25</v>
       </c>
-      <c r="O35" t="n">
+      <c r="O35" s="3" t="n">
         <v>9.311999999999999</v>
       </c>
-      <c r="P35" t="n">
+      <c r="P35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q35" s="3" t="n">
         <v>0.0302</v>
       </c>
-      <c r="R35" t="n">
+      <c r="R35" s="3" t="n">
         <v>0.439</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>61</v>
-      </c>
-      <c r="B36" t="inlineStr">
+      <c r="A36" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
         <is>
           <t>It's getting close to midnight, when should I run the washing machine?</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>Greensburg, PA</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H36" t="n">
-        <v>3</v>
-      </c>
-      <c r="I36" t="n">
+      <c r="H36" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" s="3" t="n">
         <v>0.45</v>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="1" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="K36" t="n">
+      <c r="K36" s="3" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L36" s="3" t="n">
         <v>9.34</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M36" s="3" t="n">
         <v>5.53</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N36" s="3" t="n">
         <v>3.87</v>
       </c>
-      <c r="O36" t="n">
+      <c r="O36" s="3" t="n">
         <v>7.919499999999999</v>
       </c>
-      <c r="P36" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q36" t="n">
+      <c r="P36" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q36" s="3" t="n">
         <v>0.0302</v>
       </c>
-      <c r="R36" t="n">
+      <c r="R36" s="3" t="n">
         <v>0.468</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>61</v>
-      </c>
-      <c r="B37" t="inlineStr">
+      <c r="A37" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
         <is>
           <t>It's getting close to midnight, when should I run the washing machine?</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>Greensburg, PA</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H37" t="n">
-        <v>3</v>
-      </c>
-      <c r="I37" t="n">
+      <c r="H37" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" s="3" t="n">
         <v>0.45</v>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="1" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K37" t="n">
+      <c r="K37" s="3" t="n">
         <v>9.48</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L37" s="3" t="n">
         <v>9.34</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M37" s="3" t="n">
         <v>5.92</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N37" s="3" t="n">
         <v>4.64</v>
       </c>
-      <c r="O37" t="n">
+      <c r="O37" s="3" t="n">
         <v>7.992999999999999</v>
       </c>
-      <c r="P37" t="n">
+      <c r="P37" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="Q37" s="3" t="n">
         <v>0.0743</v>
       </c>
-      <c r="R37" t="n">
+      <c r="R37" s="3" t="n">
         <v>0.468</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>63</v>
-      </c>
-      <c r="B38" t="inlineStr">
+      <c r="A38" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
         <is>
           <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>Wilkes-Barre, PA</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="H38" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="1" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K38" t="n">
+      <c r="K38" s="3" t="n">
         <v>6.98</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L38" s="3" t="n">
         <v>3.06</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M38" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N38" t="n">
+      <c r="N38" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O38" t="n">
+      <c r="O38" s="3" t="n">
         <v>6.665</v>
       </c>
-      <c r="P38" t="n">
+      <c r="P38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="Q38" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="R38" t="n">
+      <c r="R38" s="3" t="n">
         <v>2.603</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>63</v>
-      </c>
-      <c r="B39" t="inlineStr">
+      <c r="A39" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
         <is>
           <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>Wilkes-Barre, PA</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="H39" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" s="1" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="K39" t="n">
+      <c r="K39" s="3" t="n">
         <v>6.98</v>
       </c>
-      <c r="L39" t="n">
+      <c r="L39" s="3" t="n">
         <v>3.06</v>
       </c>
-      <c r="M39" t="n">
+      <c r="M39" s="3" t="n">
         <v>8.73</v>
       </c>
-      <c r="N39" t="n">
+      <c r="N39" s="3" t="n">
         <v>8.029999999999999</v>
       </c>
-      <c r="O39" t="n">
+      <c r="O39" s="3" t="n">
         <v>6.115500000000001</v>
       </c>
-      <c r="P39" t="n">
+      <c r="P39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="Q39" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="R39" t="n">
+      <c r="R39" s="3" t="n">
         <v>2.603</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>63</v>
-      </c>
-      <c r="B40" t="inlineStr">
+      <c r="A40" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
         <is>
           <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>Wilkes-Barre, PA</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H40" t="n">
+      <c r="H40" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" s="1" t="inlineStr">
         <is>
           <t>8:00 PM</t>
         </is>
       </c>
-      <c r="K40" t="n">
+      <c r="K40" s="3" t="n">
         <v>7.89</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L40" s="3" t="n">
         <v>3.06</v>
       </c>
-      <c r="M40" t="n">
+      <c r="M40" s="3" t="n">
         <v>6.11</v>
       </c>
-      <c r="N40" t="n">
+      <c r="N40" s="3" t="n">
         <v>4.64</v>
       </c>
-      <c r="O40" t="n">
+      <c r="O40" s="3" t="n">
         <v>5.356</v>
       </c>
-      <c r="P40" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q40" t="n">
+      <c r="P40" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q40" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="R40" t="n">
+      <c r="R40" s="3" t="n">
         <v>2.603</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>64</v>
-      </c>
-      <c r="B41" t="inlineStr">
+      <c r="A41" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
         <is>
           <t>It's just after 8 AM, when should I run the dishwasher?</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>Lebanon, PA</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H41" t="n">
+      <c r="H41" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="1" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K41" t="n">
+      <c r="K41" s="3" t="n">
         <v>9.16</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L41" s="3" t="n">
         <v>7.35</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M41" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N41" t="n">
+      <c r="N41" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O41" t="n">
+      <c r="O41" s="3" t="n">
         <v>8.820499999999999</v>
       </c>
-      <c r="P41" t="n">
+      <c r="P41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="Q41" s="3" t="n">
         <v>0.11</v>
       </c>
-      <c r="R41" t="n">
+      <c r="R41" s="3" t="n">
         <v>1.145</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>64</v>
-      </c>
-      <c r="B42" t="inlineStr">
+      <c r="A42" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
         <is>
           <t>It's just after 8 AM, when should I run the dishwasher?</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>Lebanon, PA</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H42" t="n">
+      <c r="H42" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I42" t="n">
+      <c r="I42" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" s="1" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K42" t="n">
+      <c r="K42" s="3" t="n">
         <v>8.76</v>
       </c>
-      <c r="L42" t="n">
+      <c r="L42" s="3" t="n">
         <v>7.35</v>
       </c>
-      <c r="M42" t="n">
+      <c r="M42" s="3" t="n">
         <v>7.09</v>
       </c>
-      <c r="N42" t="n">
+      <c r="N42" s="3" t="n">
         <v>5.81</v>
       </c>
-      <c r="O42" t="n">
+      <c r="O42" s="3" t="n">
         <v>7.49</v>
       </c>
-      <c r="P42" t="n">
+      <c r="P42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="Q42" s="3" t="n">
         <v>0.154</v>
       </c>
-      <c r="R42" t="n">
+      <c r="R42" s="3" t="n">
         <v>1.145</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>64</v>
-      </c>
-      <c r="B43" t="inlineStr">
+      <c r="A43" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
         <is>
           <t>It's just after 8 AM, when should I run the dishwasher?</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>Lebanon, PA</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H43" t="n">
+      <c r="H43" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" s="1" t="inlineStr">
         <is>
           <t>8:00 PM</t>
         </is>
       </c>
-      <c r="K43" t="n">
+      <c r="K43" s="3" t="n">
         <v>9.16</v>
       </c>
-      <c r="L43" t="n">
+      <c r="L43" s="3" t="n">
         <v>7.35</v>
       </c>
-      <c r="M43" t="n">
+      <c r="M43" s="3" t="n">
         <v>4.78</v>
       </c>
-      <c r="N43" t="n">
+      <c r="N43" s="3" t="n">
         <v>4.64</v>
       </c>
-      <c r="O43" t="n">
+      <c r="O43" s="3" t="n">
         <v>6.972499999999999</v>
       </c>
-      <c r="P43" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q43" t="n">
+      <c r="P43" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3" t="n">
         <v>0.11</v>
       </c>
-      <c r="R43" t="n">
+      <c r="R43" s="3" t="n">
         <v>1.145</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>65</v>
-      </c>
-      <c r="B44" t="inlineStr">
+      <c r="A44" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
         <is>
           <t>It's around 2 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>Allentown, PA</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H44" t="n">
+      <c r="H44" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I44" s="3" t="n">
         <v>0.38</v>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" s="1" t="inlineStr">
         <is>
           <t>2:00 AM</t>
         </is>
       </c>
-      <c r="K44" t="n">
+      <c r="K44" s="3" t="n">
         <v>9.81</v>
       </c>
-      <c r="L44" t="n">
+      <c r="L44" s="3" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M44" s="3" t="n">
         <v>7.83</v>
       </c>
-      <c r="N44" t="n">
+      <c r="N44" s="3" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="O44" t="n">
+      <c r="O44" s="3" t="n">
         <v>9.147</v>
       </c>
-      <c r="P44" t="n">
+      <c r="P44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="Q44" s="3" t="n">
         <v>0.038</v>
       </c>
-      <c r="R44" t="n">
+      <c r="R44" s="3" t="n">
         <v>0.371</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>65</v>
-      </c>
-      <c r="B45" t="inlineStr">
+      <c r="A45" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
         <is>
           <t>It's around 2 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>Allentown, PA</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H45" t="n">
+      <c r="H45" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I45" s="3" t="n">
         <v>0.38</v>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" s="1" t="inlineStr">
         <is>
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="K45" t="n">
+      <c r="K45" s="3" t="n">
         <v>9.81</v>
       </c>
-      <c r="L45" t="n">
+      <c r="L45" s="3" t="n">
         <v>9.550000000000001</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M45" s="3" t="n">
         <v>5.23</v>
       </c>
-      <c r="N45" t="n">
+      <c r="N45" s="3" t="n">
         <v>4.64</v>
       </c>
-      <c r="O45" t="n">
+      <c r="O45" s="3" t="n">
         <v>8.027500000000002</v>
       </c>
-      <c r="P45" t="n">
+      <c r="P45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="Q45" s="3" t="n">
         <v>0.038</v>
       </c>
-      <c r="R45" t="n">
+      <c r="R45" s="3" t="n">
         <v>0.396</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>65</v>
-      </c>
-      <c r="B46" t="inlineStr">
+      <c r="A46" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
         <is>
           <t>It's around 2 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>Allentown, PA</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H46" t="n">
+      <c r="H46" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I46" s="3" t="n">
         <v>0.38</v>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" s="1" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K46" t="n">
+      <c r="K46" s="3" t="n">
         <v>9.67</v>
       </c>
-      <c r="L46" t="n">
+      <c r="L46" s="3" t="n">
         <v>9.550000000000001</v>
       </c>
-      <c r="M46" t="n">
+      <c r="M46" s="3" t="n">
         <v>3.94</v>
       </c>
-      <c r="N46" t="n">
+      <c r="N46" s="3" t="n">
         <v>2.03</v>
       </c>
-      <c r="O46" t="n">
+      <c r="O46" s="3" t="n">
         <v>7.336</v>
       </c>
-      <c r="P46" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q46" t="n">
+      <c r="P46" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3" t="n">
         <v>0.0532</v>
       </c>
-      <c r="R46" t="n">
+      <c r="R46" s="3" t="n">
         <v>0.396</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>67</v>
-      </c>
-      <c r="B47" t="inlineStr">
+      <c r="A47" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
         <is>
           <t>It's late morning, just before noon and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>Easton, PA</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="3" t="n">
         <v>190</v>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H47" t="n">
-        <v>3</v>
-      </c>
-      <c r="I47" t="n">
+      <c r="H47" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" s="1" t="inlineStr">
         <is>
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="K47" t="n">
+      <c r="K47" s="3" t="n">
         <v>8.34</v>
       </c>
-      <c r="L47" t="n">
+      <c r="L47" s="3" t="n">
         <v>3.06</v>
       </c>
-      <c r="M47" t="n">
+      <c r="M47" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N47" t="n">
+      <c r="N47" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O47" t="n">
+      <c r="O47" s="3" t="n">
         <v>7.073</v>
       </c>
-      <c r="P47" t="n">
+      <c r="P47" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="Q47" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="R47" t="n">
+      <c r="R47" s="3" t="n">
         <v>2.603</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>67</v>
-      </c>
-      <c r="B48" t="inlineStr">
+      <c r="A48" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
         <is>
           <t>It's late morning, just before noon and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>Easton, PA</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="3" t="n">
         <v>190</v>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H48" t="n">
-        <v>3</v>
-      </c>
-      <c r="I48" t="n">
+      <c r="H48" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J48" s="1" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K48" t="n">
+      <c r="K48" s="3" t="n">
         <v>5.17</v>
       </c>
-      <c r="L48" t="n">
+      <c r="L48" s="3" t="n">
         <v>3.06</v>
       </c>
-      <c r="M48" t="n">
+      <c r="M48" s="3" t="n">
         <v>7.81</v>
       </c>
-      <c r="N48" t="n">
+      <c r="N48" s="3" t="n">
         <v>6.66</v>
       </c>
-      <c r="O48" t="n">
+      <c r="O48" s="3" t="n">
         <v>5.183</v>
       </c>
-      <c r="P48" t="n">
+      <c r="P48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="Q48" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="R48" t="n">
+      <c r="R48" s="3" t="n">
         <v>2.603</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>67</v>
-      </c>
-      <c r="B49" t="inlineStr">
+      <c r="A49" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
         <is>
           <t>It's late morning, just before noon and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>Easton, PA</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="3" t="n">
         <v>190</v>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H49" t="n">
-        <v>3</v>
-      </c>
-      <c r="I49" t="n">
+      <c r="H49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" s="1" t="inlineStr">
         <is>
           <t>12:00 AM</t>
         </is>
       </c>
-      <c r="K49" t="n">
+      <c r="K49" s="3" t="n">
         <v>8.34</v>
       </c>
-      <c r="L49" t="n">
+      <c r="L49" s="3" t="n">
         <v>3.54</v>
       </c>
-      <c r="M49" t="n">
+      <c r="M49" s="3" t="n">
         <v>2.86</v>
       </c>
-      <c r="N49" t="n">
+      <c r="N49" s="3" t="n">
         <v>1.51</v>
       </c>
-      <c r="O49" t="n">
+      <c r="O49" s="3" t="n">
         <v>4.539499999999999</v>
       </c>
-      <c r="P49" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q49" t="n">
+      <c r="P49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="R49" t="n">
+      <c r="R49" s="3" t="n">
         <v>2.44</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>68</v>
-      </c>
-      <c r="B50" t="inlineStr">
+      <c r="A50" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
         <is>
           <t>It's around 10 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>Chambersburg, PA</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H50" t="n">
+      <c r="H50" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I50" t="n">
+      <c r="I50" s="3" t="n">
         <v>0.32</v>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J50" s="1" t="inlineStr">
         <is>
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="K50" t="n">
+      <c r="K50" s="3" t="n">
         <v>9.92</v>
       </c>
-      <c r="L50" t="n">
+      <c r="L50" s="3" t="n">
         <v>9.74</v>
       </c>
-      <c r="M50" t="n">
+      <c r="M50" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N50" t="n">
+      <c r="N50" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O50" t="n">
+      <c r="O50" s="3" t="n">
         <v>9.885</v>
       </c>
-      <c r="P50" t="n">
+      <c r="P50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="Q50" s="3" t="n">
         <v>0.0256</v>
       </c>
-      <c r="R50" t="n">
+      <c r="R50" s="3" t="n">
         <v>0.333</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>68</v>
-      </c>
-      <c r="B51" t="inlineStr">
+      <c r="A51" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
         <is>
           <t>It's around 10 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>Chambersburg, PA</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H51" t="n">
+      <c r="H51" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I51" t="n">
+      <c r="I51" s="3" t="n">
         <v>0.32</v>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J51" s="1" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="K51" t="n">
+      <c r="K51" s="3" t="n">
         <v>9.52</v>
       </c>
-      <c r="L51" t="n">
+      <c r="L51" s="3" t="n">
         <v>9.74</v>
       </c>
-      <c r="M51" t="n">
+      <c r="M51" s="3" t="n">
         <v>7.43</v>
       </c>
-      <c r="N51" t="n">
+      <c r="N51" s="3" t="n">
         <v>6.21</v>
       </c>
-      <c r="O51" t="n">
+      <c r="O51" s="3" t="n">
         <v>8.682499999999999</v>
       </c>
-      <c r="P51" t="n">
+      <c r="P51" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="Q51" s="3" t="n">
         <v>0.0704</v>
       </c>
-      <c r="R51" t="n">
+      <c r="R51" s="3" t="n">
         <v>0.333</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v>68</v>
-      </c>
-      <c r="B52" t="inlineStr">
+      <c r="A52" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
         <is>
           <t>It's around 10 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>Chambersburg, PA</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H52" t="n">
+      <c r="H52" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I52" t="n">
+      <c r="I52" s="3" t="n">
         <v>0.32</v>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J52" s="1" t="inlineStr">
         <is>
           <t>10:00 PM</t>
         </is>
       </c>
-      <c r="K52" t="n">
+      <c r="K52" s="3" t="n">
         <v>9.92</v>
       </c>
-      <c r="L52" t="n">
+      <c r="L52" s="3" t="n">
         <v>9.74</v>
       </c>
-      <c r="M52" t="n">
+      <c r="M52" s="3" t="n">
         <v>1.53</v>
       </c>
-      <c r="N52" t="n">
+      <c r="N52" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="O52" t="n">
+      <c r="O52" s="3" t="n">
         <v>7.021</v>
       </c>
-      <c r="P52" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q52" t="n">
+      <c r="P52" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3" t="n">
         <v>0.0256</v>
       </c>
-      <c r="R52" t="n">
+      <c r="R52" s="3" t="n">
         <v>0.333</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>70</v>
-      </c>
-      <c r="B53" t="inlineStr">
+      <c r="A53" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
         <is>
           <t>It's around 3 in the afternoon and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H53" t="n">
+      <c r="H53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I53" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J53" s="1" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K53" t="n">
+      <c r="K53" s="3" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="L53" t="n">
+      <c r="L53" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M53" t="n">
+      <c r="M53" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N53" t="n">
+      <c r="N53" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O53" t="n">
+      <c r="O53" s="3" t="n">
         <v>9.916</v>
       </c>
-      <c r="P53" t="n">
+      <c r="P53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="Q53" s="3" t="n">
         <v>0.048</v>
       </c>
-      <c r="R53" t="n">
+      <c r="R53" s="3" t="n">
         <v>0.156</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>70</v>
-      </c>
-      <c r="B54" t="inlineStr">
+      <c r="A54" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
         <is>
           <t>It's around 3 in the afternoon and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H54" t="n">
+      <c r="H54" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I54" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J54" s="1" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K54" t="n">
+      <c r="K54" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L54" t="n">
+      <c r="L54" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M54" t="n">
+      <c r="M54" s="3" t="n">
         <v>7.43</v>
       </c>
-      <c r="N54" t="n">
+      <c r="N54" s="3" t="n">
         <v>6.21</v>
       </c>
-      <c r="O54" t="n">
+      <c r="O54" s="3" t="n">
         <v>8.9175</v>
       </c>
-      <c r="P54" t="n">
+      <c r="P54" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="Q54" s="3" t="n">
         <v>0.0114</v>
       </c>
-      <c r="R54" t="n">
+      <c r="R54" s="3" t="n">
         <v>0.156</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>70</v>
-      </c>
-      <c r="B55" t="inlineStr">
+      <c r="A55" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
         <is>
           <t>It's around 3 in the afternoon and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H55" t="n">
+      <c r="H55" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I55" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J55" s="1" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K55" t="n">
+      <c r="K55" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L55" t="n">
+      <c r="L55" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M55" t="n">
+      <c r="M55" s="3" t="n">
         <v>3.59</v>
       </c>
-      <c r="N55" t="n">
+      <c r="N55" s="3" t="n">
         <v>4.08</v>
       </c>
-      <c r="O55" t="n">
+      <c r="O55" s="3" t="n">
         <v>7.83</v>
       </c>
-      <c r="P55" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q55" t="n">
+      <c r="P55" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q55" s="3" t="n">
         <v>0.0114</v>
       </c>
-      <c r="R55" t="n">
+      <c r="R55" s="3" t="n">
         <v>0.146</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
-        <v>71</v>
-      </c>
-      <c r="B56" t="inlineStr">
+      <c r="A56" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
         <is>
           <t>It's just past midnight and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H56" t="n">
-        <v>3</v>
-      </c>
-      <c r="I56" t="n">
+      <c r="H56" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I56" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J56" s="1" t="inlineStr">
         <is>
           <t>12:00 AM</t>
         </is>
       </c>
-      <c r="K56" t="n">
+      <c r="K56" s="3" t="n">
         <v>7.04</v>
       </c>
-      <c r="L56" t="n">
+      <c r="L56" s="3" t="n">
         <v>3.54</v>
       </c>
-      <c r="M56" t="n">
+      <c r="M56" s="3" t="n">
         <v>7.83</v>
       </c>
-      <c r="N56" t="n">
+      <c r="N56" s="3" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="O56" t="n">
+      <c r="O56" s="3" t="n">
         <v>6.1845</v>
       </c>
-      <c r="P56" t="n">
+      <c r="P56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="Q56" s="3" t="n">
         <v>0.3438</v>
       </c>
-      <c r="R56" t="n">
+      <c r="R56" s="3" t="n">
         <v>2.44</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
-        <v>71</v>
-      </c>
-      <c r="B57" t="inlineStr">
+      <c r="A57" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
         <is>
           <t>It's just past midnight and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H57" t="n">
-        <v>3</v>
-      </c>
-      <c r="I57" t="n">
+      <c r="H57" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J57" s="1" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K57" t="n">
+      <c r="K57" s="3" t="n">
         <v>7.04</v>
       </c>
-      <c r="L57" t="n">
+      <c r="L57" s="3" t="n">
         <v>3.06</v>
       </c>
-      <c r="M57" t="n">
+      <c r="M57" s="3" t="n">
         <v>5.53</v>
       </c>
-      <c r="N57" t="n">
+      <c r="N57" s="3" t="n">
         <v>3.87</v>
       </c>
-      <c r="O57" t="n">
+      <c r="O57" s="3" t="n">
         <v>4.869499999999999</v>
       </c>
-      <c r="P57" t="n">
+      <c r="P57" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="Q57" s="3" t="n">
         <v>0.3438</v>
       </c>
-      <c r="R57" t="n">
+      <c r="R57" s="3" t="n">
         <v>2.603</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
-        <v>71</v>
-      </c>
-      <c r="B58" t="inlineStr">
+      <c r="A58" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
         <is>
           <t>It's just past midnight and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H58" t="n">
-        <v>3</v>
-      </c>
-      <c r="I58" t="n">
+      <c r="H58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J58" s="1" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K58" t="n">
+      <c r="K58" s="3" t="n">
         <v>7.04</v>
       </c>
-      <c r="L58" t="n">
+      <c r="L58" s="3" t="n">
         <v>3.06</v>
       </c>
-      <c r="M58" t="n">
+      <c r="M58" s="3" t="n">
         <v>5.13</v>
       </c>
-      <c r="N58" t="n">
+      <c r="N58" s="3" t="n">
         <v>3.42</v>
       </c>
-      <c r="O58" t="n">
+      <c r="O58" s="3" t="n">
         <v>4.722</v>
       </c>
-      <c r="P58" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q58" t="n">
+      <c r="P58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3" t="n">
         <v>0.3438</v>
       </c>
-      <c r="R58" t="n">
+      <c r="R58" s="3" t="n">
         <v>2.603</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
-        <v>72</v>
-      </c>
-      <c r="B59" t="inlineStr">
+      <c r="A59" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
         <is>
           <t>It's nearly 11 at night, when should I run the washing machine?</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>Altoona, PA</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H59" t="n">
+      <c r="H59" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I59" t="n">
+      <c r="I59" s="3" t="n">
         <v>0.42</v>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J59" s="1" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K59" t="n">
+      <c r="K59" s="3" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="L59" t="n">
+      <c r="L59" s="3" t="n">
         <v>9.51</v>
       </c>
-      <c r="M59" t="n">
+      <c r="M59" s="3" t="n">
         <v>7.83</v>
       </c>
-      <c r="N59" t="n">
+      <c r="N59" s="3" t="n">
         <v>9.25</v>
       </c>
-      <c r="O59" t="n">
+      <c r="O59" s="3" t="n">
         <v>9.245999999999999</v>
       </c>
-      <c r="P59" t="n">
+      <c r="P59" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="Q59" s="3" t="n">
         <v>0.0302</v>
       </c>
-      <c r="R59" t="n">
+      <c r="R59" s="3" t="n">
         <v>0.41</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
-        <v>72</v>
-      </c>
-      <c r="B60" t="inlineStr">
+      <c r="A60" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
         <is>
           <t>It's nearly 11 at night, when should I run the washing machine?</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>Altoona, PA</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H60" t="n">
+      <c r="H60" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I60" t="n">
+      <c r="I60" s="3" t="n">
         <v>0.42</v>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J60" s="1" t="inlineStr">
         <is>
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="K60" t="n">
+      <c r="K60" s="3" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="L60" t="n">
+      <c r="L60" s="3" t="n">
         <v>9.43</v>
       </c>
-      <c r="M60" t="n">
+      <c r="M60" s="3" t="n">
         <v>4.71</v>
       </c>
-      <c r="N60" t="n">
+      <c r="N60" s="3" t="n">
         <v>2.95</v>
       </c>
-      <c r="O60" t="n">
+      <c r="O60" s="3" t="n">
         <v>7.649</v>
       </c>
-      <c r="P60" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q60" t="n">
+      <c r="P60" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3" t="n">
         <v>0.0302</v>
       </c>
-      <c r="R60" t="n">
+      <c r="R60" s="3" t="n">
         <v>0.437</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
-        <v>72</v>
-      </c>
-      <c r="B61" t="inlineStr">
+      <c r="A61" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
         <is>
           <t>It's nearly 11 at night, when should I run the washing machine?</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>Altoona, PA</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="1" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H61" t="n">
+      <c r="H61" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I61" t="n">
+      <c r="I61" s="3" t="n">
         <v>0.42</v>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J61" s="1" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K61" t="n">
+      <c r="K61" s="3" t="n">
         <v>9.449999999999999</v>
       </c>
-      <c r="L61" t="n">
+      <c r="L61" s="3" t="n">
         <v>9.43</v>
       </c>
-      <c r="M61" t="n">
+      <c r="M61" s="3" t="n">
         <v>5.92</v>
       </c>
-      <c r="N61" t="n">
+      <c r="N61" s="3" t="n">
         <v>4.64</v>
       </c>
-      <c r="O61" t="n">
+      <c r="O61" s="3" t="n">
         <v>8.015499999999999</v>
       </c>
-      <c r="P61" t="n">
+      <c r="P61" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q61" t="n">
+      <c r="Q61" s="3" t="n">
         <v>0.07770000000000001</v>
       </c>
-      <c r="R61" t="n">
+      <c r="R61" s="3" t="n">
         <v>0.437</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
-        <v>73</v>
-      </c>
-      <c r="B62" t="inlineStr">
+      <c r="A62" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B62" s="1" t="inlineStr">
         <is>
           <t>It's barely 5 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>King of Prussia, PA</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H62" t="n">
-        <v>3</v>
-      </c>
-      <c r="I62" t="n">
+      <c r="H62" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J62" s="1" t="inlineStr">
         <is>
           <t>5:00 AM</t>
         </is>
       </c>
-      <c r="K62" t="n">
+      <c r="K62" s="3" t="n">
         <v>9.33</v>
       </c>
-      <c r="L62" t="n">
+      <c r="L62" s="3" t="n">
         <v>7.27</v>
       </c>
-      <c r="M62" t="n">
+      <c r="M62" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N62" t="n">
+      <c r="N62" s="3" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="O62" t="n">
+      <c r="O62" s="3" t="n">
         <v>8.610999999999999</v>
       </c>
-      <c r="P62" t="n">
+      <c r="P62" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q62" t="n">
+      <c r="Q62" s="3" t="n">
         <v>0.0912</v>
       </c>
-      <c r="R62" t="n">
+      <c r="R62" s="3" t="n">
         <v>1.171</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
-        <v>73</v>
-      </c>
-      <c r="B63" t="inlineStr">
+      <c r="A63" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
         <is>
           <t>It's barely 5 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>King of Prussia, PA</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H63" t="n">
-        <v>3</v>
-      </c>
-      <c r="I63" t="n">
+      <c r="H63" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I63" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J63" s="1" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K63" t="n">
+      <c r="K63" s="3" t="n">
         <v>9.33</v>
       </c>
-      <c r="L63" t="n">
+      <c r="L63" s="3" t="n">
         <v>7.04</v>
       </c>
-      <c r="M63" t="n">
+      <c r="M63" s="3" t="n">
         <v>8.02</v>
       </c>
-      <c r="N63" t="n">
+      <c r="N63" s="3" t="n">
         <v>6.91</v>
       </c>
-      <c r="O63" t="n">
+      <c r="O63" s="3" t="n">
         <v>7.9035</v>
       </c>
-      <c r="P63" t="n">
+      <c r="P63" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q63" t="n">
+      <c r="Q63" s="3" t="n">
         <v>0.0912</v>
       </c>
-      <c r="R63" t="n">
+      <c r="R63" s="3" t="n">
         <v>1.249</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
-        <v>73</v>
-      </c>
-      <c r="B64" t="inlineStr">
+      <c r="A64" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
         <is>
           <t>It's barely 5 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>King of Prussia, PA</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H64" t="n">
-        <v>3</v>
-      </c>
-      <c r="I64" t="n">
+      <c r="H64" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I64" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J64" s="1" t="inlineStr">
         <is>
           <t>7:00 PM</t>
         </is>
       </c>
-      <c r="K64" t="n">
+      <c r="K64" s="3" t="n">
         <v>9.33</v>
       </c>
-      <c r="L64" t="n">
+      <c r="L64" s="3" t="n">
         <v>7.04</v>
       </c>
-      <c r="M64" t="n">
+      <c r="M64" s="3" t="n">
         <v>5.26</v>
       </c>
-      <c r="N64" t="n">
+      <c r="N64" s="3" t="n">
         <v>4.64</v>
       </c>
-      <c r="O64" t="n">
+      <c r="O64" s="3" t="n">
         <v>7.010999999999999</v>
       </c>
-      <c r="P64" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q64" t="n">
+      <c r="P64" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q64" s="3" t="n">
         <v>0.0912</v>
       </c>
-      <c r="R64" t="n">
+      <c r="R64" s="3" t="n">
         <v>1.249</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
-        <v>75</v>
-      </c>
-      <c r="B65" t="inlineStr">
+      <c r="A65" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
         <is>
           <t>It's late afternoon, just past 3, when should I run the dishwasher?</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>Greensburg, PA</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H65" t="n">
-        <v>3</v>
-      </c>
-      <c r="I65" t="n">
+      <c r="H65" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I65" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J65" s="1" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K65" t="n">
+      <c r="K65" s="3" t="n">
         <v>8.58</v>
       </c>
-      <c r="L65" t="n">
+      <c r="L65" s="3" t="n">
         <v>7.5</v>
       </c>
-      <c r="M65" t="n">
+      <c r="M65" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N65" t="n">
+      <c r="N65" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O65" t="n">
+      <c r="O65" s="3" t="n">
         <v>8.699</v>
       </c>
-      <c r="P65" t="n">
+      <c r="P65" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q65" t="n">
+      <c r="Q65" s="3" t="n">
         <v>0.1733</v>
       </c>
-      <c r="R65" t="n">
+      <c r="R65" s="3" t="n">
         <v>1.093</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v>75</v>
-      </c>
-      <c r="B66" t="inlineStr">
+      <c r="A66" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
         <is>
           <t>It's late afternoon, just past 3, when should I run the dishwasher?</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>Greensburg, PA</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H66" t="n">
-        <v>3</v>
-      </c>
-      <c r="I66" t="n">
+      <c r="H66" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I66" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J66" s="1" t="inlineStr">
         <is>
           <t>9:00 PM</t>
         </is>
       </c>
-      <c r="K66" t="n">
+      <c r="K66" s="3" t="n">
         <v>9.52</v>
       </c>
-      <c r="L66" t="n">
+      <c r="L66" s="3" t="n">
         <v>7.5</v>
       </c>
-      <c r="M66" t="n">
+      <c r="M66" s="3" t="n">
         <v>7.09</v>
       </c>
-      <c r="N66" t="n">
+      <c r="N66" s="3" t="n">
         <v>5.81</v>
       </c>
-      <c r="O66" t="n">
+      <c r="O66" s="3" t="n">
         <v>7.7705</v>
       </c>
-      <c r="P66" t="n">
+      <c r="P66" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q66" t="n">
+      <c r="Q66" s="3" t="n">
         <v>0.0704</v>
       </c>
-      <c r="R66" t="n">
+      <c r="R66" s="3" t="n">
         <v>1.093</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
-        <v>75</v>
-      </c>
-      <c r="B67" t="inlineStr">
+      <c r="A67" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
         <is>
           <t>It's late afternoon, just past 3, when should I run the dishwasher?</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>Greensburg, PA</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H67" t="n">
-        <v>3</v>
-      </c>
-      <c r="I67" t="n">
+      <c r="H67" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I67" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J67" s="1" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K67" t="n">
+      <c r="K67" s="3" t="n">
         <v>9.52</v>
       </c>
-      <c r="L67" t="n">
+      <c r="L67" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="M67" t="n">
+      <c r="M67" s="3" t="n">
         <v>6.17</v>
       </c>
-      <c r="N67" t="n">
+      <c r="N67" s="3" t="n">
         <v>3.44</v>
       </c>
-      <c r="O67" t="n">
+      <c r="O67" s="3" t="n">
         <v>7.301</v>
       </c>
-      <c r="P67" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q67" t="n">
+      <c r="P67" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q67" s="3" t="n">
         <v>0.0704</v>
       </c>
-      <c r="R67" t="n">
+      <c r="R67" s="3" t="n">
         <v>1.025</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
-        <v>76</v>
-      </c>
-      <c r="B68" t="inlineStr">
+      <c r="A68" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
         <is>
           <t>It's around 8 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="3" t="n">
         <v>185</v>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="1" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H68" t="n">
-        <v>3</v>
-      </c>
-      <c r="I68" t="n">
+      <c r="H68" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I68" s="3" t="n">
         <v>1.85</v>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J68" s="1" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="K68" t="n">
+      <c r="K68" s="3" t="n">
         <v>7.85</v>
       </c>
-      <c r="L68" t="n">
+      <c r="L68" s="3" t="n">
         <v>5.05</v>
       </c>
-      <c r="M68" t="n">
+      <c r="M68" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N68" t="n">
+      <c r="N68" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O68" t="n">
+      <c r="O68" s="3" t="n">
         <v>7.6225</v>
       </c>
-      <c r="P68" t="n">
+      <c r="P68" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q68" t="n">
+      <c r="Q68" s="3" t="n">
         <v>0.2544</v>
       </c>
-      <c r="R68" t="n">
+      <c r="R68" s="3" t="n">
         <v>1.926</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>76</v>
-      </c>
-      <c r="B69" t="inlineStr">
+      <c r="A69" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
         <is>
           <t>It's around 8 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="3" t="n">
         <v>185</v>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" s="1" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H69" t="n">
-        <v>3</v>
-      </c>
-      <c r="I69" t="n">
+      <c r="H69" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I69" s="3" t="n">
         <v>1.85</v>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J69" s="1" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K69" t="n">
+      <c r="K69" s="3" t="n">
         <v>7.85</v>
       </c>
-      <c r="L69" t="n">
+      <c r="L69" s="3" t="n">
         <v>5.05</v>
       </c>
-      <c r="M69" t="n">
+      <c r="M69" s="3" t="n">
         <v>7.09</v>
       </c>
-      <c r="N69" t="n">
+      <c r="N69" s="3" t="n">
         <v>5.81</v>
       </c>
-      <c r="O69" t="n">
+      <c r="O69" s="3" t="n">
         <v>6.412</v>
       </c>
-      <c r="P69" t="n">
+      <c r="P69" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q69" t="n">
+      <c r="Q69" s="3" t="n">
         <v>0.2544</v>
       </c>
-      <c r="R69" t="n">
+      <c r="R69" s="3" t="n">
         <v>1.926</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
-        <v>76</v>
-      </c>
-      <c r="B70" t="inlineStr">
+      <c r="A70" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
         <is>
           <t>It's around 8 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="3" t="n">
         <v>185</v>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" s="1" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H70" t="n">
-        <v>3</v>
-      </c>
-      <c r="I70" t="n">
+      <c r="H70" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I70" s="3" t="n">
         <v>1.85</v>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="J70" s="1" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K70" t="n">
+      <c r="K70" s="3" t="n">
         <v>7.85</v>
       </c>
-      <c r="L70" t="n">
+      <c r="L70" s="3" t="n">
         <v>5.41</v>
       </c>
-      <c r="M70" t="n">
+      <c r="M70" s="3" t="n">
         <v>5.73</v>
       </c>
-      <c r="N70" t="n">
+      <c r="N70" s="3" t="n">
         <v>2.89</v>
       </c>
-      <c r="O70" t="n">
+      <c r="O70" s="3" t="n">
         <v>5.827999999999999</v>
       </c>
-      <c r="P70" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q70" t="n">
+      <c r="P70" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q70" s="3" t="n">
         <v>0.2544</v>
       </c>
-      <c r="R70" t="n">
+      <c r="R70" s="3" t="n">
         <v>1.806</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
-        <v>77</v>
-      </c>
-      <c r="B71" t="inlineStr">
+      <c r="A71" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
         <is>
           <t>It's around 2 in the afternoon and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>Erie, PA</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="3" t="n">
         <v>215</v>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E71" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" s="1" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G71" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H71" t="n">
+      <c r="H71" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I71" t="n">
+      <c r="I71" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J71" s="1" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K71" t="n">
+      <c r="K71" s="3" t="n">
         <v>3.28</v>
       </c>
-      <c r="L71" t="n">
+      <c r="L71" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M71" t="n">
+      <c r="M71" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N71" t="n">
+      <c r="N71" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O71" t="n">
+      <c r="O71" s="3" t="n">
         <v>4.484</v>
       </c>
-      <c r="P71" t="n">
+      <c r="P71" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q71" t="n">
+      <c r="Q71" s="3" t="n">
         <v>0.7585</v>
       </c>
-      <c r="R71" t="n">
+      <c r="R71" s="3" t="n">
         <v>4.268</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
-        <v>77</v>
-      </c>
-      <c r="B72" t="inlineStr">
+      <c r="A72" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B72" s="1" t="inlineStr">
         <is>
           <t>It's around 2 in the afternoon and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>Erie, PA</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="3" t="n">
         <v>215</v>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E72" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F72" s="1" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G72" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H72" t="n">
+      <c r="H72" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I72" t="n">
+      <c r="I72" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J72" s="1" t="inlineStr">
         <is>
           <t>9:00 PM</t>
         </is>
       </c>
-      <c r="K72" t="n">
+      <c r="K72" s="3" t="n">
         <v>7.48</v>
       </c>
-      <c r="L72" t="n">
+      <c r="L72" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M72" t="n">
+      <c r="M72" s="3" t="n">
         <v>6.29</v>
       </c>
-      <c r="N72" t="n">
+      <c r="N72" s="3" t="n">
         <v>4.86</v>
       </c>
-      <c r="O72" t="n">
+      <c r="O72" s="3" t="n">
         <v>4.231</v>
       </c>
-      <c r="P72" t="n">
+      <c r="P72" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q72" t="n">
+      <c r="Q72" s="3" t="n">
         <v>0.2952</v>
       </c>
-      <c r="R72" t="n">
+      <c r="R72" s="3" t="n">
         <v>4.268</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
-        <v>77</v>
-      </c>
-      <c r="B73" t="inlineStr">
+      <c r="A73" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B73" s="1" t="inlineStr">
         <is>
           <t>It's around 2 in the afternoon and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>Erie, PA</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="3" t="n">
         <v>215</v>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E73" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F73" s="1" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G73" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H73" t="n">
+      <c r="H73" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I73" t="n">
+      <c r="I73" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="J73" s="1" t="inlineStr">
         <is>
           <t>2:00 AM</t>
         </is>
       </c>
-      <c r="K73" t="n">
+      <c r="K73" s="3" t="n">
         <v>7.48</v>
       </c>
-      <c r="L73" t="n">
+      <c r="L73" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M73" t="n">
+      <c r="M73" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="N73" t="n">
+      <c r="N73" s="3" t="n">
         <v>1.51</v>
       </c>
-      <c r="O73" t="n">
+      <c r="O73" s="3" t="n">
         <v>2.7185</v>
       </c>
-      <c r="P73" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q73" t="n">
+      <c r="P73" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q73" s="3" t="n">
         <v>0.2952</v>
       </c>
-      <c r="R73" t="n">
+      <c r="R73" s="3" t="n">
         <v>4.002</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
-        <v>79</v>
-      </c>
-      <c r="B74" t="inlineStr">
+      <c r="A74" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
         <is>
           <t>It's about 10 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>Allentown, PA</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E74" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F74" s="1" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G74" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H74" t="n">
+      <c r="H74" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I74" t="n">
+      <c r="I74" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="J74" s="1" t="inlineStr">
         <is>
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="K74" t="n">
+      <c r="K74" s="3" t="n">
         <v>8.25</v>
       </c>
-      <c r="L74" t="n">
+      <c r="L74" s="3" t="n">
         <v>4.29</v>
       </c>
-      <c r="M74" t="n">
+      <c r="M74" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N74" t="n">
+      <c r="N74" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O74" t="n">
+      <c r="O74" s="3" t="n">
         <v>7.4765</v>
       </c>
-      <c r="P74" t="n">
+      <c r="P74" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q74" t="n">
+      <c r="Q74" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="R74" t="n">
+      <c r="R74" s="3" t="n">
         <v>2.186</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
-        <v>79</v>
-      </c>
-      <c r="B75" t="inlineStr">
+      <c r="A75" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B75" s="1" t="inlineStr">
         <is>
           <t>It's about 10 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>Allentown, PA</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" s="1" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H75" t="n">
+      <c r="H75" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I75" t="n">
+      <c r="I75" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="J75" s="1" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K75" t="n">
+      <c r="K75" s="3" t="n">
         <v>7.49</v>
       </c>
-      <c r="L75" t="n">
+      <c r="L75" s="3" t="n">
         <v>4.29</v>
       </c>
-      <c r="M75" t="n">
+      <c r="M75" s="3" t="n">
         <v>8.02</v>
       </c>
-      <c r="N75" t="n">
+      <c r="N75" s="3" t="n">
         <v>6.91</v>
       </c>
-      <c r="O75" t="n">
+      <c r="O75" s="3" t="n">
         <v>6.389</v>
       </c>
-      <c r="P75" t="n">
+      <c r="P75" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q75" t="n">
+      <c r="Q75" s="3" t="n">
         <v>0.294</v>
       </c>
-      <c r="R75" t="n">
+      <c r="R75" s="3" t="n">
         <v>2.186</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
-        <v>79</v>
-      </c>
-      <c r="B76" t="inlineStr">
+      <c r="A76" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B76" s="1" t="inlineStr">
         <is>
           <t>It's about 10 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>Allentown, PA</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E76" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" s="1" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G76" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H76" t="n">
+      <c r="H76" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I76" t="n">
+      <c r="I76" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="J76" s="1" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K76" t="n">
+      <c r="K76" s="3" t="n">
         <v>8.25</v>
       </c>
-      <c r="L76" t="n">
+      <c r="L76" s="3" t="n">
         <v>4.69</v>
       </c>
-      <c r="M76" t="n">
+      <c r="M76" s="3" t="n">
         <v>4.78</v>
       </c>
-      <c r="N76" t="n">
+      <c r="N76" s="3" t="n">
         <v>1.71</v>
       </c>
-      <c r="O76" t="n">
+      <c r="O76" s="3" t="n">
         <v>5.329000000000001</v>
       </c>
-      <c r="P76" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q76" t="n">
+      <c r="P76" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="R76" t="n">
+      <c r="R76" s="3" t="n">
         <v>2.05</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
-        <v>80</v>
-      </c>
-      <c r="B77" t="inlineStr">
+      <c r="A77" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
         <is>
           <t>It's just past 5 PM and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>King of Prussia, PA</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E77" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F77" s="1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G77" s="1" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H77" t="n">
+      <c r="H77" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I77" t="n">
+      <c r="I77" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="J77" s="1" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="K77" t="n">
+      <c r="K77" s="3" t="n">
         <v>6.82</v>
       </c>
-      <c r="L77" t="n">
+      <c r="L77" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="M77" t="n">
+      <c r="M77" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N77" t="n">
+      <c r="N77" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O77" t="n">
+      <c r="O77" s="3" t="n">
         <v>8.065999999999999</v>
       </c>
-      <c r="P77" t="n">
+      <c r="P77" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q77" t="n">
+      <c r="Q77" s="3" t="n">
         <v>0.368</v>
       </c>
-      <c r="R77" t="n">
+      <c r="R77" s="3" t="n">
         <v>1.197</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
-        <v>80</v>
-      </c>
-      <c r="B78" t="inlineStr">
+      <c r="A78" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
         <is>
           <t>It's just past 5 PM and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>King of Prussia, PA</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E78" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F78" s="1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G78" s="1" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H78" t="n">
+      <c r="H78" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I78" t="n">
+      <c r="I78" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="J78" s="1" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K78" t="n">
+      <c r="K78" s="3" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="L78" t="n">
+      <c r="L78" s="3" t="n">
         <v>7.42</v>
       </c>
-      <c r="M78" t="n">
+      <c r="M78" s="3" t="n">
         <v>7.43</v>
       </c>
-      <c r="N78" t="n">
+      <c r="N78" s="3" t="n">
         <v>5.19</v>
       </c>
-      <c r="O78" t="n">
+      <c r="O78" s="3" t="n">
         <v>7.669499999999999</v>
       </c>
-      <c r="P78" t="n">
+      <c r="P78" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q78" t="n">
+      <c r="Q78" s="3" t="n">
         <v>0.08740000000000001</v>
       </c>
-      <c r="R78" t="n">
+      <c r="R78" s="3" t="n">
         <v>1.122</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
-        <v>80</v>
-      </c>
-      <c r="B79" t="inlineStr">
+      <c r="A79" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B79" s="1" t="inlineStr">
         <is>
           <t>It's just past 5 PM and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>King of Prussia, PA</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E79" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" s="1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G79" s="1" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H79" t="n">
+      <c r="H79" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I79" t="n">
+      <c r="I79" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="J79" s="1" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="K79" t="n">
+      <c r="K79" s="3" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="L79" t="n">
+      <c r="L79" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="M79" t="n">
+      <c r="M79" s="3" t="n">
         <v>6.29</v>
       </c>
-      <c r="N79" t="n">
+      <c r="N79" s="3" t="n">
         <v>4.78</v>
       </c>
-      <c r="O79" t="n">
+      <c r="O79" s="3" t="n">
         <v>7.302999999999999</v>
       </c>
-      <c r="P79" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q79" t="n">
+      <c r="P79" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q79" s="3" t="n">
         <v>0.08740000000000001</v>
       </c>
-      <c r="R79" t="n">
+      <c r="R79" s="3" t="n">
         <v>1.197</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
-        <v>81</v>
-      </c>
-      <c r="B80" t="inlineStr">
+      <c r="A80" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
         <is>
           <t>It's around 10 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>Blue Bell, PA</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E80" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F80" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G80" s="1" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H80" t="n">
+      <c r="H80" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I80" t="n">
+      <c r="I80" s="3" t="n">
         <v>0.32</v>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="J80" s="1" t="inlineStr">
         <is>
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="K80" t="n">
+      <c r="K80" s="3" t="n">
         <v>9.93</v>
       </c>
-      <c r="L80" t="n">
+      <c r="L80" s="3" t="n">
         <v>9.74</v>
       </c>
-      <c r="M80" t="n">
+      <c r="M80" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N80" t="n">
+      <c r="N80" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O80" t="n">
+      <c r="O80" s="3" t="n">
         <v>9.888</v>
       </c>
-      <c r="P80" t="n">
+      <c r="P80" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" t="n">
+      <c r="Q80" s="3" t="n">
         <v>0.0243</v>
       </c>
-      <c r="R80" t="n">
+      <c r="R80" s="3" t="n">
         <v>0.333</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
-        <v>81</v>
-      </c>
-      <c r="B81" t="inlineStr">
+      <c r="A81" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B81" s="1" t="inlineStr">
         <is>
           <t>It's around 10 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>Blue Bell, PA</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E81" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F81" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G81" s="1" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H81" t="n">
+      <c r="H81" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I81" t="n">
+      <c r="I81" s="3" t="n">
         <v>0.32</v>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="J81" s="1" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K81" t="n">
+      <c r="K81" s="3" t="n">
         <v>9.23</v>
       </c>
-      <c r="L81" t="n">
+      <c r="L81" s="3" t="n">
         <v>9.74</v>
       </c>
-      <c r="M81" t="n">
+      <c r="M81" s="3" t="n">
         <v>7.83</v>
       </c>
-      <c r="N81" t="n">
+      <c r="N81" s="3" t="n">
         <v>6.69</v>
       </c>
-      <c r="O81" t="n">
+      <c r="O81" s="3" t="n">
         <v>8.7475</v>
       </c>
-      <c r="P81" t="n">
+      <c r="P81" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q81" t="n">
+      <c r="Q81" s="3" t="n">
         <v>0.1024</v>
       </c>
-      <c r="R81" t="n">
+      <c r="R81" s="3" t="n">
         <v>0.333</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" t="inlineStr">
+      <c r="A82" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B82" s="1" t="inlineStr">
         <is>
           <t>It's around 10 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>Blue Bell, PA</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E82" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F82" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G82" s="1" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H82" t="n">
+      <c r="H82" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I82" t="n">
+      <c r="I82" s="3" t="n">
         <v>0.32</v>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="J82" s="1" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K82" t="n">
+      <c r="K82" s="3" t="n">
         <v>9.93</v>
       </c>
-      <c r="L82" t="n">
+      <c r="L82" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="M82" t="n">
+      <c r="M82" s="3" t="n">
         <v>2.08</v>
       </c>
-      <c r="N82" t="n">
+      <c r="N82" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="O82" t="n">
+      <c r="O82" s="3" t="n">
         <v>7.23</v>
       </c>
-      <c r="P82" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q82" t="n">
+      <c r="P82" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q82" s="3" t="n">
         <v>0.0243</v>
       </c>
-      <c r="R82" t="n">
+      <c r="R82" s="3" t="n">
         <v>0.312</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" t="inlineStr">
+      <c r="A83" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
         <is>
           <t>It's just past 9 AM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>Doylestown, PA</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E83" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F83" s="1" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G83" s="1" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H83" t="n">
-        <v>3</v>
-      </c>
-      <c r="I83" t="n">
+      <c r="H83" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="J83" s="1" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K83" t="n">
+      <c r="K83" s="3" t="n">
         <v>8.16</v>
       </c>
-      <c r="L83" t="n">
+      <c r="L83" s="3" t="n">
         <v>1.84</v>
       </c>
-      <c r="M83" t="n">
+      <c r="M83" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N83" t="n">
+      <c r="N83" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O83" t="n">
+      <c r="O83" s="3" t="n">
         <v>6.592000000000001</v>
       </c>
-      <c r="P83" t="n">
+      <c r="P83" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q83" t="n">
+      <c r="Q83" s="3" t="n">
         <v>0.2204</v>
       </c>
-      <c r="R83" t="n">
+      <c r="R83" s="3" t="n">
         <v>3.019</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
-        <v>82</v>
-      </c>
-      <c r="B84" t="inlineStr">
+      <c r="A84" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B84" s="1" t="inlineStr">
         <is>
           <t>It's just past 9 AM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>Doylestown, PA</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E84" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F84" s="1" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G84" s="1" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H84" t="n">
-        <v>3</v>
-      </c>
-      <c r="I84" t="n">
+      <c r="H84" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I84" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="J84" s="1" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K84" t="n">
+      <c r="K84" s="3" t="n">
         <v>1.74</v>
       </c>
-      <c r="L84" t="n">
+      <c r="L84" s="3" t="n">
         <v>1.84</v>
       </c>
-      <c r="M84" t="n">
+      <c r="M84" s="3" t="n">
         <v>7.29</v>
       </c>
-      <c r="N84" t="n">
+      <c r="N84" s="3" t="n">
         <v>6.04</v>
       </c>
-      <c r="O84" t="n">
+      <c r="O84" s="3" t="n">
         <v>3.53</v>
       </c>
-      <c r="P84" t="n">
+      <c r="P84" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q84" t="n">
+      <c r="Q84" s="3" t="n">
         <v>0.928</v>
       </c>
-      <c r="R84" t="n">
+      <c r="R84" s="3" t="n">
         <v>3.019</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
-        <v>82</v>
-      </c>
-      <c r="B85" t="inlineStr">
+      <c r="A85" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B85" s="1" t="inlineStr">
         <is>
           <t>It's just past 9 AM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>Doylestown, PA</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E85" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F85" s="1" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G85" s="1" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H85" t="n">
-        <v>3</v>
-      </c>
-      <c r="I85" t="n">
+      <c r="H85" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I85" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="J85" s="1" t="inlineStr">
         <is>
           <t>10:00 PM</t>
         </is>
       </c>
-      <c r="K85" t="n">
+      <c r="K85" s="3" t="n">
         <v>8.16</v>
       </c>
-      <c r="L85" t="n">
+      <c r="L85" s="3" t="n">
         <v>1.84</v>
       </c>
-      <c r="M85" t="n">
+      <c r="M85" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="N85" t="n">
+      <c r="N85" s="3" t="n">
         <v>1.61</v>
       </c>
-      <c r="O85" t="n">
+      <c r="O85" s="3" t="n">
         <v>3.5215</v>
       </c>
-      <c r="P85" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q85" t="n">
+      <c r="P85" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q85" s="3" t="n">
         <v>0.2204</v>
       </c>
-      <c r="R85" t="n">
+      <c r="R85" s="3" t="n">
         <v>3.019</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
-        <v>83</v>
-      </c>
-      <c r="B86" t="inlineStr">
+      <c r="A86" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B86" s="1" t="inlineStr">
         <is>
           <t>It's around 2 in the afternoon and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E86" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F86" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G86" s="1" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H86" t="n">
-        <v>3</v>
-      </c>
-      <c r="I86" t="n">
+      <c r="H86" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I86" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="J86" s="1" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K86" t="n">
+      <c r="K86" s="3" t="n">
         <v>6.67</v>
       </c>
-      <c r="L86" t="n">
+      <c r="L86" s="3" t="n">
         <v>7.04</v>
       </c>
-      <c r="M86" t="n">
+      <c r="M86" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N86" t="n">
+      <c r="N86" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O86" t="n">
+      <c r="O86" s="3" t="n">
         <v>7.965</v>
       </c>
-      <c r="P86" t="n">
+      <c r="P86" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q86" t="n">
+      <c r="Q86" s="3" t="n">
         <v>0.384</v>
       </c>
-      <c r="R86" t="n">
+      <c r="R86" s="3" t="n">
         <v>1.249</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
-        <v>83</v>
-      </c>
-      <c r="B87" t="inlineStr">
+      <c r="A87" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B87" s="1" t="inlineStr">
         <is>
           <t>It's around 2 in the afternoon and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E87" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G87" s="1" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H87" t="n">
-        <v>3</v>
-      </c>
-      <c r="I87" t="n">
+      <c r="H87" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I87" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="J87" s="1" t="inlineStr">
         <is>
           <t>8:00 PM</t>
         </is>
       </c>
-      <c r="K87" t="n">
+      <c r="K87" s="3" t="n">
         <v>9.33</v>
       </c>
-      <c r="L87" t="n">
+      <c r="L87" s="3" t="n">
         <v>7.04</v>
       </c>
-      <c r="M87" t="n">
+      <c r="M87" s="3" t="n">
         <v>7.09</v>
       </c>
-      <c r="N87" t="n">
+      <c r="N87" s="3" t="n">
         <v>5.81</v>
       </c>
-      <c r="O87" t="n">
+      <c r="O87" s="3" t="n">
         <v>7.5525</v>
       </c>
-      <c r="P87" t="n">
+      <c r="P87" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q87" t="n">
+      <c r="Q87" s="3" t="n">
         <v>0.0912</v>
       </c>
-      <c r="R87" t="n">
+      <c r="R87" s="3" t="n">
         <v>1.249</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
-        <v>83</v>
-      </c>
-      <c r="B88" t="inlineStr">
+      <c r="A88" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B88" s="1" t="inlineStr">
         <is>
           <t>It's around 2 in the afternoon and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E88" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F88" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G88" s="1" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H88" t="n">
-        <v>3</v>
-      </c>
-      <c r="I88" t="n">
+      <c r="H88" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I88" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="J88" s="1" t="inlineStr">
         <is>
           <t>2:00 AM</t>
         </is>
       </c>
-      <c r="K88" t="n">
+      <c r="K88" s="3" t="n">
         <v>9.33</v>
       </c>
-      <c r="L88" t="n">
+      <c r="L88" s="3" t="n">
         <v>7.27</v>
       </c>
-      <c r="M88" t="n">
+      <c r="M88" s="3" t="n">
         <v>4.28</v>
       </c>
-      <c r="N88" t="n">
+      <c r="N88" s="3" t="n">
         <v>1.51</v>
       </c>
-      <c r="O88" t="n">
+      <c r="O88" s="3" t="n">
         <v>6.425999999999999</v>
       </c>
-      <c r="P88" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q88" t="n">
+      <c r="P88" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q88" s="3" t="n">
         <v>0.0912</v>
       </c>
-      <c r="R88" t="n">
+      <c r="R88" s="3" t="n">
         <v>1.171</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
-        <v>84</v>
-      </c>
-      <c r="B89" t="inlineStr">
+      <c r="A89" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B89" s="1" t="inlineStr">
         <is>
           <t>It's about 7 in the evening and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>Lancaster, PA</t>
         </is>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="3" t="n">
         <v>170</v>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E89" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F89" s="1" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G89" s="1" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H89" t="n">
+      <c r="H89" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I89" t="n">
+      <c r="I89" s="3" t="n">
         <v>0.42</v>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="J89" s="1" t="inlineStr">
         <is>
           <t>7:00 PM</t>
         </is>
       </c>
-      <c r="K89" t="n">
+      <c r="K89" s="3" t="n">
         <v>9.77</v>
       </c>
-      <c r="L89" t="n">
+      <c r="L89" s="3" t="n">
         <v>9.43</v>
       </c>
-      <c r="M89" t="n">
+      <c r="M89" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N89" t="n">
+      <c r="N89" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O89" t="n">
+      <c r="O89" s="3" t="n">
         <v>9.731499999999999</v>
       </c>
-      <c r="P89" t="n">
+      <c r="P89" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q89" t="n">
+      <c r="Q89" s="3" t="n">
         <v>0.042</v>
       </c>
-      <c r="R89" t="n">
+      <c r="R89" s="3" t="n">
         <v>0.437</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="n">
-        <v>84</v>
-      </c>
-      <c r="B90" t="inlineStr">
+      <c r="A90" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B90" s="1" t="inlineStr">
         <is>
           <t>It's about 7 in the evening and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>Lancaster, PA</t>
         </is>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="3" t="n">
         <v>170</v>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E90" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F90" s="1" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G90" s="1" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H90" t="n">
+      <c r="H90" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I90" t="n">
+      <c r="I90" s="3" t="n">
         <v>0.42</v>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="J90" s="1" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K90" t="n">
+      <c r="K90" s="3" t="n">
         <v>9.77</v>
       </c>
-      <c r="L90" t="n">
+      <c r="L90" s="3" t="n">
         <v>9.51</v>
       </c>
-      <c r="M90" t="n">
+      <c r="M90" s="3" t="n">
         <v>5.82</v>
       </c>
-      <c r="N90" t="n">
+      <c r="N90" s="3" t="n">
         <v>5.81</v>
       </c>
-      <c r="O90" t="n">
+      <c r="O90" s="3" t="n">
         <v>8.294999999999998</v>
       </c>
-      <c r="P90" t="n">
+      <c r="P90" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q90" t="n">
+      <c r="Q90" s="3" t="n">
         <v>0.042</v>
       </c>
-      <c r="R90" t="n">
+      <c r="R90" s="3" t="n">
         <v>0.41</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="n">
-        <v>84</v>
-      </c>
-      <c r="B91" t="inlineStr">
+      <c r="A91" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B91" s="1" t="inlineStr">
         <is>
           <t>It's about 7 in the evening and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>Lancaster, PA</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="3" t="n">
         <v>170</v>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E91" s="1" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F91" s="1" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G91" s="1" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H91" t="n">
+      <c r="H91" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I91" t="n">
+      <c r="I91" s="3" t="n">
         <v>0.42</v>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="J91" s="1" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="K91" t="n">
+      <c r="K91" s="3" t="n">
         <v>9.77</v>
       </c>
-      <c r="L91" t="n">
+      <c r="L91" s="3" t="n">
         <v>9.43</v>
       </c>
-      <c r="M91" t="n">
+      <c r="M91" s="3" t="n">
         <v>4.71</v>
       </c>
-      <c r="N91" t="n">
+      <c r="N91" s="3" t="n">
         <v>2.95</v>
       </c>
-      <c r="O91" t="n">
+      <c r="O91" s="3" t="n">
         <v>7.615999999999999</v>
       </c>
-      <c r="P91" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q91" t="n">
+      <c r="P91" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3" t="n">
         <v>0.042</v>
       </c>
-      <c r="R91" t="n">
+      <c r="R91" s="3" t="n">
         <v>0.437</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="n">
-        <v>85</v>
-      </c>
-      <c r="B92" t="inlineStr">
+      <c r="A92" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B92" s="1" t="inlineStr">
         <is>
           <t>It's around 8 in the morning and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>Norristown, PA</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="3" t="n">
         <v>195</v>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E92" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F92" s="1" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G92" s="1" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H92" t="n">
-        <v>3</v>
-      </c>
-      <c r="I92" t="n">
+      <c r="H92" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I92" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="J92" s="1" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="K92" t="n">
+      <c r="K92" s="3" t="n">
         <v>8.02</v>
       </c>
-      <c r="L92" t="n">
+      <c r="L92" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="M92" t="n">
+      <c r="M92" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N92" t="n">
+      <c r="N92" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O92" t="n">
+      <c r="O92" s="3" t="n">
         <v>6.336499999999999</v>
       </c>
-      <c r="P92" t="n">
+      <c r="P92" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q92" t="n">
+      <c r="Q92" s="3" t="n">
         <v>0.2356</v>
       </c>
-      <c r="R92" t="n">
+      <c r="R92" s="3" t="n">
         <v>3.227</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="n">
-        <v>85</v>
-      </c>
-      <c r="B93" t="inlineStr">
+      <c r="A93" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B93" s="1" t="inlineStr">
         <is>
           <t>It's around 8 in the morning and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>Norristown, PA</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="3" t="n">
         <v>195</v>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E93" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F93" s="1" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G93" s="1" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H93" t="n">
-        <v>3</v>
-      </c>
-      <c r="I93" t="n">
+      <c r="H93" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I93" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="J93" s="1" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K93" t="n">
+      <c r="K93" s="3" t="n">
         <v>1.16</v>
       </c>
-      <c r="L93" t="n">
+      <c r="L93" s="3" t="n">
         <v>1.23</v>
       </c>
-      <c r="M93" t="n">
+      <c r="M93" s="3" t="n">
         <v>6.29</v>
       </c>
-      <c r="N93" t="n">
+      <c r="N93" s="3" t="n">
         <v>4.86</v>
       </c>
-      <c r="O93" t="n">
+      <c r="O93" s="3" t="n">
         <v>2.7655</v>
       </c>
-      <c r="P93" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q93" t="n">
+      <c r="P93" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q93" s="3" t="n">
         <v>0.992</v>
       </c>
-      <c r="R93" t="n">
+      <c r="R93" s="3" t="n">
         <v>3.227</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="n">
-        <v>85</v>
-      </c>
-      <c r="B94" t="inlineStr">
+      <c r="A94" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
         <is>
           <t>It's around 8 in the morning and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>Norristown, PA</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="3" t="n">
         <v>195</v>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E94" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F94" s="1" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G94" s="1" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H94" t="n">
-        <v>3</v>
-      </c>
-      <c r="I94" t="n">
+      <c r="H94" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="J94" s="1" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K94" t="n">
+      <c r="K94" s="3" t="n">
         <v>8.02</v>
       </c>
-      <c r="L94" t="n">
+      <c r="L94" s="3" t="n">
         <v>1.82</v>
       </c>
-      <c r="M94" t="n">
+      <c r="M94" s="3" t="n">
         <v>2.86</v>
       </c>
-      <c r="N94" t="n">
+      <c r="N94" s="3" t="n">
         <v>2.63</v>
       </c>
-      <c r="O94" t="n">
+      <c r="O94" s="3" t="n">
         <v>4.0095</v>
       </c>
-      <c r="P94" t="n">
+      <c r="P94" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q94" t="n">
+      <c r="Q94" s="3" t="n">
         <v>0.2356</v>
       </c>
-      <c r="R94" t="n">
+      <c r="R94" s="3" t="n">
         <v>3.026</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="n">
-        <v>96</v>
-      </c>
-      <c r="B95" t="inlineStr">
+      <c r="A95" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B95" s="1" t="inlineStr">
         <is>
           <t>It's around 2 in the afternoon, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="3" t="n">
         <v>220</v>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E95" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F95" s="1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G95" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H95" t="n">
+      <c r="H95" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I95" t="n">
+      <c r="I95" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="J95" s="1" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K95" t="n">
+      <c r="K95" s="3" t="n">
         <v>6.91</v>
       </c>
-      <c r="L95" t="n">
+      <c r="L95" s="3" t="n">
         <v>2.76</v>
       </c>
-      <c r="M95" t="n">
+      <c r="M95" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N95" t="n">
+      <c r="N95" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O95" t="n">
+      <c r="O95" s="3" t="n">
         <v>6.539</v>
       </c>
-      <c r="P95" t="n">
+      <c r="P95" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q95" t="n">
+      <c r="Q95" s="3" t="n">
         <v>0.3575</v>
       </c>
-      <c r="R95" t="n">
+      <c r="R95" s="3" t="n">
         <v>2.707</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
-        <v>96</v>
-      </c>
-      <c r="B96" t="inlineStr">
+      <c r="A96" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B96" s="1" t="inlineStr">
         <is>
           <t>It's around 2 in the afternoon, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="3" t="n">
         <v>220</v>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E96" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F96" s="1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G96" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H96" t="n">
+      <c r="H96" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I96" t="n">
+      <c r="I96" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="J96" s="1" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K96" t="n">
+      <c r="K96" s="3" t="n">
         <v>6.91</v>
       </c>
-      <c r="L96" t="n">
+      <c r="L96" s="3" t="n">
         <v>2.76</v>
       </c>
-      <c r="M96" t="n">
+      <c r="M96" s="3" t="n">
         <v>7.29</v>
       </c>
-      <c r="N96" t="n">
+      <c r="N96" s="3" t="n">
         <v>6.04</v>
       </c>
-      <c r="O96" t="n">
+      <c r="O96" s="3" t="n">
         <v>5.403</v>
       </c>
-      <c r="P96" t="n">
+      <c r="P96" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q96" t="n">
+      <c r="Q96" s="3" t="n">
         <v>0.3575</v>
       </c>
-      <c r="R96" t="n">
+      <c r="R96" s="3" t="n">
         <v>2.707</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" t="inlineStr">
+      <c r="A97" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B97" s="1" t="inlineStr">
         <is>
           <t>It's around 2 in the afternoon, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="3" t="n">
         <v>220</v>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E97" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F97" s="1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G97" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H97" t="n">
+      <c r="H97" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I97" t="n">
+      <c r="I97" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="J97" s="1" t="inlineStr">
         <is>
           <t>10:00 PM</t>
         </is>
       </c>
-      <c r="K97" t="n">
+      <c r="K97" s="3" t="n">
         <v>6.91</v>
       </c>
-      <c r="L97" t="n">
+      <c r="L97" s="3" t="n">
         <v>2.76</v>
       </c>
-      <c r="M97" t="n">
+      <c r="M97" s="3" t="n">
         <v>3.36</v>
       </c>
-      <c r="N97" t="n">
+      <c r="N97" s="3" t="n">
         <v>3.11</v>
       </c>
-      <c r="O97" t="n">
+      <c r="O97" s="3" t="n">
         <v>4.1775</v>
       </c>
-      <c r="P97" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q97" t="n">
+      <c r="P97" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q97" s="3" t="n">
         <v>0.3575</v>
       </c>
-      <c r="R97" t="n">
+      <c r="R97" s="3" t="n">
         <v>2.707</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" t="inlineStr">
+      <c r="A98" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B98" s="1" t="inlineStr">
         <is>
           <t>I've just got home, it's around 6 PM, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E98" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F98" s="1" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G98" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H98" t="n">
+      <c r="H98" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="I98" t="n">
+      <c r="I98" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="J98" s="1" t="inlineStr">
         <is>
           <t>6:00 PM</t>
         </is>
       </c>
-      <c r="K98" t="n">
+      <c r="K98" s="3" t="n">
         <v>8.609999999999999</v>
       </c>
-      <c r="L98" t="n">
+      <c r="L98" s="3" t="n">
         <v>5.51</v>
       </c>
-      <c r="M98" t="n">
+      <c r="M98" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N98" t="n">
+      <c r="N98" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O98" t="n">
+      <c r="O98" s="3" t="n">
         <v>8.0115</v>
       </c>
-      <c r="P98" t="n">
+      <c r="P98" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q98" t="n">
+      <c r="Q98" s="3" t="n">
         <v>0.17</v>
       </c>
-      <c r="R98" t="n">
+      <c r="R98" s="3" t="n">
         <v>1.77</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="n">
-        <v>97</v>
-      </c>
-      <c r="B99" t="inlineStr">
+      <c r="A99" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B99" s="1" t="inlineStr">
         <is>
           <t>I've just got home, it's around 6 PM, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E99" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F99" s="1" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G99" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H99" t="n">
+      <c r="H99" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="I99" t="n">
+      <c r="I99" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="J99" s="1" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K99" t="n">
+      <c r="K99" s="3" t="n">
         <v>8.609999999999999</v>
       </c>
-      <c r="L99" t="n">
+      <c r="L99" s="3" t="n">
         <v>5.51</v>
       </c>
-      <c r="M99" t="n">
+      <c r="M99" s="3" t="n">
         <v>5.21</v>
       </c>
-      <c r="N99" t="n">
+      <c r="N99" s="3" t="n">
         <v>4.64</v>
       </c>
-      <c r="O99" t="n">
+      <c r="O99" s="3" t="n">
         <v>6.249499999999999</v>
       </c>
-      <c r="P99" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q99" t="n">
+      <c r="P99" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q99" s="3" t="n">
         <v>0.17</v>
       </c>
-      <c r="R99" t="n">
+      <c r="R99" s="3" t="n">
         <v>1.77</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="n">
-        <v>97</v>
-      </c>
-      <c r="B100" t="inlineStr">
+      <c r="A100" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B100" s="1" t="inlineStr">
         <is>
           <t>I've just got home, it's around 6 PM, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E100" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F100" s="1" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G100" s="1" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H100" t="n">
+      <c r="H100" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="I100" t="n">
+      <c r="I100" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="J100" s="1" t="inlineStr">
         <is>
           <t>10:00 PM</t>
         </is>
       </c>
-      <c r="K100" t="n">
+      <c r="K100" s="3" t="n">
         <v>8.609999999999999</v>
       </c>
-      <c r="L100" t="n">
+      <c r="L100" s="3" t="n">
         <v>5.51</v>
       </c>
-      <c r="M100" t="n">
+      <c r="M100" s="3" t="n">
         <v>7.83</v>
       </c>
-      <c r="N100" t="n">
+      <c r="N100" s="3" t="n">
         <v>5.71</v>
       </c>
-      <c r="O100" t="n">
+      <c r="O100" s="3" t="n">
         <v>6.933999999999999</v>
       </c>
-      <c r="P100" t="n">
+      <c r="P100" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q100" t="n">
+      <c r="Q100" s="3" t="n">
         <v>0.17</v>
       </c>
-      <c r="R100" t="n">
+      <c r="R100" s="3" t="n">
         <v>1.77</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="n">
-        <v>98</v>
-      </c>
-      <c r="B101" t="inlineStr">
+      <c r="A101" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B101" s="1" t="inlineStr">
         <is>
           <t>Laundry finished around 6 PM in Harrisburg. When should I run the dryer?</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E101" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F101" s="1" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G101" s="1" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H101" t="n">
+      <c r="H101" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I101" t="n">
+      <c r="I101" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>6pm</t>
-        </is>
-      </c>
-      <c r="K101" t="n">
+      <c r="J101" s="1" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="n">
         <v>7.98</v>
       </c>
-      <c r="L101" t="n">
+      <c r="L101" s="3" t="n">
         <v>3.37</v>
       </c>
-      <c r="M101" t="n">
+      <c r="M101" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N101" t="n">
+      <c r="N101" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O101" t="n">
+      <c r="O101" s="3" t="n">
         <v>7.0735</v>
       </c>
-      <c r="P101" t="n">
+      <c r="P101" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q101" t="n">
+      <c r="Q101" s="3" t="n">
         <v>0.24</v>
       </c>
-      <c r="R101" t="n">
+      <c r="R101" s="3" t="n">
         <v>2.498</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="n">
-        <v>98</v>
-      </c>
-      <c r="B102" t="inlineStr">
+      <c r="A102" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B102" s="1" t="inlineStr">
         <is>
           <t>Laundry finished around 6 PM in Harrisburg. When should I run the dryer?</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E102" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F102" s="1" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G102" s="1" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H102" t="n">
+      <c r="H102" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I102" t="n">
+      <c r="I102" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>10pm</t>
-        </is>
-      </c>
-      <c r="K102" t="n">
+      <c r="J102" s="1" t="inlineStr">
+        <is>
+          <t>10:00 PM</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="n">
         <v>7.98</v>
       </c>
-      <c r="L102" t="n">
+      <c r="L102" s="3" t="n">
         <v>3.37</v>
       </c>
-      <c r="M102" t="n">
+      <c r="M102" s="3" t="n">
         <v>5.69</v>
       </c>
-      <c r="N102" t="n">
+      <c r="N102" s="3" t="n">
         <v>5.67</v>
       </c>
-      <c r="O102" t="n">
+      <c r="O102" s="3" t="n">
         <v>5.562</v>
       </c>
-      <c r="P102" t="n">
+      <c r="P102" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q102" t="n">
+      <c r="Q102" s="3" t="n">
         <v>0.24</v>
       </c>
-      <c r="R102" t="n">
+      <c r="R102" s="3" t="n">
         <v>2.498</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="n">
-        <v>98</v>
-      </c>
-      <c r="B103" t="inlineStr">
+      <c r="A103" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B103" s="1" t="inlineStr">
         <is>
           <t>Laundry finished around 6 PM in Harrisburg. When should I run the dryer?</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E103" s="1" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F103" s="1" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G103" s="1" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H103" t="n">
+      <c r="H103" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I103" t="n">
+      <c r="I103" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>6am</t>
-        </is>
-      </c>
-      <c r="K103" t="n">
+      <c r="J103" s="1" t="inlineStr">
+        <is>
+          <t>6:00 AM</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="n">
         <v>7.98</v>
       </c>
-      <c r="L103" t="n">
+      <c r="L103" s="3" t="n">
         <v>3.83</v>
       </c>
-      <c r="M103" t="n">
+      <c r="M103" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="N103" t="n">
+      <c r="N103" s="3" t="n">
         <v>2.47</v>
       </c>
-      <c r="O103" t="n">
+      <c r="O103" s="3" t="n">
         <v>4.353</v>
       </c>
-      <c r="P103" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q103" t="n">
+      <c r="P103" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q103" s="3" t="n">
         <v>0.24</v>
       </c>
-      <c r="R103" t="n">
+      <c r="R103" s="3" t="n">
         <v>2.342</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="n">
-        <v>99</v>
-      </c>
-      <c r="B104" t="inlineStr">
+      <c r="A104" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B104" s="1" t="inlineStr">
         <is>
           <t>It's around 8 in the morning and I need to run the dishwasher in Doylestown. When should I start it?</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>Doylestown, PA</t>
         </is>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E104" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F104" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G104" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H104" t="n">
-        <v>3</v>
-      </c>
-      <c r="I104" t="n">
+      <c r="H104" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I104" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>8am</t>
-        </is>
-      </c>
-      <c r="K104" t="n">
+      <c r="J104" s="1" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="n">
         <v>9.43</v>
       </c>
-      <c r="L104" t="n">
+      <c r="L104" s="3" t="n">
         <v>7.5</v>
       </c>
-      <c r="M104" t="n">
+      <c r="M104" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="N104" t="n">
+      <c r="N104" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O104" t="n">
+      <c r="O104" s="3" t="n">
         <v>8.954000000000001</v>
       </c>
-      <c r="P104" t="n">
+      <c r="P104" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q104" t="n">
+      <c r="Q104" s="3" t="n">
         <v>0.0798</v>
       </c>
-      <c r="R104" t="n">
+      <c r="R104" s="3" t="n">
         <v>1.093</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="n">
-        <v>99</v>
-      </c>
-      <c r="B105" t="inlineStr">
+      <c r="A105" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
         <is>
           <t>It's around 8 in the morning and I need to run the dishwasher in Doylestown. When should I start it?</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>Doylestown, PA</t>
         </is>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E105" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F105" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G105" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H105" t="n">
-        <v>3</v>
-      </c>
-      <c r="I105" t="n">
+      <c r="H105" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I105" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>2pm</t>
-        </is>
-      </c>
-      <c r="K105" t="n">
+      <c r="J105" s="1" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="n">
         <v>7.11</v>
       </c>
-      <c r="L105" t="n">
+      <c r="L105" s="3" t="n">
         <v>7.5</v>
       </c>
-      <c r="M105" t="n">
+      <c r="M105" s="3" t="n">
         <v>7.09</v>
       </c>
-      <c r="N105" t="n">
+      <c r="N105" s="3" t="n">
         <v>5.81</v>
       </c>
-      <c r="O105" t="n">
+      <c r="O105" s="3" t="n">
         <v>7.0475</v>
       </c>
-      <c r="P105" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q105" t="n">
+      <c r="P105" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q105" s="3" t="n">
         <v>0.336</v>
       </c>
-      <c r="R105" t="n">
+      <c r="R105" s="3" t="n">
         <v>1.093</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="n">
-        <v>99</v>
-      </c>
-      <c r="B106" t="inlineStr">
+      <c r="A106" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B106" s="1" t="inlineStr">
         <is>
           <t>It's around 8 in the morning and I need to run the dishwasher in Doylestown. When should I start it?</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>Doylestown, PA</t>
         </is>
       </c>
-      <c r="D106" t="n">
+      <c r="D106" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E106" s="1" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F106" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="G106" s="1" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H106" t="n">
-        <v>3</v>
-      </c>
-      <c r="I106" t="n">
+      <c r="H106" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I106" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>11pm</t>
-        </is>
-      </c>
-      <c r="K106" t="n">
+      <c r="J106" s="1" t="inlineStr">
+        <is>
+          <t>11:00 PM</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="n">
         <v>9.43</v>
       </c>
-      <c r="L106" t="n">
+      <c r="L106" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="M106" t="n">
+      <c r="M106" s="3" t="n">
         <v>5.73</v>
       </c>
-      <c r="N106" t="n">
+      <c r="N106" s="3" t="n">
         <v>2.89</v>
       </c>
-      <c r="O106" t="n">
+      <c r="O106" s="3" t="n">
         <v>7.103499999999999</v>
       </c>
-      <c r="P106" t="n">
+      <c r="P106" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q106" t="n">
+      <c r="Q106" s="3" t="n">
         <v>0.0798</v>
       </c>
-      <c r="R106" t="n">
+      <c r="R106" s="3" t="n">
         <v>1.025</v>
       </c>
     </row>

--- a/workbooks/scenarios/ApplianceRAGScenarios.xlsx
+++ b/workbooks/scenarios/ApplianceRAGScenarios.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.######"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -48,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,7234 +417,7234 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>scenario_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>question</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>utility_budget</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>appliance</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>appliance_age</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>housing_type</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>household_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>kwh_per_cycle</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>alternative</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>energy_cost_score</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>environmental_score</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>comfort_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>practicality_score</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>mavt_score</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>raw_cost</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>raw_emissions</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>It's mid-morning, about 10 and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Johnstown, PA</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" t="n">
         <v>260</v>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" s="3" t="n">
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
         <v>2.8</v>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" t="n">
         <v>8.33</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="L2" t="n">
         <v>2.14</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="M2" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="N2" t="n">
         <v>9.15</v>
       </c>
-      <c r="O2" s="3" t="n">
+      <c r="O2" t="n">
         <v>6.512500000000001</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="Q2" t="n">
         <v>0.2016</v>
       </c>
-      <c r="R2" s="3" t="n">
+      <c r="R2" t="n">
         <v>2.915</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>It's mid-morning, about 10 and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Johnstown, PA</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" t="n">
         <v>260</v>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" s="3" t="n">
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" t="n">
         <v>8.33</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L3" t="n">
         <v>2.14</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="M3" t="n">
         <v>8.9</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="N3" t="n">
         <v>8.23</v>
       </c>
-      <c r="O3" s="3" t="n">
+      <c r="O3" t="n">
         <v>6.2625</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="P3" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="Q3" t="n">
         <v>0.2016</v>
       </c>
-      <c r="R3" s="3" t="n">
+      <c r="R3" t="n">
         <v>2.915</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>It's mid-morning, about 10 and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Johnstown, PA</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" t="n">
         <v>260</v>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" s="3" t="n">
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
         <v>2.8</v>
       </c>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" t="n">
         <v>5.46</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" t="n">
         <v>2.14</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" t="n">
         <v>6.74</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="N4" t="n">
         <v>5.4</v>
       </c>
-      <c r="O4" s="3" t="n">
+      <c r="O4" t="n">
         <v>4.545</v>
       </c>
-      <c r="P4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q4" s="3" t="n">
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0.518</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" t="n">
         <v>2.915</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>It's just past 9 AM, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Meadville, PA</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" t="n">
         <v>320</v>
       </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" t="n">
         <v>4</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" t="n">
         <v>3.5</v>
       </c>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" t="n">
         <v>7.87</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" t="n">
         <v>10</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" t="n">
         <v>10</v>
       </c>
-      <c r="O5" s="3" t="n">
+      <c r="O5" t="n">
         <v>5.861</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="P5" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" t="n">
         <v>0.252</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" t="n">
         <v>3.643</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>It's just past 9 AM, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Meadville, PA</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" t="n">
         <v>320</v>
       </c>
-      <c r="E6" s="1" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" t="n">
         <v>4</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" t="n">
         <v>3.5</v>
       </c>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" t="n">
         <v>7.87</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" t="n">
         <v>7.81</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" t="n">
         <v>6.66</v>
       </c>
-      <c r="O6" s="3" t="n">
+      <c r="O6" t="n">
         <v>4.922</v>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" t="n">
         <v>0.252</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" t="n">
         <v>3.643</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>It's just past 9 AM, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Meadville, PA</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" t="n">
         <v>320</v>
       </c>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" t="n">
         <v>4</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" t="n">
         <v>3.5</v>
       </c>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" t="n">
         <v>4.28</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" t="n">
         <v>5.92</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" t="n">
         <v>4.31</v>
       </c>
-      <c r="O7" s="3" t="n">
+      <c r="O7" t="n">
         <v>3.1145</v>
       </c>
-      <c r="P7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="3" t="n">
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0.6475</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" t="n">
         <v>3.643</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>It's just past 9 AM and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Lancaster, PA</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" t="n">
         <v>150</v>
       </c>
-      <c r="E8" s="1" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" t="n">
         <v>4</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" t="n">
         <v>0.35</v>
       </c>
-      <c r="J8" s="1" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" t="n">
         <v>9.84</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" t="n">
         <v>9.65</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" t="n">
         <v>10</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="N8" t="n">
         <v>10</v>
       </c>
-      <c r="O8" s="3" t="n">
+      <c r="O8" t="n">
         <v>9.829499999999999</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P8" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" t="n">
         <v>0.035</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" t="n">
         <v>0.364</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>It's just past 9 AM and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Lancaster, PA</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" t="n">
         <v>150</v>
       </c>
-      <c r="E9" s="1" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" t="n">
         <v>4</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" t="n">
         <v>0.35</v>
       </c>
-      <c r="J9" s="1" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" t="n">
         <v>9.710000000000001</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" t="n">
         <v>9.65</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" t="n">
         <v>6.92</v>
       </c>
-      <c r="N9" s="3" t="n">
+      <c r="N9" t="n">
         <v>5.61</v>
       </c>
-      <c r="O9" s="3" t="n">
+      <c r="O9" t="n">
         <v>8.516</v>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="P9" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" t="n">
         <v>0.049</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" t="n">
         <v>0.364</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>It's just past 9 AM and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Lancaster, PA</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" t="n">
         <v>150</v>
       </c>
-      <c r="E10" s="1" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" t="n">
         <v>4</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" t="n">
         <v>0.35</v>
       </c>
-      <c r="J10" s="1" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>12:00 AM</t>
         </is>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" t="n">
         <v>9.84</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" t="n">
         <v>9.710000000000001</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" t="n">
         <v>3.83</v>
       </c>
-      <c r="N10" s="3" t="n">
+      <c r="N10" t="n">
         <v>1.51</v>
       </c>
-      <c r="O10" s="3" t="n">
+      <c r="O10" t="n">
         <v>7.343</v>
       </c>
-      <c r="P10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3" t="n">
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0.035</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" t="n">
         <v>0.342</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>It's late morning, around 11 and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Norristown, PA</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" t="n">
         <v>175</v>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="H11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" t="n">
         <v>1.1</v>
       </c>
-      <c r="J11" s="1" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" t="n">
         <v>9.4</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" t="n">
         <v>7.35</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" t="n">
         <v>10</v>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="N11" t="n">
         <v>10</v>
       </c>
-      <c r="O11" s="3" t="n">
+      <c r="O11" t="n">
         <v>8.8925</v>
       </c>
-      <c r="P11" s="2" t="n">
+      <c r="P11" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" s="3" t="n">
+      <c r="Q11" t="n">
         <v>0.08359999999999999</v>
       </c>
-      <c r="R11" s="3" t="n">
+      <c r="R11" t="n">
         <v>1.145</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>It's late morning, around 11 and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Norristown, PA</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" t="n">
         <v>175</v>
       </c>
-      <c r="E12" s="1" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="H12" t="n">
         <v>2</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" t="n">
         <v>1.1</v>
       </c>
-      <c r="J12" s="1" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" t="n">
         <v>6.96</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" t="n">
         <v>7.35</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" t="n">
         <v>7.83</v>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="N12" t="n">
         <v>6.69</v>
       </c>
-      <c r="O12" s="3" t="n">
+      <c r="O12" t="n">
         <v>7.23</v>
       </c>
-      <c r="P12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="3" t="n">
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
         <v>0.352</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" t="n">
         <v>1.145</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>It's late morning, around 11 and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Norristown, PA</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" t="n">
         <v>175</v>
       </c>
-      <c r="E13" s="1" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="H13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="I13" t="n">
         <v>1.1</v>
       </c>
-      <c r="J13" s="1" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>8:00 PM</t>
         </is>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" t="n">
         <v>9.4</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" t="n">
         <v>7.35</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" t="n">
         <v>6.29</v>
       </c>
-      <c r="N13" s="3" t="n">
+      <c r="N13" t="n">
         <v>4.78</v>
       </c>
-      <c r="O13" s="3" t="n">
+      <c r="O13" t="n">
         <v>7.3675</v>
       </c>
-      <c r="P13" s="2" t="n">
+      <c r="P13" t="n">
         <v>2</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" t="n">
         <v>0.08359999999999999</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" t="n">
         <v>1.145</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>It's just past 9 AM and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Reading, PA</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" t="n">
         <v>150</v>
       </c>
-      <c r="E14" s="1" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="n">
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
         <v>0.45</v>
       </c>
-      <c r="J14" s="1" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" t="n">
         <v>9.75</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" t="n">
         <v>9.34</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" t="n">
         <v>10</v>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="N14" t="n">
         <v>10</v>
       </c>
-      <c r="O14" s="3" t="n">
+      <c r="O14" t="n">
         <v>9.693999999999999</v>
       </c>
-      <c r="P14" s="2" t="n">
+      <c r="P14" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" t="n">
         <v>0.045</v>
       </c>
-      <c r="R14" s="3" t="n">
+      <c r="R14" t="n">
         <v>0.468</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" t="n">
         <v>5</v>
       </c>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>It's just past 9 AM and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Reading, PA</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" t="n">
         <v>150</v>
       </c>
-      <c r="E15" s="1" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="n">
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
         <v>0.45</v>
       </c>
-      <c r="J15" s="1" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>8:00 PM</t>
         </is>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" t="n">
         <v>9.75</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" t="n">
         <v>9.34</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" t="n">
         <v>4.71</v>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="N15" t="n">
         <v>2.95</v>
       </c>
-      <c r="O15" s="3" t="n">
+      <c r="O15" t="n">
         <v>7.578499999999999</v>
       </c>
-      <c r="P15" s="2" t="n">
+      <c r="P15" t="n">
         <v>2</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" t="n">
         <v>0.045</v>
       </c>
-      <c r="R15" s="3" t="n">
+      <c r="R15" t="n">
         <v>0.468</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" t="n">
         <v>5</v>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>It's just past 9 AM and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Reading, PA</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" t="n">
         <v>150</v>
       </c>
-      <c r="E16" s="1" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" s="3" t="n">
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
         <v>0.45</v>
       </c>
-      <c r="J16" s="1" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>12:00 AM</t>
         </is>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" t="n">
         <v>9.75</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" t="n">
         <v>9.43</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" t="n">
         <v>2.86</v>
       </c>
-      <c r="N16" s="3" t="n">
+      <c r="N16" t="n">
         <v>1.51</v>
       </c>
-      <c r="O16" s="3" t="n">
+      <c r="O16" t="n">
         <v>7.023999999999999</v>
       </c>
-      <c r="P16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q16" s="3" t="n">
+      <c r="P16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" t="n">
         <v>0.045</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" t="n">
         <v>0.439</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" t="n">
         <v>6</v>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>It's just past 9 AM, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" t="n">
         <v>200</v>
       </c>
-      <c r="E17" s="1" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G17" s="1" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="n">
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
         <v>2.8</v>
       </c>
-      <c r="J17" s="1" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" t="n">
         <v>6.66</v>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="L17" t="n">
         <v>2.14</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" t="n">
         <v>10</v>
       </c>
-      <c r="N17" s="3" t="n">
+      <c r="N17" t="n">
         <v>10</v>
       </c>
-      <c r="O17" s="3" t="n">
+      <c r="O17" t="n">
         <v>6.247</v>
       </c>
-      <c r="P17" s="2" t="n">
+      <c r="P17" t="n">
         <v>1</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" t="n">
         <v>0.385</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" t="n">
         <v>2.915</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>It's just past 9 AM, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" t="n">
         <v>200</v>
       </c>
-      <c r="E18" s="1" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="n">
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
         <v>2.8</v>
       </c>
-      <c r="J18" s="1" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" t="n">
         <v>6.66</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" t="n">
         <v>2.14</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" t="n">
         <v>7.29</v>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="N18" t="n">
         <v>6.04</v>
       </c>
-      <c r="O18" s="3" t="n">
+      <c r="O18" t="n">
         <v>5.111</v>
       </c>
-      <c r="P18" s="2" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="Q18" s="3" t="n">
+      <c r="Q18" t="n">
         <v>0.385</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" t="n">
         <v>2.915</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" t="n">
         <v>6</v>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>It's just past 9 AM, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" t="n">
         <v>200</v>
       </c>
-      <c r="E19" s="1" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H19" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" s="3" t="n">
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
         <v>2.8</v>
       </c>
-      <c r="J19" s="1" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" t="n">
         <v>6.66</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" t="n">
         <v>2.68</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" t="n">
         <v>2.35</v>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="N19" t="n">
         <v>2.13</v>
       </c>
-      <c r="O19" s="3" t="n">
+      <c r="O19" t="n">
         <v>3.7255</v>
       </c>
-      <c r="P19" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q19" s="3" t="n">
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" t="n">
         <v>0.385</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" t="n">
         <v>2.733</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" t="n">
         <v>7</v>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>State College, PA</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" t="n">
         <v>150</v>
       </c>
-      <c r="E20" s="1" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I20" t="n">
         <v>0.2</v>
       </c>
-      <c r="J20" s="1" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" t="n">
         <v>9.9</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" t="n">
         <v>10</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" t="n">
         <v>10</v>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="N20" t="n">
         <v>10</v>
       </c>
-      <c r="O20" s="3" t="n">
+      <c r="O20" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="P20" s="2" t="n">
+      <c r="P20" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" t="n">
         <v>0.028</v>
       </c>
-      <c r="R20" s="3" t="n">
+      <c r="R20" t="n">
         <v>0.208</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" t="n">
         <v>7</v>
       </c>
-      <c r="B21" s="1" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>State College, PA</t>
         </is>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" t="n">
         <v>150</v>
       </c>
-      <c r="E21" s="1" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F21" s="1" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H21" s="2" t="n">
+      <c r="H21" t="n">
         <v>2</v>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="I21" t="n">
         <v>0.2</v>
       </c>
-      <c r="J21" s="1" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" t="n">
         <v>10</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" t="n">
         <v>7</v>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="N21" t="n">
         <v>5.71</v>
       </c>
-      <c r="O21" s="3" t="n">
+      <c r="O21" t="n">
         <v>8.7475</v>
       </c>
-      <c r="P21" s="2" t="n">
+      <c r="P21" t="n">
         <v>2</v>
       </c>
-      <c r="Q21" s="3" t="n">
+      <c r="Q21" t="n">
         <v>0.02</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" t="n">
         <v>0.208</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" t="n">
         <v>7</v>
       </c>
-      <c r="B22" s="1" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>State College, PA</t>
         </is>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" t="n">
         <v>150</v>
       </c>
-      <c r="E22" s="1" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F22" s="1" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="H22" t="n">
         <v>2</v>
       </c>
-      <c r="I22" s="3" t="n">
+      <c r="I22" t="n">
         <v>0.2</v>
       </c>
-      <c r="J22" s="1" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>12:00 AM</t>
         </is>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="L22" t="n">
         <v>10</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" t="n">
         <v>3.59</v>
       </c>
-      <c r="N22" s="3" t="n">
+      <c r="N22" t="n">
         <v>2.86</v>
       </c>
-      <c r="O22" s="3" t="n">
+      <c r="O22" t="n">
         <v>7.638</v>
       </c>
-      <c r="P22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="3" t="n">
+      <c r="P22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q22" t="n">
         <v>0.02</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" t="n">
         <v>0.195</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>It's around 5 in the evening, when should I run the washing machine?</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" t="n">
         <v>120</v>
       </c>
-      <c r="E23" s="1" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H23" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="n">
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
         <v>0.23</v>
       </c>
-      <c r="J23" s="1" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" t="n">
         <v>10</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" t="n">
         <v>10</v>
       </c>
-      <c r="N23" s="3" t="n">
+      <c r="N23" t="n">
         <v>10</v>
       </c>
-      <c r="O23" s="3" t="n">
+      <c r="O23" t="n">
         <v>9.958</v>
       </c>
-      <c r="P23" s="2" t="n">
+      <c r="P23" t="n">
         <v>1</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" t="n">
         <v>0.0322</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" t="n">
         <v>0.239</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" t="n">
         <v>8</v>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>It's around 5 in the evening, when should I run the washing machine?</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" t="n">
         <v>120</v>
       </c>
-      <c r="E24" s="1" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H24" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="n">
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
         <v>0.23</v>
       </c>
-      <c r="J24" s="1" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K24" s="3" t="n">
+      <c r="K24" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="L24" t="n">
         <v>10</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" t="n">
         <v>5.92</v>
       </c>
-      <c r="N24" s="3" t="n">
+      <c r="N24" t="n">
         <v>4.64</v>
       </c>
-      <c r="O24" s="3" t="n">
+      <c r="O24" t="n">
         <v>8.365</v>
       </c>
-      <c r="P24" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3" t="n">
+      <c r="P24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q24" t="n">
         <v>0.023</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" t="n">
         <v>0.239</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" t="n">
         <v>8</v>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>It's around 5 in the evening, when should I run the washing machine?</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" t="n">
         <v>120</v>
       </c>
-      <c r="E25" s="1" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H25" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I25" s="3" t="n">
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
         <v>0.23</v>
       </c>
-      <c r="J25" s="1" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>10:00 PM</t>
         </is>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" t="n">
         <v>10</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="M25" t="n">
         <v>6.01</v>
       </c>
-      <c r="N25" s="3" t="n">
+      <c r="N25" t="n">
         <v>5.19</v>
       </c>
-      <c r="O25" s="3" t="n">
+      <c r="O25" t="n">
         <v>8.465499999999999</v>
       </c>
-      <c r="P25" s="2" t="n">
+      <c r="P25" t="n">
         <v>2</v>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="Q25" t="n">
         <v>0.023</v>
       </c>
-      <c r="R25" s="3" t="n">
+      <c r="R25" t="n">
         <v>0.239</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" t="n">
         <v>9</v>
       </c>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>It's just past 7 PM, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Bethlehem, PA</t>
         </is>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" t="n">
         <v>175</v>
       </c>
-      <c r="E26" s="1" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F26" s="1" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="n">
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
         <v>3.5</v>
       </c>
-      <c r="J26" s="1" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>7:00 PM</t>
         </is>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" t="n">
         <v>6.98</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" t="n">
         <v>10</v>
       </c>
-      <c r="N26" s="3" t="n">
+      <c r="N26" t="n">
         <v>10</v>
       </c>
-      <c r="O26" s="3" t="n">
+      <c r="O26" t="n">
         <v>5.593999999999999</v>
       </c>
-      <c r="P26" s="2" t="n">
+      <c r="P26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" t="n">
         <v>0.35</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" t="n">
         <v>3.643</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" t="n">
         <v>9</v>
       </c>
-      <c r="B27" s="1" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>It's just past 7 PM, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Bethlehem, PA</t>
         </is>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" t="n">
         <v>175</v>
       </c>
-      <c r="E27" s="1" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F27" s="1" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G27" s="1" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="n">
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
         <v>3.5</v>
       </c>
-      <c r="J27" s="1" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" t="n">
         <v>6.98</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" t="n">
         <v>0</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" t="n">
         <v>5.13</v>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="N27" t="n">
         <v>3.42</v>
       </c>
-      <c r="O27" s="3" t="n">
+      <c r="O27" t="n">
         <v>3.633</v>
       </c>
-      <c r="P27" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="n">
+      <c r="P27" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q27" t="n">
         <v>0.35</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" t="n">
         <v>3.643</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" t="n">
         <v>9</v>
       </c>
-      <c r="B28" s="1" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>It's just past 7 PM, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Bethlehem, PA</t>
         </is>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" t="n">
         <v>175</v>
       </c>
-      <c r="E28" s="1" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I28" s="3" t="n">
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
         <v>3.5</v>
       </c>
-      <c r="J28" s="1" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>12:00 AM</t>
         </is>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" t="n">
         <v>6.98</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" t="n">
         <v>0.67</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="M28" t="n">
         <v>5.06</v>
       </c>
-      <c r="N28" s="3" t="n">
+      <c r="N28" t="n">
         <v>3.88</v>
       </c>
-      <c r="O28" s="3" t="n">
+      <c r="O28" t="n">
         <v>3.9225</v>
       </c>
-      <c r="P28" s="2" t="n">
+      <c r="P28" t="n">
         <v>2</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" t="n">
         <v>0.35</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" t="n">
         <v>3.416</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="1" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>It's around 3 in the afternoon and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Exton, PA</t>
         </is>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" t="n">
         <v>150</v>
       </c>
-      <c r="E29" s="1" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F29" s="1" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="H29" t="n">
         <v>2</v>
       </c>
-      <c r="I29" s="3" t="n">
+      <c r="I29" t="n">
         <v>0.72</v>
       </c>
-      <c r="J29" s="1" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" t="n">
         <v>8.07</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="L29" t="n">
         <v>8.51</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" t="n">
         <v>10</v>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="N29" t="n">
         <v>10</v>
       </c>
-      <c r="O29" s="3" t="n">
+      <c r="O29" t="n">
         <v>8.8995</v>
       </c>
-      <c r="P29" s="2" t="n">
+      <c r="P29" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" t="n">
         <v>0.2304</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" t="n">
         <v>0.75</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" t="n">
         <v>10</v>
       </c>
-      <c r="B30" s="1" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>It's around 3 in the afternoon and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Exton, PA</t>
         </is>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D30" t="n">
         <v>150</v>
       </c>
-      <c r="E30" s="1" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F30" s="1" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="H30" t="n">
         <v>2</v>
       </c>
-      <c r="I30" s="3" t="n">
+      <c r="I30" t="n">
         <v>0.72</v>
       </c>
-      <c r="J30" s="1" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" t="n">
         <v>9.66</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" t="n">
         <v>8.51</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" t="n">
         <v>7.43</v>
       </c>
-      <c r="N30" s="3" t="n">
+      <c r="N30" t="n">
         <v>6.21</v>
       </c>
-      <c r="O30" s="3" t="n">
+      <c r="O30" t="n">
         <v>8.294</v>
       </c>
-      <c r="P30" s="2" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" t="n">
         <v>0.0547</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" t="n">
         <v>0.75</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" t="n">
         <v>10</v>
       </c>
-      <c r="B31" s="1" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>It's around 3 in the afternoon and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Exton, PA</t>
         </is>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" t="n">
         <v>150</v>
       </c>
-      <c r="E31" s="1" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F31" s="1" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H31" s="2" t="n">
+      <c r="H31" t="n">
         <v>2</v>
       </c>
-      <c r="I31" s="3" t="n">
+      <c r="I31" t="n">
         <v>0.72</v>
       </c>
-      <c r="J31" s="1" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>10:00 PM</t>
         </is>
       </c>
-      <c r="K31" s="3" t="n">
+      <c r="K31" t="n">
         <v>9.66</v>
       </c>
-      <c r="L31" s="3" t="n">
+      <c r="L31" t="n">
         <v>8.51</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" t="n">
         <v>7</v>
       </c>
-      <c r="N31" s="3" t="n">
+      <c r="N31" t="n">
         <v>4.64</v>
       </c>
-      <c r="O31" s="3" t="n">
+      <c r="O31" t="n">
         <v>7.9725</v>
       </c>
-      <c r="P31" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q31" s="3" t="n">
+      <c r="P31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q31" t="n">
         <v>0.0547</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" t="n">
         <v>0.75</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" t="n">
         <v>11</v>
       </c>
-      <c r="B32" s="1" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>It's late, just past 10 PM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" t="n">
         <v>150</v>
       </c>
-      <c r="E32" s="1" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F32" s="1" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="H32" t="n">
         <v>4</v>
       </c>
-      <c r="I32" s="3" t="n">
+      <c r="I32" t="n">
         <v>2.5</v>
       </c>
-      <c r="J32" s="1" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>10:00 PM</t>
         </is>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" t="n">
         <v>8.43</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="L32" t="n">
         <v>3.06</v>
       </c>
-      <c r="M32" s="3" t="n">
+      <c r="M32" t="n">
         <v>7.83</v>
       </c>
-      <c r="N32" s="3" t="n">
+      <c r="N32" t="n">
         <v>9.25</v>
       </c>
-      <c r="O32" s="3" t="n">
+      <c r="O32" t="n">
         <v>6.5535</v>
       </c>
-      <c r="P32" s="2" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="Q32" s="3" t="n">
+      <c r="Q32" t="n">
         <v>0.19</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" t="n">
         <v>2.603</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" t="n">
         <v>11</v>
       </c>
-      <c r="B33" s="1" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>It's late, just past 10 PM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" t="n">
         <v>150</v>
       </c>
-      <c r="E33" s="1" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F33" s="1" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H33" s="2" t="n">
+      <c r="H33" t="n">
         <v>4</v>
       </c>
-      <c r="I33" s="3" t="n">
+      <c r="I33" t="n">
         <v>2.5</v>
       </c>
-      <c r="J33" s="1" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" t="n">
         <v>8.43</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" t="n">
         <v>3.06</v>
       </c>
-      <c r="M33" s="3" t="n">
+      <c r="M33" t="n">
         <v>4.71</v>
       </c>
-      <c r="N33" s="3" t="n">
+      <c r="N33" t="n">
         <v>2.95</v>
       </c>
-      <c r="O33" s="3" t="n">
+      <c r="O33" t="n">
         <v>4.9845</v>
       </c>
-      <c r="P33" s="2" t="n">
+      <c r="P33" t="n">
         <v>2</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" t="n">
         <v>0.19</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" t="n">
         <v>2.603</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" t="n">
         <v>11</v>
       </c>
-      <c r="B34" s="1" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>It's late, just past 10 PM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" t="n">
         <v>150</v>
       </c>
-      <c r="E34" s="1" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F34" s="1" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H34" s="2" t="n">
+      <c r="H34" t="n">
         <v>4</v>
       </c>
-      <c r="I34" s="3" t="n">
+      <c r="I34" t="n">
         <v>2.5</v>
       </c>
-      <c r="J34" s="1" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" t="n">
         <v>2.9</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" t="n">
         <v>3.06</v>
       </c>
-      <c r="M34" s="3" t="n">
+      <c r="M34" t="n">
         <v>5.92</v>
       </c>
-      <c r="N34" s="3" t="n">
+      <c r="N34" t="n">
         <v>4.31</v>
       </c>
-      <c r="O34" s="3" t="n">
+      <c r="O34" t="n">
         <v>3.7715</v>
       </c>
-      <c r="P34" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q34" s="3" t="n">
+      <c r="P34" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q34" t="n">
         <v>0.8</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" t="n">
         <v>2.603</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" t="n">
         <v>12</v>
       </c>
-      <c r="B35" s="1" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>It's getting close to midnight, when should I run the washing machine?</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Greensburg, PA</t>
         </is>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" t="n">
         <v>175</v>
       </c>
-      <c r="E35" s="1" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F35" s="1" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G35" s="1" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H35" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="n">
+      <c r="H35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" t="n">
         <v>0.45</v>
       </c>
-      <c r="J35" s="1" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" t="n">
         <v>9.43</v>
       </c>
-      <c r="M35" s="3" t="n">
+      <c r="M35" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="N35" s="3" t="n">
+      <c r="N35" t="n">
         <v>9.25</v>
       </c>
-      <c r="O35" s="3" t="n">
+      <c r="O35" t="n">
         <v>9.311999999999999</v>
       </c>
-      <c r="P35" s="2" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="Q35" s="3" t="n">
+      <c r="Q35" t="n">
         <v>0.0302</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" t="n">
         <v>0.439</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" t="n">
         <v>12</v>
       </c>
-      <c r="B36" s="1" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>It's getting close to midnight, when should I run the washing machine?</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Greensburg, PA</t>
         </is>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" t="n">
         <v>175</v>
       </c>
-      <c r="E36" s="1" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F36" s="1" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G36" s="1" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H36" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I36" s="3" t="n">
+      <c r="H36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" t="n">
         <v>0.45</v>
       </c>
-      <c r="J36" s="1" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" t="n">
         <v>9.34</v>
       </c>
-      <c r="M36" s="3" t="n">
+      <c r="M36" t="n">
         <v>5.53</v>
       </c>
-      <c r="N36" s="3" t="n">
+      <c r="N36" t="n">
         <v>3.87</v>
       </c>
-      <c r="O36" s="3" t="n">
+      <c r="O36" t="n">
         <v>7.919499999999999</v>
       </c>
-      <c r="P36" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q36" s="3" t="n">
+      <c r="P36" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q36" t="n">
         <v>0.0302</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" t="n">
         <v>0.468</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" t="n">
         <v>12</v>
       </c>
-      <c r="B37" s="1" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>It's getting close to midnight, when should I run the washing machine?</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Greensburg, PA</t>
         </is>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" t="n">
         <v>175</v>
       </c>
-      <c r="E37" s="1" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F37" s="1" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H37" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I37" s="3" t="n">
+      <c r="H37" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" t="n">
         <v>0.45</v>
       </c>
-      <c r="J37" s="1" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" t="n">
         <v>9.48</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" t="n">
         <v>9.34</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" t="n">
         <v>5.92</v>
       </c>
-      <c r="N37" s="3" t="n">
+      <c r="N37" t="n">
         <v>4.64</v>
       </c>
-      <c r="O37" s="3" t="n">
+      <c r="O37" t="n">
         <v>7.992999999999999</v>
       </c>
-      <c r="P37" s="2" t="n">
+      <c r="P37" t="n">
         <v>2</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" t="n">
         <v>0.0743</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" t="n">
         <v>0.468</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" t="n">
         <v>13</v>
       </c>
-      <c r="B38" s="1" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Wilkes-Barre, PA</t>
         </is>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" t="n">
         <v>200</v>
       </c>
-      <c r="E38" s="1" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F38" s="1" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G38" s="1" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="H38" t="n">
         <v>5</v>
       </c>
-      <c r="I38" s="3" t="n">
+      <c r="I38" t="n">
         <v>2.5</v>
       </c>
-      <c r="J38" s="1" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K38" s="3" t="n">
+      <c r="K38" t="n">
         <v>6.98</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="L38" t="n">
         <v>3.06</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" t="n">
         <v>10</v>
       </c>
-      <c r="N38" s="3" t="n">
+      <c r="N38" t="n">
         <v>10</v>
       </c>
-      <c r="O38" s="3" t="n">
+      <c r="O38" t="n">
         <v>6.665</v>
       </c>
-      <c r="P38" s="2" t="n">
+      <c r="P38" t="n">
         <v>1</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" t="n">
         <v>0.35</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" t="n">
         <v>2.603</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" t="n">
         <v>13</v>
       </c>
-      <c r="B39" s="1" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Wilkes-Barre, PA</t>
         </is>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" t="n">
         <v>200</v>
       </c>
-      <c r="E39" s="1" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F39" s="1" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G39" s="1" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H39" s="2" t="n">
+      <c r="H39" t="n">
         <v>5</v>
       </c>
-      <c r="I39" s="3" t="n">
+      <c r="I39" t="n">
         <v>2.5</v>
       </c>
-      <c r="J39" s="1" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" t="n">
         <v>6.98</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="L39" t="n">
         <v>3.06</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" t="n">
         <v>8.73</v>
       </c>
-      <c r="N39" s="3" t="n">
+      <c r="N39" t="n">
         <v>8.029999999999999</v>
       </c>
-      <c r="O39" s="3" t="n">
+      <c r="O39" t="n">
         <v>6.115500000000001</v>
       </c>
-      <c r="P39" s="2" t="n">
+      <c r="P39" t="n">
         <v>2</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" t="n">
         <v>0.35</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" t="n">
         <v>2.603</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" t="n">
         <v>13</v>
       </c>
-      <c r="B40" s="1" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Wilkes-Barre, PA</t>
         </is>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D40" t="n">
         <v>200</v>
       </c>
-      <c r="E40" s="1" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F40" s="1" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G40" s="1" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H40" s="2" t="n">
+      <c r="H40" t="n">
         <v>5</v>
       </c>
-      <c r="I40" s="3" t="n">
+      <c r="I40" t="n">
         <v>2.5</v>
       </c>
-      <c r="J40" s="1" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>8:00 PM</t>
         </is>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" t="n">
         <v>7.89</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" t="n">
         <v>3.06</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" t="n">
         <v>6.11</v>
       </c>
-      <c r="N40" s="3" t="n">
+      <c r="N40" t="n">
         <v>4.64</v>
       </c>
-      <c r="O40" s="3" t="n">
+      <c r="O40" t="n">
         <v>5.356</v>
       </c>
-      <c r="P40" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q40" s="3" t="n">
+      <c r="P40" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q40" t="n">
         <v>0.25</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" t="n">
         <v>2.603</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" t="n">
         <v>14</v>
       </c>
-      <c r="B41" s="1" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>It's just after 8 AM, when should I run the dishwasher?</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Lebanon, PA</t>
         </is>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" t="n">
         <v>150</v>
       </c>
-      <c r="E41" s="1" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F41" s="1" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H41" s="2" t="n">
+      <c r="H41" t="n">
         <v>4</v>
       </c>
-      <c r="I41" s="3" t="n">
+      <c r="I41" t="n">
         <v>1.1</v>
       </c>
-      <c r="J41" s="1" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" t="n">
         <v>9.16</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" t="n">
         <v>7.35</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" t="n">
         <v>10</v>
       </c>
-      <c r="N41" s="3" t="n">
+      <c r="N41" t="n">
         <v>10</v>
       </c>
-      <c r="O41" s="3" t="n">
+      <c r="O41" t="n">
         <v>8.820499999999999</v>
       </c>
-      <c r="P41" s="2" t="n">
+      <c r="P41" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" t="n">
         <v>0.11</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" t="n">
         <v>1.145</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" t="n">
         <v>14</v>
       </c>
-      <c r="B42" s="1" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>It's just after 8 AM, when should I run the dishwasher?</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Lebanon, PA</t>
         </is>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" t="n">
         <v>150</v>
       </c>
-      <c r="E42" s="1" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F42" s="1" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="H42" t="n">
         <v>4</v>
       </c>
-      <c r="I42" s="3" t="n">
+      <c r="I42" t="n">
         <v>1.1</v>
       </c>
-      <c r="J42" s="1" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" t="n">
         <v>8.76</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="L42" t="n">
         <v>7.35</v>
       </c>
-      <c r="M42" s="3" t="n">
+      <c r="M42" t="n">
         <v>7.09</v>
       </c>
-      <c r="N42" s="3" t="n">
+      <c r="N42" t="n">
         <v>5.81</v>
       </c>
-      <c r="O42" s="3" t="n">
+      <c r="O42" t="n">
         <v>7.49</v>
       </c>
-      <c r="P42" s="2" t="n">
+      <c r="P42" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="Q42" t="n">
         <v>0.154</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" t="n">
         <v>1.145</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" t="n">
         <v>14</v>
       </c>
-      <c r="B43" s="1" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>It's just after 8 AM, when should I run the dishwasher?</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Lebanon, PA</t>
         </is>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="D43" t="n">
         <v>150</v>
       </c>
-      <c r="E43" s="1" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F43" s="1" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G43" s="1" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H43" s="2" t="n">
+      <c r="H43" t="n">
         <v>4</v>
       </c>
-      <c r="I43" s="3" t="n">
+      <c r="I43" t="n">
         <v>1.1</v>
       </c>
-      <c r="J43" s="1" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>8:00 PM</t>
         </is>
       </c>
-      <c r="K43" s="3" t="n">
+      <c r="K43" t="n">
         <v>9.16</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="L43" t="n">
         <v>7.35</v>
       </c>
-      <c r="M43" s="3" t="n">
+      <c r="M43" t="n">
         <v>4.78</v>
       </c>
-      <c r="N43" s="3" t="n">
+      <c r="N43" t="n">
         <v>4.64</v>
       </c>
-      <c r="O43" s="3" t="n">
+      <c r="O43" t="n">
         <v>6.972499999999999</v>
       </c>
-      <c r="P43" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="3" t="n">
+      <c r="P43" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q43" t="n">
         <v>0.11</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" t="n">
         <v>1.145</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" t="n">
         <v>15</v>
       </c>
-      <c r="B44" s="1" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>It's around 2 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Allentown, PA</t>
         </is>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="D44" t="n">
         <v>120</v>
       </c>
-      <c r="E44" s="1" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F44" s="1" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G44" s="1" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H44" s="2" t="n">
+      <c r="H44" t="n">
         <v>6</v>
       </c>
-      <c r="I44" s="3" t="n">
+      <c r="I44" t="n">
         <v>0.38</v>
       </c>
-      <c r="J44" s="1" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>2:00 AM</t>
         </is>
       </c>
-      <c r="K44" s="3" t="n">
+      <c r="K44" t="n">
         <v>9.81</v>
       </c>
-      <c r="L44" s="3" t="n">
+      <c r="L44" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="M44" s="3" t="n">
+      <c r="M44" t="n">
         <v>7.83</v>
       </c>
-      <c r="N44" s="3" t="n">
+      <c r="N44" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="O44" s="3" t="n">
+      <c r="O44" t="n">
         <v>9.147</v>
       </c>
-      <c r="P44" s="2" t="n">
+      <c r="P44" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" s="3" t="n">
+      <c r="Q44" t="n">
         <v>0.038</v>
       </c>
-      <c r="R44" s="3" t="n">
+      <c r="R44" t="n">
         <v>0.371</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" t="n">
         <v>15</v>
       </c>
-      <c r="B45" s="1" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>It's around 2 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Allentown, PA</t>
         </is>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="D45" t="n">
         <v>120</v>
       </c>
-      <c r="E45" s="1" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F45" s="1" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G45" s="1" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H45" s="2" t="n">
+      <c r="H45" t="n">
         <v>6</v>
       </c>
-      <c r="I45" s="3" t="n">
+      <c r="I45" t="n">
         <v>0.38</v>
       </c>
-      <c r="J45" s="1" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" t="n">
         <v>9.81</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" t="n">
         <v>9.550000000000001</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" t="n">
         <v>5.23</v>
       </c>
-      <c r="N45" s="3" t="n">
+      <c r="N45" t="n">
         <v>4.64</v>
       </c>
-      <c r="O45" s="3" t="n">
+      <c r="O45" t="n">
         <v>8.027500000000002</v>
       </c>
-      <c r="P45" s="2" t="n">
+      <c r="P45" t="n">
         <v>2</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" t="n">
         <v>0.038</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" t="n">
         <v>0.396</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" t="n">
         <v>15</v>
       </c>
-      <c r="B46" s="1" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>It's around 2 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Allentown, PA</t>
         </is>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="D46" t="n">
         <v>120</v>
       </c>
-      <c r="E46" s="1" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F46" s="1" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G46" s="1" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H46" s="2" t="n">
+      <c r="H46" t="n">
         <v>6</v>
       </c>
-      <c r="I46" s="3" t="n">
+      <c r="I46" t="n">
         <v>0.38</v>
       </c>
-      <c r="J46" s="1" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K46" s="3" t="n">
+      <c r="K46" t="n">
         <v>9.67</v>
       </c>
-      <c r="L46" s="3" t="n">
+      <c r="L46" t="n">
         <v>9.550000000000001</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" t="n">
         <v>3.94</v>
       </c>
-      <c r="N46" s="3" t="n">
+      <c r="N46" t="n">
         <v>2.03</v>
       </c>
-      <c r="O46" s="3" t="n">
+      <c r="O46" t="n">
         <v>7.336</v>
       </c>
-      <c r="P46" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q46" s="3" t="n">
+      <c r="P46" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q46" t="n">
         <v>0.0532</v>
       </c>
-      <c r="R46" s="3" t="n">
+      <c r="R46" t="n">
         <v>0.396</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" t="n">
         <v>16</v>
       </c>
-      <c r="B47" s="1" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>It's late morning, just before noon and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Easton, PA</t>
         </is>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="D47" t="n">
         <v>190</v>
       </c>
-      <c r="E47" s="1" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F47" s="1" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G47" s="1" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H47" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="n">
+      <c r="H47" t="n">
+        <v>3</v>
+      </c>
+      <c r="I47" t="n">
         <v>2.5</v>
       </c>
-      <c r="J47" s="1" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="K47" s="3" t="n">
+      <c r="K47" t="n">
         <v>8.34</v>
       </c>
-      <c r="L47" s="3" t="n">
+      <c r="L47" t="n">
         <v>3.06</v>
       </c>
-      <c r="M47" s="3" t="n">
+      <c r="M47" t="n">
         <v>10</v>
       </c>
-      <c r="N47" s="3" t="n">
+      <c r="N47" t="n">
         <v>10</v>
       </c>
-      <c r="O47" s="3" t="n">
+      <c r="O47" t="n">
         <v>7.073</v>
       </c>
-      <c r="P47" s="2" t="n">
+      <c r="P47" t="n">
         <v>1</v>
       </c>
-      <c r="Q47" s="3" t="n">
+      <c r="Q47" t="n">
         <v>0.2</v>
       </c>
-      <c r="R47" s="3" t="n">
+      <c r="R47" t="n">
         <v>2.603</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" t="n">
         <v>16</v>
       </c>
-      <c r="B48" s="1" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>It's late morning, just before noon and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Easton, PA</t>
         </is>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="D48" t="n">
         <v>190</v>
       </c>
-      <c r="E48" s="1" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F48" s="1" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G48" s="1" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H48" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="n">
+      <c r="H48" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" t="n">
         <v>2.5</v>
       </c>
-      <c r="J48" s="1" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K48" s="3" t="n">
+      <c r="K48" t="n">
         <v>5.17</v>
       </c>
-      <c r="L48" s="3" t="n">
+      <c r="L48" t="n">
         <v>3.06</v>
       </c>
-      <c r="M48" s="3" t="n">
+      <c r="M48" t="n">
         <v>7.81</v>
       </c>
-      <c r="N48" s="3" t="n">
+      <c r="N48" t="n">
         <v>6.66</v>
       </c>
-      <c r="O48" s="3" t="n">
+      <c r="O48" t="n">
         <v>5.183</v>
       </c>
-      <c r="P48" s="2" t="n">
+      <c r="P48" t="n">
         <v>2</v>
       </c>
-      <c r="Q48" s="3" t="n">
+      <c r="Q48" t="n">
         <v>0.55</v>
       </c>
-      <c r="R48" s="3" t="n">
+      <c r="R48" t="n">
         <v>2.603</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" t="n">
         <v>16</v>
       </c>
-      <c r="B49" s="1" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>It's late morning, just before noon and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Easton, PA</t>
         </is>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="D49" t="n">
         <v>190</v>
       </c>
-      <c r="E49" s="1" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F49" s="1" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G49" s="1" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H49" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="n">
+      <c r="H49" t="n">
+        <v>3</v>
+      </c>
+      <c r="I49" t="n">
         <v>2.5</v>
       </c>
-      <c r="J49" s="1" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>12:00 AM</t>
         </is>
       </c>
-      <c r="K49" s="3" t="n">
+      <c r="K49" t="n">
         <v>8.34</v>
       </c>
-      <c r="L49" s="3" t="n">
+      <c r="L49" t="n">
         <v>3.54</v>
       </c>
-      <c r="M49" s="3" t="n">
+      <c r="M49" t="n">
         <v>2.86</v>
       </c>
-      <c r="N49" s="3" t="n">
+      <c r="N49" t="n">
         <v>1.51</v>
       </c>
-      <c r="O49" s="3" t="n">
+      <c r="O49" t="n">
         <v>4.539499999999999</v>
       </c>
-      <c r="P49" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q49" s="3" t="n">
+      <c r="P49" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q49" t="n">
         <v>0.2</v>
       </c>
-      <c r="R49" s="3" t="n">
+      <c r="R49" t="n">
         <v>2.44</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" t="n">
         <v>17</v>
       </c>
-      <c r="B50" s="1" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>It's around 10 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Chambersburg, PA</t>
         </is>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="D50" t="n">
         <v>165</v>
       </c>
-      <c r="E50" s="1" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F50" s="1" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G50" s="1" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H50" s="2" t="n">
+      <c r="H50" t="n">
         <v>2</v>
       </c>
-      <c r="I50" s="3" t="n">
+      <c r="I50" t="n">
         <v>0.32</v>
       </c>
-      <c r="J50" s="1" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="K50" s="3" t="n">
+      <c r="K50" t="n">
         <v>9.92</v>
       </c>
-      <c r="L50" s="3" t="n">
+      <c r="L50" t="n">
         <v>9.74</v>
       </c>
-      <c r="M50" s="3" t="n">
+      <c r="M50" t="n">
         <v>10</v>
       </c>
-      <c r="N50" s="3" t="n">
+      <c r="N50" t="n">
         <v>10</v>
       </c>
-      <c r="O50" s="3" t="n">
+      <c r="O50" t="n">
         <v>9.885</v>
       </c>
-      <c r="P50" s="2" t="n">
+      <c r="P50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" s="3" t="n">
+      <c r="Q50" t="n">
         <v>0.0256</v>
       </c>
-      <c r="R50" s="3" t="n">
+      <c r="R50" t="n">
         <v>0.333</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" t="n">
         <v>17</v>
       </c>
-      <c r="B51" s="1" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>It's around 10 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Chambersburg, PA</t>
         </is>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="D51" t="n">
         <v>165</v>
       </c>
-      <c r="E51" s="1" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F51" s="1" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G51" s="1" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H51" s="2" t="n">
+      <c r="H51" t="n">
         <v>2</v>
       </c>
-      <c r="I51" s="3" t="n">
+      <c r="I51" t="n">
         <v>0.32</v>
       </c>
-      <c r="J51" s="1" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="K51" s="3" t="n">
+      <c r="K51" t="n">
         <v>9.52</v>
       </c>
-      <c r="L51" s="3" t="n">
+      <c r="L51" t="n">
         <v>9.74</v>
       </c>
-      <c r="M51" s="3" t="n">
+      <c r="M51" t="n">
         <v>7.43</v>
       </c>
-      <c r="N51" s="3" t="n">
+      <c r="N51" t="n">
         <v>6.21</v>
       </c>
-      <c r="O51" s="3" t="n">
+      <c r="O51" t="n">
         <v>8.682499999999999</v>
       </c>
-      <c r="P51" s="2" t="n">
+      <c r="P51" t="n">
         <v>2</v>
       </c>
-      <c r="Q51" s="3" t="n">
+      <c r="Q51" t="n">
         <v>0.0704</v>
       </c>
-      <c r="R51" s="3" t="n">
+      <c r="R51" t="n">
         <v>0.333</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" t="n">
         <v>17</v>
       </c>
-      <c r="B52" s="1" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>It's around 10 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Chambersburg, PA</t>
         </is>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="D52" t="n">
         <v>165</v>
       </c>
-      <c r="E52" s="1" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F52" s="1" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G52" s="1" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H52" s="2" t="n">
+      <c r="H52" t="n">
         <v>2</v>
       </c>
-      <c r="I52" s="3" t="n">
+      <c r="I52" t="n">
         <v>0.32</v>
       </c>
-      <c r="J52" s="1" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>10:00 PM</t>
         </is>
       </c>
-      <c r="K52" s="3" t="n">
+      <c r="K52" t="n">
         <v>9.92</v>
       </c>
-      <c r="L52" s="3" t="n">
+      <c r="L52" t="n">
         <v>9.74</v>
       </c>
-      <c r="M52" s="3" t="n">
+      <c r="M52" t="n">
         <v>1.53</v>
       </c>
-      <c r="N52" s="3" t="n">
+      <c r="N52" t="n">
         <v>2.2</v>
       </c>
-      <c r="O52" s="3" t="n">
+      <c r="O52" t="n">
         <v>7.021</v>
       </c>
-      <c r="P52" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q52" s="3" t="n">
+      <c r="P52" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q52" t="n">
         <v>0.0256</v>
       </c>
-      <c r="R52" s="3" t="n">
+      <c r="R52" t="n">
         <v>0.333</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" t="n">
         <v>18</v>
       </c>
-      <c r="B53" s="1" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>It's around 3 in the afternoon and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="D53" t="n">
         <v>140</v>
       </c>
-      <c r="E53" s="1" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F53" s="1" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G53" s="1" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H53" s="2" t="n">
+      <c r="H53" t="n">
         <v>1</v>
       </c>
-      <c r="I53" s="3" t="n">
+      <c r="I53" t="n">
         <v>0.15</v>
       </c>
-      <c r="J53" s="1" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K53" s="3" t="n">
+      <c r="K53" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="L53" s="3" t="n">
+      <c r="L53" t="n">
         <v>10</v>
       </c>
-      <c r="M53" s="3" t="n">
+      <c r="M53" t="n">
         <v>10</v>
       </c>
-      <c r="N53" s="3" t="n">
+      <c r="N53" t="n">
         <v>10</v>
       </c>
-      <c r="O53" s="3" t="n">
+      <c r="O53" t="n">
         <v>9.916</v>
       </c>
-      <c r="P53" s="2" t="n">
+      <c r="P53" t="n">
         <v>1</v>
       </c>
-      <c r="Q53" s="3" t="n">
+      <c r="Q53" t="n">
         <v>0.048</v>
       </c>
-      <c r="R53" s="3" t="n">
+      <c r="R53" t="n">
         <v>0.156</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" t="n">
         <v>18</v>
       </c>
-      <c r="B54" s="1" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>It's around 3 in the afternoon and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="D54" t="n">
         <v>140</v>
       </c>
-      <c r="E54" s="1" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F54" s="1" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G54" s="1" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H54" s="2" t="n">
+      <c r="H54" t="n">
         <v>1</v>
       </c>
-      <c r="I54" s="3" t="n">
+      <c r="I54" t="n">
         <v>0.15</v>
       </c>
-      <c r="J54" s="1" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K54" s="3" t="n">
+      <c r="K54" t="n">
         <v>10</v>
       </c>
-      <c r="L54" s="3" t="n">
+      <c r="L54" t="n">
         <v>10</v>
       </c>
-      <c r="M54" s="3" t="n">
+      <c r="M54" t="n">
         <v>7.43</v>
       </c>
-      <c r="N54" s="3" t="n">
+      <c r="N54" t="n">
         <v>6.21</v>
       </c>
-      <c r="O54" s="3" t="n">
+      <c r="O54" t="n">
         <v>8.9175</v>
       </c>
-      <c r="P54" s="2" t="n">
+      <c r="P54" t="n">
         <v>2</v>
       </c>
-      <c r="Q54" s="3" t="n">
+      <c r="Q54" t="n">
         <v>0.0114</v>
       </c>
-      <c r="R54" s="3" t="n">
+      <c r="R54" t="n">
         <v>0.156</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" t="n">
         <v>18</v>
       </c>
-      <c r="B55" s="1" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>It's around 3 in the afternoon and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="D55" t="n">
         <v>140</v>
       </c>
-      <c r="E55" s="1" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F55" s="1" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G55" s="1" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H55" s="2" t="n">
+      <c r="H55" t="n">
         <v>1</v>
       </c>
-      <c r="I55" s="3" t="n">
+      <c r="I55" t="n">
         <v>0.15</v>
       </c>
-      <c r="J55" s="1" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K55" s="3" t="n">
+      <c r="K55" t="n">
         <v>10</v>
       </c>
-      <c r="L55" s="3" t="n">
+      <c r="L55" t="n">
         <v>10</v>
       </c>
-      <c r="M55" s="3" t="n">
+      <c r="M55" t="n">
         <v>3.59</v>
       </c>
-      <c r="N55" s="3" t="n">
+      <c r="N55" t="n">
         <v>4.08</v>
       </c>
-      <c r="O55" s="3" t="n">
+      <c r="O55" t="n">
         <v>7.83</v>
       </c>
-      <c r="P55" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q55" s="3" t="n">
+      <c r="P55" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q55" t="n">
         <v>0.0114</v>
       </c>
-      <c r="R55" s="3" t="n">
+      <c r="R55" t="n">
         <v>0.146</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" t="n">
         <v>19</v>
       </c>
-      <c r="B56" s="1" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>It's just past midnight and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="D56" t="n">
         <v>180</v>
       </c>
-      <c r="E56" s="1" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F56" s="1" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G56" s="1" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H56" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I56" s="3" t="n">
+      <c r="H56" t="n">
+        <v>3</v>
+      </c>
+      <c r="I56" t="n">
         <v>2.5</v>
       </c>
-      <c r="J56" s="1" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>12:00 AM</t>
         </is>
       </c>
-      <c r="K56" s="3" t="n">
+      <c r="K56" t="n">
         <v>7.04</v>
       </c>
-      <c r="L56" s="3" t="n">
+      <c r="L56" t="n">
         <v>3.54</v>
       </c>
-      <c r="M56" s="3" t="n">
+      <c r="M56" t="n">
         <v>7.83</v>
       </c>
-      <c r="N56" s="3" t="n">
+      <c r="N56" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="O56" s="3" t="n">
+      <c r="O56" t="n">
         <v>6.1845</v>
       </c>
-      <c r="P56" s="2" t="n">
+      <c r="P56" t="n">
         <v>1</v>
       </c>
-      <c r="Q56" s="3" t="n">
+      <c r="Q56" t="n">
         <v>0.3438</v>
       </c>
-      <c r="R56" s="3" t="n">
+      <c r="R56" t="n">
         <v>2.44</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" t="n">
         <v>19</v>
       </c>
-      <c r="B57" s="1" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>It's just past midnight and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="D57" t="n">
         <v>180</v>
       </c>
-      <c r="E57" s="1" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F57" s="1" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G57" s="1" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H57" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="n">
+      <c r="H57" t="n">
+        <v>3</v>
+      </c>
+      <c r="I57" t="n">
         <v>2.5</v>
       </c>
-      <c r="J57" s="1" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K57" s="3" t="n">
+      <c r="K57" t="n">
         <v>7.04</v>
       </c>
-      <c r="L57" s="3" t="n">
+      <c r="L57" t="n">
         <v>3.06</v>
       </c>
-      <c r="M57" s="3" t="n">
+      <c r="M57" t="n">
         <v>5.53</v>
       </c>
-      <c r="N57" s="3" t="n">
+      <c r="N57" t="n">
         <v>3.87</v>
       </c>
-      <c r="O57" s="3" t="n">
+      <c r="O57" t="n">
         <v>4.869499999999999</v>
       </c>
-      <c r="P57" s="2" t="n">
+      <c r="P57" t="n">
         <v>2</v>
       </c>
-      <c r="Q57" s="3" t="n">
+      <c r="Q57" t="n">
         <v>0.3438</v>
       </c>
-      <c r="R57" s="3" t="n">
+      <c r="R57" t="n">
         <v>2.603</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" t="n">
         <v>19</v>
       </c>
-      <c r="B58" s="1" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>It's just past midnight and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="D58" t="n">
         <v>180</v>
       </c>
-      <c r="E58" s="1" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F58" s="1" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G58" s="1" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H58" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="n">
+      <c r="H58" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" t="n">
         <v>2.5</v>
       </c>
-      <c r="J58" s="1" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K58" s="3" t="n">
+      <c r="K58" t="n">
         <v>7.04</v>
       </c>
-      <c r="L58" s="3" t="n">
+      <c r="L58" t="n">
         <v>3.06</v>
       </c>
-      <c r="M58" s="3" t="n">
+      <c r="M58" t="n">
         <v>5.13</v>
       </c>
-      <c r="N58" s="3" t="n">
+      <c r="N58" t="n">
         <v>3.42</v>
       </c>
-      <c r="O58" s="3" t="n">
+      <c r="O58" t="n">
         <v>4.722</v>
       </c>
-      <c r="P58" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3" t="n">
+      <c r="P58" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q58" t="n">
         <v>0.3438</v>
       </c>
-      <c r="R58" s="3" t="n">
+      <c r="R58" t="n">
         <v>2.603</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" t="n">
         <v>20</v>
       </c>
-      <c r="B59" s="1" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>It's nearly 11 at night, when should I run the washing machine?</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Altoona, PA</t>
         </is>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="D59" t="n">
         <v>155</v>
       </c>
-      <c r="E59" s="1" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F59" s="1" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G59" s="1" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H59" s="2" t="n">
+      <c r="H59" t="n">
         <v>4</v>
       </c>
-      <c r="I59" s="3" t="n">
+      <c r="I59" t="n">
         <v>0.42</v>
       </c>
-      <c r="J59" s="1" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K59" s="3" t="n">
+      <c r="K59" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="L59" s="3" t="n">
+      <c r="L59" t="n">
         <v>9.51</v>
       </c>
-      <c r="M59" s="3" t="n">
+      <c r="M59" t="n">
         <v>7.83</v>
       </c>
-      <c r="N59" s="3" t="n">
+      <c r="N59" t="n">
         <v>9.25</v>
       </c>
-      <c r="O59" s="3" t="n">
+      <c r="O59" t="n">
         <v>9.245999999999999</v>
       </c>
-      <c r="P59" s="2" t="n">
+      <c r="P59" t="n">
         <v>1</v>
       </c>
-      <c r="Q59" s="3" t="n">
+      <c r="Q59" t="n">
         <v>0.0302</v>
       </c>
-      <c r="R59" s="3" t="n">
+      <c r="R59" t="n">
         <v>0.41</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" t="n">
         <v>20</v>
       </c>
-      <c r="B60" s="1" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>It's nearly 11 at night, when should I run the washing machine?</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Altoona, PA</t>
         </is>
       </c>
-      <c r="D60" s="3" t="n">
+      <c r="D60" t="n">
         <v>155</v>
       </c>
-      <c r="E60" s="1" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F60" s="1" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G60" s="1" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H60" s="2" t="n">
+      <c r="H60" t="n">
         <v>4</v>
       </c>
-      <c r="I60" s="3" t="n">
+      <c r="I60" t="n">
         <v>0.42</v>
       </c>
-      <c r="J60" s="1" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="K60" s="3" t="n">
+      <c r="K60" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="L60" s="3" t="n">
+      <c r="L60" t="n">
         <v>9.43</v>
       </c>
-      <c r="M60" s="3" t="n">
+      <c r="M60" t="n">
         <v>4.71</v>
       </c>
-      <c r="N60" s="3" t="n">
+      <c r="N60" t="n">
         <v>2.95</v>
       </c>
-      <c r="O60" s="3" t="n">
+      <c r="O60" t="n">
         <v>7.649</v>
       </c>
-      <c r="P60" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="3" t="n">
+      <c r="P60" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q60" t="n">
         <v>0.0302</v>
       </c>
-      <c r="R60" s="3" t="n">
+      <c r="R60" t="n">
         <v>0.437</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" t="n">
         <v>20</v>
       </c>
-      <c r="B61" s="1" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>It's nearly 11 at night, when should I run the washing machine?</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Altoona, PA</t>
         </is>
       </c>
-      <c r="D61" s="3" t="n">
+      <c r="D61" t="n">
         <v>155</v>
       </c>
-      <c r="E61" s="1" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F61" s="1" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G61" s="1" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Apartment</t>
         </is>
       </c>
-      <c r="H61" s="2" t="n">
+      <c r="H61" t="n">
         <v>4</v>
       </c>
-      <c r="I61" s="3" t="n">
+      <c r="I61" t="n">
         <v>0.42</v>
       </c>
-      <c r="J61" s="1" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K61" s="3" t="n">
+      <c r="K61" t="n">
         <v>9.449999999999999</v>
       </c>
-      <c r="L61" s="3" t="n">
+      <c r="L61" t="n">
         <v>9.43</v>
       </c>
-      <c r="M61" s="3" t="n">
+      <c r="M61" t="n">
         <v>5.92</v>
       </c>
-      <c r="N61" s="3" t="n">
+      <c r="N61" t="n">
         <v>4.64</v>
       </c>
-      <c r="O61" s="3" t="n">
+      <c r="O61" t="n">
         <v>8.015499999999999</v>
       </c>
-      <c r="P61" s="2" t="n">
+      <c r="P61" t="n">
         <v>2</v>
       </c>
-      <c r="Q61" s="3" t="n">
+      <c r="Q61" t="n">
         <v>0.07770000000000001</v>
       </c>
-      <c r="R61" s="3" t="n">
+      <c r="R61" t="n">
         <v>0.437</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" t="n">
         <v>21</v>
       </c>
-      <c r="B62" s="1" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>It's barely 5 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>King of Prussia, PA</t>
         </is>
       </c>
-      <c r="D62" s="3" t="n">
+      <c r="D62" t="n">
         <v>165</v>
       </c>
-      <c r="E62" s="1" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F62" s="1" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G62" s="1" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H62" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="n">
+      <c r="H62" t="n">
+        <v>3</v>
+      </c>
+      <c r="I62" t="n">
         <v>1.2</v>
       </c>
-      <c r="J62" s="1" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>5:00 AM</t>
         </is>
       </c>
-      <c r="K62" s="3" t="n">
+      <c r="K62" t="n">
         <v>9.33</v>
       </c>
-      <c r="L62" s="3" t="n">
+      <c r="L62" t="n">
         <v>7.27</v>
       </c>
-      <c r="M62" s="3" t="n">
+      <c r="M62" t="n">
         <v>10</v>
       </c>
-      <c r="N62" s="3" t="n">
+      <c r="N62" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="O62" s="3" t="n">
+      <c r="O62" t="n">
         <v>8.610999999999999</v>
       </c>
-      <c r="P62" s="2" t="n">
+      <c r="P62" t="n">
         <v>1</v>
       </c>
-      <c r="Q62" s="3" t="n">
+      <c r="Q62" t="n">
         <v>0.0912</v>
       </c>
-      <c r="R62" s="3" t="n">
+      <c r="R62" t="n">
         <v>1.171</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" t="n">
         <v>21</v>
       </c>
-      <c r="B63" s="1" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>It's barely 5 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>King of Prussia, PA</t>
         </is>
       </c>
-      <c r="D63" s="3" t="n">
+      <c r="D63" t="n">
         <v>165</v>
       </c>
-      <c r="E63" s="1" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F63" s="1" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G63" s="1" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H63" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I63" s="3" t="n">
+      <c r="H63" t="n">
+        <v>3</v>
+      </c>
+      <c r="I63" t="n">
         <v>1.2</v>
       </c>
-      <c r="J63" s="1" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K63" s="3" t="n">
+      <c r="K63" t="n">
         <v>9.33</v>
       </c>
-      <c r="L63" s="3" t="n">
+      <c r="L63" t="n">
         <v>7.04</v>
       </c>
-      <c r="M63" s="3" t="n">
+      <c r="M63" t="n">
         <v>8.02</v>
       </c>
-      <c r="N63" s="3" t="n">
+      <c r="N63" t="n">
         <v>6.91</v>
       </c>
-      <c r="O63" s="3" t="n">
+      <c r="O63" t="n">
         <v>7.9035</v>
       </c>
-      <c r="P63" s="2" t="n">
+      <c r="P63" t="n">
         <v>2</v>
       </c>
-      <c r="Q63" s="3" t="n">
+      <c r="Q63" t="n">
         <v>0.0912</v>
       </c>
-      <c r="R63" s="3" t="n">
+      <c r="R63" t="n">
         <v>1.249</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" t="n">
         <v>21</v>
       </c>
-      <c r="B64" s="1" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>It's barely 5 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>King of Prussia, PA</t>
         </is>
       </c>
-      <c r="D64" s="3" t="n">
+      <c r="D64" t="n">
         <v>165</v>
       </c>
-      <c r="E64" s="1" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F64" s="1" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G64" s="1" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H64" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I64" s="3" t="n">
+      <c r="H64" t="n">
+        <v>3</v>
+      </c>
+      <c r="I64" t="n">
         <v>1.2</v>
       </c>
-      <c r="J64" s="1" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>7:00 PM</t>
         </is>
       </c>
-      <c r="K64" s="3" t="n">
+      <c r="K64" t="n">
         <v>9.33</v>
       </c>
-      <c r="L64" s="3" t="n">
+      <c r="L64" t="n">
         <v>7.04</v>
       </c>
-      <c r="M64" s="3" t="n">
+      <c r="M64" t="n">
         <v>5.26</v>
       </c>
-      <c r="N64" s="3" t="n">
+      <c r="N64" t="n">
         <v>4.64</v>
       </c>
-      <c r="O64" s="3" t="n">
+      <c r="O64" t="n">
         <v>7.010999999999999</v>
       </c>
-      <c r="P64" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q64" s="3" t="n">
+      <c r="P64" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q64" t="n">
         <v>0.0912</v>
       </c>
-      <c r="R64" s="3" t="n">
+      <c r="R64" t="n">
         <v>1.249</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" t="n">
         <v>22</v>
       </c>
-      <c r="B65" s="1" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>It's late afternoon, just past 3, when should I run the dishwasher?</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Greensburg, PA</t>
         </is>
       </c>
-      <c r="D65" s="3" t="n">
+      <c r="D65" t="n">
         <v>180</v>
       </c>
-      <c r="E65" s="1" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F65" s="1" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G65" s="1" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H65" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I65" s="3" t="n">
+      <c r="H65" t="n">
+        <v>3</v>
+      </c>
+      <c r="I65" t="n">
         <v>1.05</v>
       </c>
-      <c r="J65" s="1" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K65" s="3" t="n">
+      <c r="K65" t="n">
         <v>8.58</v>
       </c>
-      <c r="L65" s="3" t="n">
+      <c r="L65" t="n">
         <v>7.5</v>
       </c>
-      <c r="M65" s="3" t="n">
+      <c r="M65" t="n">
         <v>10</v>
       </c>
-      <c r="N65" s="3" t="n">
+      <c r="N65" t="n">
         <v>10</v>
       </c>
-      <c r="O65" s="3" t="n">
+      <c r="O65" t="n">
         <v>8.699</v>
       </c>
-      <c r="P65" s="2" t="n">
+      <c r="P65" t="n">
         <v>1</v>
       </c>
-      <c r="Q65" s="3" t="n">
+      <c r="Q65" t="n">
         <v>0.1733</v>
       </c>
-      <c r="R65" s="3" t="n">
+      <c r="R65" t="n">
         <v>1.093</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" t="n">
         <v>22</v>
       </c>
-      <c r="B66" s="1" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>It's late afternoon, just past 3, when should I run the dishwasher?</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Greensburg, PA</t>
         </is>
       </c>
-      <c r="D66" s="3" t="n">
+      <c r="D66" t="n">
         <v>180</v>
       </c>
-      <c r="E66" s="1" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F66" s="1" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G66" s="1" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H66" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="n">
+      <c r="H66" t="n">
+        <v>3</v>
+      </c>
+      <c r="I66" t="n">
         <v>1.05</v>
       </c>
-      <c r="J66" s="1" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>9:00 PM</t>
         </is>
       </c>
-      <c r="K66" s="3" t="n">
+      <c r="K66" t="n">
         <v>9.52</v>
       </c>
-      <c r="L66" s="3" t="n">
+      <c r="L66" t="n">
         <v>7.5</v>
       </c>
-      <c r="M66" s="3" t="n">
+      <c r="M66" t="n">
         <v>7.09</v>
       </c>
-      <c r="N66" s="3" t="n">
+      <c r="N66" t="n">
         <v>5.81</v>
       </c>
-      <c r="O66" s="3" t="n">
+      <c r="O66" t="n">
         <v>7.7705</v>
       </c>
-      <c r="P66" s="2" t="n">
+      <c r="P66" t="n">
         <v>2</v>
       </c>
-      <c r="Q66" s="3" t="n">
+      <c r="Q66" t="n">
         <v>0.0704</v>
       </c>
-      <c r="R66" s="3" t="n">
+      <c r="R66" t="n">
         <v>1.093</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" t="n">
         <v>22</v>
       </c>
-      <c r="B67" s="1" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>It's late afternoon, just past 3, when should I run the dishwasher?</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Greensburg, PA</t>
         </is>
       </c>
-      <c r="D67" s="3" t="n">
+      <c r="D67" t="n">
         <v>180</v>
       </c>
-      <c r="E67" s="1" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F67" s="1" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G67" s="1" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H67" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I67" s="3" t="n">
+      <c r="H67" t="n">
+        <v>3</v>
+      </c>
+      <c r="I67" t="n">
         <v>1.05</v>
       </c>
-      <c r="J67" s="1" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K67" s="3" t="n">
+      <c r="K67" t="n">
         <v>9.52</v>
       </c>
-      <c r="L67" s="3" t="n">
+      <c r="L67" t="n">
         <v>7.7</v>
       </c>
-      <c r="M67" s="3" t="n">
+      <c r="M67" t="n">
         <v>6.17</v>
       </c>
-      <c r="N67" s="3" t="n">
+      <c r="N67" t="n">
         <v>3.44</v>
       </c>
-      <c r="O67" s="3" t="n">
+      <c r="O67" t="n">
         <v>7.301</v>
       </c>
-      <c r="P67" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q67" s="3" t="n">
+      <c r="P67" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q67" t="n">
         <v>0.0704</v>
       </c>
-      <c r="R67" s="3" t="n">
+      <c r="R67" t="n">
         <v>1.025</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" t="n">
         <v>23</v>
       </c>
-      <c r="B68" s="1" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>It's around 8 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D68" s="3" t="n">
+      <c r="D68" t="n">
         <v>185</v>
       </c>
-      <c r="E68" s="1" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F68" s="1" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="G68" s="1" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H68" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I68" s="3" t="n">
+      <c r="H68" t="n">
+        <v>3</v>
+      </c>
+      <c r="I68" t="n">
         <v>1.85</v>
       </c>
-      <c r="J68" s="1" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="K68" s="3" t="n">
+      <c r="K68" t="n">
         <v>7.85</v>
       </c>
-      <c r="L68" s="3" t="n">
+      <c r="L68" t="n">
         <v>5.05</v>
       </c>
-      <c r="M68" s="3" t="n">
+      <c r="M68" t="n">
         <v>10</v>
       </c>
-      <c r="N68" s="3" t="n">
+      <c r="N68" t="n">
         <v>10</v>
       </c>
-      <c r="O68" s="3" t="n">
+      <c r="O68" t="n">
         <v>7.6225</v>
       </c>
-      <c r="P68" s="2" t="n">
+      <c r="P68" t="n">
         <v>1</v>
       </c>
-      <c r="Q68" s="3" t="n">
+      <c r="Q68" t="n">
         <v>0.2544</v>
       </c>
-      <c r="R68" s="3" t="n">
+      <c r="R68" t="n">
         <v>1.926</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" t="n">
         <v>23</v>
       </c>
-      <c r="B69" s="1" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>It's around 8 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D69" s="3" t="n">
+      <c r="D69" t="n">
         <v>185</v>
       </c>
-      <c r="E69" s="1" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F69" s="1" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="G69" s="1" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H69" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I69" s="3" t="n">
+      <c r="H69" t="n">
+        <v>3</v>
+      </c>
+      <c r="I69" t="n">
         <v>1.85</v>
       </c>
-      <c r="J69" s="1" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K69" s="3" t="n">
+      <c r="K69" t="n">
         <v>7.85</v>
       </c>
-      <c r="L69" s="3" t="n">
+      <c r="L69" t="n">
         <v>5.05</v>
       </c>
-      <c r="M69" s="3" t="n">
+      <c r="M69" t="n">
         <v>7.09</v>
       </c>
-      <c r="N69" s="3" t="n">
+      <c r="N69" t="n">
         <v>5.81</v>
       </c>
-      <c r="O69" s="3" t="n">
+      <c r="O69" t="n">
         <v>6.412</v>
       </c>
-      <c r="P69" s="2" t="n">
+      <c r="P69" t="n">
         <v>2</v>
       </c>
-      <c r="Q69" s="3" t="n">
+      <c r="Q69" t="n">
         <v>0.2544</v>
       </c>
-      <c r="R69" s="3" t="n">
+      <c r="R69" t="n">
         <v>1.926</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" t="n">
         <v>23</v>
       </c>
-      <c r="B70" s="1" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>It's around 8 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Pittsburgh, PA</t>
         </is>
       </c>
-      <c r="D70" s="3" t="n">
+      <c r="D70" t="n">
         <v>185</v>
       </c>
-      <c r="E70" s="1" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F70" s="1" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="G70" s="1" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H70" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I70" s="3" t="n">
+      <c r="H70" t="n">
+        <v>3</v>
+      </c>
+      <c r="I70" t="n">
         <v>1.85</v>
       </c>
-      <c r="J70" s="1" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K70" s="3" t="n">
+      <c r="K70" t="n">
         <v>7.85</v>
       </c>
-      <c r="L70" s="3" t="n">
+      <c r="L70" t="n">
         <v>5.41</v>
       </c>
-      <c r="M70" s="3" t="n">
+      <c r="M70" t="n">
         <v>5.73</v>
       </c>
-      <c r="N70" s="3" t="n">
+      <c r="N70" t="n">
         <v>2.89</v>
       </c>
-      <c r="O70" s="3" t="n">
+      <c r="O70" t="n">
         <v>5.827999999999999</v>
       </c>
-      <c r="P70" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q70" s="3" t="n">
+      <c r="P70" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q70" t="n">
         <v>0.2544</v>
       </c>
-      <c r="R70" s="3" t="n">
+      <c r="R70" t="n">
         <v>1.806</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" t="n">
         <v>24</v>
       </c>
-      <c r="B71" s="1" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>It's around 2 in the afternoon and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Erie, PA</t>
         </is>
       </c>
-      <c r="D71" s="3" t="n">
+      <c r="D71" t="n">
         <v>215</v>
       </c>
-      <c r="E71" s="1" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F71" s="1" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="G71" s="1" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H71" s="2" t="n">
+      <c r="H71" t="n">
         <v>4</v>
       </c>
-      <c r="I71" s="3" t="n">
+      <c r="I71" t="n">
         <v>4.1</v>
       </c>
-      <c r="J71" s="1" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K71" s="3" t="n">
+      <c r="K71" t="n">
         <v>3.28</v>
       </c>
-      <c r="L71" s="3" t="n">
+      <c r="L71" t="n">
         <v>0</v>
       </c>
-      <c r="M71" s="3" t="n">
+      <c r="M71" t="n">
         <v>10</v>
       </c>
-      <c r="N71" s="3" t="n">
+      <c r="N71" t="n">
         <v>10</v>
       </c>
-      <c r="O71" s="3" t="n">
+      <c r="O71" t="n">
         <v>4.484</v>
       </c>
-      <c r="P71" s="2" t="n">
+      <c r="P71" t="n">
         <v>1</v>
       </c>
-      <c r="Q71" s="3" t="n">
+      <c r="Q71" t="n">
         <v>0.7585</v>
       </c>
-      <c r="R71" s="3" t="n">
+      <c r="R71" t="n">
         <v>4.268</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" t="n">
         <v>24</v>
       </c>
-      <c r="B72" s="1" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>It's around 2 in the afternoon and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Erie, PA</t>
         </is>
       </c>
-      <c r="D72" s="3" t="n">
+      <c r="D72" t="n">
         <v>215</v>
       </c>
-      <c r="E72" s="1" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F72" s="1" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="G72" s="1" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H72" s="2" t="n">
+      <c r="H72" t="n">
         <v>4</v>
       </c>
-      <c r="I72" s="3" t="n">
+      <c r="I72" t="n">
         <v>4.1</v>
       </c>
-      <c r="J72" s="1" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>9:00 PM</t>
         </is>
       </c>
-      <c r="K72" s="3" t="n">
+      <c r="K72" t="n">
         <v>7.48</v>
       </c>
-      <c r="L72" s="3" t="n">
+      <c r="L72" t="n">
         <v>0</v>
       </c>
-      <c r="M72" s="3" t="n">
+      <c r="M72" t="n">
         <v>6.29</v>
       </c>
-      <c r="N72" s="3" t="n">
+      <c r="N72" t="n">
         <v>4.86</v>
       </c>
-      <c r="O72" s="3" t="n">
+      <c r="O72" t="n">
         <v>4.231</v>
       </c>
-      <c r="P72" s="2" t="n">
+      <c r="P72" t="n">
         <v>2</v>
       </c>
-      <c r="Q72" s="3" t="n">
+      <c r="Q72" t="n">
         <v>0.2952</v>
       </c>
-      <c r="R72" s="3" t="n">
+      <c r="R72" t="n">
         <v>4.268</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" t="n">
         <v>24</v>
       </c>
-      <c r="B73" s="1" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>It's around 2 in the afternoon and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Erie, PA</t>
         </is>
       </c>
-      <c r="D73" s="3" t="n">
+      <c r="D73" t="n">
         <v>215</v>
       </c>
-      <c r="E73" s="1" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F73" s="1" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="G73" s="1" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H73" s="2" t="n">
+      <c r="H73" t="n">
         <v>4</v>
       </c>
-      <c r="I73" s="3" t="n">
+      <c r="I73" t="n">
         <v>4.1</v>
       </c>
-      <c r="J73" s="1" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>2:00 AM</t>
         </is>
       </c>
-      <c r="K73" s="3" t="n">
+      <c r="K73" t="n">
         <v>7.48</v>
       </c>
-      <c r="L73" s="3" t="n">
+      <c r="L73" t="n">
         <v>0</v>
       </c>
-      <c r="M73" s="3" t="n">
+      <c r="M73" t="n">
         <v>1.24</v>
       </c>
-      <c r="N73" s="3" t="n">
+      <c r="N73" t="n">
         <v>1.51</v>
       </c>
-      <c r="O73" s="3" t="n">
+      <c r="O73" t="n">
         <v>2.7185</v>
       </c>
-      <c r="P73" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q73" s="3" t="n">
+      <c r="P73" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q73" t="n">
         <v>0.2952</v>
       </c>
-      <c r="R73" s="3" t="n">
+      <c r="R73" t="n">
         <v>4.002</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" t="n">
         <v>25</v>
       </c>
-      <c r="B74" s="1" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>It's about 10 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Allentown, PA</t>
         </is>
       </c>
-      <c r="D74" s="3" t="n">
+      <c r="D74" t="n">
         <v>200</v>
       </c>
-      <c r="E74" s="1" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F74" s="1" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G74" s="1" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H74" s="2" t="n">
+      <c r="H74" t="n">
         <v>4</v>
       </c>
-      <c r="I74" s="3" t="n">
+      <c r="I74" t="n">
         <v>2.1</v>
       </c>
-      <c r="J74" s="1" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="K74" s="3" t="n">
+      <c r="K74" t="n">
         <v>8.25</v>
       </c>
-      <c r="L74" s="3" t="n">
+      <c r="L74" t="n">
         <v>4.29</v>
       </c>
-      <c r="M74" s="3" t="n">
+      <c r="M74" t="n">
         <v>10</v>
       </c>
-      <c r="N74" s="3" t="n">
+      <c r="N74" t="n">
         <v>10</v>
       </c>
-      <c r="O74" s="3" t="n">
+      <c r="O74" t="n">
         <v>7.4765</v>
       </c>
-      <c r="P74" s="2" t="n">
+      <c r="P74" t="n">
         <v>1</v>
       </c>
-      <c r="Q74" s="3" t="n">
+      <c r="Q74" t="n">
         <v>0.21</v>
       </c>
-      <c r="R74" s="3" t="n">
+      <c r="R74" t="n">
         <v>2.186</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" t="n">
         <v>25</v>
       </c>
-      <c r="B75" s="1" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>It's about 10 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Allentown, PA</t>
         </is>
       </c>
-      <c r="D75" s="3" t="n">
+      <c r="D75" t="n">
         <v>200</v>
       </c>
-      <c r="E75" s="1" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F75" s="1" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G75" s="1" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H75" s="2" t="n">
+      <c r="H75" t="n">
         <v>4</v>
       </c>
-      <c r="I75" s="3" t="n">
+      <c r="I75" t="n">
         <v>2.1</v>
       </c>
-      <c r="J75" s="1" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K75" s="3" t="n">
+      <c r="K75" t="n">
         <v>7.49</v>
       </c>
-      <c r="L75" s="3" t="n">
+      <c r="L75" t="n">
         <v>4.29</v>
       </c>
-      <c r="M75" s="3" t="n">
+      <c r="M75" t="n">
         <v>8.02</v>
       </c>
-      <c r="N75" s="3" t="n">
+      <c r="N75" t="n">
         <v>6.91</v>
       </c>
-      <c r="O75" s="3" t="n">
+      <c r="O75" t="n">
         <v>6.389</v>
       </c>
-      <c r="P75" s="2" t="n">
+      <c r="P75" t="n">
         <v>2</v>
       </c>
-      <c r="Q75" s="3" t="n">
+      <c r="Q75" t="n">
         <v>0.294</v>
       </c>
-      <c r="R75" s="3" t="n">
+      <c r="R75" t="n">
         <v>2.186</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" t="n">
         <v>25</v>
       </c>
-      <c r="B76" s="1" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>It's about 10 in the morning and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Allentown, PA</t>
         </is>
       </c>
-      <c r="D76" s="3" t="n">
+      <c r="D76" t="n">
         <v>200</v>
       </c>
-      <c r="E76" s="1" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F76" s="1" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G76" s="1" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H76" s="2" t="n">
+      <c r="H76" t="n">
         <v>4</v>
       </c>
-      <c r="I76" s="3" t="n">
+      <c r="I76" t="n">
         <v>2.1</v>
       </c>
-      <c r="J76" s="1" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K76" s="3" t="n">
+      <c r="K76" t="n">
         <v>8.25</v>
       </c>
-      <c r="L76" s="3" t="n">
+      <c r="L76" t="n">
         <v>4.69</v>
       </c>
-      <c r="M76" s="3" t="n">
+      <c r="M76" t="n">
         <v>4.78</v>
       </c>
-      <c r="N76" s="3" t="n">
+      <c r="N76" t="n">
         <v>1.71</v>
       </c>
-      <c r="O76" s="3" t="n">
+      <c r="O76" t="n">
         <v>5.329000000000001</v>
       </c>
-      <c r="P76" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="3" t="n">
+      <c r="P76" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q76" t="n">
         <v>0.21</v>
       </c>
-      <c r="R76" s="3" t="n">
+      <c r="R76" t="n">
         <v>2.05</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" t="n">
         <v>26</v>
       </c>
-      <c r="B77" s="1" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>It's just past 5 PM and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>King of Prussia, PA</t>
         </is>
       </c>
-      <c r="D77" s="3" t="n">
+      <c r="D77" t="n">
         <v>165</v>
       </c>
-      <c r="E77" s="1" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F77" s="1" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G77" s="1" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H77" s="2" t="n">
+      <c r="H77" t="n">
         <v>2</v>
       </c>
-      <c r="I77" s="3" t="n">
+      <c r="I77" t="n">
         <v>1.15</v>
       </c>
-      <c r="J77" s="1" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="K77" s="3" t="n">
+      <c r="K77" t="n">
         <v>6.82</v>
       </c>
-      <c r="L77" s="3" t="n">
+      <c r="L77" t="n">
         <v>7.2</v>
       </c>
-      <c r="M77" s="3" t="n">
+      <c r="M77" t="n">
         <v>10</v>
       </c>
-      <c r="N77" s="3" t="n">
+      <c r="N77" t="n">
         <v>10</v>
       </c>
-      <c r="O77" s="3" t="n">
+      <c r="O77" t="n">
         <v>8.065999999999999</v>
       </c>
-      <c r="P77" s="2" t="n">
+      <c r="P77" t="n">
         <v>1</v>
       </c>
-      <c r="Q77" s="3" t="n">
+      <c r="Q77" t="n">
         <v>0.368</v>
       </c>
-      <c r="R77" s="3" t="n">
+      <c r="R77" t="n">
         <v>1.197</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" t="n">
         <v>26</v>
       </c>
-      <c r="B78" s="1" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>It's just past 5 PM and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>King of Prussia, PA</t>
         </is>
       </c>
-      <c r="D78" s="3" t="n">
+      <c r="D78" t="n">
         <v>165</v>
       </c>
-      <c r="E78" s="1" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F78" s="1" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G78" s="1" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H78" s="2" t="n">
+      <c r="H78" t="n">
         <v>2</v>
       </c>
-      <c r="I78" s="3" t="n">
+      <c r="I78" t="n">
         <v>1.15</v>
       </c>
-      <c r="J78" s="1" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K78" s="3" t="n">
+      <c r="K78" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="L78" s="3" t="n">
+      <c r="L78" t="n">
         <v>7.42</v>
       </c>
-      <c r="M78" s="3" t="n">
+      <c r="M78" t="n">
         <v>7.43</v>
       </c>
-      <c r="N78" s="3" t="n">
+      <c r="N78" t="n">
         <v>5.19</v>
       </c>
-      <c r="O78" s="3" t="n">
+      <c r="O78" t="n">
         <v>7.669499999999999</v>
       </c>
-      <c r="P78" s="2" t="n">
+      <c r="P78" t="n">
         <v>2</v>
       </c>
-      <c r="Q78" s="3" t="n">
+      <c r="Q78" t="n">
         <v>0.08740000000000001</v>
       </c>
-      <c r="R78" s="3" t="n">
+      <c r="R78" t="n">
         <v>1.122</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" t="n">
         <v>26</v>
       </c>
-      <c r="B79" s="1" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>It's just past 5 PM and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>King of Prussia, PA</t>
         </is>
       </c>
-      <c r="D79" s="3" t="n">
+      <c r="D79" t="n">
         <v>165</v>
       </c>
-      <c r="E79" s="1" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F79" s="1" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G79" s="1" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H79" s="2" t="n">
+      <c r="H79" t="n">
         <v>2</v>
       </c>
-      <c r="I79" s="3" t="n">
+      <c r="I79" t="n">
         <v>1.15</v>
       </c>
-      <c r="J79" s="1" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="K79" s="3" t="n">
+      <c r="K79" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="L79" s="3" t="n">
+      <c r="L79" t="n">
         <v>7.2</v>
       </c>
-      <c r="M79" s="3" t="n">
+      <c r="M79" t="n">
         <v>6.29</v>
       </c>
-      <c r="N79" s="3" t="n">
+      <c r="N79" t="n">
         <v>4.78</v>
       </c>
-      <c r="O79" s="3" t="n">
+      <c r="O79" t="n">
         <v>7.302999999999999</v>
       </c>
-      <c r="P79" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q79" s="3" t="n">
+      <c r="P79" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q79" t="n">
         <v>0.08740000000000001</v>
       </c>
-      <c r="R79" s="3" t="n">
+      <c r="R79" t="n">
         <v>1.197</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" t="n">
         <v>27</v>
       </c>
-      <c r="B80" s="1" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>It's around 10 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Blue Bell, PA</t>
         </is>
       </c>
-      <c r="D80" s="3" t="n">
+      <c r="D80" t="n">
         <v>145</v>
       </c>
-      <c r="E80" s="1" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F80" s="1" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G80" s="1" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H80" s="2" t="n">
+      <c r="H80" t="n">
         <v>2</v>
       </c>
-      <c r="I80" s="3" t="n">
+      <c r="I80" t="n">
         <v>0.32</v>
       </c>
-      <c r="J80" s="1" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="K80" s="3" t="n">
+      <c r="K80" t="n">
         <v>9.93</v>
       </c>
-      <c r="L80" s="3" t="n">
+      <c r="L80" t="n">
         <v>9.74</v>
       </c>
-      <c r="M80" s="3" t="n">
+      <c r="M80" t="n">
         <v>10</v>
       </c>
-      <c r="N80" s="3" t="n">
+      <c r="N80" t="n">
         <v>10</v>
       </c>
-      <c r="O80" s="3" t="n">
+      <c r="O80" t="n">
         <v>9.888</v>
       </c>
-      <c r="P80" s="2" t="n">
+      <c r="P80" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" s="3" t="n">
+      <c r="Q80" t="n">
         <v>0.0243</v>
       </c>
-      <c r="R80" s="3" t="n">
+      <c r="R80" t="n">
         <v>0.333</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" t="n">
         <v>27</v>
       </c>
-      <c r="B81" s="1" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>It's around 10 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Blue Bell, PA</t>
         </is>
       </c>
-      <c r="D81" s="3" t="n">
+      <c r="D81" t="n">
         <v>145</v>
       </c>
-      <c r="E81" s="1" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F81" s="1" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G81" s="1" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H81" s="2" t="n">
+      <c r="H81" t="n">
         <v>2</v>
       </c>
-      <c r="I81" s="3" t="n">
+      <c r="I81" t="n">
         <v>0.32</v>
       </c>
-      <c r="J81" s="1" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K81" s="3" t="n">
+      <c r="K81" t="n">
         <v>9.23</v>
       </c>
-      <c r="L81" s="3" t="n">
+      <c r="L81" t="n">
         <v>9.74</v>
       </c>
-      <c r="M81" s="3" t="n">
+      <c r="M81" t="n">
         <v>7.83</v>
       </c>
-      <c r="N81" s="3" t="n">
+      <c r="N81" t="n">
         <v>6.69</v>
       </c>
-      <c r="O81" s="3" t="n">
+      <c r="O81" t="n">
         <v>8.7475</v>
       </c>
-      <c r="P81" s="2" t="n">
+      <c r="P81" t="n">
         <v>2</v>
       </c>
-      <c r="Q81" s="3" t="n">
+      <c r="Q81" t="n">
         <v>0.1024</v>
       </c>
-      <c r="R81" s="3" t="n">
+      <c r="R81" t="n">
         <v>0.333</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" t="n">
         <v>27</v>
       </c>
-      <c r="B82" s="1" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>It's around 10 in the morning and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Blue Bell, PA</t>
         </is>
       </c>
-      <c r="D82" s="3" t="n">
+      <c r="D82" t="n">
         <v>145</v>
       </c>
-      <c r="E82" s="1" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F82" s="1" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G82" s="1" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H82" s="2" t="n">
+      <c r="H82" t="n">
         <v>2</v>
       </c>
-      <c r="I82" s="3" t="n">
+      <c r="I82" t="n">
         <v>0.32</v>
       </c>
-      <c r="J82" s="1" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K82" s="3" t="n">
+      <c r="K82" t="n">
         <v>9.93</v>
       </c>
-      <c r="L82" s="3" t="n">
+      <c r="L82" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="M82" s="3" t="n">
+      <c r="M82" t="n">
         <v>2.08</v>
       </c>
-      <c r="N82" s="3" t="n">
+      <c r="N82" t="n">
         <v>2.7</v>
       </c>
-      <c r="O82" s="3" t="n">
+      <c r="O82" t="n">
         <v>7.23</v>
       </c>
-      <c r="P82" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q82" s="3" t="n">
+      <c r="P82" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q82" t="n">
         <v>0.0243</v>
       </c>
-      <c r="R82" s="3" t="n">
+      <c r="R82" t="n">
         <v>0.312</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" t="n">
         <v>28</v>
       </c>
-      <c r="B83" s="1" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>It's just past 9 AM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Doylestown, PA</t>
         </is>
       </c>
-      <c r="D83" s="3" t="n">
+      <c r="D83" t="n">
         <v>175</v>
       </c>
-      <c r="E83" s="1" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F83" s="1" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G83" s="1" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H83" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="n">
+      <c r="H83" t="n">
+        <v>3</v>
+      </c>
+      <c r="I83" t="n">
         <v>2.9</v>
       </c>
-      <c r="J83" s="1" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K83" s="3" t="n">
+      <c r="K83" t="n">
         <v>8.16</v>
       </c>
-      <c r="L83" s="3" t="n">
+      <c r="L83" t="n">
         <v>1.84</v>
       </c>
-      <c r="M83" s="3" t="n">
+      <c r="M83" t="n">
         <v>10</v>
       </c>
-      <c r="N83" s="3" t="n">
+      <c r="N83" t="n">
         <v>10</v>
       </c>
-      <c r="O83" s="3" t="n">
+      <c r="O83" t="n">
         <v>6.592000000000001</v>
       </c>
-      <c r="P83" s="2" t="n">
+      <c r="P83" t="n">
         <v>1</v>
       </c>
-      <c r="Q83" s="3" t="n">
+      <c r="Q83" t="n">
         <v>0.2204</v>
       </c>
-      <c r="R83" s="3" t="n">
+      <c r="R83" t="n">
         <v>3.019</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" t="n">
         <v>28</v>
       </c>
-      <c r="B84" s="1" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>It's just past 9 AM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Doylestown, PA</t>
         </is>
       </c>
-      <c r="D84" s="3" t="n">
+      <c r="D84" t="n">
         <v>175</v>
       </c>
-      <c r="E84" s="1" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F84" s="1" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G84" s="1" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H84" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I84" s="3" t="n">
+      <c r="H84" t="n">
+        <v>3</v>
+      </c>
+      <c r="I84" t="n">
         <v>2.9</v>
       </c>
-      <c r="J84" s="1" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K84" s="3" t="n">
+      <c r="K84" t="n">
         <v>1.74</v>
       </c>
-      <c r="L84" s="3" t="n">
+      <c r="L84" t="n">
         <v>1.84</v>
       </c>
-      <c r="M84" s="3" t="n">
+      <c r="M84" t="n">
         <v>7.29</v>
       </c>
-      <c r="N84" s="3" t="n">
+      <c r="N84" t="n">
         <v>6.04</v>
       </c>
-      <c r="O84" s="3" t="n">
+      <c r="O84" t="n">
         <v>3.53</v>
       </c>
-      <c r="P84" s="2" t="n">
+      <c r="P84" t="n">
         <v>2</v>
       </c>
-      <c r="Q84" s="3" t="n">
+      <c r="Q84" t="n">
         <v>0.928</v>
       </c>
-      <c r="R84" s="3" t="n">
+      <c r="R84" t="n">
         <v>3.019</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" t="n">
         <v>28</v>
       </c>
-      <c r="B85" s="1" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>It's just past 9 AM and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Doylestown, PA</t>
         </is>
       </c>
-      <c r="D85" s="3" t="n">
+      <c r="D85" t="n">
         <v>175</v>
       </c>
-      <c r="E85" s="1" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F85" s="1" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G85" s="1" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>Condo</t>
         </is>
       </c>
-      <c r="H85" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I85" s="3" t="n">
+      <c r="H85" t="n">
+        <v>3</v>
+      </c>
+      <c r="I85" t="n">
         <v>2.9</v>
       </c>
-      <c r="J85" s="1" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>10:00 PM</t>
         </is>
       </c>
-      <c r="K85" s="3" t="n">
+      <c r="K85" t="n">
         <v>8.16</v>
       </c>
-      <c r="L85" s="3" t="n">
+      <c r="L85" t="n">
         <v>1.84</v>
       </c>
-      <c r="M85" s="3" t="n">
+      <c r="M85" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="N85" s="3" t="n">
+      <c r="N85" t="n">
         <v>1.61</v>
       </c>
-      <c r="O85" s="3" t="n">
+      <c r="O85" t="n">
         <v>3.5215</v>
       </c>
-      <c r="P85" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q85" s="3" t="n">
+      <c r="P85" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q85" t="n">
         <v>0.2204</v>
       </c>
-      <c r="R85" s="3" t="n">
+      <c r="R85" t="n">
         <v>3.019</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" t="n">
         <v>29</v>
       </c>
-      <c r="B86" s="1" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>It's around 2 in the afternoon and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D86" s="3" t="n">
+      <c r="D86" t="n">
         <v>165</v>
       </c>
-      <c r="E86" s="1" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F86" s="1" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G86" s="1" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H86" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I86" s="3" t="n">
+      <c r="H86" t="n">
+        <v>3</v>
+      </c>
+      <c r="I86" t="n">
         <v>1.2</v>
       </c>
-      <c r="J86" s="1" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K86" s="3" t="n">
+      <c r="K86" t="n">
         <v>6.67</v>
       </c>
-      <c r="L86" s="3" t="n">
+      <c r="L86" t="n">
         <v>7.04</v>
       </c>
-      <c r="M86" s="3" t="n">
+      <c r="M86" t="n">
         <v>10</v>
       </c>
-      <c r="N86" s="3" t="n">
+      <c r="N86" t="n">
         <v>10</v>
       </c>
-      <c r="O86" s="3" t="n">
+      <c r="O86" t="n">
         <v>7.965</v>
       </c>
-      <c r="P86" s="2" t="n">
+      <c r="P86" t="n">
         <v>1</v>
       </c>
-      <c r="Q86" s="3" t="n">
+      <c r="Q86" t="n">
         <v>0.384</v>
       </c>
-      <c r="R86" s="3" t="n">
+      <c r="R86" t="n">
         <v>1.249</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" t="n">
         <v>29</v>
       </c>
-      <c r="B87" s="1" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>It's around 2 in the afternoon and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D87" s="3" t="n">
+      <c r="D87" t="n">
         <v>165</v>
       </c>
-      <c r="E87" s="1" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F87" s="1" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G87" s="1" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H87" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I87" s="3" t="n">
+      <c r="H87" t="n">
+        <v>3</v>
+      </c>
+      <c r="I87" t="n">
         <v>1.2</v>
       </c>
-      <c r="J87" s="1" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>8:00 PM</t>
         </is>
       </c>
-      <c r="K87" s="3" t="n">
+      <c r="K87" t="n">
         <v>9.33</v>
       </c>
-      <c r="L87" s="3" t="n">
+      <c r="L87" t="n">
         <v>7.04</v>
       </c>
-      <c r="M87" s="3" t="n">
+      <c r="M87" t="n">
         <v>7.09</v>
       </c>
-      <c r="N87" s="3" t="n">
+      <c r="N87" t="n">
         <v>5.81</v>
       </c>
-      <c r="O87" s="3" t="n">
+      <c r="O87" t="n">
         <v>7.5525</v>
       </c>
-      <c r="P87" s="2" t="n">
+      <c r="P87" t="n">
         <v>2</v>
       </c>
-      <c r="Q87" s="3" t="n">
+      <c r="Q87" t="n">
         <v>0.0912</v>
       </c>
-      <c r="R87" s="3" t="n">
+      <c r="R87" t="n">
         <v>1.249</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" t="n">
         <v>29</v>
       </c>
-      <c r="B88" s="1" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>It's around 2 in the afternoon and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="D88" s="3" t="n">
+      <c r="D88" t="n">
         <v>165</v>
       </c>
-      <c r="E88" s="1" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F88" s="1" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G88" s="1" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H88" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I88" s="3" t="n">
+      <c r="H88" t="n">
+        <v>3</v>
+      </c>
+      <c r="I88" t="n">
         <v>1.2</v>
       </c>
-      <c r="J88" s="1" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>2:00 AM</t>
         </is>
       </c>
-      <c r="K88" s="3" t="n">
+      <c r="K88" t="n">
         <v>9.33</v>
       </c>
-      <c r="L88" s="3" t="n">
+      <c r="L88" t="n">
         <v>7.27</v>
       </c>
-      <c r="M88" s="3" t="n">
+      <c r="M88" t="n">
         <v>4.28</v>
       </c>
-      <c r="N88" s="3" t="n">
+      <c r="N88" t="n">
         <v>1.51</v>
       </c>
-      <c r="O88" s="3" t="n">
+      <c r="O88" t="n">
         <v>6.425999999999999</v>
       </c>
-      <c r="P88" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q88" s="3" t="n">
+      <c r="P88" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q88" t="n">
         <v>0.0912</v>
       </c>
-      <c r="R88" s="3" t="n">
+      <c r="R88" t="n">
         <v>1.171</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" t="n">
         <v>30</v>
       </c>
-      <c r="B89" s="1" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>It's about 7 in the evening and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Lancaster, PA</t>
         </is>
       </c>
-      <c r="D89" s="3" t="n">
+      <c r="D89" t="n">
         <v>170</v>
       </c>
-      <c r="E89" s="1" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F89" s="1" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G89" s="1" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H89" s="2" t="n">
+      <c r="H89" t="n">
         <v>4</v>
       </c>
-      <c r="I89" s="3" t="n">
+      <c r="I89" t="n">
         <v>0.42</v>
       </c>
-      <c r="J89" s="1" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>7:00 PM</t>
         </is>
       </c>
-      <c r="K89" s="3" t="n">
+      <c r="K89" t="n">
         <v>9.77</v>
       </c>
-      <c r="L89" s="3" t="n">
+      <c r="L89" t="n">
         <v>9.43</v>
       </c>
-      <c r="M89" s="3" t="n">
+      <c r="M89" t="n">
         <v>10</v>
       </c>
-      <c r="N89" s="3" t="n">
+      <c r="N89" t="n">
         <v>10</v>
       </c>
-      <c r="O89" s="3" t="n">
+      <c r="O89" t="n">
         <v>9.731499999999999</v>
       </c>
-      <c r="P89" s="2" t="n">
+      <c r="P89" t="n">
         <v>1</v>
       </c>
-      <c r="Q89" s="3" t="n">
+      <c r="Q89" t="n">
         <v>0.042</v>
       </c>
-      <c r="R89" s="3" t="n">
+      <c r="R89" t="n">
         <v>0.437</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" t="n">
         <v>30</v>
       </c>
-      <c r="B90" s="1" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>It's about 7 in the evening and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Lancaster, PA</t>
         </is>
       </c>
-      <c r="D90" s="3" t="n">
+      <c r="D90" t="n">
         <v>170</v>
       </c>
-      <c r="E90" s="1" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F90" s="1" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G90" s="1" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H90" s="2" t="n">
+      <c r="H90" t="n">
         <v>4</v>
       </c>
-      <c r="I90" s="3" t="n">
+      <c r="I90" t="n">
         <v>0.42</v>
       </c>
-      <c r="J90" s="1" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K90" s="3" t="n">
+      <c r="K90" t="n">
         <v>9.77</v>
       </c>
-      <c r="L90" s="3" t="n">
+      <c r="L90" t="n">
         <v>9.51</v>
       </c>
-      <c r="M90" s="3" t="n">
+      <c r="M90" t="n">
         <v>5.82</v>
       </c>
-      <c r="N90" s="3" t="n">
+      <c r="N90" t="n">
         <v>5.81</v>
       </c>
-      <c r="O90" s="3" t="n">
+      <c r="O90" t="n">
         <v>8.294999999999998</v>
       </c>
-      <c r="P90" s="2" t="n">
+      <c r="P90" t="n">
         <v>2</v>
       </c>
-      <c r="Q90" s="3" t="n">
+      <c r="Q90" t="n">
         <v>0.042</v>
       </c>
-      <c r="R90" s="3" t="n">
+      <c r="R90" t="n">
         <v>0.41</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" t="n">
         <v>30</v>
       </c>
-      <c r="B91" s="1" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>It's about 7 in the evening and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Lancaster, PA</t>
         </is>
       </c>
-      <c r="D91" s="3" t="n">
+      <c r="D91" t="n">
         <v>170</v>
       </c>
-      <c r="E91" s="1" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>washing_machine</t>
         </is>
       </c>
-      <c r="F91" s="1" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G91" s="1" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H91" s="2" t="n">
+      <c r="H91" t="n">
         <v>4</v>
       </c>
-      <c r="I91" s="3" t="n">
+      <c r="I91" t="n">
         <v>0.42</v>
       </c>
-      <c r="J91" s="1" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="K91" s="3" t="n">
+      <c r="K91" t="n">
         <v>9.77</v>
       </c>
-      <c r="L91" s="3" t="n">
+      <c r="L91" t="n">
         <v>9.43</v>
       </c>
-      <c r="M91" s="3" t="n">
+      <c r="M91" t="n">
         <v>4.71</v>
       </c>
-      <c r="N91" s="3" t="n">
+      <c r="N91" t="n">
         <v>2.95</v>
       </c>
-      <c r="O91" s="3" t="n">
+      <c r="O91" t="n">
         <v>7.615999999999999</v>
       </c>
-      <c r="P91" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3" t="n">
+      <c r="P91" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q91" t="n">
         <v>0.042</v>
       </c>
-      <c r="R91" s="3" t="n">
+      <c r="R91" t="n">
         <v>0.437</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" t="n">
         <v>31</v>
       </c>
-      <c r="B92" s="1" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>It's around 8 in the morning and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Norristown, PA</t>
         </is>
       </c>
-      <c r="D92" s="3" t="n">
+      <c r="D92" t="n">
         <v>195</v>
       </c>
-      <c r="E92" s="1" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F92" s="1" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="G92" s="1" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H92" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I92" s="3" t="n">
+      <c r="H92" t="n">
+        <v>3</v>
+      </c>
+      <c r="I92" t="n">
         <v>3.1</v>
       </c>
-      <c r="J92" s="1" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="K92" s="3" t="n">
+      <c r="K92" t="n">
         <v>8.02</v>
       </c>
-      <c r="L92" s="3" t="n">
+      <c r="L92" t="n">
         <v>1.23</v>
       </c>
-      <c r="M92" s="3" t="n">
+      <c r="M92" t="n">
         <v>10</v>
       </c>
-      <c r="N92" s="3" t="n">
+      <c r="N92" t="n">
         <v>10</v>
       </c>
-      <c r="O92" s="3" t="n">
+      <c r="O92" t="n">
         <v>6.336499999999999</v>
       </c>
-      <c r="P92" s="2" t="n">
+      <c r="P92" t="n">
         <v>1</v>
       </c>
-      <c r="Q92" s="3" t="n">
+      <c r="Q92" t="n">
         <v>0.2356</v>
       </c>
-      <c r="R92" s="3" t="n">
+      <c r="R92" t="n">
         <v>3.227</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" t="n">
         <v>31</v>
       </c>
-      <c r="B93" s="1" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>It's around 8 in the morning and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Norristown, PA</t>
         </is>
       </c>
-      <c r="D93" s="3" t="n">
+      <c r="D93" t="n">
         <v>195</v>
       </c>
-      <c r="E93" s="1" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F93" s="1" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="G93" s="1" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H93" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I93" s="3" t="n">
+      <c r="H93" t="n">
+        <v>3</v>
+      </c>
+      <c r="I93" t="n">
         <v>3.1</v>
       </c>
-      <c r="J93" s="1" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="K93" s="3" t="n">
+      <c r="K93" t="n">
         <v>1.16</v>
       </c>
-      <c r="L93" s="3" t="n">
+      <c r="L93" t="n">
         <v>1.23</v>
       </c>
-      <c r="M93" s="3" t="n">
+      <c r="M93" t="n">
         <v>6.29</v>
       </c>
-      <c r="N93" s="3" t="n">
+      <c r="N93" t="n">
         <v>4.86</v>
       </c>
-      <c r="O93" s="3" t="n">
+      <c r="O93" t="n">
         <v>2.7655</v>
       </c>
-      <c r="P93" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q93" s="3" t="n">
+      <c r="P93" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q93" t="n">
         <v>0.992</v>
       </c>
-      <c r="R93" s="3" t="n">
+      <c r="R93" t="n">
         <v>3.227</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" t="n">
         <v>31</v>
       </c>
-      <c r="B94" s="1" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>It's around 8 in the morning and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Norristown, PA</t>
         </is>
       </c>
-      <c r="D94" s="3" t="n">
+      <c r="D94" t="n">
         <v>195</v>
       </c>
-      <c r="E94" s="1" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F94" s="1" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="G94" s="1" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H94" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="n">
+      <c r="H94" t="n">
+        <v>3</v>
+      </c>
+      <c r="I94" t="n">
         <v>3.1</v>
       </c>
-      <c r="J94" s="1" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K94" s="3" t="n">
+      <c r="K94" t="n">
         <v>8.02</v>
       </c>
-      <c r="L94" s="3" t="n">
+      <c r="L94" t="n">
         <v>1.82</v>
       </c>
-      <c r="M94" s="3" t="n">
+      <c r="M94" t="n">
         <v>2.86</v>
       </c>
-      <c r="N94" s="3" t="n">
+      <c r="N94" t="n">
         <v>2.63</v>
       </c>
-      <c r="O94" s="3" t="n">
+      <c r="O94" t="n">
         <v>4.0095</v>
       </c>
-      <c r="P94" s="2" t="n">
+      <c r="P94" t="n">
         <v>2</v>
       </c>
-      <c r="Q94" s="3" t="n">
+      <c r="Q94" t="n">
         <v>0.2356</v>
       </c>
-      <c r="R94" s="3" t="n">
+      <c r="R94" t="n">
         <v>3.026</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" t="n">
         <v>32</v>
       </c>
-      <c r="B95" s="1" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>It's around 2 in the afternoon, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D95" s="3" t="n">
+      <c r="D95" t="n">
         <v>220</v>
       </c>
-      <c r="E95" s="1" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F95" s="1" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G95" s="1" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H95" s="2" t="n">
+      <c r="H95" t="n">
         <v>4</v>
       </c>
-      <c r="I95" s="3" t="n">
+      <c r="I95" t="n">
         <v>2.6</v>
       </c>
-      <c r="J95" s="1" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K95" s="3" t="n">
+      <c r="K95" t="n">
         <v>6.91</v>
       </c>
-      <c r="L95" s="3" t="n">
+      <c r="L95" t="n">
         <v>2.76</v>
       </c>
-      <c r="M95" s="3" t="n">
+      <c r="M95" t="n">
         <v>10</v>
       </c>
-      <c r="N95" s="3" t="n">
+      <c r="N95" t="n">
         <v>10</v>
       </c>
-      <c r="O95" s="3" t="n">
+      <c r="O95" t="n">
         <v>6.539</v>
       </c>
-      <c r="P95" s="2" t="n">
+      <c r="P95" t="n">
         <v>1</v>
       </c>
-      <c r="Q95" s="3" t="n">
+      <c r="Q95" t="n">
         <v>0.3575</v>
       </c>
-      <c r="R95" s="3" t="n">
+      <c r="R95" t="n">
         <v>2.707</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" t="n">
         <v>32</v>
       </c>
-      <c r="B96" s="1" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>It's around 2 in the afternoon, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D96" s="3" t="n">
+      <c r="D96" t="n">
         <v>220</v>
       </c>
-      <c r="E96" s="1" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F96" s="1" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G96" s="1" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H96" s="2" t="n">
+      <c r="H96" t="n">
         <v>4</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I96" t="n">
         <v>2.6</v>
       </c>
-      <c r="J96" s="1" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K96" s="3" t="n">
+      <c r="K96" t="n">
         <v>6.91</v>
       </c>
-      <c r="L96" s="3" t="n">
+      <c r="L96" t="n">
         <v>2.76</v>
       </c>
-      <c r="M96" s="3" t="n">
+      <c r="M96" t="n">
         <v>7.29</v>
       </c>
-      <c r="N96" s="3" t="n">
+      <c r="N96" t="n">
         <v>6.04</v>
       </c>
-      <c r="O96" s="3" t="n">
+      <c r="O96" t="n">
         <v>5.403</v>
       </c>
-      <c r="P96" s="2" t="n">
+      <c r="P96" t="n">
         <v>2</v>
       </c>
-      <c r="Q96" s="3" t="n">
+      <c r="Q96" t="n">
         <v>0.3575</v>
       </c>
-      <c r="R96" s="3" t="n">
+      <c r="R96" t="n">
         <v>2.707</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" t="n">
         <v>32</v>
       </c>
-      <c r="B97" s="1" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>It's around 2 in the afternoon, when should I run the dryer?</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>McKeesport, PA</t>
         </is>
       </c>
-      <c r="D97" s="3" t="n">
+      <c r="D97" t="n">
         <v>220</v>
       </c>
-      <c r="E97" s="1" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F97" s="1" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G97" s="1" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H97" s="2" t="n">
+      <c r="H97" t="n">
         <v>4</v>
       </c>
-      <c r="I97" s="3" t="n">
+      <c r="I97" t="n">
         <v>2.6</v>
       </c>
-      <c r="J97" s="1" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>10:00 PM</t>
         </is>
       </c>
-      <c r="K97" s="3" t="n">
+      <c r="K97" t="n">
         <v>6.91</v>
       </c>
-      <c r="L97" s="3" t="n">
+      <c r="L97" t="n">
         <v>2.76</v>
       </c>
-      <c r="M97" s="3" t="n">
+      <c r="M97" t="n">
         <v>3.36</v>
       </c>
-      <c r="N97" s="3" t="n">
+      <c r="N97" t="n">
         <v>3.11</v>
       </c>
-      <c r="O97" s="3" t="n">
+      <c r="O97" t="n">
         <v>4.1775</v>
       </c>
-      <c r="P97" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q97" s="3" t="n">
+      <c r="P97" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q97" t="n">
         <v>0.3575</v>
       </c>
-      <c r="R97" s="3" t="n">
+      <c r="R97" t="n">
         <v>2.707</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" t="n">
         <v>33</v>
       </c>
-      <c r="B98" s="1" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>I've just got home, it's around 6 PM, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D98" s="3" t="n">
+      <c r="D98" t="n">
         <v>200</v>
       </c>
-      <c r="E98" s="1" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F98" s="1" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G98" s="1" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H98" s="2" t="n">
+      <c r="H98" t="n">
         <v>6</v>
       </c>
-      <c r="I98" s="3" t="n">
+      <c r="I98" t="n">
         <v>1.7</v>
       </c>
-      <c r="J98" s="1" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>6:00 PM</t>
         </is>
       </c>
-      <c r="K98" s="3" t="n">
+      <c r="K98" t="n">
         <v>8.609999999999999</v>
       </c>
-      <c r="L98" s="3" t="n">
+      <c r="L98" t="n">
         <v>5.51</v>
       </c>
-      <c r="M98" s="3" t="n">
+      <c r="M98" t="n">
         <v>10</v>
       </c>
-      <c r="N98" s="3" t="n">
+      <c r="N98" t="n">
         <v>10</v>
       </c>
-      <c r="O98" s="3" t="n">
+      <c r="O98" t="n">
         <v>8.0115</v>
       </c>
-      <c r="P98" s="2" t="n">
+      <c r="P98" t="n">
         <v>1</v>
       </c>
-      <c r="Q98" s="3" t="n">
+      <c r="Q98" t="n">
         <v>0.17</v>
       </c>
-      <c r="R98" s="3" t="n">
+      <c r="R98" t="n">
         <v>1.77</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" t="n">
         <v>33</v>
       </c>
-      <c r="B99" s="1" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>I've just got home, it's around 6 PM, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D99" s="3" t="n">
+      <c r="D99" t="n">
         <v>200</v>
       </c>
-      <c r="E99" s="1" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F99" s="1" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G99" s="1" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H99" s="2" t="n">
+      <c r="H99" t="n">
         <v>6</v>
       </c>
-      <c r="I99" s="3" t="n">
+      <c r="I99" t="n">
         <v>1.7</v>
       </c>
-      <c r="J99" s="1" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="K99" s="3" t="n">
+      <c r="K99" t="n">
         <v>8.609999999999999</v>
       </c>
-      <c r="L99" s="3" t="n">
+      <c r="L99" t="n">
         <v>5.51</v>
       </c>
-      <c r="M99" s="3" t="n">
+      <c r="M99" t="n">
         <v>5.21</v>
       </c>
-      <c r="N99" s="3" t="n">
+      <c r="N99" t="n">
         <v>4.64</v>
       </c>
-      <c r="O99" s="3" t="n">
+      <c r="O99" t="n">
         <v>6.249499999999999</v>
       </c>
-      <c r="P99" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q99" s="3" t="n">
+      <c r="P99" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q99" t="n">
         <v>0.17</v>
       </c>
-      <c r="R99" s="3" t="n">
+      <c r="R99" t="n">
         <v>1.77</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" t="n">
         <v>33</v>
       </c>
-      <c r="B100" s="1" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>I've just got home, it's around 6 PM, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D100" s="3" t="n">
+      <c r="D100" t="n">
         <v>200</v>
       </c>
-      <c r="E100" s="1" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F100" s="1" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G100" s="1" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>Single-family</t>
         </is>
       </c>
-      <c r="H100" s="2" t="n">
+      <c r="H100" t="n">
         <v>6</v>
       </c>
-      <c r="I100" s="3" t="n">
+      <c r="I100" t="n">
         <v>1.7</v>
       </c>
-      <c r="J100" s="1" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>10:00 PM</t>
         </is>
       </c>
-      <c r="K100" s="3" t="n">
+      <c r="K100" t="n">
         <v>8.609999999999999</v>
       </c>
-      <c r="L100" s="3" t="n">
+      <c r="L100" t="n">
         <v>5.51</v>
       </c>
-      <c r="M100" s="3" t="n">
+      <c r="M100" t="n">
         <v>7.83</v>
       </c>
-      <c r="N100" s="3" t="n">
+      <c r="N100" t="n">
         <v>5.71</v>
       </c>
-      <c r="O100" s="3" t="n">
+      <c r="O100" t="n">
         <v>6.933999999999999</v>
       </c>
-      <c r="P100" s="2" t="n">
+      <c r="P100" t="n">
         <v>2</v>
       </c>
-      <c r="Q100" s="3" t="n">
+      <c r="Q100" t="n">
         <v>0.17</v>
       </c>
-      <c r="R100" s="3" t="n">
+      <c r="R100" t="n">
         <v>1.77</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" t="n">
         <v>34</v>
       </c>
-      <c r="B101" s="1" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>Laundry finished around 6 PM in Harrisburg. When should I run the dryer?</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D101" s="3" t="n">
+      <c r="D101" t="n">
         <v>260</v>
       </c>
-      <c r="E101" s="1" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F101" s="1" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G101" s="1" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H101" s="2" t="n">
+      <c r="H101" t="n">
         <v>4</v>
       </c>
-      <c r="I101" s="3" t="n">
+      <c r="I101" t="n">
         <v>2.4</v>
       </c>
-      <c r="J101" s="1" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>6:00 PM</t>
         </is>
       </c>
-      <c r="K101" s="3" t="n">
+      <c r="K101" t="n">
         <v>7.98</v>
       </c>
-      <c r="L101" s="3" t="n">
+      <c r="L101" t="n">
         <v>3.37</v>
       </c>
-      <c r="M101" s="3" t="n">
+      <c r="M101" t="n">
         <v>10</v>
       </c>
-      <c r="N101" s="3" t="n">
+      <c r="N101" t="n">
         <v>10</v>
       </c>
-      <c r="O101" s="3" t="n">
+      <c r="O101" t="n">
         <v>7.0735</v>
       </c>
-      <c r="P101" s="2" t="n">
+      <c r="P101" t="n">
         <v>1</v>
       </c>
-      <c r="Q101" s="3" t="n">
+      <c r="Q101" t="n">
         <v>0.24</v>
       </c>
-      <c r="R101" s="3" t="n">
+      <c r="R101" t="n">
         <v>2.498</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" t="n">
         <v>34</v>
       </c>
-      <c r="B102" s="1" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>Laundry finished around 6 PM in Harrisburg. When should I run the dryer?</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D102" s="3" t="n">
+      <c r="D102" t="n">
         <v>260</v>
       </c>
-      <c r="E102" s="1" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F102" s="1" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G102" s="1" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H102" s="2" t="n">
+      <c r="H102" t="n">
         <v>4</v>
       </c>
-      <c r="I102" s="3" t="n">
+      <c r="I102" t="n">
         <v>2.4</v>
       </c>
-      <c r="J102" s="1" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>10:00 PM</t>
         </is>
       </c>
-      <c r="K102" s="3" t="n">
+      <c r="K102" t="n">
         <v>7.98</v>
       </c>
-      <c r="L102" s="3" t="n">
+      <c r="L102" t="n">
         <v>3.37</v>
       </c>
-      <c r="M102" s="3" t="n">
+      <c r="M102" t="n">
         <v>5.69</v>
       </c>
-      <c r="N102" s="3" t="n">
+      <c r="N102" t="n">
         <v>5.67</v>
       </c>
-      <c r="O102" s="3" t="n">
+      <c r="O102" t="n">
         <v>5.562</v>
       </c>
-      <c r="P102" s="2" t="n">
+      <c r="P102" t="n">
         <v>2</v>
       </c>
-      <c r="Q102" s="3" t="n">
+      <c r="Q102" t="n">
         <v>0.24</v>
       </c>
-      <c r="R102" s="3" t="n">
+      <c r="R102" t="n">
         <v>2.498</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" t="n">
         <v>34</v>
       </c>
-      <c r="B103" s="1" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>Laundry finished around 6 PM in Harrisburg. When should I run the dryer?</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>Harrisburg, PA</t>
         </is>
       </c>
-      <c r="D103" s="3" t="n">
+      <c r="D103" t="n">
         <v>260</v>
       </c>
-      <c r="E103" s="1" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>dryer</t>
         </is>
       </c>
-      <c r="F103" s="1" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G103" s="1" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>Rowhouse</t>
         </is>
       </c>
-      <c r="H103" s="2" t="n">
+      <c r="H103" t="n">
         <v>4</v>
       </c>
-      <c r="I103" s="3" t="n">
+      <c r="I103" t="n">
         <v>2.4</v>
       </c>
-      <c r="J103" s="1" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>6:00 AM</t>
         </is>
       </c>
-      <c r="K103" s="3" t="n">
+      <c r="K103" t="n">
         <v>7.98</v>
       </c>
-      <c r="L103" s="3" t="n">
+      <c r="L103" t="n">
         <v>3.83</v>
       </c>
-      <c r="M103" s="3" t="n">
+      <c r="M103" t="n">
         <v>1.24</v>
       </c>
-      <c r="N103" s="3" t="n">
+      <c r="N103" t="n">
         <v>2.47</v>
       </c>
-      <c r="O103" s="3" t="n">
+      <c r="O103" t="n">
         <v>4.353</v>
       </c>
-      <c r="P103" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q103" s="3" t="n">
+      <c r="P103" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q103" t="n">
         <v>0.24</v>
       </c>
-      <c r="R103" s="3" t="n">
+      <c r="R103" t="n">
         <v>2.342</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" t="n">
         <v>35</v>
       </c>
-      <c r="B104" s="1" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>It's around 8 in the morning and I need to run the dishwasher in Doylestown. When should I start it?</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>Doylestown, PA</t>
         </is>
       </c>
-      <c r="D104" s="3" t="n">
+      <c r="D104" t="n">
         <v>210</v>
       </c>
-      <c r="E104" s="1" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F104" s="1" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G104" s="1" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H104" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I104" s="3" t="n">
+      <c r="H104" t="n">
+        <v>3</v>
+      </c>
+      <c r="I104" t="n">
         <v>1.05</v>
       </c>
-      <c r="J104" s="1" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="K104" s="3" t="n">
+      <c r="K104" t="n">
         <v>9.43</v>
       </c>
-      <c r="L104" s="3" t="n">
+      <c r="L104" t="n">
         <v>7.5</v>
       </c>
-      <c r="M104" s="3" t="n">
+      <c r="M104" t="n">
         <v>10</v>
       </c>
-      <c r="N104" s="3" t="n">
+      <c r="N104" t="n">
         <v>10</v>
       </c>
-      <c r="O104" s="3" t="n">
+      <c r="O104" t="n">
         <v>8.954000000000001</v>
       </c>
-      <c r="P104" s="2" t="n">
+      <c r="P104" t="n">
         <v>1</v>
       </c>
-      <c r="Q104" s="3" t="n">
+      <c r="Q104" t="n">
         <v>0.0798</v>
       </c>
-      <c r="R104" s="3" t="n">
+      <c r="R104" t="n">
         <v>1.093</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" t="n">
         <v>35</v>
       </c>
-      <c r="B105" s="1" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>It's around 8 in the morning and I need to run the dishwasher in Doylestown. When should I start it?</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>Doylestown, PA</t>
         </is>
       </c>
-      <c r="D105" s="3" t="n">
+      <c r="D105" t="n">
         <v>210</v>
       </c>
-      <c r="E105" s="1" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F105" s="1" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G105" s="1" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H105" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I105" s="3" t="n">
+      <c r="H105" t="n">
+        <v>3</v>
+      </c>
+      <c r="I105" t="n">
         <v>1.05</v>
       </c>
-      <c r="J105" s="1" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="K105" s="3" t="n">
+      <c r="K105" t="n">
         <v>7.11</v>
       </c>
-      <c r="L105" s="3" t="n">
+      <c r="L105" t="n">
         <v>7.5</v>
       </c>
-      <c r="M105" s="3" t="n">
+      <c r="M105" t="n">
         <v>7.09</v>
       </c>
-      <c r="N105" s="3" t="n">
+      <c r="N105" t="n">
         <v>5.81</v>
       </c>
-      <c r="O105" s="3" t="n">
+      <c r="O105" t="n">
         <v>7.0475</v>
       </c>
-      <c r="P105" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q105" s="3" t="n">
+      <c r="P105" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q105" t="n">
         <v>0.336</v>
       </c>
-      <c r="R105" s="3" t="n">
+      <c r="R105" t="n">
         <v>1.093</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" t="n">
         <v>35</v>
       </c>
-      <c r="B106" s="1" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>It's around 8 in the morning and I need to run the dishwasher in Doylestown. When should I start it?</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>Doylestown, PA</t>
         </is>
       </c>
-      <c r="D106" s="3" t="n">
+      <c r="D106" t="n">
         <v>210</v>
       </c>
-      <c r="E106" s="1" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>dishwasher</t>
         </is>
       </c>
-      <c r="F106" s="1" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G106" s="1" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>Townhouse</t>
         </is>
       </c>
-      <c r="H106" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I106" s="3" t="n">
+      <c r="H106" t="n">
+        <v>3</v>
+      </c>
+      <c r="I106" t="n">
         <v>1.05</v>
       </c>
-      <c r="J106" s="1" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>11:00 PM</t>
         </is>
       </c>
-      <c r="K106" s="3" t="n">
+      <c r="K106" t="n">
         <v>9.43</v>
       </c>
-      <c r="L106" s="3" t="n">
+      <c r="L106" t="n">
         <v>7.7</v>
       </c>
-      <c r="M106" s="3" t="n">
+      <c r="M106" t="n">
         <v>5.73</v>
       </c>
-      <c r="N106" s="3" t="n">
+      <c r="N106" t="n">
         <v>2.89</v>
       </c>
-      <c r="O106" s="3" t="n">
+      <c r="O106" t="n">
         <v>7.103499999999999</v>
       </c>
-      <c r="P106" s="2" t="n">
+      <c r="P106" t="n">
         <v>2</v>
       </c>
-      <c r="Q106" s="3" t="n">
+      <c r="Q106" t="n">
         <v>0.0798</v>
       </c>
-      <c r="R106" s="3" t="n">
+      <c r="R106" t="n">
         <v>1.025</v>
       </c>
     </row>

--- a/workbooks/scenarios/ApplianceRAGScenarios.xlsx
+++ b/workbooks/scenarios/ApplianceRAGScenarios.xlsx
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>8.33</v>
+        <v>7.8</v>
       </c>
       <c r="L2" t="n">
         <v>2.14</v>
@@ -564,13 +564,13 @@
         <v>9.15</v>
       </c>
       <c r="O2" t="n">
-        <v>6.512500000000001</v>
+        <v>6.3535</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2016</v>
+        <v>0.2604</v>
       </c>
       <c r="R2" t="n">
         <v>2.915</v>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8.33</v>
+        <v>7.8</v>
       </c>
       <c r="L3" t="n">
         <v>2.14</v>
@@ -632,13 +632,13 @@
         <v>8.23</v>
       </c>
       <c r="O3" t="n">
-        <v>6.2625</v>
+        <v>6.103499999999999</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2016</v>
+        <v>0.2604</v>
       </c>
       <c r="R3" t="n">
         <v>2.915</v>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>7.87</v>
+        <v>7.21</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -768,13 +768,13 @@
         <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>5.861</v>
+        <v>5.663</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.252</v>
+        <v>0.3255</v>
       </c>
       <c r="R5" t="n">
         <v>3.643</v>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7.87</v>
+        <v>7.21</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -836,13 +836,13 @@
         <v>6.66</v>
       </c>
       <c r="O6" t="n">
-        <v>4.922</v>
+        <v>4.723999999999999</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.252</v>
+        <v>0.3255</v>
       </c>
       <c r="R6" t="n">
         <v>3.643</v>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>4.31</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1145</v>
+        <v>3.1175</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>9.84</v>
+        <v>9.94</v>
       </c>
       <c r="L8" t="n">
         <v>9.65</v>
@@ -972,13 +972,13 @@
         <v>10</v>
       </c>
       <c r="O8" t="n">
-        <v>9.829499999999999</v>
+        <v>9.859500000000001</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.035</v>
+        <v>0.0245</v>
       </c>
       <c r="R8" t="n">
         <v>0.364</v>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>9.710000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="L9" t="n">
         <v>9.65</v>
@@ -1040,13 +1040,13 @@
         <v>5.61</v>
       </c>
       <c r="O9" t="n">
-        <v>8.516</v>
+        <v>8.498000000000001</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.049</v>
+        <v>0.056</v>
       </c>
       <c r="R9" t="n">
         <v>0.364</v>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>9.84</v>
+        <v>9.94</v>
       </c>
       <c r="L10" t="n">
         <v>9.710000000000001</v>
@@ -1108,13 +1108,13 @@
         <v>1.51</v>
       </c>
       <c r="O10" t="n">
-        <v>7.343</v>
+        <v>7.372999999999999</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.035</v>
+        <v>0.0245</v>
       </c>
       <c r="R10" t="n">
         <v>0.342</v>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>6.96</v>
+        <v>6.97</v>
       </c>
       <c r="L12" t="n">
         <v>7.35</v>
@@ -1244,7 +1244,7 @@
         <v>6.69</v>
       </c>
       <c r="O12" t="n">
-        <v>7.23</v>
+        <v>7.232999999999999</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>9.75</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="L14" t="n">
         <v>9.34</v>
@@ -1380,13 +1380,13 @@
         <v>10</v>
       </c>
       <c r="O14" t="n">
-        <v>9.693999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.045</v>
+        <v>0.0315</v>
       </c>
       <c r="R14" t="n">
         <v>0.468</v>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>9.75</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="L15" t="n">
         <v>9.34</v>
@@ -1448,13 +1448,13 @@
         <v>2.95</v>
       </c>
       <c r="O15" t="n">
-        <v>7.578499999999999</v>
+        <v>7.6145</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.045</v>
+        <v>0.0315</v>
       </c>
       <c r="R15" t="n">
         <v>0.468</v>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>9.75</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="L16" t="n">
         <v>9.43</v>
@@ -1516,13 +1516,13 @@
         <v>1.51</v>
       </c>
       <c r="O16" t="n">
-        <v>7.023999999999999</v>
+        <v>7.06</v>
       </c>
       <c r="P16" t="n">
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.045</v>
+        <v>0.0315</v>
       </c>
       <c r="R16" t="n">
         <v>0.439</v>
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>6.66</v>
+        <v>6.67</v>
       </c>
       <c r="L17" t="n">
         <v>2.14</v>
@@ -1584,7 +1584,7 @@
         <v>10</v>
       </c>
       <c r="O17" t="n">
-        <v>6.247</v>
+        <v>6.25</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>6.66</v>
+        <v>6.67</v>
       </c>
       <c r="L18" t="n">
         <v>2.14</v>
@@ -1652,7 +1652,7 @@
         <v>6.04</v>
       </c>
       <c r="O18" t="n">
-        <v>5.111</v>
+        <v>5.114</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>6.66</v>
+        <v>6.67</v>
       </c>
       <c r="L19" t="n">
         <v>2.68</v>
@@ -1720,7 +1720,7 @@
         <v>2.13</v>
       </c>
       <c r="O19" t="n">
-        <v>3.7255</v>
+        <v>3.7285</v>
       </c>
       <c r="P19" t="n">
         <v>3</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>9.9</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="L20" t="n">
         <v>10</v>
@@ -1788,13 +1788,13 @@
         <v>10</v>
       </c>
       <c r="O20" t="n">
-        <v>9.970000000000001</v>
+        <v>9.961</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.028</v>
+        <v>0.032</v>
       </c>
       <c r="R20" t="n">
         <v>0.208</v>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="L21" t="n">
         <v>10</v>
@@ -1856,13 +1856,13 @@
         <v>5.71</v>
       </c>
       <c r="O21" t="n">
-        <v>8.7475</v>
+        <v>8.756500000000001</v>
       </c>
       <c r="P21" t="n">
         <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
       <c r="R21" t="n">
         <v>0.208</v>
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="L22" t="n">
         <v>10</v>
@@ -1924,13 +1924,13 @@
         <v>2.86</v>
       </c>
       <c r="O22" t="n">
-        <v>7.638</v>
+        <v>7.647</v>
       </c>
       <c r="P22" t="n">
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
       <c r="R22" t="n">
         <v>0.195</v>
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>9.859999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="L23" t="n">
         <v>10</v>
@@ -1992,13 +1992,13 @@
         <v>10</v>
       </c>
       <c r="O23" t="n">
-        <v>9.958</v>
+        <v>9.946</v>
       </c>
       <c r="P23" t="n">
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.0322</v>
+        <v>0.0368</v>
       </c>
       <c r="R23" t="n">
         <v>0.239</v>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>9.949999999999999</v>
+        <v>10</v>
       </c>
       <c r="L24" t="n">
         <v>10</v>
@@ -2060,13 +2060,13 @@
         <v>4.64</v>
       </c>
       <c r="O24" t="n">
-        <v>8.365</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="P24" t="n">
         <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.023</v>
+        <v>0.0161</v>
       </c>
       <c r="R24" t="n">
         <v>0.239</v>
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>9.949999999999999</v>
+        <v>10</v>
       </c>
       <c r="L25" t="n">
         <v>10</v>
@@ -2128,13 +2128,13 @@
         <v>5.19</v>
       </c>
       <c r="O25" t="n">
-        <v>8.465499999999999</v>
+        <v>8.480499999999999</v>
       </c>
       <c r="P25" t="n">
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.023</v>
+        <v>0.0161</v>
       </c>
       <c r="R25" t="n">
         <v>0.239</v>
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>6.98</v>
+        <v>7.94</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2196,13 +2196,13 @@
         <v>10</v>
       </c>
       <c r="O26" t="n">
-        <v>5.593999999999999</v>
+        <v>5.882</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.35</v>
+        <v>0.245</v>
       </c>
       <c r="R26" t="n">
         <v>3.643</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>6.98</v>
+        <v>7.94</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2264,13 +2264,13 @@
         <v>3.42</v>
       </c>
       <c r="O27" t="n">
-        <v>3.633</v>
+        <v>3.921</v>
       </c>
       <c r="P27" t="n">
         <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.35</v>
+        <v>0.245</v>
       </c>
       <c r="R27" t="n">
         <v>3.643</v>
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>6.98</v>
+        <v>7.94</v>
       </c>
       <c r="L28" t="n">
         <v>0.67</v>
@@ -2332,13 +2332,13 @@
         <v>3.88</v>
       </c>
       <c r="O28" t="n">
-        <v>3.9225</v>
+        <v>4.210500000000001</v>
       </c>
       <c r="P28" t="n">
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.35</v>
+        <v>0.245</v>
       </c>
       <c r="R28" t="n">
         <v>3.416</v>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>8.43</v>
+        <v>8.44</v>
       </c>
       <c r="L32" t="n">
         <v>3.06</v>
@@ -2604,7 +2604,7 @@
         <v>9.25</v>
       </c>
       <c r="O32" t="n">
-        <v>6.5535</v>
+        <v>6.5565</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>8.43</v>
+        <v>8.44</v>
       </c>
       <c r="L33" t="n">
         <v>3.06</v>
@@ -2672,7 +2672,7 @@
         <v>2.95</v>
       </c>
       <c r="O33" t="n">
-        <v>4.9845</v>
+        <v>4.9875</v>
       </c>
       <c r="P33" t="n">
         <v>2</v>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>9.880000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L35" t="n">
         <v>9.43</v>
@@ -2808,13 +2808,13 @@
         <v>9.25</v>
       </c>
       <c r="O35" t="n">
-        <v>9.311999999999999</v>
+        <v>9.287999999999998</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.0302</v>
+        <v>0.0396</v>
       </c>
       <c r="R35" t="n">
         <v>0.439</v>
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>9.880000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L36" t="n">
         <v>9.34</v>
@@ -2876,13 +2876,13 @@
         <v>3.87</v>
       </c>
       <c r="O36" t="n">
-        <v>7.919499999999999</v>
+        <v>7.895499999999999</v>
       </c>
       <c r="P36" t="n">
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0302</v>
+        <v>0.0396</v>
       </c>
       <c r="R36" t="n">
         <v>0.468</v>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>9.48</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="L37" t="n">
         <v>9.34</v>
@@ -2944,13 +2944,13 @@
         <v>4.64</v>
       </c>
       <c r="O37" t="n">
-        <v>7.992999999999999</v>
+        <v>7.986999999999999</v>
       </c>
       <c r="P37" t="n">
         <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.0743</v>
+        <v>0.0774</v>
       </c>
       <c r="R37" t="n">
         <v>0.468</v>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>6.98</v>
+        <v>6.53</v>
       </c>
       <c r="L38" t="n">
         <v>3.06</v>
@@ -3012,13 +3012,13 @@
         <v>10</v>
       </c>
       <c r="O38" t="n">
-        <v>6.665</v>
+        <v>6.53</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="R38" t="n">
         <v>2.603</v>
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>6.98</v>
+        <v>6.53</v>
       </c>
       <c r="L39" t="n">
         <v>3.06</v>
@@ -3080,13 +3080,13 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>6.115500000000001</v>
+        <v>5.980500000000001</v>
       </c>
       <c r="P39" t="n">
         <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="R39" t="n">
         <v>2.603</v>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>7.89</v>
+        <v>8.57</v>
       </c>
       <c r="L40" t="n">
         <v>3.06</v>
@@ -3148,13 +3148,13 @@
         <v>4.64</v>
       </c>
       <c r="O40" t="n">
-        <v>5.356</v>
+        <v>5.56</v>
       </c>
       <c r="P40" t="n">
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.25</v>
+        <v>0.175</v>
       </c>
       <c r="R40" t="n">
         <v>2.603</v>
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>9.16</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="L41" t="n">
         <v>7.35</v>
@@ -3216,13 +3216,13 @@
         <v>10</v>
       </c>
       <c r="O41" t="n">
-        <v>8.820499999999999</v>
+        <v>8.910499999999999</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.11</v>
+        <v>0.077</v>
       </c>
       <c r="R41" t="n">
         <v>1.145</v>
@@ -3272,7 +3272,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>8.76</v>
+        <v>8.56</v>
       </c>
       <c r="L42" t="n">
         <v>7.35</v>
@@ -3284,13 +3284,13 @@
         <v>5.81</v>
       </c>
       <c r="O42" t="n">
-        <v>7.49</v>
+        <v>7.43</v>
       </c>
       <c r="P42" t="n">
         <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.154</v>
+        <v>0.176</v>
       </c>
       <c r="R42" t="n">
         <v>1.145</v>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>9.16</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="L43" t="n">
         <v>7.35</v>
@@ -3352,13 +3352,13 @@
         <v>4.64</v>
       </c>
       <c r="O43" t="n">
-        <v>6.972499999999999</v>
+        <v>7.0625</v>
       </c>
       <c r="P43" t="n">
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.11</v>
+        <v>0.077</v>
       </c>
       <c r="R43" t="n">
         <v>1.145</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>9.81</v>
+        <v>9.92</v>
       </c>
       <c r="L44" t="n">
         <v>9.630000000000001</v>
@@ -3420,13 +3420,13 @@
         <v>8.449999999999999</v>
       </c>
       <c r="O44" t="n">
-        <v>9.147</v>
+        <v>9.18</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.038</v>
+        <v>0.0266</v>
       </c>
       <c r="R44" t="n">
         <v>0.371</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>9.81</v>
+        <v>9.92</v>
       </c>
       <c r="L45" t="n">
         <v>9.550000000000001</v>
@@ -3488,13 +3488,13 @@
         <v>4.64</v>
       </c>
       <c r="O45" t="n">
-        <v>8.027500000000002</v>
+        <v>8.060500000000001</v>
       </c>
       <c r="P45" t="n">
         <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.038</v>
+        <v>0.0266</v>
       </c>
       <c r="R45" t="n">
         <v>0.396</v>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>9.67</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="L46" t="n">
         <v>9.550000000000001</v>
@@ -3556,13 +3556,13 @@
         <v>2.03</v>
       </c>
       <c r="O46" t="n">
-        <v>7.336</v>
+        <v>7.318000000000001</v>
       </c>
       <c r="P46" t="n">
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.0532</v>
+        <v>0.0608</v>
       </c>
       <c r="R46" t="n">
         <v>0.396</v>
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>8.34</v>
+        <v>7.89</v>
       </c>
       <c r="L47" t="n">
         <v>3.06</v>
@@ -3624,13 +3624,13 @@
         <v>10</v>
       </c>
       <c r="O47" t="n">
-        <v>7.073</v>
+        <v>6.938</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="R47" t="n">
         <v>2.603</v>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>5.17</v>
+        <v>5.56</v>
       </c>
       <c r="L48" t="n">
         <v>3.06</v>
@@ -3692,13 +3692,13 @@
         <v>6.66</v>
       </c>
       <c r="O48" t="n">
-        <v>5.183</v>
+        <v>5.3</v>
       </c>
       <c r="P48" t="n">
         <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.55</v>
+        <v>0.5075</v>
       </c>
       <c r="R48" t="n">
         <v>2.603</v>
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>8.34</v>
+        <v>7.89</v>
       </c>
       <c r="L49" t="n">
         <v>3.54</v>
@@ -3760,13 +3760,13 @@
         <v>1.51</v>
       </c>
       <c r="O49" t="n">
-        <v>4.539499999999999</v>
+        <v>4.4045</v>
       </c>
       <c r="P49" t="n">
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="R49" t="n">
         <v>2.44</v>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>9.92</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="L50" t="n">
         <v>9.74</v>
@@ -3828,13 +3828,13 @@
         <v>10</v>
       </c>
       <c r="O50" t="n">
-        <v>9.885</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.0256</v>
+        <v>0.032</v>
       </c>
       <c r="R50" t="n">
         <v>0.333</v>
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>9.52</v>
+        <v>9.57</v>
       </c>
       <c r="L51" t="n">
         <v>9.74</v>
@@ -3896,13 +3896,13 @@
         <v>6.21</v>
       </c>
       <c r="O51" t="n">
-        <v>8.682499999999999</v>
+        <v>8.6975</v>
       </c>
       <c r="P51" t="n">
         <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.0704</v>
+        <v>0.065</v>
       </c>
       <c r="R51" t="n">
         <v>0.333</v>
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>9.92</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="L52" t="n">
         <v>9.74</v>
@@ -3964,13 +3964,13 @@
         <v>2.2</v>
       </c>
       <c r="O52" t="n">
-        <v>7.021</v>
+        <v>7.005999999999999</v>
       </c>
       <c r="P52" t="n">
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.0256</v>
+        <v>0.032</v>
       </c>
       <c r="R52" t="n">
         <v>0.333</v>
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>9.880000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L59" t="n">
         <v>9.51</v>
@@ -4440,13 +4440,13 @@
         <v>9.25</v>
       </c>
       <c r="O59" t="n">
-        <v>9.245999999999999</v>
+        <v>9.222</v>
       </c>
       <c r="P59" t="n">
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.0302</v>
+        <v>0.0391</v>
       </c>
       <c r="R59" t="n">
         <v>0.41</v>
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>9.880000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L60" t="n">
         <v>9.43</v>
@@ -4508,13 +4508,13 @@
         <v>2.95</v>
       </c>
       <c r="O60" t="n">
-        <v>7.649</v>
+        <v>7.624999999999999</v>
       </c>
       <c r="P60" t="n">
         <v>3</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.0302</v>
+        <v>0.0391</v>
       </c>
       <c r="R60" t="n">
         <v>0.437</v>
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>8.58</v>
+        <v>8.52</v>
       </c>
       <c r="L65" t="n">
         <v>7.5</v>
@@ -4848,13 +4848,13 @@
         <v>10</v>
       </c>
       <c r="O65" t="n">
-        <v>8.699</v>
+        <v>8.680999999999999</v>
       </c>
       <c r="P65" t="n">
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.1733</v>
+        <v>0.1806</v>
       </c>
       <c r="R65" t="n">
         <v>1.093</v>
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>9.52</v>
+        <v>9.32</v>
       </c>
       <c r="L66" t="n">
         <v>7.5</v>
@@ -4916,13 +4916,13 @@
         <v>5.81</v>
       </c>
       <c r="O66" t="n">
-        <v>7.7705</v>
+        <v>7.7105</v>
       </c>
       <c r="P66" t="n">
         <v>2</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.0704</v>
+        <v>0.0924</v>
       </c>
       <c r="R66" t="n">
         <v>1.093</v>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>9.52</v>
+        <v>9.32</v>
       </c>
       <c r="L67" t="n">
         <v>7.7</v>
@@ -4984,13 +4984,13 @@
         <v>3.44</v>
       </c>
       <c r="O67" t="n">
-        <v>7.301</v>
+        <v>7.241</v>
       </c>
       <c r="P67" t="n">
         <v>3</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.0704</v>
+        <v>0.0924</v>
       </c>
       <c r="R67" t="n">
         <v>1.025</v>
@@ -5312,7 +5312,7 @@
         </is>
       </c>
       <c r="K72" t="n">
-        <v>7.48</v>
+        <v>6.7</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -5324,13 +5324,13 @@
         <v>4.86</v>
       </c>
       <c r="O72" t="n">
-        <v>4.231</v>
+        <v>3.997</v>
       </c>
       <c r="P72" t="n">
         <v>2</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.2952</v>
+        <v>0.3813</v>
       </c>
       <c r="R72" t="n">
         <v>4.268</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>7.48</v>
+        <v>6.7</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -5392,13 +5392,13 @@
         <v>1.51</v>
       </c>
       <c r="O73" t="n">
-        <v>2.7185</v>
+        <v>2.4845</v>
       </c>
       <c r="P73" t="n">
         <v>3</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.2952</v>
+        <v>0.3813</v>
       </c>
       <c r="R73" t="n">
         <v>4.002</v>
@@ -5448,7 +5448,7 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>8.25</v>
+        <v>8.83</v>
       </c>
       <c r="L74" t="n">
         <v>4.29</v>
@@ -5460,13 +5460,13 @@
         <v>10</v>
       </c>
       <c r="O74" t="n">
-        <v>7.4765</v>
+        <v>7.6505</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.21</v>
+        <v>0.147</v>
       </c>
       <c r="R74" t="n">
         <v>2.186</v>
@@ -5516,7 +5516,7 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>7.49</v>
+        <v>7.11</v>
       </c>
       <c r="L75" t="n">
         <v>4.29</v>
@@ -5528,13 +5528,13 @@
         <v>6.91</v>
       </c>
       <c r="O75" t="n">
-        <v>6.389</v>
+        <v>6.275</v>
       </c>
       <c r="P75" t="n">
         <v>2</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.294</v>
+        <v>0.336</v>
       </c>
       <c r="R75" t="n">
         <v>2.186</v>
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>8.25</v>
+        <v>8.83</v>
       </c>
       <c r="L76" t="n">
         <v>4.69</v>
@@ -5596,13 +5596,13 @@
         <v>1.71</v>
       </c>
       <c r="O76" t="n">
-        <v>5.329000000000001</v>
+        <v>5.503</v>
       </c>
       <c r="P76" t="n">
         <v>3</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.21</v>
+        <v>0.147</v>
       </c>
       <c r="R76" t="n">
         <v>2.05</v>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>9.359999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L78" t="n">
         <v>7.42</v>
@@ -5732,7 +5732,7 @@
         <v>5.19</v>
       </c>
       <c r="O78" t="n">
-        <v>7.669499999999999</v>
+        <v>7.672499999999999</v>
       </c>
       <c r="P78" t="n">
         <v>2</v>
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>9.359999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L79" t="n">
         <v>7.2</v>
@@ -5800,7 +5800,7 @@
         <v>4.78</v>
       </c>
       <c r="O79" t="n">
-        <v>7.302999999999999</v>
+        <v>7.305999999999999</v>
       </c>
       <c r="P79" t="n">
         <v>3</v>
@@ -5856,7 +5856,7 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>9.93</v>
+        <v>9.94</v>
       </c>
       <c r="L80" t="n">
         <v>9.74</v>
@@ -5868,7 +5868,7 @@
         <v>10</v>
       </c>
       <c r="O80" t="n">
-        <v>9.888</v>
+        <v>9.891</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>9.93</v>
+        <v>9.94</v>
       </c>
       <c r="L82" t="n">
         <v>9.800000000000001</v>
@@ -6004,7 +6004,7 @@
         <v>2.7</v>
       </c>
       <c r="O82" t="n">
-        <v>7.23</v>
+        <v>7.233000000000001</v>
       </c>
       <c r="P82" t="n">
         <v>3</v>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>6.67</v>
+        <v>6.68</v>
       </c>
       <c r="L86" t="n">
         <v>7.04</v>
@@ -6276,7 +6276,7 @@
         <v>10</v>
       </c>
       <c r="O86" t="n">
-        <v>7.965</v>
+        <v>7.968</v>
       </c>
       <c r="P86" t="n">
         <v>1</v>
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>9.77</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="L89" t="n">
         <v>9.43</v>
@@ -6480,13 +6480,13 @@
         <v>10</v>
       </c>
       <c r="O89" t="n">
-        <v>9.731499999999999</v>
+        <v>9.7675</v>
       </c>
       <c r="P89" t="n">
         <v>1</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.042</v>
+        <v>0.0294</v>
       </c>
       <c r="R89" t="n">
         <v>0.437</v>
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>9.77</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="L90" t="n">
         <v>9.51</v>
@@ -6548,13 +6548,13 @@
         <v>5.81</v>
       </c>
       <c r="O90" t="n">
-        <v>8.294999999999998</v>
+        <v>8.331</v>
       </c>
       <c r="P90" t="n">
         <v>2</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.042</v>
+        <v>0.0294</v>
       </c>
       <c r="R90" t="n">
         <v>0.41</v>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>9.77</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="L91" t="n">
         <v>9.43</v>
@@ -6616,13 +6616,13 @@
         <v>2.95</v>
       </c>
       <c r="O91" t="n">
-        <v>7.615999999999999</v>
+        <v>7.652</v>
       </c>
       <c r="P91" t="n">
         <v>3</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.042</v>
+        <v>0.0294</v>
       </c>
       <c r="R91" t="n">
         <v>0.437</v>
@@ -6876,7 +6876,7 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>6.91</v>
+        <v>6.92</v>
       </c>
       <c r="L95" t="n">
         <v>2.76</v>
@@ -6888,7 +6888,7 @@
         <v>10</v>
       </c>
       <c r="O95" t="n">
-        <v>6.539</v>
+        <v>6.542</v>
       </c>
       <c r="P95" t="n">
         <v>1</v>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>6.91</v>
+        <v>6.92</v>
       </c>
       <c r="L96" t="n">
         <v>2.76</v>
@@ -6956,7 +6956,7 @@
         <v>6.04</v>
       </c>
       <c r="O96" t="n">
-        <v>5.403</v>
+        <v>5.406</v>
       </c>
       <c r="P96" t="n">
         <v>2</v>
@@ -7012,7 +7012,7 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>6.91</v>
+        <v>6.92</v>
       </c>
       <c r="L97" t="n">
         <v>2.76</v>
@@ -7024,7 +7024,7 @@
         <v>3.11</v>
       </c>
       <c r="O97" t="n">
-        <v>4.1775</v>
+        <v>4.1805</v>
       </c>
       <c r="P97" t="n">
         <v>3</v>
@@ -7080,7 +7080,7 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>8.609999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="L98" t="n">
         <v>5.51</v>
@@ -7092,13 +7092,13 @@
         <v>10</v>
       </c>
       <c r="O98" t="n">
-        <v>8.0115</v>
+        <v>8.1525</v>
       </c>
       <c r="P98" t="n">
         <v>1</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.17</v>
+        <v>0.119</v>
       </c>
       <c r="R98" t="n">
         <v>1.77</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>8.609999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="L99" t="n">
         <v>5.51</v>
@@ -7160,13 +7160,13 @@
         <v>4.64</v>
       </c>
       <c r="O99" t="n">
-        <v>6.249499999999999</v>
+        <v>6.390499999999999</v>
       </c>
       <c r="P99" t="n">
         <v>3</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.17</v>
+        <v>0.119</v>
       </c>
       <c r="R99" t="n">
         <v>1.77</v>
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>8.609999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="L100" t="n">
         <v>5.51</v>
@@ -7228,13 +7228,13 @@
         <v>5.71</v>
       </c>
       <c r="O100" t="n">
-        <v>6.933999999999999</v>
+        <v>7.074999999999999</v>
       </c>
       <c r="P100" t="n">
         <v>2</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.17</v>
+        <v>0.119</v>
       </c>
       <c r="R100" t="n">
         <v>1.77</v>
@@ -7284,7 +7284,7 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>7.98</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L101" t="n">
         <v>3.37</v>
@@ -7296,13 +7296,13 @@
         <v>10</v>
       </c>
       <c r="O101" t="n">
-        <v>7.0735</v>
+        <v>7.2685</v>
       </c>
       <c r="P101" t="n">
         <v>1</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.24</v>
+        <v>0.168</v>
       </c>
       <c r="R101" t="n">
         <v>2.498</v>
@@ -7352,7 +7352,7 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>7.98</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L102" t="n">
         <v>3.37</v>
@@ -7364,13 +7364,13 @@
         <v>5.67</v>
       </c>
       <c r="O102" t="n">
-        <v>5.562</v>
+        <v>5.757000000000001</v>
       </c>
       <c r="P102" t="n">
         <v>2</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.24</v>
+        <v>0.168</v>
       </c>
       <c r="R102" t="n">
         <v>2.498</v>
@@ -7420,7 +7420,7 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>7.98</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L103" t="n">
         <v>3.83</v>
@@ -7432,13 +7432,13 @@
         <v>2.47</v>
       </c>
       <c r="O103" t="n">
-        <v>4.353</v>
+        <v>4.548</v>
       </c>
       <c r="P103" t="n">
         <v>3</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.24</v>
+        <v>0.168</v>
       </c>
       <c r="R103" t="n">
         <v>2.342</v>

--- a/workbooks/scenarios/ApplianceRAGScenarios.xlsx
+++ b/workbooks/scenarios/ApplianceRAGScenarios.xlsx
@@ -552,10 +552,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>7.8</v>
+        <v>6.56</v>
       </c>
       <c r="L2" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="M2" t="n">
         <v>9.460000000000001</v>
@@ -564,7 +564,7 @@
         <v>9.15</v>
       </c>
       <c r="O2" t="n">
-        <v>6.3535</v>
+        <v>5.992000000000001</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -620,10 +620,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>7.8</v>
+        <v>6.56</v>
       </c>
       <c r="L3" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="M3" t="n">
         <v>8.9</v>
@@ -632,7 +632,7 @@
         <v>8.23</v>
       </c>
       <c r="O3" t="n">
-        <v>6.103499999999999</v>
+        <v>5.742</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5.46</v>
+        <v>2.8</v>
       </c>
       <c r="L4" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="M4" t="n">
         <v>6.74</v>
@@ -700,7 +700,7 @@
         <v>5.4</v>
       </c>
       <c r="O4" t="n">
-        <v>4.545</v>
+        <v>3.7575</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>7.21</v>
+        <v>5.61</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -768,7 +768,7 @@
         <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>5.663</v>
+        <v>5.183</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7.21</v>
+        <v>5.61</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>6.66</v>
       </c>
       <c r="O6" t="n">
-        <v>4.723999999999999</v>
+        <v>4.244</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4.29</v>
+        <v>0.91</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>4.31</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1175</v>
+        <v>2.1035</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>9.94</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>9.65</v>
+        <v>9.77</v>
       </c>
       <c r="M8" t="n">
         <v>10</v>
@@ -972,7 +972,7 @@
         <v>10</v>
       </c>
       <c r="O8" t="n">
-        <v>9.859500000000001</v>
+        <v>9.919499999999999</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>9.65</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>9.65</v>
+        <v>9.77</v>
       </c>
       <c r="M9" t="n">
         <v>6.92</v>
@@ -1040,7 +1040,7 @@
         <v>5.61</v>
       </c>
       <c r="O9" t="n">
-        <v>8.498000000000001</v>
+        <v>8.51</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>9.94</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>9.710000000000001</v>
+        <v>9.84</v>
       </c>
       <c r="M10" t="n">
         <v>3.83</v>
@@ -1108,7 +1108,7 @@
         <v>1.51</v>
       </c>
       <c r="O10" t="n">
-        <v>7.372999999999999</v>
+        <v>7.4365</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>9.4</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>7.35</v>
+        <v>7.45</v>
       </c>
       <c r="M11" t="n">
         <v>10</v>
@@ -1176,7 +1176,7 @@
         <v>10</v>
       </c>
       <c r="O11" t="n">
-        <v>8.8925</v>
+        <v>8.849499999999999</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>6.97</v>
+        <v>5.23</v>
       </c>
       <c r="L12" t="n">
-        <v>7.35</v>
+        <v>7.45</v>
       </c>
       <c r="M12" t="n">
         <v>7.83</v>
@@ -1244,7 +1244,7 @@
         <v>6.69</v>
       </c>
       <c r="O12" t="n">
-        <v>7.232999999999999</v>
+        <v>6.746</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>9.4</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>7.35</v>
+        <v>7.45</v>
       </c>
       <c r="M13" t="n">
         <v>6.29</v>
@@ -1312,7 +1312,7 @@
         <v>4.78</v>
       </c>
       <c r="O13" t="n">
-        <v>7.3675</v>
+        <v>7.3245</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
@@ -1368,10 +1368,10 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>9.869999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="L14" t="n">
-        <v>9.34</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>10</v>
@@ -1380,7 +1380,7 @@
         <v>10</v>
       </c>
       <c r="O14" t="n">
-        <v>9.73</v>
+        <v>9.783999999999999</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>9.869999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="L15" t="n">
-        <v>9.34</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M15" t="n">
         <v>4.71</v>
@@ -1448,7 +1448,7 @@
         <v>2.95</v>
       </c>
       <c r="O15" t="n">
-        <v>7.6145</v>
+        <v>7.6685</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>9.869999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="L16" t="n">
-        <v>9.43</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="M16" t="n">
         <v>2.86</v>
@@ -1516,7 +1516,7 @@
         <v>1.51</v>
       </c>
       <c r="O16" t="n">
-        <v>7.06</v>
+        <v>7.114</v>
       </c>
       <c r="P16" t="n">
         <v>3</v>
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>6.67</v>
+        <v>4.74</v>
       </c>
       <c r="L17" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="M17" t="n">
         <v>10</v>
@@ -1584,7 +1584,7 @@
         <v>10</v>
       </c>
       <c r="O17" t="n">
-        <v>6.25</v>
+        <v>5.6815</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>6.67</v>
+        <v>4.74</v>
       </c>
       <c r="L18" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="M18" t="n">
         <v>7.29</v>
@@ -1652,7 +1652,7 @@
         <v>6.04</v>
       </c>
       <c r="O18" t="n">
-        <v>5.114</v>
+        <v>4.5455</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>6.67</v>
+        <v>4.74</v>
       </c>
       <c r="L19" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="M19" t="n">
         <v>2.35</v>
@@ -1720,7 +1720,7 @@
         <v>2.13</v>
       </c>
       <c r="O19" t="n">
-        <v>3.7285</v>
+        <v>3.16</v>
       </c>
       <c r="P19" t="n">
         <v>3</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>9.869999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="L20" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
         <v>10</v>
       </c>
       <c r="O20" t="n">
-        <v>9.961</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>9.82</v>
+        <v>9.83</v>
       </c>
       <c r="L23" t="n">
         <v>10</v>
@@ -1992,7 +1992,7 @@
         <v>10</v>
       </c>
       <c r="O23" t="n">
-        <v>9.946</v>
+        <v>9.949</v>
       </c>
       <c r="P23" t="n">
         <v>1</v>
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>7.94</v>
+        <v>6.79</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>10</v>
       </c>
       <c r="O26" t="n">
-        <v>5.882</v>
+        <v>5.537</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>7.94</v>
+        <v>6.79</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2264,7 +2264,7 @@
         <v>3.42</v>
       </c>
       <c r="O27" t="n">
-        <v>3.921</v>
+        <v>3.576</v>
       </c>
       <c r="P27" t="n">
         <v>3</v>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>7.94</v>
+        <v>6.79</v>
       </c>
       <c r="L28" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="M28" t="n">
         <v>5.06</v>
@@ -2332,7 +2332,7 @@
         <v>3.88</v>
       </c>
       <c r="O28" t="n">
-        <v>4.210500000000001</v>
+        <v>3.869</v>
       </c>
       <c r="P28" t="n">
         <v>2</v>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>8.07</v>
+        <v>7</v>
       </c>
       <c r="L29" t="n">
-        <v>8.51</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M29" t="n">
         <v>10</v>
@@ -2400,7 +2400,7 @@
         <v>10</v>
       </c>
       <c r="O29" t="n">
-        <v>8.8995</v>
+        <v>8.616999999999999</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>9.66</v>
+        <v>9.57</v>
       </c>
       <c r="L30" t="n">
-        <v>8.51</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M30" t="n">
         <v>7.43</v>
@@ -2468,7 +2468,7 @@
         <v>6.21</v>
       </c>
       <c r="O30" t="n">
-        <v>8.294</v>
+        <v>8.3055</v>
       </c>
       <c r="P30" t="n">
         <v>2</v>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>9.66</v>
+        <v>9.57</v>
       </c>
       <c r="L31" t="n">
-        <v>8.51</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M31" t="n">
         <v>7</v>
@@ -2536,7 +2536,7 @@
         <v>4.64</v>
       </c>
       <c r="O31" t="n">
-        <v>7.9725</v>
+        <v>7.984</v>
       </c>
       <c r="P31" t="n">
         <v>3</v>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>8.44</v>
+        <v>7.59</v>
       </c>
       <c r="L32" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="M32" t="n">
         <v>7.83</v>
@@ -2604,7 +2604,7 @@
         <v>9.25</v>
       </c>
       <c r="O32" t="n">
-        <v>6.5565</v>
+        <v>6.3155</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>8.44</v>
+        <v>7.59</v>
       </c>
       <c r="L33" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="M33" t="n">
         <v>4.71</v>
@@ -2672,7 +2672,7 @@
         <v>2.95</v>
       </c>
       <c r="O33" t="n">
-        <v>4.9875</v>
+        <v>4.746499999999999</v>
       </c>
       <c r="P33" t="n">
         <v>2</v>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="M34" t="n">
         <v>5.92</v>
@@ -2740,7 +2740,7 @@
         <v>4.31</v>
       </c>
       <c r="O34" t="n">
-        <v>3.7715</v>
+        <v>2.9155</v>
       </c>
       <c r="P34" t="n">
         <v>3</v>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>9.800000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>9.43</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="M35" t="n">
         <v>8.300000000000001</v>
@@ -2808,7 +2808,7 @@
         <v>9.25</v>
       </c>
       <c r="O35" t="n">
-        <v>9.287999999999998</v>
+        <v>9.327</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>9.800000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>9.34</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M36" t="n">
         <v>5.53</v>
@@ -2876,7 +2876,7 @@
         <v>3.87</v>
       </c>
       <c r="O36" t="n">
-        <v>7.895499999999999</v>
+        <v>7.934499999999999</v>
       </c>
       <c r="P36" t="n">
         <v>3</v>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="K37" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="L37" t="n">
         <v>9.460000000000001</v>
-      </c>
-      <c r="L37" t="n">
-        <v>9.34</v>
       </c>
       <c r="M37" t="n">
         <v>5.92</v>
@@ -2944,7 +2944,7 @@
         <v>4.64</v>
       </c>
       <c r="O37" t="n">
-        <v>7.986999999999999</v>
+        <v>7.963</v>
       </c>
       <c r="P37" t="n">
         <v>2</v>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>6.53</v>
+        <v>4.53</v>
       </c>
       <c r="L38" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="M38" t="n">
         <v>10</v>
@@ -3012,7 +3012,7 @@
         <v>10</v>
       </c>
       <c r="O38" t="n">
-        <v>6.53</v>
+        <v>5.944</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>6.53</v>
+        <v>4.53</v>
       </c>
       <c r="L39" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="M39" t="n">
         <v>8.73</v>
@@ -3080,7 +3080,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>5.980500000000001</v>
+        <v>5.394500000000001</v>
       </c>
       <c r="P39" t="n">
         <v>2</v>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>8.57</v>
+        <v>7.81</v>
       </c>
       <c r="L40" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="M40" t="n">
         <v>6.11</v>
@@ -3148,7 +3148,7 @@
         <v>4.64</v>
       </c>
       <c r="O40" t="n">
-        <v>5.56</v>
+        <v>5.346</v>
       </c>
       <c r="P40" t="n">
         <v>3</v>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>9.460000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="L41" t="n">
-        <v>7.35</v>
+        <v>7.45</v>
       </c>
       <c r="M41" t="n">
         <v>10</v>
@@ -3216,7 +3216,7 @@
         <v>10</v>
       </c>
       <c r="O41" t="n">
-        <v>8.910499999999999</v>
+        <v>8.8795</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>8.56</v>
+        <v>7.8</v>
       </c>
       <c r="L42" t="n">
-        <v>7.35</v>
+        <v>7.45</v>
       </c>
       <c r="M42" t="n">
         <v>7.09</v>
@@ -3284,7 +3284,7 @@
         <v>5.81</v>
       </c>
       <c r="O42" t="n">
-        <v>7.43</v>
+        <v>7.237</v>
       </c>
       <c r="P42" t="n">
         <v>2</v>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>9.460000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="L43" t="n">
-        <v>7.35</v>
+        <v>7.45</v>
       </c>
       <c r="M43" t="n">
         <v>4.78</v>
@@ -3352,7 +3352,7 @@
         <v>4.64</v>
       </c>
       <c r="O43" t="n">
-        <v>7.0625</v>
+        <v>7.0315</v>
       </c>
       <c r="P43" t="n">
         <v>3</v>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>9.92</v>
+        <v>9.98</v>
       </c>
       <c r="L44" t="n">
-        <v>9.630000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="M44" t="n">
         <v>7.83</v>
@@ -3420,7 +3420,7 @@
         <v>8.449999999999999</v>
       </c>
       <c r="O44" t="n">
-        <v>9.18</v>
+        <v>9.239999999999998</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>9.92</v>
+        <v>9.98</v>
       </c>
       <c r="L45" t="n">
-        <v>9.550000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="M45" t="n">
         <v>5.23</v>
@@ -3488,7 +3488,7 @@
         <v>4.64</v>
       </c>
       <c r="O45" t="n">
-        <v>8.060500000000001</v>
+        <v>8.124000000000001</v>
       </c>
       <c r="P45" t="n">
         <v>2</v>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>9.609999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="L46" t="n">
-        <v>9.550000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="M46" t="n">
         <v>3.94</v>
@@ -3556,7 +3556,7 @@
         <v>2.03</v>
       </c>
       <c r="O46" t="n">
-        <v>7.318000000000001</v>
+        <v>7.3245</v>
       </c>
       <c r="P46" t="n">
         <v>3</v>
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>7.89</v>
+        <v>6.72</v>
       </c>
       <c r="L47" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="M47" t="n">
         <v>10</v>
@@ -3624,7 +3624,7 @@
         <v>10</v>
       </c>
       <c r="O47" t="n">
-        <v>6.938</v>
+        <v>6.601</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>5.56</v>
+        <v>2.96</v>
       </c>
       <c r="L48" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="M48" t="n">
         <v>7.81</v>
@@ -3692,7 +3692,7 @@
         <v>6.66</v>
       </c>
       <c r="O48" t="n">
-        <v>5.3</v>
+        <v>4.534</v>
       </c>
       <c r="P48" t="n">
         <v>2</v>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>7.89</v>
+        <v>6.72</v>
       </c>
       <c r="L49" t="n">
-        <v>3.54</v>
+        <v>3.59</v>
       </c>
       <c r="M49" t="n">
         <v>2.86</v>
@@ -3760,7 +3760,7 @@
         <v>1.51</v>
       </c>
       <c r="O49" t="n">
-        <v>4.4045</v>
+        <v>4.071</v>
       </c>
       <c r="P49" t="n">
         <v>3</v>
@@ -3816,11 +3816,11 @@
         </is>
       </c>
       <c r="K50" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L50" t="n">
         <v>9.869999999999999</v>
       </c>
-      <c r="L50" t="n">
-        <v>9.74</v>
-      </c>
       <c r="M50" t="n">
         <v>10</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>10</v>
       </c>
       <c r="O50" t="n">
-        <v>9.869999999999999</v>
+        <v>9.9245</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>9.57</v>
+        <v>9.42</v>
       </c>
       <c r="L51" t="n">
-        <v>9.74</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="M51" t="n">
         <v>7.43</v>
@@ -3896,7 +3896,7 @@
         <v>6.21</v>
       </c>
       <c r="O51" t="n">
-        <v>8.6975</v>
+        <v>8.698</v>
       </c>
       <c r="P51" t="n">
         <v>2</v>
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="K52" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L52" t="n">
         <v>9.869999999999999</v>
-      </c>
-      <c r="L52" t="n">
-        <v>9.74</v>
       </c>
       <c r="M52" t="n">
         <v>1.53</v>
@@ -3964,7 +3964,7 @@
         <v>2.2</v>
       </c>
       <c r="O52" t="n">
-        <v>7.005999999999999</v>
+        <v>7.0605</v>
       </c>
       <c r="P52" t="n">
         <v>3</v>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>9.720000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="L53" t="n">
         <v>10</v>
@@ -4032,7 +4032,7 @@
         <v>10</v>
       </c>
       <c r="O53" t="n">
-        <v>9.916</v>
+        <v>9.898</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>7.04</v>
+        <v>5.35</v>
       </c>
       <c r="L56" t="n">
-        <v>3.54</v>
+        <v>3.59</v>
       </c>
       <c r="M56" t="n">
         <v>7.83</v>
@@ -4236,7 +4236,7 @@
         <v>8.449999999999999</v>
       </c>
       <c r="O56" t="n">
-        <v>6.1845</v>
+        <v>5.694999999999999</v>
       </c>
       <c r="P56" t="n">
         <v>1</v>
@@ -4292,10 +4292,10 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>7.04</v>
+        <v>5.35</v>
       </c>
       <c r="L57" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="M57" t="n">
         <v>5.53</v>
@@ -4304,7 +4304,7 @@
         <v>3.87</v>
       </c>
       <c r="O57" t="n">
-        <v>4.869499999999999</v>
+        <v>4.376499999999999</v>
       </c>
       <c r="P57" t="n">
         <v>2</v>
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>7.04</v>
+        <v>5.35</v>
       </c>
       <c r="L58" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="M58" t="n">
         <v>5.13</v>
@@ -4372,7 +4372,7 @@
         <v>3.42</v>
       </c>
       <c r="O58" t="n">
-        <v>4.722</v>
+        <v>4.228999999999999</v>
       </c>
       <c r="P58" t="n">
         <v>3</v>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>9.800000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>9.51</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="M59" t="n">
         <v>7.83</v>
@@ -4440,7 +4440,7 @@
         <v>9.25</v>
       </c>
       <c r="O59" t="n">
-        <v>9.222</v>
+        <v>9.2645</v>
       </c>
       <c r="P59" t="n">
         <v>1</v>
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>9.800000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>9.43</v>
+        <v>9.56</v>
       </c>
       <c r="M60" t="n">
         <v>4.71</v>
@@ -4508,7 +4508,7 @@
         <v>2.95</v>
       </c>
       <c r="O60" t="n">
-        <v>7.624999999999999</v>
+        <v>7.6675</v>
       </c>
       <c r="P60" t="n">
         <v>3</v>
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>9.449999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="L61" t="n">
-        <v>9.43</v>
+        <v>9.56</v>
       </c>
       <c r="M61" t="n">
         <v>5.92</v>
@@ -4576,7 +4576,7 @@
         <v>4.64</v>
       </c>
       <c r="O61" t="n">
-        <v>8.015499999999999</v>
+        <v>7.995</v>
       </c>
       <c r="P61" t="n">
         <v>2</v>
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>9.33</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>7.27</v>
+        <v>7.37</v>
       </c>
       <c r="M62" t="n">
         <v>10</v>
@@ -4644,7 +4644,7 @@
         <v>8.449999999999999</v>
       </c>
       <c r="O62" t="n">
-        <v>8.610999999999999</v>
+        <v>8.555999999999999</v>
       </c>
       <c r="P62" t="n">
         <v>1</v>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>9.33</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>7.04</v>
+        <v>7.14</v>
       </c>
       <c r="M63" t="n">
         <v>8.02</v>
@@ -4712,7 +4712,7 @@
         <v>6.91</v>
       </c>
       <c r="O63" t="n">
-        <v>7.9035</v>
+        <v>7.8485</v>
       </c>
       <c r="P63" t="n">
         <v>2</v>
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>9.33</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>7.04</v>
+        <v>7.14</v>
       </c>
       <c r="M64" t="n">
         <v>5.26</v>
@@ -4780,7 +4780,7 @@
         <v>4.64</v>
       </c>
       <c r="O64" t="n">
-        <v>7.010999999999999</v>
+        <v>6.956</v>
       </c>
       <c r="P64" t="n">
         <v>3</v>
@@ -4836,10 +4836,10 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>8.52</v>
+        <v>7.73</v>
       </c>
       <c r="L65" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M65" t="n">
         <v>10</v>
@@ -4848,7 +4848,7 @@
         <v>10</v>
       </c>
       <c r="O65" t="n">
-        <v>8.680999999999999</v>
+        <v>8.478999999999999</v>
       </c>
       <c r="P65" t="n">
         <v>1</v>
@@ -4904,10 +4904,10 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>9.32</v>
+        <v>9.02</v>
       </c>
       <c r="L66" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M66" t="n">
         <v>7.09</v>
@@ -4916,7 +4916,7 @@
         <v>5.81</v>
       </c>
       <c r="O66" t="n">
-        <v>7.7105</v>
+        <v>7.6555</v>
       </c>
       <c r="P66" t="n">
         <v>2</v>
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>9.32</v>
+        <v>9.02</v>
       </c>
       <c r="L67" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M67" t="n">
         <v>6.17</v>
@@ -4984,7 +4984,7 @@
         <v>3.44</v>
       </c>
       <c r="O67" t="n">
-        <v>7.241</v>
+        <v>7.186</v>
       </c>
       <c r="P67" t="n">
         <v>3</v>
@@ -5040,10 +5040,10 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>7.85</v>
+        <v>6.65</v>
       </c>
       <c r="L68" t="n">
-        <v>5.05</v>
+        <v>5.12</v>
       </c>
       <c r="M68" t="n">
         <v>10</v>
@@ -5052,7 +5052,7 @@
         <v>10</v>
       </c>
       <c r="O68" t="n">
-        <v>7.6225</v>
+        <v>7.287</v>
       </c>
       <c r="P68" t="n">
         <v>1</v>
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>7.85</v>
+        <v>6.65</v>
       </c>
       <c r="L69" t="n">
-        <v>5.05</v>
+        <v>5.12</v>
       </c>
       <c r="M69" t="n">
         <v>7.09</v>
@@ -5120,7 +5120,7 @@
         <v>5.81</v>
       </c>
       <c r="O69" t="n">
-        <v>6.412</v>
+        <v>6.0765</v>
       </c>
       <c r="P69" t="n">
         <v>2</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>7.85</v>
+        <v>6.65</v>
       </c>
       <c r="L70" t="n">
-        <v>5.41</v>
+        <v>5.48</v>
       </c>
       <c r="M70" t="n">
         <v>5.73</v>
@@ -5188,7 +5188,7 @@
         <v>2.89</v>
       </c>
       <c r="O70" t="n">
-        <v>5.827999999999999</v>
+        <v>5.4925</v>
       </c>
       <c r="P70" t="n">
         <v>3</v>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -5256,7 +5256,7 @@
         <v>10</v>
       </c>
       <c r="O71" t="n">
-        <v>4.484</v>
+        <v>3.5</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
@@ -5312,7 +5312,7 @@
         </is>
       </c>
       <c r="K72" t="n">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -5324,7 +5324,7 @@
         <v>4.86</v>
       </c>
       <c r="O72" t="n">
-        <v>3.997</v>
+        <v>3.427</v>
       </c>
       <c r="P72" t="n">
         <v>2</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>1.51</v>
       </c>
       <c r="O73" t="n">
-        <v>2.4845</v>
+        <v>1.9145</v>
       </c>
       <c r="P73" t="n">
         <v>3</v>
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>8.83</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>4.29</v>
+        <v>4.34</v>
       </c>
       <c r="M74" t="n">
         <v>10</v>
@@ -5460,7 +5460,7 @@
         <v>10</v>
       </c>
       <c r="O74" t="n">
-        <v>7.6505</v>
+        <v>7.485</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
@@ -5516,10 +5516,10 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>7.11</v>
+        <v>5.46</v>
       </c>
       <c r="L75" t="n">
-        <v>4.29</v>
+        <v>4.34</v>
       </c>
       <c r="M75" t="n">
         <v>8.02</v>
@@ -5528,7 +5528,7 @@
         <v>6.91</v>
       </c>
       <c r="O75" t="n">
-        <v>6.275</v>
+        <v>5.7975</v>
       </c>
       <c r="P75" t="n">
         <v>2</v>
@@ -5584,10 +5584,10 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>8.83</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="M76" t="n">
         <v>4.78</v>
@@ -5596,7 +5596,7 @@
         <v>1.71</v>
       </c>
       <c r="O76" t="n">
-        <v>5.503</v>
+        <v>5.341</v>
       </c>
       <c r="P76" t="n">
         <v>3</v>
@@ -5652,10 +5652,10 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>6.82</v>
+        <v>4.99</v>
       </c>
       <c r="L77" t="n">
-        <v>7.2</v>
+        <v>7.29</v>
       </c>
       <c r="M77" t="n">
         <v>10</v>
@@ -5664,10 +5664,10 @@
         <v>10</v>
       </c>
       <c r="O77" t="n">
-        <v>8.065999999999999</v>
+        <v>7.5485</v>
       </c>
       <c r="P77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q77" t="n">
         <v>0.368</v>
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>9.369999999999999</v>
+        <v>9.09</v>
       </c>
       <c r="L78" t="n">
-        <v>7.42</v>
+        <v>7.51</v>
       </c>
       <c r="M78" t="n">
         <v>7.43</v>
@@ -5732,10 +5732,10 @@
         <v>5.19</v>
       </c>
       <c r="O78" t="n">
-        <v>7.672499999999999</v>
+        <v>7.619999999999999</v>
       </c>
       <c r="P78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q78" t="n">
         <v>0.08740000000000001</v>
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>9.369999999999999</v>
+        <v>9.09</v>
       </c>
       <c r="L79" t="n">
-        <v>7.2</v>
+        <v>7.29</v>
       </c>
       <c r="M79" t="n">
         <v>6.29</v>
@@ -5800,7 +5800,7 @@
         <v>4.78</v>
       </c>
       <c r="O79" t="n">
-        <v>7.305999999999999</v>
+        <v>7.253499999999999</v>
       </c>
       <c r="P79" t="n">
         <v>3</v>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>9.94</v>
+        <v>10</v>
       </c>
       <c r="L80" t="n">
-        <v>9.74</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="M80" t="n">
         <v>10</v>
@@ -5868,7 +5868,7 @@
         <v>10</v>
       </c>
       <c r="O80" t="n">
-        <v>9.891</v>
+        <v>9.954499999999999</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
@@ -5924,10 +5924,10 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>9.23</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>9.74</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="M81" t="n">
         <v>7.83</v>
@@ -5936,7 +5936,7 @@
         <v>6.69</v>
       </c>
       <c r="O81" t="n">
-        <v>8.7475</v>
+        <v>8.684999999999999</v>
       </c>
       <c r="P81" t="n">
         <v>2</v>
@@ -5992,10 +5992,10 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>9.94</v>
+        <v>10</v>
       </c>
       <c r="L82" t="n">
-        <v>9.800000000000001</v>
+        <v>9.93</v>
       </c>
       <c r="M82" t="n">
         <v>2.08</v>
@@ -6004,7 +6004,7 @@
         <v>2.7</v>
       </c>
       <c r="O82" t="n">
-        <v>7.233000000000001</v>
+        <v>7.296500000000001</v>
       </c>
       <c r="P82" t="n">
         <v>3</v>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>8.16</v>
+        <v>7.15</v>
       </c>
       <c r="L83" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="M83" t="n">
         <v>10</v>
@@ -6072,7 +6072,7 @@
         <v>10</v>
       </c>
       <c r="O83" t="n">
-        <v>6.592000000000001</v>
+        <v>6.296</v>
       </c>
       <c r="P83" t="n">
         <v>1</v>
@@ -6128,10 +6128,10 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="M84" t="n">
         <v>7.29</v>
@@ -6140,10 +6140,10 @@
         <v>6.04</v>
       </c>
       <c r="O84" t="n">
-        <v>3.53</v>
+        <v>3.015</v>
       </c>
       <c r="P84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q84" t="n">
         <v>0.928</v>
@@ -6196,10 +6196,10 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>8.16</v>
+        <v>7.15</v>
       </c>
       <c r="L85" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="M85" t="n">
         <v>0.9399999999999999</v>
@@ -6208,10 +6208,10 @@
         <v>1.61</v>
       </c>
       <c r="O85" t="n">
-        <v>3.5215</v>
+        <v>3.2255</v>
       </c>
       <c r="P85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q85" t="n">
         <v>0.2204</v>
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>6.68</v>
+        <v>4.76</v>
       </c>
       <c r="L86" t="n">
-        <v>7.04</v>
+        <v>7.14</v>
       </c>
       <c r="M86" t="n">
         <v>10</v>
@@ -6276,10 +6276,10 @@
         <v>10</v>
       </c>
       <c r="O86" t="n">
-        <v>7.968</v>
+        <v>7.427</v>
       </c>
       <c r="P86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q86" t="n">
         <v>0.384</v>
@@ -6332,10 +6332,10 @@
         </is>
       </c>
       <c r="K87" t="n">
-        <v>9.33</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="L87" t="n">
-        <v>7.04</v>
+        <v>7.14</v>
       </c>
       <c r="M87" t="n">
         <v>7.09</v>
@@ -6344,10 +6344,10 @@
         <v>5.81</v>
       </c>
       <c r="O87" t="n">
-        <v>7.5525</v>
+        <v>7.4975</v>
       </c>
       <c r="P87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q87" t="n">
         <v>0.0912</v>
@@ -6400,10 +6400,10 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>9.33</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="L88" t="n">
-        <v>7.27</v>
+        <v>7.37</v>
       </c>
       <c r="M88" t="n">
         <v>4.28</v>
@@ -6412,7 +6412,7 @@
         <v>1.51</v>
       </c>
       <c r="O88" t="n">
-        <v>6.425999999999999</v>
+        <v>6.370999999999999</v>
       </c>
       <c r="P88" t="n">
         <v>3</v>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>9.890000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="L89" t="n">
-        <v>9.43</v>
+        <v>9.56</v>
       </c>
       <c r="M89" t="n">
         <v>10</v>
@@ -6480,7 +6480,7 @@
         <v>10</v>
       </c>
       <c r="O89" t="n">
-        <v>9.7675</v>
+        <v>9.827999999999999</v>
       </c>
       <c r="P89" t="n">
         <v>1</v>
@@ -6536,10 +6536,10 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>9.890000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="L90" t="n">
-        <v>9.51</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="M90" t="n">
         <v>5.82</v>
@@ -6548,7 +6548,7 @@
         <v>5.81</v>
       </c>
       <c r="O90" t="n">
-        <v>8.331</v>
+        <v>8.391499999999999</v>
       </c>
       <c r="P90" t="n">
         <v>2</v>
@@ -6604,10 +6604,10 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>9.890000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="L91" t="n">
-        <v>9.43</v>
+        <v>9.56</v>
       </c>
       <c r="M91" t="n">
         <v>4.71</v>
@@ -6616,7 +6616,7 @@
         <v>2.95</v>
       </c>
       <c r="O91" t="n">
-        <v>7.652</v>
+        <v>7.712499999999999</v>
       </c>
       <c r="P91" t="n">
         <v>3</v>
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="K92" t="n">
-        <v>8.02</v>
+        <v>6.93</v>
       </c>
       <c r="L92" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M92" t="n">
         <v>10</v>
@@ -6684,7 +6684,7 @@
         <v>10</v>
       </c>
       <c r="O92" t="n">
-        <v>6.336499999999999</v>
+        <v>6.013</v>
       </c>
       <c r="P92" t="n">
         <v>1</v>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="K93" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M93" t="n">
         <v>6.29</v>
@@ -6752,7 +6752,7 @@
         <v>4.86</v>
       </c>
       <c r="O93" t="n">
-        <v>2.7655</v>
+        <v>2.421</v>
       </c>
       <c r="P93" t="n">
         <v>3</v>
@@ -6808,10 +6808,10 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>8.02</v>
+        <v>6.93</v>
       </c>
       <c r="L94" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="M94" t="n">
         <v>2.86</v>
@@ -6820,7 +6820,7 @@
         <v>2.63</v>
       </c>
       <c r="O94" t="n">
-        <v>4.0095</v>
+        <v>3.6895</v>
       </c>
       <c r="P94" t="n">
         <v>2</v>
@@ -6876,10 +6876,10 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>6.92</v>
+        <v>5.15</v>
       </c>
       <c r="L95" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="M95" t="n">
         <v>10</v>
@@ -6888,7 +6888,7 @@
         <v>10</v>
       </c>
       <c r="O95" t="n">
-        <v>6.542</v>
+        <v>6.0215</v>
       </c>
       <c r="P95" t="n">
         <v>1</v>
@@ -6944,10 +6944,10 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>6.92</v>
+        <v>5.15</v>
       </c>
       <c r="L96" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="M96" t="n">
         <v>7.29</v>
@@ -6956,7 +6956,7 @@
         <v>6.04</v>
       </c>
       <c r="O96" t="n">
-        <v>5.406</v>
+        <v>4.8855</v>
       </c>
       <c r="P96" t="n">
         <v>2</v>
@@ -7012,10 +7012,10 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>6.92</v>
+        <v>5.15</v>
       </c>
       <c r="L97" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="M97" t="n">
         <v>3.36</v>
@@ -7024,7 +7024,7 @@
         <v>3.11</v>
       </c>
       <c r="O97" t="n">
-        <v>4.1805</v>
+        <v>3.66</v>
       </c>
       <c r="P97" t="n">
         <v>3</v>
@@ -7080,10 +7080,10 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>9.08</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L98" t="n">
-        <v>5.51</v>
+        <v>5.58</v>
       </c>
       <c r="M98" t="n">
         <v>10</v>
@@ -7092,7 +7092,7 @@
         <v>10</v>
       </c>
       <c r="O98" t="n">
-        <v>8.1525</v>
+        <v>8.042</v>
       </c>
       <c r="P98" t="n">
         <v>1</v>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>9.08</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L99" t="n">
-        <v>5.51</v>
+        <v>5.58</v>
       </c>
       <c r="M99" t="n">
         <v>5.21</v>
@@ -7160,7 +7160,7 @@
         <v>4.64</v>
       </c>
       <c r="O99" t="n">
-        <v>6.390499999999999</v>
+        <v>6.279999999999999</v>
       </c>
       <c r="P99" t="n">
         <v>3</v>
@@ -7216,10 +7216,10 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>9.08</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L100" t="n">
-        <v>5.51</v>
+        <v>5.58</v>
       </c>
       <c r="M100" t="n">
         <v>7.83</v>
@@ -7228,7 +7228,7 @@
         <v>5.71</v>
       </c>
       <c r="O100" t="n">
-        <v>7.074999999999999</v>
+        <v>6.964499999999999</v>
       </c>
       <c r="P100" t="n">
         <v>2</v>
@@ -7284,10 +7284,10 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>8.630000000000001</v>
+        <v>7.91</v>
       </c>
       <c r="L101" t="n">
-        <v>3.37</v>
+        <v>3.41</v>
       </c>
       <c r="M101" t="n">
         <v>10</v>
@@ -7296,7 +7296,7 @@
         <v>10</v>
       </c>
       <c r="O101" t="n">
-        <v>7.2685</v>
+        <v>7.0665</v>
       </c>
       <c r="P101" t="n">
         <v>1</v>
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>8.630000000000001</v>
+        <v>7.91</v>
       </c>
       <c r="L102" t="n">
-        <v>3.37</v>
+        <v>3.41</v>
       </c>
       <c r="M102" t="n">
         <v>5.69</v>
@@ -7364,7 +7364,7 @@
         <v>5.67</v>
       </c>
       <c r="O102" t="n">
-        <v>5.757000000000001</v>
+        <v>5.555</v>
       </c>
       <c r="P102" t="n">
         <v>2</v>
@@ -7420,10 +7420,10 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>8.630000000000001</v>
+        <v>7.91</v>
       </c>
       <c r="L103" t="n">
-        <v>3.83</v>
+        <v>3.88</v>
       </c>
       <c r="M103" t="n">
         <v>1.24</v>
@@ -7432,7 +7432,7 @@
         <v>2.47</v>
       </c>
       <c r="O103" t="n">
-        <v>4.548</v>
+        <v>4.3495</v>
       </c>
       <c r="P103" t="n">
         <v>3</v>
@@ -7488,10 +7488,10 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>9.43</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L104" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M104" t="n">
         <v>10</v>
@@ -7500,7 +7500,7 @@
         <v>10</v>
       </c>
       <c r="O104" t="n">
-        <v>8.954000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="P104" t="n">
         <v>1</v>
@@ -7556,10 +7556,10 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>7.11</v>
+        <v>5.46</v>
       </c>
       <c r="L105" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M105" t="n">
         <v>7.09</v>
@@ -7568,7 +7568,7 @@
         <v>5.81</v>
       </c>
       <c r="O105" t="n">
-        <v>7.0475</v>
+        <v>6.5875</v>
       </c>
       <c r="P105" t="n">
         <v>3</v>
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="K106" t="n">
-        <v>9.43</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L106" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M106" t="n">
         <v>5.73</v>
@@ -7636,7 +7636,7 @@
         <v>2.89</v>
       </c>
       <c r="O106" t="n">
-        <v>7.103499999999999</v>
+        <v>7.0695</v>
       </c>
       <c r="P106" t="n">
         <v>2</v>

--- a/workbooks/scenarios/ApplianceRAGScenarios.xlsx
+++ b/workbooks/scenarios/ApplianceRAGScenarios.xlsx
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6.56</v>
+        <v>0.66</v>
       </c>
       <c r="L2" t="n">
-        <v>2.17</v>
+        <v>0.22</v>
       </c>
       <c r="M2" t="n">
-        <v>9.460000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="N2" t="n">
-        <v>9.15</v>
+        <v>0.91</v>
       </c>
       <c r="O2" t="n">
-        <v>5.992000000000001</v>
+        <v>0.6015</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -620,19 +620,19 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6.56</v>
+        <v>0.66</v>
       </c>
       <c r="L3" t="n">
-        <v>2.17</v>
+        <v>0.22</v>
       </c>
       <c r="M3" t="n">
-        <v>8.9</v>
+        <v>0.89</v>
       </c>
       <c r="N3" t="n">
-        <v>8.23</v>
+        <v>0.82</v>
       </c>
       <c r="O3" t="n">
-        <v>5.742</v>
+        <v>0.5760000000000001</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2.8</v>
+        <v>0.28</v>
       </c>
       <c r="L4" t="n">
-        <v>2.17</v>
+        <v>0.22</v>
       </c>
       <c r="M4" t="n">
-        <v>6.74</v>
+        <v>0.67</v>
       </c>
       <c r="N4" t="n">
-        <v>5.4</v>
+        <v>0.54</v>
       </c>
       <c r="O4" t="n">
-        <v>3.7575</v>
+        <v>0.3760000000000001</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -756,19 +756,19 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>5.183</v>
+        <v>0.518</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>7.81</v>
+        <v>0.78</v>
       </c>
       <c r="N6" t="n">
-        <v>6.66</v>
+        <v>0.67</v>
       </c>
       <c r="O6" t="n">
-        <v>4.244</v>
+        <v>0.4245000000000001</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
@@ -892,19 +892,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.91</v>
+        <v>0.09</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5.92</v>
+        <v>0.59</v>
       </c>
       <c r="N7" t="n">
-        <v>4.31</v>
+        <v>0.43</v>
       </c>
       <c r="O7" t="n">
-        <v>2.1035</v>
+        <v>0.2095</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>9.77</v>
+        <v>0.98</v>
       </c>
       <c r="M8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>9.919499999999999</v>
+        <v>0.993</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1028,19 +1028,19 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>9.550000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="L9" t="n">
-        <v>9.77</v>
+        <v>0.98</v>
       </c>
       <c r="M9" t="n">
-        <v>6.92</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>5.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>8.51</v>
+        <v>0.8499999999999999</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>9.84</v>
+        <v>0.98</v>
       </c>
       <c r="M10" t="n">
-        <v>3.83</v>
+        <v>0.38</v>
       </c>
       <c r="N10" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="O10" t="n">
-        <v>7.4365</v>
+        <v>0.7415</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>9.140000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="L11" t="n">
-        <v>7.45</v>
+        <v>0.74</v>
       </c>
       <c r="M11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>8.849499999999999</v>
+        <v>0.882</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -1232,19 +1232,19 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>5.23</v>
+        <v>0.52</v>
       </c>
       <c r="L12" t="n">
-        <v>7.45</v>
+        <v>0.74</v>
       </c>
       <c r="M12" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="N12" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O12" t="n">
-        <v>6.746</v>
+        <v>0.6715000000000001</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1300,19 +1300,19 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>9.140000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="L13" t="n">
-        <v>7.45</v>
+        <v>0.74</v>
       </c>
       <c r="M13" t="n">
-        <v>6.29</v>
+        <v>0.63</v>
       </c>
       <c r="N13" t="n">
-        <v>4.78</v>
+        <v>0.48</v>
       </c>
       <c r="O13" t="n">
-        <v>7.3245</v>
+        <v>0.73</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
@@ -1368,19 +1368,19 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>9.91</v>
+        <v>0.99</v>
       </c>
       <c r="L14" t="n">
-        <v>9.460000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="M14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>9.783999999999999</v>
+        <v>0.9794999999999999</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
@@ -1436,19 +1436,19 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>9.91</v>
+        <v>0.99</v>
       </c>
       <c r="L15" t="n">
-        <v>9.460000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="M15" t="n">
-        <v>4.71</v>
+        <v>0.47</v>
       </c>
       <c r="N15" t="n">
-        <v>2.95</v>
+        <v>0.3</v>
       </c>
       <c r="O15" t="n">
-        <v>7.6685</v>
+        <v>0.7685</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
@@ -1504,19 +1504,19 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>9.91</v>
+        <v>0.99</v>
       </c>
       <c r="L16" t="n">
-        <v>9.550000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="M16" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="N16" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="O16" t="n">
-        <v>7.114</v>
+        <v>0.71</v>
       </c>
       <c r="P16" t="n">
         <v>3</v>
@@ -1572,19 +1572,19 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>4.74</v>
+        <v>0.47</v>
       </c>
       <c r="L17" t="n">
-        <v>2.17</v>
+        <v>0.22</v>
       </c>
       <c r="M17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>5.6815</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -1640,19 +1640,19 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>4.74</v>
+        <v>0.47</v>
       </c>
       <c r="L18" t="n">
-        <v>2.17</v>
+        <v>0.22</v>
       </c>
       <c r="M18" t="n">
-        <v>7.29</v>
+        <v>0.73</v>
       </c>
       <c r="N18" t="n">
-        <v>6.04</v>
+        <v>0.6</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5455</v>
+        <v>0.454</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
@@ -1708,19 +1708,19 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>4.74</v>
+        <v>0.47</v>
       </c>
       <c r="L19" t="n">
-        <v>2.71</v>
+        <v>0.27</v>
       </c>
       <c r="M19" t="n">
-        <v>2.35</v>
+        <v>0.23</v>
       </c>
       <c r="N19" t="n">
-        <v>2.13</v>
+        <v>0.21</v>
       </c>
       <c r="O19" t="n">
-        <v>3.16</v>
+        <v>0.3129999999999999</v>
       </c>
       <c r="P19" t="n">
         <v>3</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>9.9</v>
+        <v>0.99</v>
       </c>
       <c r="L20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>9.970000000000001</v>
+        <v>0.997</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
@@ -1844,19 +1844,19 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="N21" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O21" t="n">
-        <v>8.756500000000001</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="P21" t="n">
         <v>2</v>
@@ -1912,19 +1912,19 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>3.59</v>
+        <v>0.36</v>
       </c>
       <c r="N22" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="O22" t="n">
-        <v>7.647</v>
+        <v>0.7654999999999998</v>
       </c>
       <c r="P22" t="n">
         <v>3</v>
@@ -1980,19 +1980,19 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>9.83</v>
+        <v>0.98</v>
       </c>
       <c r="L23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>9.949</v>
+        <v>0.9939999999999999</v>
       </c>
       <c r="P23" t="n">
         <v>1</v>
@@ -2048,19 +2048,19 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>5.92</v>
+        <v>0.59</v>
       </c>
       <c r="N24" t="n">
-        <v>4.64</v>
+        <v>0.43</v>
       </c>
       <c r="O24" t="n">
-        <v>8.380000000000001</v>
+        <v>0.8324999999999999</v>
       </c>
       <c r="P24" t="n">
         <v>3</v>
@@ -2116,19 +2116,19 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>6.01</v>
+        <v>0.6</v>
       </c>
       <c r="N25" t="n">
-        <v>5.19</v>
+        <v>0.52</v>
       </c>
       <c r="O25" t="n">
-        <v>8.480499999999999</v>
+        <v>0.8479999999999999</v>
       </c>
       <c r="P25" t="n">
         <v>2</v>
@@ -2184,19 +2184,19 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>6.79</v>
+        <v>0.68</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>5.537</v>
+        <v>0.554</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
@@ -2252,19 +2252,19 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>6.79</v>
+        <v>0.68</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N27" t="n">
-        <v>3.42</v>
+        <v>0.34</v>
       </c>
       <c r="O27" t="n">
-        <v>3.576</v>
+        <v>0.357</v>
       </c>
       <c r="P27" t="n">
         <v>3</v>
@@ -2320,19 +2320,19 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>6.79</v>
+        <v>0.68</v>
       </c>
       <c r="L28" t="n">
-        <v>0.68</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>5.06</v>
+        <v>0.51</v>
       </c>
       <c r="N28" t="n">
-        <v>3.88</v>
+        <v>0.39</v>
       </c>
       <c r="O28" t="n">
-        <v>3.869</v>
+        <v>0.389</v>
       </c>
       <c r="P28" t="n">
         <v>2</v>
@@ -2388,19 +2388,19 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="L29" t="n">
-        <v>8.619999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="M29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>8.616999999999999</v>
+        <v>0.8610000000000001</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
@@ -2456,19 +2456,19 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>9.57</v>
+        <v>0.96</v>
       </c>
       <c r="L30" t="n">
-        <v>8.619999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="M30" t="n">
-        <v>7.43</v>
+        <v>0.74</v>
       </c>
       <c r="N30" t="n">
-        <v>6.21</v>
+        <v>0.62</v>
       </c>
       <c r="O30" t="n">
-        <v>8.3055</v>
+        <v>0.83</v>
       </c>
       <c r="P30" t="n">
         <v>2</v>
@@ -2524,19 +2524,19 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>9.57</v>
+        <v>0.96</v>
       </c>
       <c r="L31" t="n">
-        <v>8.619999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="M31" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="N31" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O31" t="n">
-        <v>7.984</v>
+        <v>0.798</v>
       </c>
       <c r="P31" t="n">
         <v>3</v>
@@ -2592,19 +2592,19 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>7.59</v>
+        <v>0.76</v>
       </c>
       <c r="L32" t="n">
-        <v>3.1</v>
+        <v>0.31</v>
       </c>
       <c r="M32" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="N32" t="n">
-        <v>9.25</v>
+        <v>0.93</v>
       </c>
       <c r="O32" t="n">
-        <v>6.3155</v>
+        <v>0.632</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
@@ -2660,19 +2660,19 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>7.59</v>
+        <v>0.76</v>
       </c>
       <c r="L33" t="n">
-        <v>3.1</v>
+        <v>0.31</v>
       </c>
       <c r="M33" t="n">
-        <v>4.71</v>
+        <v>0.47</v>
       </c>
       <c r="N33" t="n">
-        <v>2.95</v>
+        <v>0.3</v>
       </c>
       <c r="O33" t="n">
-        <v>4.746499999999999</v>
+        <v>0.4755</v>
       </c>
       <c r="P33" t="n">
         <v>2</v>
@@ -2731,16 +2731,16 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>3.1</v>
+        <v>0.31</v>
       </c>
       <c r="M34" t="n">
-        <v>5.92</v>
+        <v>0.59</v>
       </c>
       <c r="N34" t="n">
-        <v>4.31</v>
+        <v>0.43</v>
       </c>
       <c r="O34" t="n">
-        <v>2.9155</v>
+        <v>0.291</v>
       </c>
       <c r="P34" t="n">
         <v>3</v>
@@ -2796,19 +2796,19 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>9.789999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="L35" t="n">
-        <v>9.550000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="M35" t="n">
-        <v>8.300000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="N35" t="n">
-        <v>9.25</v>
+        <v>0.93</v>
       </c>
       <c r="O35" t="n">
-        <v>9.327</v>
+        <v>0.9319999999999999</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
@@ -2864,22 +2864,22 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>9.789999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="L36" t="n">
-        <v>9.460000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="M36" t="n">
-        <v>5.53</v>
+        <v>0.55</v>
       </c>
       <c r="N36" t="n">
-        <v>3.87</v>
+        <v>0.39</v>
       </c>
       <c r="O36" t="n">
-        <v>7.934499999999999</v>
+        <v>0.7949999999999999</v>
       </c>
       <c r="P36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
         <v>0.0396</v>
@@ -2932,22 +2932,22 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>9.24</v>
+        <v>0.92</v>
       </c>
       <c r="L37" t="n">
-        <v>9.460000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="M37" t="n">
-        <v>5.92</v>
+        <v>0.59</v>
       </c>
       <c r="N37" t="n">
-        <v>4.64</v>
+        <v>0.43</v>
       </c>
       <c r="O37" t="n">
-        <v>7.963</v>
+        <v>0.791</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q37" t="n">
         <v>0.0774</v>
@@ -3000,19 +3000,19 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>4.53</v>
+        <v>0.45</v>
       </c>
       <c r="L38" t="n">
-        <v>3.1</v>
+        <v>0.31</v>
       </c>
       <c r="M38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>5.944</v>
+        <v>0.5935</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
@@ -3068,19 +3068,19 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>4.53</v>
+        <v>0.45</v>
       </c>
       <c r="L39" t="n">
-        <v>3.1</v>
+        <v>0.31</v>
       </c>
       <c r="M39" t="n">
-        <v>8.73</v>
+        <v>0.87</v>
       </c>
       <c r="N39" t="n">
-        <v>8.029999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="O39" t="n">
-        <v>5.394500000000001</v>
+        <v>0.5375</v>
       </c>
       <c r="P39" t="n">
         <v>2</v>
@@ -3136,19 +3136,19 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>7.81</v>
+        <v>0.78</v>
       </c>
       <c r="L40" t="n">
-        <v>3.1</v>
+        <v>0.31</v>
       </c>
       <c r="M40" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="N40" t="n">
-        <v>4.64</v>
+        <v>0.46</v>
       </c>
       <c r="O40" t="n">
-        <v>5.346</v>
+        <v>0.5335</v>
       </c>
       <c r="P40" t="n">
         <v>3</v>
@@ -3204,19 +3204,19 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>9.24</v>
+        <v>0.92</v>
       </c>
       <c r="L41" t="n">
-        <v>7.45</v>
+        <v>0.74</v>
       </c>
       <c r="M41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>8.8795</v>
+        <v>0.8850000000000001</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
@@ -3272,19 +3272,19 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>7.8</v>
+        <v>0.78</v>
       </c>
       <c r="L42" t="n">
-        <v>7.45</v>
+        <v>0.74</v>
       </c>
       <c r="M42" t="n">
-        <v>7.09</v>
+        <v>0.71</v>
       </c>
       <c r="N42" t="n">
-        <v>5.81</v>
+        <v>0.58</v>
       </c>
       <c r="O42" t="n">
-        <v>7.237</v>
+        <v>0.722</v>
       </c>
       <c r="P42" t="n">
         <v>2</v>
@@ -3340,19 +3340,19 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>9.24</v>
+        <v>0.92</v>
       </c>
       <c r="L43" t="n">
-        <v>7.45</v>
+        <v>0.74</v>
       </c>
       <c r="M43" t="n">
-        <v>4.78</v>
+        <v>0.48</v>
       </c>
       <c r="N43" t="n">
-        <v>4.64</v>
+        <v>0.3</v>
       </c>
       <c r="O43" t="n">
-        <v>7.0315</v>
+        <v>0.676</v>
       </c>
       <c r="P43" t="n">
         <v>3</v>
@@ -3408,19 +3408,19 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>9.98</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>9.75</v>
+        <v>0.98</v>
       </c>
       <c r="M44" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="N44" t="n">
-        <v>8.449999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="O44" t="n">
-        <v>9.239999999999998</v>
+        <v>0.9265000000000001</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -3476,19 +3476,19 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>9.98</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>9.68</v>
+        <v>0.97</v>
       </c>
       <c r="M45" t="n">
-        <v>5.23</v>
+        <v>0.52</v>
       </c>
       <c r="N45" t="n">
-        <v>4.64</v>
+        <v>0.35</v>
       </c>
       <c r="O45" t="n">
-        <v>8.124000000000001</v>
+        <v>0.7959999999999999</v>
       </c>
       <c r="P45" t="n">
         <v>2</v>
@@ -3544,19 +3544,19 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>9.48</v>
+        <v>0.95</v>
       </c>
       <c r="L46" t="n">
-        <v>9.68</v>
+        <v>0.97</v>
       </c>
       <c r="M46" t="n">
-        <v>3.94</v>
+        <v>0.39</v>
       </c>
       <c r="N46" t="n">
-        <v>2.03</v>
+        <v>0.2</v>
       </c>
       <c r="O46" t="n">
-        <v>7.3245</v>
+        <v>0.7324999999999999</v>
       </c>
       <c r="P46" t="n">
         <v>3</v>
@@ -3612,19 +3612,19 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>6.72</v>
+        <v>0.67</v>
       </c>
       <c r="L47" t="n">
-        <v>3.1</v>
+        <v>0.31</v>
       </c>
       <c r="M47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>6.601</v>
+        <v>0.6595000000000001</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3680,19 +3680,19 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>2.96</v>
+        <v>0.3</v>
       </c>
       <c r="L48" t="n">
-        <v>3.1</v>
+        <v>0.31</v>
       </c>
       <c r="M48" t="n">
-        <v>7.81</v>
+        <v>0.78</v>
       </c>
       <c r="N48" t="n">
-        <v>6.66</v>
+        <v>0.67</v>
       </c>
       <c r="O48" t="n">
-        <v>4.534</v>
+        <v>0.4550000000000001</v>
       </c>
       <c r="P48" t="n">
         <v>2</v>
@@ -3748,19 +3748,19 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>6.72</v>
+        <v>0.67</v>
       </c>
       <c r="L49" t="n">
-        <v>3.59</v>
+        <v>0.36</v>
       </c>
       <c r="M49" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="N49" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="O49" t="n">
-        <v>4.071</v>
+        <v>0.4075</v>
       </c>
       <c r="P49" t="n">
         <v>3</v>
@@ -3816,19 +3816,19 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>9.9</v>
+        <v>0.99</v>
       </c>
       <c r="L50" t="n">
-        <v>9.869999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="M50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>9.9245</v>
+        <v>0.9934999999999999</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -3884,19 +3884,19 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>9.42</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>9.869999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="M51" t="n">
-        <v>7.43</v>
+        <v>0.74</v>
       </c>
       <c r="N51" t="n">
-        <v>6.21</v>
+        <v>0.62</v>
       </c>
       <c r="O51" t="n">
-        <v>8.698</v>
+        <v>0.8694999999999999</v>
       </c>
       <c r="P51" t="n">
         <v>2</v>
@@ -3952,19 +3952,19 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>9.9</v>
+        <v>0.99</v>
       </c>
       <c r="L52" t="n">
-        <v>9.869999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="M52" t="n">
-        <v>1.53</v>
+        <v>0.15</v>
       </c>
       <c r="N52" t="n">
-        <v>2.2</v>
+        <v>0.22</v>
       </c>
       <c r="O52" t="n">
-        <v>7.0605</v>
+        <v>0.7065</v>
       </c>
       <c r="P52" t="n">
         <v>3</v>
@@ -4020,19 +4020,19 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>9.66</v>
+        <v>0.97</v>
       </c>
       <c r="L53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>9.898</v>
+        <v>0.991</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4088,19 +4088,19 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>7.43</v>
+        <v>0.74</v>
       </c>
       <c r="N54" t="n">
-        <v>6.21</v>
+        <v>0.62</v>
       </c>
       <c r="O54" t="n">
-        <v>8.9175</v>
+        <v>0.8909999999999999</v>
       </c>
       <c r="P54" t="n">
         <v>2</v>
@@ -4156,19 +4156,19 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>3.59</v>
+        <v>0.36</v>
       </c>
       <c r="N55" t="n">
-        <v>4.08</v>
+        <v>0.41</v>
       </c>
       <c r="O55" t="n">
-        <v>7.83</v>
+        <v>0.7834999999999999</v>
       </c>
       <c r="P55" t="n">
         <v>3</v>
@@ -4224,19 +4224,19 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>5.35</v>
+        <v>0.53</v>
       </c>
       <c r="L56" t="n">
-        <v>3.59</v>
+        <v>0.36</v>
       </c>
       <c r="M56" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="N56" t="n">
-        <v>8.449999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="O56" t="n">
-        <v>5.694999999999999</v>
+        <v>0.5685</v>
       </c>
       <c r="P56" t="n">
         <v>1</v>
@@ -4292,19 +4292,19 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>5.35</v>
+        <v>0.53</v>
       </c>
       <c r="L57" t="n">
-        <v>3.1</v>
+        <v>0.31</v>
       </c>
       <c r="M57" t="n">
-        <v>5.53</v>
+        <v>0.55</v>
       </c>
       <c r="N57" t="n">
-        <v>3.87</v>
+        <v>0.39</v>
       </c>
       <c r="O57" t="n">
-        <v>4.376499999999999</v>
+        <v>0.4360000000000001</v>
       </c>
       <c r="P57" t="n">
         <v>2</v>
@@ -4360,19 +4360,19 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>5.35</v>
+        <v>0.53</v>
       </c>
       <c r="L58" t="n">
-        <v>3.1</v>
+        <v>0.31</v>
       </c>
       <c r="M58" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="N58" t="n">
-        <v>3.42</v>
+        <v>0.34</v>
       </c>
       <c r="O58" t="n">
-        <v>4.228999999999999</v>
+        <v>0.4205</v>
       </c>
       <c r="P58" t="n">
         <v>3</v>
@@ -4428,19 +4428,19 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>9.789999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="L59" t="n">
-        <v>9.640000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="M59" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="N59" t="n">
-        <v>9.25</v>
+        <v>0.93</v>
       </c>
       <c r="O59" t="n">
-        <v>9.2645</v>
+        <v>0.9255</v>
       </c>
       <c r="P59" t="n">
         <v>1</v>
@@ -4496,19 +4496,19 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>9.789999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="L60" t="n">
-        <v>9.56</v>
+        <v>0.96</v>
       </c>
       <c r="M60" t="n">
-        <v>4.71</v>
+        <v>0.47</v>
       </c>
       <c r="N60" t="n">
-        <v>2.95</v>
+        <v>0.3</v>
       </c>
       <c r="O60" t="n">
-        <v>7.6675</v>
+        <v>0.7689999999999999</v>
       </c>
       <c r="P60" t="n">
         <v>3</v>
@@ -4564,19 +4564,19 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>9.23</v>
+        <v>0.92</v>
       </c>
       <c r="L61" t="n">
-        <v>9.56</v>
+        <v>0.96</v>
       </c>
       <c r="M61" t="n">
-        <v>5.92</v>
+        <v>0.59</v>
       </c>
       <c r="N61" t="n">
-        <v>4.64</v>
+        <v>0.43</v>
       </c>
       <c r="O61" t="n">
-        <v>7.995</v>
+        <v>0.7945</v>
       </c>
       <c r="P61" t="n">
         <v>2</v>
@@ -4632,19 +4632,19 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>9.029999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="L62" t="n">
-        <v>7.37</v>
+        <v>0.74</v>
       </c>
       <c r="M62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>8.449999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="O62" t="n">
-        <v>8.555999999999999</v>
+        <v>0.8565</v>
       </c>
       <c r="P62" t="n">
         <v>1</v>
@@ -4700,19 +4700,19 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>9.029999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="L63" t="n">
-        <v>7.14</v>
+        <v>0.71</v>
       </c>
       <c r="M63" t="n">
-        <v>8.02</v>
+        <v>0.8</v>
       </c>
       <c r="N63" t="n">
-        <v>6.91</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O63" t="n">
-        <v>7.8485</v>
+        <v>0.782</v>
       </c>
       <c r="P63" t="n">
         <v>2</v>
@@ -4768,19 +4768,19 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>9.029999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="L64" t="n">
-        <v>7.14</v>
+        <v>0.71</v>
       </c>
       <c r="M64" t="n">
-        <v>5.26</v>
+        <v>0.53</v>
       </c>
       <c r="N64" t="n">
-        <v>4.64</v>
+        <v>0.36</v>
       </c>
       <c r="O64" t="n">
-        <v>6.956</v>
+        <v>0.6785</v>
       </c>
       <c r="P64" t="n">
         <v>3</v>
@@ -4836,19 +4836,19 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>7.73</v>
+        <v>0.77</v>
       </c>
       <c r="L65" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="M65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>8.478999999999999</v>
+        <v>0.847</v>
       </c>
       <c r="P65" t="n">
         <v>1</v>
@@ -4904,19 +4904,19 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>9.02</v>
+        <v>0.9</v>
       </c>
       <c r="L66" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="M66" t="n">
-        <v>7.09</v>
+        <v>0.71</v>
       </c>
       <c r="N66" t="n">
-        <v>5.81</v>
+        <v>0.58</v>
       </c>
       <c r="O66" t="n">
-        <v>7.6555</v>
+        <v>0.765</v>
       </c>
       <c r="P66" t="n">
         <v>2</v>
@@ -4972,19 +4972,19 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>9.02</v>
+        <v>0.9</v>
       </c>
       <c r="L67" t="n">
-        <v>7.8</v>
+        <v>0.78</v>
       </c>
       <c r="M67" t="n">
-        <v>6.17</v>
+        <v>0.62</v>
       </c>
       <c r="N67" t="n">
-        <v>3.44</v>
+        <v>0.34</v>
       </c>
       <c r="O67" t="n">
-        <v>7.186</v>
+        <v>0.718</v>
       </c>
       <c r="P67" t="n">
         <v>3</v>
@@ -5040,19 +5040,19 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>6.65</v>
+        <v>0.67</v>
       </c>
       <c r="L68" t="n">
-        <v>5.12</v>
+        <v>0.51</v>
       </c>
       <c r="M68" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N68" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>7.287</v>
+        <v>0.7295</v>
       </c>
       <c r="P68" t="n">
         <v>1</v>
@@ -5108,19 +5108,19 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>6.65</v>
+        <v>0.67</v>
       </c>
       <c r="L69" t="n">
-        <v>5.12</v>
+        <v>0.51</v>
       </c>
       <c r="M69" t="n">
-        <v>7.09</v>
+        <v>0.71</v>
       </c>
       <c r="N69" t="n">
-        <v>5.81</v>
+        <v>0.58</v>
       </c>
       <c r="O69" t="n">
-        <v>6.0765</v>
+        <v>0.6084999999999999</v>
       </c>
       <c r="P69" t="n">
         <v>2</v>
@@ -5176,19 +5176,19 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>6.65</v>
+        <v>0.67</v>
       </c>
       <c r="L70" t="n">
-        <v>5.48</v>
+        <v>0.55</v>
       </c>
       <c r="M70" t="n">
-        <v>5.73</v>
+        <v>0.57</v>
       </c>
       <c r="N70" t="n">
-        <v>2.89</v>
+        <v>0.29</v>
       </c>
       <c r="O70" t="n">
-        <v>5.4925</v>
+        <v>0.551</v>
       </c>
       <c r="P70" t="n">
         <v>3</v>
@@ -5250,13 +5250,13 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>3.5</v>
+        <v>0.35</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
@@ -5312,19 +5312,19 @@
         </is>
       </c>
       <c r="K72" t="n">
-        <v>4.8</v>
+        <v>0.48</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>6.29</v>
+        <v>0.63</v>
       </c>
       <c r="N72" t="n">
-        <v>4.86</v>
+        <v>0.49</v>
       </c>
       <c r="O72" t="n">
-        <v>3.427</v>
+        <v>0.3435</v>
       </c>
       <c r="P72" t="n">
         <v>2</v>
@@ -5380,19 +5380,19 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>4.8</v>
+        <v>0.48</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>1.24</v>
+        <v>0.12</v>
       </c>
       <c r="N73" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="O73" t="n">
-        <v>1.9145</v>
+        <v>0.1905</v>
       </c>
       <c r="P73" t="n">
         <v>3</v>
@@ -5448,19 +5448,19 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>8.220000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="L74" t="n">
-        <v>4.34</v>
+        <v>0.43</v>
       </c>
       <c r="M74" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N74" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>7.485</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
@@ -5516,19 +5516,19 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>5.46</v>
+        <v>0.55</v>
       </c>
       <c r="L75" t="n">
-        <v>4.34</v>
+        <v>0.43</v>
       </c>
       <c r="M75" t="n">
-        <v>8.02</v>
+        <v>0.8</v>
       </c>
       <c r="N75" t="n">
-        <v>6.91</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O75" t="n">
-        <v>5.7975</v>
+        <v>0.5790000000000001</v>
       </c>
       <c r="P75" t="n">
         <v>2</v>
@@ -5584,19 +5584,19 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>8.220000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="L76" t="n">
-        <v>4.75</v>
+        <v>0.47</v>
       </c>
       <c r="M76" t="n">
-        <v>4.78</v>
+        <v>0.48</v>
       </c>
       <c r="N76" t="n">
-        <v>1.71</v>
+        <v>0.17</v>
       </c>
       <c r="O76" t="n">
-        <v>5.341</v>
+        <v>0.5319999999999999</v>
       </c>
       <c r="P76" t="n">
         <v>3</v>
@@ -5652,19 +5652,19 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>4.99</v>
+        <v>0.5</v>
       </c>
       <c r="L77" t="n">
-        <v>7.29</v>
+        <v>0.73</v>
       </c>
       <c r="M77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>7.5485</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="P77" t="n">
         <v>2</v>
@@ -5720,19 +5720,19 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>9.09</v>
+        <v>0.91</v>
       </c>
       <c r="L78" t="n">
-        <v>7.51</v>
+        <v>0.75</v>
       </c>
       <c r="M78" t="n">
-        <v>7.43</v>
+        <v>0.74</v>
       </c>
       <c r="N78" t="n">
-        <v>5.19</v>
+        <v>0.52</v>
       </c>
       <c r="O78" t="n">
-        <v>7.619999999999999</v>
+        <v>0.7615</v>
       </c>
       <c r="P78" t="n">
         <v>1</v>
@@ -5788,19 +5788,19 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>9.09</v>
+        <v>0.91</v>
       </c>
       <c r="L79" t="n">
-        <v>7.29</v>
+        <v>0.73</v>
       </c>
       <c r="M79" t="n">
-        <v>6.29</v>
+        <v>0.63</v>
       </c>
       <c r="N79" t="n">
-        <v>4.78</v>
+        <v>0.48</v>
       </c>
       <c r="O79" t="n">
-        <v>7.253499999999999</v>
+        <v>0.7264999999999999</v>
       </c>
       <c r="P79" t="n">
         <v>3</v>
@@ -5856,19 +5856,19 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L80" t="n">
-        <v>9.869999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="M80" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>9.954499999999999</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
@@ -5924,19 +5924,19 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>8.869999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="L81" t="n">
-        <v>9.869999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="M81" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="N81" t="n">
-        <v>6.69</v>
+        <v>0.67</v>
       </c>
       <c r="O81" t="n">
-        <v>8.684999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="P81" t="n">
         <v>2</v>
@@ -5992,19 +5992,19 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L82" t="n">
-        <v>9.93</v>
+        <v>0.99</v>
       </c>
       <c r="M82" t="n">
-        <v>2.08</v>
+        <v>0.21</v>
       </c>
       <c r="N82" t="n">
-        <v>2.7</v>
+        <v>0.27</v>
       </c>
       <c r="O82" t="n">
-        <v>7.296500000000001</v>
+        <v>0.729</v>
       </c>
       <c r="P82" t="n">
         <v>3</v>
@@ -6060,19 +6060,19 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>7.15</v>
+        <v>0.71</v>
       </c>
       <c r="L83" t="n">
-        <v>1.86</v>
+        <v>0.19</v>
       </c>
       <c r="M83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O83" t="n">
-        <v>6.296</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="P83" t="n">
         <v>1</v>
@@ -6131,16 +6131,16 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>1.86</v>
+        <v>0.19</v>
       </c>
       <c r="M84" t="n">
-        <v>7.29</v>
+        <v>0.73</v>
       </c>
       <c r="N84" t="n">
-        <v>6.04</v>
+        <v>0.6</v>
       </c>
       <c r="O84" t="n">
-        <v>3.015</v>
+        <v>0.3025</v>
       </c>
       <c r="P84" t="n">
         <v>3</v>
@@ -6196,19 +6196,19 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>7.15</v>
+        <v>0.71</v>
       </c>
       <c r="L85" t="n">
-        <v>1.86</v>
+        <v>0.19</v>
       </c>
       <c r="M85" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="N85" t="n">
-        <v>1.61</v>
+        <v>0.16</v>
       </c>
       <c r="O85" t="n">
-        <v>3.2255</v>
+        <v>0.3215</v>
       </c>
       <c r="P85" t="n">
         <v>2</v>
@@ -6264,19 +6264,19 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>4.76</v>
+        <v>0.48</v>
       </c>
       <c r="L86" t="n">
-        <v>7.14</v>
+        <v>0.71</v>
       </c>
       <c r="M86" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N86" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>7.427</v>
+        <v>0.7425</v>
       </c>
       <c r="P86" t="n">
         <v>2</v>
@@ -6332,19 +6332,19 @@
         </is>
       </c>
       <c r="K87" t="n">
-        <v>9.029999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="L87" t="n">
-        <v>7.14</v>
+        <v>0.71</v>
       </c>
       <c r="M87" t="n">
-        <v>7.09</v>
+        <v>0.71</v>
       </c>
       <c r="N87" t="n">
-        <v>5.81</v>
+        <v>0.58</v>
       </c>
       <c r="O87" t="n">
-        <v>7.4975</v>
+        <v>0.7474999999999999</v>
       </c>
       <c r="P87" t="n">
         <v>1</v>
@@ -6400,19 +6400,19 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>9.029999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="L88" t="n">
-        <v>7.37</v>
+        <v>0.74</v>
       </c>
       <c r="M88" t="n">
-        <v>4.28</v>
+        <v>0.43</v>
       </c>
       <c r="N88" t="n">
-        <v>1.51</v>
+        <v>0.15</v>
       </c>
       <c r="O88" t="n">
-        <v>6.370999999999999</v>
+        <v>0.6375</v>
       </c>
       <c r="P88" t="n">
         <v>3</v>
@@ -6468,19 +6468,19 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>9.94</v>
+        <v>0.99</v>
       </c>
       <c r="L89" t="n">
-        <v>9.56</v>
+        <v>0.96</v>
       </c>
       <c r="M89" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N89" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O89" t="n">
-        <v>9.827999999999999</v>
+        <v>0.983</v>
       </c>
       <c r="P89" t="n">
         <v>1</v>
@@ -6536,19 +6536,19 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>9.94</v>
+        <v>0.99</v>
       </c>
       <c r="L90" t="n">
-        <v>9.640000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="M90" t="n">
-        <v>5.82</v>
+        <v>0.58</v>
       </c>
       <c r="N90" t="n">
-        <v>5.81</v>
+        <v>0.58</v>
       </c>
       <c r="O90" t="n">
-        <v>8.391499999999999</v>
+        <v>0.836</v>
       </c>
       <c r="P90" t="n">
         <v>2</v>
@@ -6604,19 +6604,19 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>9.94</v>
+        <v>0.99</v>
       </c>
       <c r="L91" t="n">
-        <v>9.56</v>
+        <v>0.96</v>
       </c>
       <c r="M91" t="n">
-        <v>4.71</v>
+        <v>0.47</v>
       </c>
       <c r="N91" t="n">
-        <v>2.95</v>
+        <v>0.3</v>
       </c>
       <c r="O91" t="n">
-        <v>7.712499999999999</v>
+        <v>0.772</v>
       </c>
       <c r="P91" t="n">
         <v>3</v>
@@ -6672,19 +6672,19 @@
         </is>
       </c>
       <c r="K92" t="n">
-        <v>6.93</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L92" t="n">
-        <v>1.24</v>
+        <v>0.12</v>
       </c>
       <c r="M92" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N92" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>6.013</v>
+        <v>0.599</v>
       </c>
       <c r="P92" t="n">
         <v>1</v>
@@ -6743,16 +6743,16 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>1.24</v>
+        <v>0.12</v>
       </c>
       <c r="M93" t="n">
-        <v>6.29</v>
+        <v>0.63</v>
       </c>
       <c r="N93" t="n">
-        <v>4.86</v>
+        <v>0.49</v>
       </c>
       <c r="O93" t="n">
-        <v>2.421</v>
+        <v>0.2415</v>
       </c>
       <c r="P93" t="n">
         <v>3</v>
@@ -6808,19 +6808,19 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>6.93</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L94" t="n">
-        <v>1.84</v>
+        <v>0.18</v>
       </c>
       <c r="M94" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="N94" t="n">
-        <v>2.63</v>
+        <v>0.26</v>
       </c>
       <c r="O94" t="n">
-        <v>3.6895</v>
+        <v>0.367</v>
       </c>
       <c r="P94" t="n">
         <v>2</v>
@@ -6876,19 +6876,19 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>5.15</v>
+        <v>0.51</v>
       </c>
       <c r="L95" t="n">
-        <v>2.79</v>
+        <v>0.28</v>
       </c>
       <c r="M95" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N95" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O95" t="n">
-        <v>6.0215</v>
+        <v>0.601</v>
       </c>
       <c r="P95" t="n">
         <v>1</v>
@@ -6944,19 +6944,19 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>5.15</v>
+        <v>0.51</v>
       </c>
       <c r="L96" t="n">
-        <v>2.79</v>
+        <v>0.28</v>
       </c>
       <c r="M96" t="n">
-        <v>7.29</v>
+        <v>0.73</v>
       </c>
       <c r="N96" t="n">
-        <v>6.04</v>
+        <v>0.6</v>
       </c>
       <c r="O96" t="n">
-        <v>4.8855</v>
+        <v>0.487</v>
       </c>
       <c r="P96" t="n">
         <v>2</v>
@@ -7012,19 +7012,19 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>5.15</v>
+        <v>0.51</v>
       </c>
       <c r="L97" t="n">
-        <v>2.79</v>
+        <v>0.28</v>
       </c>
       <c r="M97" t="n">
-        <v>3.36</v>
+        <v>0.34</v>
       </c>
       <c r="N97" t="n">
-        <v>3.11</v>
+        <v>0.31</v>
       </c>
       <c r="O97" t="n">
-        <v>3.66</v>
+        <v>0.3655</v>
       </c>
       <c r="P97" t="n">
         <v>3</v>
@@ -7080,19 +7080,19 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>8.630000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="L98" t="n">
-        <v>5.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M98" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N98" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>8.042</v>
+        <v>0.804</v>
       </c>
       <c r="P98" t="n">
         <v>1</v>
@@ -7148,19 +7148,19 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>8.630000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="L99" t="n">
-        <v>5.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M99" t="n">
-        <v>5.21</v>
+        <v>0.52</v>
       </c>
       <c r="N99" t="n">
-        <v>4.64</v>
+        <v>0.35</v>
       </c>
       <c r="O99" t="n">
-        <v>6.279999999999999</v>
+        <v>0.6105</v>
       </c>
       <c r="P99" t="n">
         <v>3</v>
@@ -7216,19 +7216,19 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>8.630000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="L100" t="n">
-        <v>5.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M100" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="N100" t="n">
-        <v>5.71</v>
+        <v>0.57</v>
       </c>
       <c r="O100" t="n">
-        <v>6.964499999999999</v>
+        <v>0.6955000000000001</v>
       </c>
       <c r="P100" t="n">
         <v>2</v>
@@ -7284,19 +7284,19 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>7.91</v>
+        <v>0.79</v>
       </c>
       <c r="L101" t="n">
-        <v>3.41</v>
+        <v>0.34</v>
       </c>
       <c r="M101" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N101" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>7.0665</v>
+        <v>0.7060000000000001</v>
       </c>
       <c r="P101" t="n">
         <v>1</v>
@@ -7352,19 +7352,19 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>7.91</v>
+        <v>0.79</v>
       </c>
       <c r="L102" t="n">
-        <v>3.41</v>
+        <v>0.34</v>
       </c>
       <c r="M102" t="n">
-        <v>5.69</v>
+        <v>0.57</v>
       </c>
       <c r="N102" t="n">
-        <v>5.67</v>
+        <v>0.57</v>
       </c>
       <c r="O102" t="n">
-        <v>5.555</v>
+        <v>0.5555</v>
       </c>
       <c r="P102" t="n">
         <v>2</v>
@@ -7420,19 +7420,19 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>7.91</v>
+        <v>0.79</v>
       </c>
       <c r="L103" t="n">
-        <v>3.88</v>
+        <v>0.39</v>
       </c>
       <c r="M103" t="n">
-        <v>1.24</v>
+        <v>0.12</v>
       </c>
       <c r="N103" t="n">
-        <v>2.47</v>
+        <v>0.25</v>
       </c>
       <c r="O103" t="n">
-        <v>4.3495</v>
+        <v>0.4349999999999999</v>
       </c>
       <c r="P103" t="n">
         <v>3</v>
@@ -7488,19 +7488,19 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>9.199999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="L104" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="M104" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N104" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O104" t="n">
-        <v>8.92</v>
+        <v>0.892</v>
       </c>
       <c r="P104" t="n">
         <v>1</v>
@@ -7556,19 +7556,19 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>5.46</v>
+        <v>0.55</v>
       </c>
       <c r="L105" t="n">
-        <v>7.6</v>
+        <v>0.76</v>
       </c>
       <c r="M105" t="n">
-        <v>7.09</v>
+        <v>0.71</v>
       </c>
       <c r="N105" t="n">
-        <v>5.81</v>
+        <v>0.58</v>
       </c>
       <c r="O105" t="n">
-        <v>6.5875</v>
+        <v>0.6599999999999999</v>
       </c>
       <c r="P105" t="n">
         <v>3</v>
@@ -7624,19 +7624,19 @@
         </is>
       </c>
       <c r="K106" t="n">
-        <v>9.199999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="L106" t="n">
-        <v>7.8</v>
+        <v>0.78</v>
       </c>
       <c r="M106" t="n">
-        <v>5.73</v>
+        <v>0.57</v>
       </c>
       <c r="N106" t="n">
-        <v>2.89</v>
+        <v>0.29</v>
       </c>
       <c r="O106" t="n">
-        <v>7.0695</v>
+        <v>0.7064999999999999</v>
       </c>
       <c r="P106" t="n">
         <v>2</v>

--- a/workbooks/scenarios/ApplianceRAGScenarios.xlsx
+++ b/workbooks/scenarios/ApplianceRAGScenarios.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>It's mid-morning, about 10 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-morning, about 10, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -570,7 +570,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2604</v>
+        <v>0.279</v>
       </c>
       <c r="R2" t="n">
         <v>2.915</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>It's mid-morning, about 10 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-morning, about 10, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -632,13 +632,13 @@
         <v>0.82</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5760000000000001</v>
+        <v>0.576</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2604</v>
+        <v>0.279</v>
       </c>
       <c r="R3" t="n">
         <v>2.915</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>It's mid-morning, about 10 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-morning, about 10, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="L4" t="n">
         <v>0.22</v>
@@ -700,13 +700,13 @@
         <v>0.54</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3760000000000001</v>
+        <v>0.382</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.518</v>
+        <v>0.5523</v>
       </c>
       <c r="R4" t="n">
         <v>2.915</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>It's just past 9 AM, when should I run the dryer?</t>
+          <t>It's just past 9 AM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -768,13 +768,13 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.518</v>
+        <v>0.521</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3255</v>
+        <v>0.3487</v>
       </c>
       <c r="R5" t="n">
         <v>3.643</v>
@@ -786,7 +786,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>It's just past 9 AM, when should I run the dryer?</t>
+          <t>It's just past 9 AM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -836,13 +836,13 @@
         <v>0.67</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4245000000000001</v>
+        <v>0.4275</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3255</v>
+        <v>0.3487</v>
       </c>
       <c r="R6" t="n">
         <v>3.643</v>
@@ -854,7 +854,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>It's just past 9 AM, when should I run the dryer?</t>
+          <t>It's just past 9 AM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -904,13 +904,13 @@
         <v>0.43</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2095</v>
+        <v>0.2155</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6475</v>
+        <v>0.6904</v>
       </c>
       <c r="R7" t="n">
         <v>3.643</v>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="L8" t="n">
         <v>0.98</v>
@@ -972,13 +972,13 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.993</v>
+        <v>0.987</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0245</v>
+        <v>0.042</v>
       </c>
       <c r="R8" t="n">
         <v>0.364</v>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="L9" t="n">
         <v>0.98</v>
@@ -1040,13 +1040,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8499999999999999</v>
+        <v>0.859</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.056</v>
+        <v>0.042</v>
       </c>
       <c r="R9" t="n">
         <v>0.364</v>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="L10" t="n">
         <v>0.98</v>
@@ -1108,13 +1108,13 @@
         <v>0.15</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7415</v>
+        <v>0.7355</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0245</v>
+        <v>0.042</v>
       </c>
       <c r="R10" t="n">
         <v>0.342</v>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>It's late morning, around 11 and I need to run the dishwasher. When should I start it?</t>
+          <t>It's late morning, around 11, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1182,7 +1182,7 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0922</v>
       </c>
       <c r="R11" t="n">
         <v>1.145</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>It's late morning, around 11 and I need to run the dishwasher. When should I start it?</t>
+          <t>It's late morning, around 11, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="L12" t="n">
         <v>0.74</v>
@@ -1244,13 +1244,13 @@
         <v>0.67</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6715000000000001</v>
+        <v>0.6805</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.352</v>
+        <v>0.3602</v>
       </c>
       <c r="R12" t="n">
         <v>1.145</v>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>It's late morning, around 11 and I need to run the dishwasher. When should I start it?</t>
+          <t>It's late morning, around 11, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1318,7 +1318,7 @@
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0922</v>
       </c>
       <c r="R13" t="n">
         <v>1.145</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="L14" t="n">
         <v>0.95</v>
@@ -1380,13 +1380,13 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9794999999999999</v>
+        <v>0.9735</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0315</v>
+        <v>0.049</v>
       </c>
       <c r="R14" t="n">
         <v>0.468</v>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="L15" t="n">
         <v>0.95</v>
@@ -1448,13 +1448,13 @@
         <v>0.3</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7685</v>
+        <v>0.7415</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0315</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="R15" t="n">
         <v>0.468</v>
@@ -1522,7 +1522,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0315</v>
+        <v>0.0363</v>
       </c>
       <c r="R16" t="n">
         <v>0.439</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>It's just past 9 AM, when should I run the dryer?</t>
+          <t>It's just past 9 AM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="L17" t="n">
         <v>0.22</v>
@@ -1584,7 +1584,7 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.583</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>It's just past 9 AM, when should I run the dryer?</t>
+          <t>It's just past 9 AM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="L18" t="n">
         <v>0.22</v>
@@ -1652,7 +1652,7 @@
         <v>0.6</v>
       </c>
       <c r="O18" t="n">
-        <v>0.454</v>
+        <v>0.469</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>It's just past 9 AM, when should I run the dryer?</t>
+          <t>It's just past 9 AM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="L19" t="n">
         <v>0.27</v>
@@ -1720,7 +1720,7 @@
         <v>0.21</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3129999999999999</v>
+        <v>0.328</v>
       </c>
       <c r="P19" t="n">
         <v>3</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1794,7 +1794,7 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.032</v>
+        <v>0.0365</v>
       </c>
       <c r="R20" t="n">
         <v>0.208</v>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1862,7 +1862,7 @@
         <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.014</v>
+        <v>0.0187</v>
       </c>
       <c r="R21" t="n">
         <v>0.208</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1924,13 +1924,13 @@
         <v>0.29</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7654999999999998</v>
+        <v>0.7655</v>
       </c>
       <c r="P22" t="n">
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.014</v>
+        <v>0.0138</v>
       </c>
       <c r="R22" t="n">
         <v>0.195</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>It's around 5 in the evening, when should I run the washing machine?</t>
+          <t>It's around 5 in the evening. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
@@ -1992,13 +1992,13 @@
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9939999999999999</v>
+        <v>0.997</v>
       </c>
       <c r="P23" t="n">
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.0368</v>
+        <v>0.0322</v>
       </c>
       <c r="R23" t="n">
         <v>0.239</v>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>It's around 5 in the evening, when should I run the washing machine?</t>
+          <t>It's around 5 in the evening. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2060,13 +2060,13 @@
         <v>0.43</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8324999999999999</v>
+        <v>0.8325</v>
       </c>
       <c r="P24" t="n">
         <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.0161</v>
+        <v>0.0276</v>
       </c>
       <c r="R24" t="n">
         <v>0.239</v>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>It's around 5 in the evening, when should I run the washing machine?</t>
+          <t>It's around 5 in the evening. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2128,13 +2128,13 @@
         <v>0.52</v>
       </c>
       <c r="O25" t="n">
-        <v>0.8479999999999999</v>
+        <v>0.848</v>
       </c>
       <c r="P25" t="n">
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0161</v>
+        <v>0.0276</v>
       </c>
       <c r="R25" t="n">
         <v>0.239</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>It's just past 7 PM, when should I run the dryer?</t>
+          <t>It's just past 7 PM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0.68</v>
+        <v>0.38</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2196,13 +2196,13 @@
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.554</v>
+        <v>0.464</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.245</v>
+        <v>0.4895</v>
       </c>
       <c r="R26" t="n">
         <v>3.643</v>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>It's just past 7 PM, when should I run the dryer?</t>
+          <t>It's just past 7 PM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2264,13 +2264,13 @@
         <v>0.34</v>
       </c>
       <c r="O27" t="n">
-        <v>0.357</v>
+        <v>0.297</v>
       </c>
       <c r="P27" t="n">
         <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.245</v>
+        <v>0.4195</v>
       </c>
       <c r="R27" t="n">
         <v>3.643</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>It's just past 7 PM, when should I run the dryer?</t>
+          <t>It's just past 7 PM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="L28" t="n">
         <v>0.07000000000000001</v>
@@ -2332,13 +2332,13 @@
         <v>0.39</v>
       </c>
       <c r="O28" t="n">
-        <v>0.389</v>
+        <v>0.329</v>
       </c>
       <c r="P28" t="n">
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.245</v>
+        <v>0.4195</v>
       </c>
       <c r="R28" t="n">
         <v>3.416</v>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="L29" t="n">
         <v>0.86</v>
@@ -2400,13 +2400,13 @@
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8610000000000001</v>
+        <v>0.867</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.2304</v>
+        <v>0.2358</v>
       </c>
       <c r="R29" t="n">
         <v>0.75</v>
@@ -2474,7 +2474,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.0547</v>
+        <v>0.0604</v>
       </c>
       <c r="R30" t="n">
         <v>0.75</v>
@@ -2542,7 +2542,7 @@
         <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0547</v>
+        <v>0.0604</v>
       </c>
       <c r="R31" t="n">
         <v>0.75</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>It's late, just past 10 PM and I need to run the dryer. When should I start it?</t>
+          <t>It's late, just past 10 PM, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2610,7 +2610,7 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.19</v>
+        <v>0.2096</v>
       </c>
       <c r="R32" t="n">
         <v>2.603</v>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>It's late, just past 10 PM and I need to run the dryer. When should I start it?</t>
+          <t>It's late, just past 10 PM, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2678,7 +2678,7 @@
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.19</v>
+        <v>0.2096</v>
       </c>
       <c r="R33" t="n">
         <v>2.603</v>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>It's late, just past 10 PM and I need to run the dryer. When should I start it?</t>
+          <t>It's late, just past 10 PM, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2746,7 +2746,7 @@
         <v>3</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.8</v>
+        <v>0.8187</v>
       </c>
       <c r="R34" t="n">
         <v>2.603</v>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>It's getting close to midnight, when should I run the washing machine?</t>
+          <t>It's getting close to midnight. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>0.95</v>
@@ -2808,13 +2808,13 @@
         <v>0.93</v>
       </c>
       <c r="O35" t="n">
-        <v>0.9319999999999999</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.0396</v>
+        <v>0.031</v>
       </c>
       <c r="R35" t="n">
         <v>0.439</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>It's getting close to midnight, when should I run the washing machine?</t>
+          <t>It's getting close to midnight. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2876,13 +2876,13 @@
         <v>0.39</v>
       </c>
       <c r="O36" t="n">
-        <v>0.7949999999999999</v>
+        <v>0.795</v>
       </c>
       <c r="P36" t="n">
         <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0396</v>
+        <v>0.0421</v>
       </c>
       <c r="R36" t="n">
         <v>0.468</v>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>It's getting close to midnight, when should I run the washing machine?</t>
+          <t>It's getting close to midnight. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="L37" t="n">
         <v>0.95</v>
@@ -2944,13 +2944,13 @@
         <v>0.43</v>
       </c>
       <c r="O37" t="n">
-        <v>0.791</v>
+        <v>0.794</v>
       </c>
       <c r="P37" t="n">
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.0774</v>
+        <v>0.082</v>
       </c>
       <c r="R37" t="n">
         <v>0.468</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-afternoon, about 2, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0.45</v>
+        <v>0.64</v>
       </c>
       <c r="L38" t="n">
         <v>0.31</v>
@@ -3012,13 +3012,13 @@
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>0.5935</v>
+        <v>0.6505</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.4</v>
+        <v>0.2997</v>
       </c>
       <c r="R38" t="n">
         <v>2.603</v>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-afternoon, about 2, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="L39" t="n">
         <v>0.31</v>
@@ -3080,13 +3080,13 @@
         <v>0.8</v>
       </c>
       <c r="O39" t="n">
-        <v>0.5375</v>
+        <v>0.5735</v>
       </c>
       <c r="P39" t="n">
         <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.4</v>
+        <v>0.3497</v>
       </c>
       <c r="R39" t="n">
         <v>2.603</v>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-afternoon, about 2, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="L40" t="n">
         <v>0.31</v>
@@ -3148,13 +3148,13 @@
         <v>0.46</v>
       </c>
       <c r="O40" t="n">
-        <v>0.5335</v>
+        <v>0.4915</v>
       </c>
       <c r="P40" t="n">
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.175</v>
+        <v>0.2997</v>
       </c>
       <c r="R40" t="n">
         <v>2.603</v>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>It's just after 8 AM, when should I run the dishwasher?</t>
+          <t>It's just after 9 AM. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="L41" t="n">
         <v>0.74</v>
@@ -3216,13 +3216,13 @@
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>0.8850000000000001</v>
+        <v>0.873</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.077</v>
+        <v>0.1198</v>
       </c>
       <c r="R41" t="n">
         <v>1.145</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>It's just after 8 AM, when should I run the dishwasher?</t>
+          <t>It's just after 9 AM. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3272,7 +3272,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0.78</v>
+        <v>0.71</v>
       </c>
       <c r="L42" t="n">
         <v>0.74</v>
@@ -3284,13 +3284,13 @@
         <v>0.58</v>
       </c>
       <c r="O42" t="n">
-        <v>0.722</v>
+        <v>0.701</v>
       </c>
       <c r="P42" t="n">
         <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.176</v>
+        <v>0.2433</v>
       </c>
       <c r="R42" t="n">
         <v>1.145</v>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>It's just after 8 AM, when should I run the dishwasher?</t>
+          <t>It's just after 9 AM. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0.92</v>
+        <v>0.71</v>
       </c>
       <c r="L43" t="n">
         <v>0.74</v>
@@ -3352,13 +3352,13 @@
         <v>0.3</v>
       </c>
       <c r="O43" t="n">
-        <v>0.676</v>
+        <v>0.613</v>
       </c>
       <c r="P43" t="n">
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.077</v>
+        <v>0.2433</v>
       </c>
       <c r="R43" t="n">
         <v>1.145</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="L44" t="n">
         <v>0.98</v>
@@ -3420,13 +3420,13 @@
         <v>0.85</v>
       </c>
       <c r="O44" t="n">
-        <v>0.9265000000000001</v>
+        <v>0.9205</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.0266</v>
+        <v>0.0456</v>
       </c>
       <c r="R44" t="n">
         <v>0.371</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="L45" t="n">
         <v>0.97</v>
@@ -3488,13 +3488,13 @@
         <v>0.35</v>
       </c>
       <c r="O45" t="n">
-        <v>0.7959999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="P45" t="n">
         <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.0266</v>
+        <v>0.0456</v>
       </c>
       <c r="R45" t="n">
         <v>0.396</v>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="L46" t="n">
         <v>0.97</v>
@@ -3556,13 +3556,13 @@
         <v>0.2</v>
       </c>
       <c r="O46" t="n">
-        <v>0.7324999999999999</v>
+        <v>0.7415</v>
       </c>
       <c r="P46" t="n">
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.0608</v>
+        <v>0.0456</v>
       </c>
       <c r="R46" t="n">
         <v>0.396</v>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>It's late morning, just before noon and I need to run the dryer. When should I start it?</t>
+          <t>It's late morning, just before noon, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3624,13 +3624,13 @@
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>0.6595000000000001</v>
+        <v>0.6595</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.25</v>
+        <v>0.2722</v>
       </c>
       <c r="R47" t="n">
         <v>2.603</v>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>It's late morning, just before noon and I need to run the dryer. When should I start it?</t>
+          <t>It's late morning, just before noon, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3692,13 +3692,13 @@
         <v>0.67</v>
       </c>
       <c r="O48" t="n">
-        <v>0.4550000000000001</v>
+        <v>0.455</v>
       </c>
       <c r="P48" t="n">
         <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.5075</v>
+        <v>0.553</v>
       </c>
       <c r="R48" t="n">
         <v>2.603</v>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>It's late morning, just before noon and I need to run the dryer. When should I start it?</t>
+          <t>It's late morning, just before noon, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="L49" t="n">
         <v>0.36</v>
@@ -3760,13 +3760,13 @@
         <v>0.15</v>
       </c>
       <c r="O49" t="n">
-        <v>0.4075</v>
+        <v>0.4375</v>
       </c>
       <c r="P49" t="n">
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.25</v>
+        <v>0.2014</v>
       </c>
       <c r="R49" t="n">
         <v>2.44</v>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
         <v>0.99</v>
@@ -3828,13 +3828,13 @@
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>0.9934999999999999</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.032</v>
+        <v>0.0299</v>
       </c>
       <c r="R50" t="n">
         <v>0.333</v>
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="L51" t="n">
         <v>0.99</v>
@@ -3896,13 +3896,13 @@
         <v>0.62</v>
       </c>
       <c r="O51" t="n">
-        <v>0.8694999999999999</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="P51" t="n">
         <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.065</v>
+        <v>0.0583</v>
       </c>
       <c r="R51" t="n">
         <v>0.333</v>
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
         <v>0.99</v>
@@ -3964,13 +3964,13 @@
         <v>0.22</v>
       </c>
       <c r="O52" t="n">
-        <v>0.7065</v>
+        <v>0.7095</v>
       </c>
       <c r="P52" t="n">
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.032</v>
+        <v>0.0299</v>
       </c>
       <c r="R52" t="n">
         <v>0.333</v>
@@ -4038,7 +4038,7 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.048</v>
+        <v>0.0491</v>
       </c>
       <c r="R53" t="n">
         <v>0.156</v>
@@ -4100,13 +4100,13 @@
         <v>0.62</v>
       </c>
       <c r="O54" t="n">
-        <v>0.8909999999999999</v>
+        <v>0.891</v>
       </c>
       <c r="P54" t="n">
         <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.0114</v>
+        <v>0.0126</v>
       </c>
       <c r="R54" t="n">
         <v>0.156</v>
@@ -4168,13 +4168,13 @@
         <v>0.41</v>
       </c>
       <c r="O55" t="n">
-        <v>0.7834999999999999</v>
+        <v>0.7835</v>
       </c>
       <c r="P55" t="n">
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.0114</v>
+        <v>0.0126</v>
       </c>
       <c r="R55" t="n">
         <v>0.146</v>
@@ -4224,7 +4224,7 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="L56" t="n">
         <v>0.36</v>
@@ -4236,7 +4236,7 @@
         <v>0.85</v>
       </c>
       <c r="O56" t="n">
-        <v>0.5685</v>
+        <v>0.5835</v>
       </c>
       <c r="P56" t="n">
         <v>1</v>
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="L57" t="n">
         <v>0.31</v>
@@ -4304,7 +4304,7 @@
         <v>0.39</v>
       </c>
       <c r="O57" t="n">
-        <v>0.4360000000000001</v>
+        <v>0.451</v>
       </c>
       <c r="P57" t="n">
         <v>2</v>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="L58" t="n">
         <v>0.31</v>
@@ -4372,7 +4372,7 @@
         <v>0.34</v>
       </c>
       <c r="O58" t="n">
-        <v>0.4205</v>
+        <v>0.4355</v>
       </c>
       <c r="P58" t="n">
         <v>3</v>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>It's nearly 11 at night, when should I run the washing machine?</t>
+          <t>It's nearly 11 at night. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="L59" t="n">
         <v>0.96</v>
@@ -4440,13 +4440,13 @@
         <v>0.93</v>
       </c>
       <c r="O59" t="n">
-        <v>0.9255</v>
+        <v>0.9285</v>
       </c>
       <c r="P59" t="n">
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.0391</v>
+        <v>0.0321</v>
       </c>
       <c r="R59" t="n">
         <v>0.41</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>It's nearly 11 at night, when should I run the washing machine?</t>
+          <t>It's nearly 11 at night. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4508,13 +4508,13 @@
         <v>0.3</v>
       </c>
       <c r="O60" t="n">
-        <v>0.7689999999999999</v>
+        <v>0.769</v>
       </c>
       <c r="P60" t="n">
         <v>3</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.0391</v>
+        <v>0.0418</v>
       </c>
       <c r="R60" t="n">
         <v>0.437</v>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>It's nearly 11 at night, when should I run the washing machine?</t>
+          <t>It's nearly 11 at night. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="L61" t="n">
         <v>0.96</v>
@@ -4576,13 +4576,13 @@
         <v>0.43</v>
       </c>
       <c r="O61" t="n">
-        <v>0.7945</v>
+        <v>0.7975</v>
       </c>
       <c r="P61" t="n">
         <v>2</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0828</v>
       </c>
       <c r="R61" t="n">
         <v>0.437</v>
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L62" t="n">
         <v>0.74</v>
@@ -4644,13 +4644,13 @@
         <v>0.85</v>
       </c>
       <c r="O62" t="n">
-        <v>0.8565</v>
+        <v>0.8685</v>
       </c>
       <c r="P62" t="n">
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.0912</v>
+        <v>0.0727</v>
       </c>
       <c r="R62" t="n">
         <v>1.171</v>
@@ -4718,7 +4718,7 @@
         <v>2</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.0912</v>
+        <v>0.1006</v>
       </c>
       <c r="R63" t="n">
         <v>1.249</v>
@@ -4786,7 +4786,7 @@
         <v>3</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.0912</v>
+        <v>0.1006</v>
       </c>
       <c r="R64" t="n">
         <v>1.249</v>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3, when should I run the dishwasher?</t>
+          <t>It's late afternoon, just past 3. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="L65" t="n">
         <v>0.76</v>
@@ -4848,13 +4848,13 @@
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>0.847</v>
+        <v>0.85</v>
       </c>
       <c r="P65" t="n">
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.1806</v>
+        <v>0.1914</v>
       </c>
       <c r="R65" t="n">
         <v>1.093</v>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3, when should I run the dishwasher?</t>
+          <t>It's late afternoon, just past 3. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="L66" t="n">
         <v>0.76</v>
@@ -4916,13 +4916,13 @@
         <v>0.58</v>
       </c>
       <c r="O66" t="n">
-        <v>0.765</v>
+        <v>0.768</v>
       </c>
       <c r="P66" t="n">
         <v>2</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.0924</v>
+        <v>0.0982</v>
       </c>
       <c r="R66" t="n">
         <v>1.093</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3, when should I run the dishwasher?</t>
+          <t>It's late afternoon, just past 3. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L67" t="n">
         <v>0.78</v>
@@ -4984,13 +4984,13 @@
         <v>0.34</v>
       </c>
       <c r="O67" t="n">
-        <v>0.718</v>
+        <v>0.73</v>
       </c>
       <c r="P67" t="n">
         <v>3</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.0924</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="R67" t="n">
         <v>1.025</v>
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="L68" t="n">
         <v>0.51</v>
@@ -5052,7 +5052,7 @@
         <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>0.7295</v>
+        <v>0.7385</v>
       </c>
       <c r="P68" t="n">
         <v>1</v>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="L69" t="n">
         <v>0.51</v>
@@ -5120,7 +5120,7 @@
         <v>0.58</v>
       </c>
       <c r="O69" t="n">
-        <v>0.6084999999999999</v>
+        <v>0.6175</v>
       </c>
       <c r="P69" t="n">
         <v>2</v>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="L70" t="n">
         <v>0.55</v>
@@ -5188,7 +5188,7 @@
         <v>0.29</v>
       </c>
       <c r="O70" t="n">
-        <v>0.551</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P70" t="n">
         <v>3</v>
@@ -5262,7 +5262,7 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.7585</v>
+        <v>0.8087</v>
       </c>
       <c r="R71" t="n">
         <v>4.268</v>
@@ -5312,7 +5312,7 @@
         </is>
       </c>
       <c r="K72" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -5324,13 +5324,13 @@
         <v>0.49</v>
       </c>
       <c r="O72" t="n">
-        <v>0.3435</v>
+        <v>0.3465</v>
       </c>
       <c r="P72" t="n">
         <v>2</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.3813</v>
+        <v>0.4085</v>
       </c>
       <c r="R72" t="n">
         <v>4.268</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>0.48</v>
+        <v>0.62</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -5392,13 +5392,13 @@
         <v>0.15</v>
       </c>
       <c r="O73" t="n">
-        <v>0.1905</v>
+        <v>0.2325</v>
       </c>
       <c r="P73" t="n">
         <v>3</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.3813</v>
+        <v>0.3135</v>
       </c>
       <c r="R73" t="n">
         <v>4.002</v>
@@ -5448,7 +5448,7 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>0.82</v>
+        <v>0.7</v>
       </c>
       <c r="L74" t="n">
         <v>0.43</v>
@@ -5460,13 +5460,13 @@
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.7105</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.147</v>
+        <v>0.2517</v>
       </c>
       <c r="R74" t="n">
         <v>2.186</v>
@@ -5516,7 +5516,7 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>0.55</v>
+        <v>0.7</v>
       </c>
       <c r="L75" t="n">
         <v>0.43</v>
@@ -5528,13 +5528,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O75" t="n">
-        <v>0.5790000000000001</v>
+        <v>0.624</v>
       </c>
       <c r="P75" t="n">
         <v>2</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.336</v>
+        <v>0.2517</v>
       </c>
       <c r="R75" t="n">
         <v>2.186</v>
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>0.82</v>
+        <v>0.7</v>
       </c>
       <c r="L76" t="n">
         <v>0.47</v>
@@ -5596,13 +5596,13 @@
         <v>0.17</v>
       </c>
       <c r="O76" t="n">
-        <v>0.5319999999999999</v>
+        <v>0.496</v>
       </c>
       <c r="P76" t="n">
         <v>3</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.147</v>
+        <v>0.2517</v>
       </c>
       <c r="R76" t="n">
         <v>2.05</v>
@@ -5652,7 +5652,7 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="L77" t="n">
         <v>0.73</v>
@@ -5664,13 +5664,13 @@
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7645</v>
       </c>
       <c r="P77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.368</v>
+        <v>0.3766</v>
       </c>
       <c r="R77" t="n">
         <v>1.197</v>
@@ -5735,10 +5735,10 @@
         <v>0.7615</v>
       </c>
       <c r="P78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0964</v>
       </c>
       <c r="R78" t="n">
         <v>1.122</v>
@@ -5800,13 +5800,13 @@
         <v>0.48</v>
       </c>
       <c r="O79" t="n">
-        <v>0.7264999999999999</v>
+        <v>0.7265</v>
       </c>
       <c r="P79" t="n">
         <v>3</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0964</v>
       </c>
       <c r="R79" t="n">
         <v>1.197</v>
@@ -5874,7 +5874,7 @@
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.0243</v>
+        <v>0.0268</v>
       </c>
       <c r="R80" t="n">
         <v>0.333</v>
@@ -5924,7 +5924,7 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="L81" t="n">
         <v>0.99</v>
@@ -5936,13 +5936,13 @@
         <v>0.67</v>
       </c>
       <c r="O81" t="n">
-        <v>0.87</v>
+        <v>0.873</v>
       </c>
       <c r="P81" t="n">
         <v>2</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.1024</v>
+        <v>0.1048</v>
       </c>
       <c r="R81" t="n">
         <v>0.333</v>
@@ -6010,7 +6010,7 @@
         <v>3</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.0243</v>
+        <v>0.0268</v>
       </c>
       <c r="R82" t="n">
         <v>0.312</v>
@@ -6078,7 +6078,7 @@
         <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.2204</v>
+        <v>0.2431</v>
       </c>
       <c r="R83" t="n">
         <v>3.019</v>
@@ -6146,7 +6146,7 @@
         <v>3</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.928</v>
+        <v>0.9497</v>
       </c>
       <c r="R84" t="n">
         <v>3.019</v>
@@ -6214,7 +6214,7 @@
         <v>2</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.2204</v>
+        <v>0.2431</v>
       </c>
       <c r="R85" t="n">
         <v>3.019</v>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="L86" t="n">
         <v>0.71</v>
@@ -6276,13 +6276,13 @@
         <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>0.7425</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="P86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.384</v>
+        <v>0.393</v>
       </c>
       <c r="R86" t="n">
         <v>1.249</v>
@@ -6344,13 +6344,13 @@
         <v>0.58</v>
       </c>
       <c r="O87" t="n">
-        <v>0.7474999999999999</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="P87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.0912</v>
+        <v>0.1006</v>
       </c>
       <c r="R87" t="n">
         <v>1.249</v>
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L88" t="n">
         <v>0.74</v>
@@ -6412,13 +6412,13 @@
         <v>0.15</v>
       </c>
       <c r="O88" t="n">
-        <v>0.6375</v>
+        <v>0.6495</v>
       </c>
       <c r="P88" t="n">
         <v>3</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.0912</v>
+        <v>0.0727</v>
       </c>
       <c r="R88" t="n">
         <v>1.171</v>
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="L89" t="n">
         <v>0.96</v>
@@ -6480,13 +6480,13 @@
         <v>1</v>
       </c>
       <c r="O89" t="n">
-        <v>0.983</v>
+        <v>0.974</v>
       </c>
       <c r="P89" t="n">
         <v>1</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.0294</v>
+        <v>0.0587</v>
       </c>
       <c r="R89" t="n">
         <v>0.437</v>
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="L90" t="n">
         <v>0.96</v>
@@ -6548,13 +6548,13 @@
         <v>0.58</v>
       </c>
       <c r="O90" t="n">
-        <v>0.836</v>
+        <v>0.83</v>
       </c>
       <c r="P90" t="n">
         <v>2</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.0294</v>
+        <v>0.0503</v>
       </c>
       <c r="R90" t="n">
         <v>0.41</v>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="L91" t="n">
         <v>0.96</v>
@@ -6616,13 +6616,13 @@
         <v>0.3</v>
       </c>
       <c r="O91" t="n">
-        <v>0.772</v>
+        <v>0.766</v>
       </c>
       <c r="P91" t="n">
         <v>3</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.0294</v>
+        <v>0.0503</v>
       </c>
       <c r="R91" t="n">
         <v>0.437</v>
@@ -6690,7 +6690,7 @@
         <v>1</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.2356</v>
+        <v>0.2598</v>
       </c>
       <c r="R92" t="n">
         <v>3.227</v>
@@ -6758,7 +6758,7 @@
         <v>3</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.992</v>
+        <v>1.0152</v>
       </c>
       <c r="R93" t="n">
         <v>3.227</v>
@@ -6826,7 +6826,7 @@
         <v>2</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.2356</v>
+        <v>0.2598</v>
       </c>
       <c r="R94" t="n">
         <v>3.026</v>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>It's around 2 in the afternoon, when should I run the dryer?</t>
+          <t>It's around 2 in the afternoon. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6876,7 +6876,7 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L95" t="n">
         <v>0.28</v>
@@ -6888,7 +6888,7 @@
         <v>1</v>
       </c>
       <c r="O95" t="n">
-        <v>0.601</v>
+        <v>0.616</v>
       </c>
       <c r="P95" t="n">
         <v>1</v>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>It's around 2 in the afternoon, when should I run the dryer?</t>
+          <t>It's around 2 in the afternoon. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L96" t="n">
         <v>0.28</v>
@@ -6956,7 +6956,7 @@
         <v>0.6</v>
       </c>
       <c r="O96" t="n">
-        <v>0.487</v>
+        <v>0.502</v>
       </c>
       <c r="P96" t="n">
         <v>2</v>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>It's around 2 in the afternoon, when should I run the dryer?</t>
+          <t>It's around 2 in the afternoon. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7012,7 +7012,7 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L97" t="n">
         <v>0.28</v>
@@ -7024,7 +7024,7 @@
         <v>0.31</v>
       </c>
       <c r="O97" t="n">
-        <v>0.3655</v>
+        <v>0.3805</v>
       </c>
       <c r="P97" t="n">
         <v>3</v>
@@ -7080,7 +7080,7 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>0.86</v>
+        <v>0.72</v>
       </c>
       <c r="L98" t="n">
         <v>0.5600000000000001</v>
@@ -7092,13 +7092,13 @@
         <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>0.804</v>
+        <v>0.762</v>
       </c>
       <c r="P98" t="n">
         <v>1</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.119</v>
+        <v>0.2378</v>
       </c>
       <c r="R98" t="n">
         <v>1.77</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="L99" t="n">
         <v>0.5600000000000001</v>
@@ -7160,13 +7160,13 @@
         <v>0.35</v>
       </c>
       <c r="O99" t="n">
-        <v>0.6105</v>
+        <v>0.5805</v>
       </c>
       <c r="P99" t="n">
         <v>3</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.119</v>
+        <v>0.2038</v>
       </c>
       <c r="R99" t="n">
         <v>1.77</v>
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="L100" t="n">
         <v>0.5600000000000001</v>
@@ -7228,13 +7228,13 @@
         <v>0.57</v>
       </c>
       <c r="O100" t="n">
-        <v>0.6955000000000001</v>
+        <v>0.6655</v>
       </c>
       <c r="P100" t="n">
         <v>2</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.119</v>
+        <v>0.2038</v>
       </c>
       <c r="R100" t="n">
         <v>1.77</v>
@@ -7284,7 +7284,7 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>0.79</v>
+        <v>0.59</v>
       </c>
       <c r="L101" t="n">
         <v>0.34</v>
@@ -7296,13 +7296,13 @@
         <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>0.7060000000000001</v>
+        <v>0.646</v>
       </c>
       <c r="P101" t="n">
         <v>1</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.168</v>
+        <v>0.3357</v>
       </c>
       <c r="R101" t="n">
         <v>2.498</v>
@@ -7352,7 +7352,7 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="L102" t="n">
         <v>0.34</v>
@@ -7364,13 +7364,13 @@
         <v>0.57</v>
       </c>
       <c r="O102" t="n">
-        <v>0.5555</v>
+        <v>0.5135</v>
       </c>
       <c r="P102" t="n">
         <v>2</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.168</v>
+        <v>0.2877</v>
       </c>
       <c r="R102" t="n">
         <v>2.498</v>
@@ -7420,7 +7420,7 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="L103" t="n">
         <v>0.39</v>
@@ -7432,13 +7432,13 @@
         <v>0.25</v>
       </c>
       <c r="O103" t="n">
-        <v>0.4349999999999999</v>
+        <v>0.393</v>
       </c>
       <c r="P103" t="n">
         <v>3</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.168</v>
+        <v>0.2877</v>
       </c>
       <c r="R103" t="n">
         <v>2.342</v>
@@ -7506,7 +7506,7 @@
         <v>1</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.0798</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="R104" t="n">
         <v>1.093</v>
@@ -7556,7 +7556,7 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="L105" t="n">
         <v>0.76</v>
@@ -7568,13 +7568,13 @@
         <v>0.58</v>
       </c>
       <c r="O105" t="n">
-        <v>0.6599999999999999</v>
+        <v>0.669</v>
       </c>
       <c r="P105" t="n">
         <v>3</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.336</v>
+        <v>0.3438</v>
       </c>
       <c r="R105" t="n">
         <v>1.093</v>
@@ -7636,13 +7636,13 @@
         <v>0.29</v>
       </c>
       <c r="O106" t="n">
-        <v>0.7064999999999999</v>
+        <v>0.7065</v>
       </c>
       <c r="P106" t="n">
         <v>2</v>
       </c>
       <c r="Q106" t="n">
-        <v>0.0798</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="R106" t="n">
         <v>1.025</v>
